--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -326,7 +326,7 @@
     <t>Entrega</t>
   </si>
   <si>
-    <t>Entrega del Proyecto</t>
+    <t>Entrega del Proyecto GITCHECK</t>
   </si>
 </sst>
 </file>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -326,7 +326,7 @@
     <t>Entrega</t>
   </si>
   <si>
-    <t>Entrega del Proyecto GITCHECK</t>
+    <t>Entrega del Proyecto ***</t>
   </si>
 </sst>
 </file>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="106">
   <si>
     <t>Etapa</t>
   </si>
@@ -240,6 +240,9 @@
   </si>
   <si>
     <t>RNOF Perfil Cliente</t>
+  </si>
+  <si>
+    <t>Automatizacion de Reportes al Cliente</t>
   </si>
   <si>
     <t>RNOF Perfil Director</t>
@@ -2592,28 +2595,28 @@
     </row>
     <row r="43" ht="29.25" customHeight="1">
       <c r="A43" s="10" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="C43" s="12" t="s">
         <v>76</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="G43" s="14">
-        <v>46288.0</v>
+        <v>46285.0</v>
       </c>
       <c r="H43" s="14">
-        <v>46289.0</v>
+        <v>46285.0</v>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="15"/>
@@ -2640,513 +2643,532 @@
       <c r="AE43" s="16"/>
     </row>
     <row r="44" ht="29.25" customHeight="1">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="10" t="s">
         <v>26</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="22" t="s">
+      <c r="C44" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D44" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G44" s="8">
+      <c r="E44" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G44" s="14">
         <v>46288.0</v>
       </c>
-      <c r="H44" s="8">
+      <c r="H44" s="14">
         <v>46289.0</v>
       </c>
-      <c r="I44" s="8"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="9"/>
-      <c r="L44" s="9"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="15"/>
+      <c r="L44" s="15"/>
+      <c r="M44" s="16"/>
+      <c r="N44" s="16"/>
+      <c r="O44" s="16"/>
+      <c r="P44" s="16"/>
+      <c r="Q44" s="16"/>
+      <c r="R44" s="16"/>
+      <c r="S44" s="16"/>
+      <c r="T44" s="16"/>
+      <c r="U44" s="16"/>
+      <c r="V44" s="16"/>
+      <c r="W44" s="16"/>
+      <c r="X44" s="16"/>
+      <c r="Y44" s="16"/>
+      <c r="Z44" s="16"/>
+      <c r="AA44" s="16"/>
+      <c r="AB44" s="16"/>
+      <c r="AC44" s="16"/>
+      <c r="AD44" s="16"/>
+      <c r="AE44" s="16"/>
     </row>
     <row r="45" ht="29.25" customHeight="1">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="C45" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G45" s="14">
-        <v>46285.0</v>
-      </c>
-      <c r="H45" s="14">
+      <c r="E45" s="7"/>
+      <c r="F45" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G45" s="8">
+        <v>46288.0</v>
+      </c>
+      <c r="H45" s="8">
         <v>46289.0</v>
       </c>
-      <c r="I45" s="14"/>
-      <c r="J45" s="15"/>
-      <c r="K45" s="15"/>
-      <c r="L45" s="15"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="16"/>
-      <c r="O45" s="16"/>
-      <c r="P45" s="16"/>
-      <c r="Q45" s="16"/>
-      <c r="R45" s="16"/>
-      <c r="S45" s="16"/>
-      <c r="T45" s="16"/>
-      <c r="U45" s="16"/>
-      <c r="V45" s="16"/>
-      <c r="W45" s="16"/>
-      <c r="X45" s="16"/>
-      <c r="Y45" s="16"/>
-      <c r="Z45" s="16"/>
-      <c r="AA45" s="16"/>
-      <c r="AB45" s="16"/>
-      <c r="AC45" s="16"/>
-      <c r="AD45" s="16"/>
-      <c r="AE45" s="16"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="17"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="9"/>
     </row>
     <row r="46" ht="29.25" customHeight="1">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="10" t="s">
         <v>26</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C46" s="22" t="s">
+      <c r="C46" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D46" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G46" s="8">
-        <v>46286.0</v>
-      </c>
-      <c r="H46" s="8">
-        <v>46288.0</v>
-      </c>
-      <c r="I46" s="8"/>
-      <c r="J46" s="17"/>
-      <c r="K46" s="9"/>
-      <c r="L46" s="9"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G46" s="14">
+        <v>46285.0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>46289.0</v>
+      </c>
+      <c r="I46" s="14"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="15"/>
+      <c r="L46" s="15"/>
+      <c r="M46" s="16"/>
+      <c r="N46" s="16"/>
+      <c r="O46" s="16"/>
+      <c r="P46" s="16"/>
+      <c r="Q46" s="16"/>
+      <c r="R46" s="16"/>
+      <c r="S46" s="16"/>
+      <c r="T46" s="16"/>
+      <c r="U46" s="16"/>
+      <c r="V46" s="16"/>
+      <c r="W46" s="16"/>
+      <c r="X46" s="16"/>
+      <c r="Y46" s="16"/>
+      <c r="Z46" s="16"/>
+      <c r="AA46" s="16"/>
+      <c r="AB46" s="16"/>
+      <c r="AC46" s="16"/>
+      <c r="AD46" s="16"/>
+      <c r="AE46" s="16"/>
     </row>
     <row r="47" ht="29.25" customHeight="1">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C47" s="12" t="s">
+      <c r="C47" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G47" s="14">
+      <c r="E47" s="7"/>
+      <c r="F47" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G47" s="8">
         <v>46286.0</v>
       </c>
-      <c r="H47" s="14">
+      <c r="H47" s="8">
         <v>46288.0</v>
       </c>
-      <c r="I47" s="14"/>
-      <c r="J47" s="15"/>
-      <c r="K47" s="15"/>
-      <c r="L47" s="15"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="16"/>
-      <c r="O47" s="16"/>
-      <c r="P47" s="16"/>
-      <c r="Q47" s="16"/>
-      <c r="R47" s="16"/>
-      <c r="S47" s="16"/>
-      <c r="T47" s="16"/>
-      <c r="U47" s="16"/>
-      <c r="V47" s="16"/>
-      <c r="W47" s="16"/>
-      <c r="X47" s="16"/>
-      <c r="Y47" s="16"/>
-      <c r="Z47" s="16"/>
-      <c r="AA47" s="16"/>
-      <c r="AB47" s="16"/>
-      <c r="AC47" s="16"/>
-      <c r="AD47" s="16"/>
-      <c r="AE47" s="16"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="17"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="9"/>
     </row>
     <row r="48" ht="29.25" customHeight="1">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="10" t="s">
         <v>26</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="D48" s="7" t="s">
+      <c r="C48" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D48" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="8">
+      <c r="E48" s="13"/>
+      <c r="F48" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="G48" s="14">
         <v>46286.0</v>
       </c>
-      <c r="H48" s="8">
+      <c r="H48" s="14">
         <v>46288.0</v>
       </c>
-      <c r="I48" s="8"/>
-      <c r="J48" s="17"/>
-      <c r="K48" s="9"/>
-      <c r="L48" s="9"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="15"/>
+      <c r="K48" s="15"/>
+      <c r="L48" s="15"/>
+      <c r="M48" s="16"/>
+      <c r="N48" s="16"/>
+      <c r="O48" s="16"/>
+      <c r="P48" s="16"/>
+      <c r="Q48" s="16"/>
+      <c r="R48" s="16"/>
+      <c r="S48" s="16"/>
+      <c r="T48" s="16"/>
+      <c r="U48" s="16"/>
+      <c r="V48" s="16"/>
+      <c r="W48" s="16"/>
+      <c r="X48" s="16"/>
+      <c r="Y48" s="16"/>
+      <c r="Z48" s="16"/>
+      <c r="AA48" s="16"/>
+      <c r="AB48" s="16"/>
+      <c r="AC48" s="16"/>
+      <c r="AD48" s="16"/>
+      <c r="AE48" s="16"/>
     </row>
     <row r="49" ht="29.25" customHeight="1">
-      <c r="A49" s="10" t="s">
+      <c r="A49" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C49" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="8">
+        <v>46286.0</v>
+      </c>
+      <c r="H49" s="8">
+        <v>46288.0</v>
+      </c>
+      <c r="I49" s="8"/>
+      <c r="J49" s="17"/>
+      <c r="K49" s="9"/>
+      <c r="L49" s="9"/>
+    </row>
+    <row r="50" ht="29.25" customHeight="1">
+      <c r="A50" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B50" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="D49" s="13" t="s">
+      <c r="C50" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D50" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="E49" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="F49" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G49" s="14">
+      <c r="E50" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="G50" s="14">
         <v>46287.0</v>
       </c>
-      <c r="H49" s="14">
+      <c r="H50" s="14">
         <v>46290.0</v>
       </c>
-      <c r="I49" s="14"/>
-      <c r="J49" s="15"/>
-      <c r="K49" s="15"/>
-      <c r="L49" s="15"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="16"/>
-      <c r="O49" s="16"/>
-      <c r="P49" s="16"/>
-      <c r="Q49" s="16"/>
-      <c r="R49" s="16"/>
-      <c r="S49" s="16"/>
-      <c r="T49" s="16"/>
-      <c r="U49" s="16"/>
-      <c r="V49" s="16"/>
-      <c r="W49" s="16"/>
-      <c r="X49" s="16"/>
-      <c r="Y49" s="16"/>
-      <c r="Z49" s="16"/>
-      <c r="AA49" s="16"/>
-      <c r="AB49" s="16"/>
-      <c r="AC49" s="16"/>
-      <c r="AD49" s="16"/>
-      <c r="AE49" s="16"/>
-    </row>
-    <row r="50" ht="29.25" customHeight="1">
-      <c r="A50" s="4" t="s">
+      <c r="I50" s="14"/>
+      <c r="J50" s="15"/>
+      <c r="K50" s="15"/>
+      <c r="L50" s="15"/>
+      <c r="M50" s="16"/>
+      <c r="N50" s="16"/>
+      <c r="O50" s="16"/>
+      <c r="P50" s="16"/>
+      <c r="Q50" s="16"/>
+      <c r="R50" s="16"/>
+      <c r="S50" s="16"/>
+      <c r="T50" s="16"/>
+      <c r="U50" s="16"/>
+      <c r="V50" s="16"/>
+      <c r="W50" s="16"/>
+      <c r="X50" s="16"/>
+      <c r="Y50" s="16"/>
+      <c r="Z50" s="16"/>
+      <c r="AA50" s="16"/>
+      <c r="AB50" s="16"/>
+      <c r="AC50" s="16"/>
+      <c r="AD50" s="16"/>
+      <c r="AE50" s="16"/>
+    </row>
+    <row r="51" ht="29.25" customHeight="1">
+      <c r="A51" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B50" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D50" s="7" t="s">
+      <c r="B51" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D51" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E50" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G50" s="8">
+      <c r="E51" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G51" s="8">
         <v>46288.0</v>
       </c>
-      <c r="H50" s="8">
+      <c r="H51" s="8">
         <v>46290.0</v>
       </c>
-      <c r="I50" s="8"/>
-      <c r="J50" s="17"/>
-      <c r="K50" s="9"/>
-      <c r="L50" s="9"/>
-    </row>
-    <row r="51" ht="29.25" customHeight="1">
-      <c r="A51" s="10" t="s">
+      <c r="I51" s="8"/>
+      <c r="J51" s="17"/>
+      <c r="K51" s="9"/>
+      <c r="L51" s="9"/>
+    </row>
+    <row r="52" ht="29.25" customHeight="1">
+      <c r="A52" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B51" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C51" s="12" t="s">
+      <c r="B52" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="C52" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D52" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13" t="s">
+      <c r="E52" s="13"/>
+      <c r="F52" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="G51" s="14">
+      <c r="G52" s="14">
         <v>46291.0</v>
       </c>
-      <c r="H51" s="14">
+      <c r="H52" s="14">
         <v>46291.0</v>
       </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="15"/>
-      <c r="K51" s="15"/>
-      <c r="L51" s="15"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="16"/>
-      <c r="O51" s="16"/>
-      <c r="P51" s="16"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="16"/>
-      <c r="S51" s="16"/>
-      <c r="T51" s="16"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="16"/>
-      <c r="W51" s="16"/>
-      <c r="X51" s="16"/>
-      <c r="Y51" s="16"/>
-      <c r="Z51" s="16"/>
-      <c r="AA51" s="16"/>
-      <c r="AB51" s="16"/>
-      <c r="AC51" s="16"/>
-      <c r="AD51" s="16"/>
-      <c r="AE51" s="16"/>
-    </row>
-    <row r="52" ht="29.25" customHeight="1">
-      <c r="A52" s="4" t="s">
+      <c r="I52" s="14"/>
+      <c r="J52" s="15"/>
+      <c r="K52" s="15"/>
+      <c r="L52" s="15"/>
+      <c r="M52" s="16"/>
+      <c r="N52" s="16"/>
+      <c r="O52" s="16"/>
+      <c r="P52" s="16"/>
+      <c r="Q52" s="16"/>
+      <c r="R52" s="16"/>
+      <c r="S52" s="16"/>
+      <c r="T52" s="16"/>
+      <c r="U52" s="16"/>
+      <c r="V52" s="16"/>
+      <c r="W52" s="16"/>
+      <c r="X52" s="16"/>
+      <c r="Y52" s="16"/>
+      <c r="Z52" s="16"/>
+      <c r="AA52" s="16"/>
+      <c r="AB52" s="16"/>
+      <c r="AC52" s="16"/>
+      <c r="AD52" s="16"/>
+      <c r="AE52" s="16"/>
+    </row>
+    <row r="53" ht="29.25" customHeight="1">
+      <c r="A53" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C52" s="6" t="s">
+      <c r="B53" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="C53" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D53" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E52" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="F52" s="7" t="s">
+      <c r="E53" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F53" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G52" s="8">
+      <c r="G53" s="8">
         <v>46291.0</v>
       </c>
-      <c r="H52" s="8">
+      <c r="H53" s="8">
         <v>46291.0</v>
       </c>
-      <c r="I52" s="8"/>
-      <c r="J52" s="9"/>
-      <c r="K52" s="9"/>
-      <c r="L52" s="9"/>
-    </row>
-    <row r="53" ht="29.25" customHeight="1">
-      <c r="A53" s="10" t="s">
+      <c r="I53" s="8"/>
+      <c r="J53" s="9"/>
+      <c r="K53" s="9"/>
+      <c r="L53" s="9"/>
+    </row>
+    <row r="54" ht="29.25" customHeight="1">
+      <c r="A54" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B53" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="C53" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D53" s="13" t="s">
+      <c r="B54" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D54" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13" t="s">
+      <c r="E54" s="13"/>
+      <c r="F54" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="G53" s="14">
+      <c r="G54" s="14">
         <v>46291.0</v>
       </c>
-      <c r="H53" s="14">
+      <c r="H54" s="14">
         <v>46291.0</v>
       </c>
-      <c r="I53" s="14"/>
-      <c r="J53" s="15"/>
-      <c r="K53" s="15"/>
-      <c r="L53" s="15"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="16"/>
-      <c r="O53" s="16"/>
-      <c r="P53" s="16"/>
-      <c r="Q53" s="16"/>
-      <c r="R53" s="16"/>
-      <c r="S53" s="16"/>
-      <c r="T53" s="16"/>
-      <c r="U53" s="16"/>
-      <c r="V53" s="16"/>
-      <c r="W53" s="16"/>
-      <c r="X53" s="16"/>
-      <c r="Y53" s="16"/>
-      <c r="Z53" s="16"/>
-      <c r="AA53" s="16"/>
-      <c r="AB53" s="16"/>
-      <c r="AC53" s="16"/>
-      <c r="AD53" s="16"/>
-      <c r="AE53" s="16"/>
-    </row>
-    <row r="54" ht="29.25" customHeight="1">
-      <c r="A54" s="4" t="s">
+      <c r="I54" s="14"/>
+      <c r="J54" s="15"/>
+      <c r="K54" s="15"/>
+      <c r="L54" s="15"/>
+      <c r="M54" s="16"/>
+      <c r="N54" s="16"/>
+      <c r="O54" s="16"/>
+      <c r="P54" s="16"/>
+      <c r="Q54" s="16"/>
+      <c r="R54" s="16"/>
+      <c r="S54" s="16"/>
+      <c r="T54" s="16"/>
+      <c r="U54" s="16"/>
+      <c r="V54" s="16"/>
+      <c r="W54" s="16"/>
+      <c r="X54" s="16"/>
+      <c r="Y54" s="16"/>
+      <c r="Z54" s="16"/>
+      <c r="AA54" s="16"/>
+      <c r="AB54" s="16"/>
+      <c r="AC54" s="16"/>
+      <c r="AD54" s="16"/>
+      <c r="AE54" s="16"/>
+    </row>
+    <row r="55" ht="29.25" customHeight="1">
+      <c r="A55" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B54" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D54" s="7" t="s">
+      <c r="B55" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D55" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E54" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G54" s="8">
+      <c r="E55" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G55" s="8">
         <v>46286.0</v>
       </c>
-      <c r="H54" s="8">
+      <c r="H55" s="8">
         <v>46293.0</v>
       </c>
-      <c r="I54" s="8"/>
-      <c r="J54" s="9"/>
-      <c r="K54" s="9"/>
-      <c r="L54" s="9"/>
-    </row>
-    <row r="55" ht="29.25" customHeight="1">
-      <c r="A55" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B55" s="11" t="s">
+      <c r="I55" s="8"/>
+      <c r="J55" s="9"/>
+      <c r="K55" s="9"/>
+      <c r="L55" s="9"/>
+    </row>
+    <row r="56" ht="29.25" customHeight="1">
+      <c r="A56" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="C55" s="12" t="s">
+      <c r="B56" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="D55" s="13" t="s">
+      <c r="C56" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D56" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="E55" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="F55" s="13" t="s">
+      <c r="E56" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F56" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="G55" s="14">
+      <c r="G56" s="14">
         <v>46289.0</v>
       </c>
-      <c r="H55" s="14">
+      <c r="H56" s="14">
         <v>46289.0</v>
       </c>
-      <c r="I55" s="14"/>
-      <c r="J55" s="15"/>
-      <c r="K55" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="L55" s="15"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="16"/>
-      <c r="O55" s="16"/>
-      <c r="P55" s="16"/>
-      <c r="Q55" s="16"/>
-      <c r="R55" s="16"/>
-      <c r="S55" s="16"/>
-      <c r="T55" s="16"/>
-      <c r="U55" s="16"/>
-      <c r="V55" s="16"/>
-      <c r="W55" s="16"/>
-      <c r="X55" s="16"/>
-      <c r="Y55" s="16"/>
-      <c r="Z55" s="16"/>
-      <c r="AA55" s="16"/>
-      <c r="AB55" s="16"/>
-      <c r="AC55" s="16"/>
-      <c r="AD55" s="16"/>
-      <c r="AE55" s="16"/>
-    </row>
-    <row r="56" ht="29.25" customHeight="1">
-      <c r="A56" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G56" s="8">
-        <v>46289.0</v>
-      </c>
-      <c r="H56" s="8">
-        <v>46289.0</v>
-      </c>
-      <c r="I56" s="8"/>
-      <c r="J56" s="9"/>
-      <c r="K56" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="L56" s="9"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="15"/>
+      <c r="K56" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="L56" s="15"/>
+      <c r="M56" s="16"/>
+      <c r="N56" s="16"/>
+      <c r="O56" s="16"/>
+      <c r="P56" s="16"/>
+      <c r="Q56" s="16"/>
+      <c r="R56" s="16"/>
+      <c r="S56" s="16"/>
+      <c r="T56" s="16"/>
+      <c r="U56" s="16"/>
+      <c r="V56" s="16"/>
+      <c r="W56" s="16"/>
+      <c r="X56" s="16"/>
+      <c r="Y56" s="16"/>
+      <c r="Z56" s="16"/>
+      <c r="AA56" s="16"/>
+      <c r="AB56" s="16"/>
+      <c r="AC56" s="16"/>
+      <c r="AD56" s="16"/>
+      <c r="AE56" s="16"/>
     </row>
     <row r="57" ht="29.25" customHeight="1">
       <c r="A57" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E57" s="7"/>
+      <c r="E57" s="7" t="s">
+        <v>69</v>
+      </c>
       <c r="F57" s="7" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="G57" s="8">
         <v>46289.0</v>
@@ -3156,249 +3178,263 @@
       </c>
       <c r="I57" s="8"/>
       <c r="J57" s="9"/>
-      <c r="K57" s="9"/>
+      <c r="K57" s="9" t="s">
+        <v>94</v>
+      </c>
       <c r="L57" s="9"/>
     </row>
     <row r="58" ht="29.25" customHeight="1">
-      <c r="A58" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B58" s="11" t="s">
+      <c r="A58" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C58" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C58" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="D58" s="13" t="s">
+      <c r="D58" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E58" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="F58" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G58" s="14">
+      <c r="E58" s="7"/>
+      <c r="F58" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G58" s="8">
+        <v>46289.0</v>
+      </c>
+      <c r="H58" s="8">
+        <v>46289.0</v>
+      </c>
+      <c r="I58" s="8"/>
+      <c r="J58" s="9"/>
+      <c r="K58" s="9"/>
+      <c r="L58" s="9"/>
+    </row>
+    <row r="59" ht="29.25" customHeight="1">
+      <c r="A59" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F59" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="G59" s="14">
         <v>46286.0</v>
       </c>
-      <c r="H58" s="14">
+      <c r="H59" s="14">
         <v>46293.0</v>
       </c>
-      <c r="I58" s="14"/>
-      <c r="J58" s="15"/>
-      <c r="K58" s="15"/>
-      <c r="L58" s="15"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="16"/>
-      <c r="O58" s="16"/>
-      <c r="P58" s="16"/>
-      <c r="Q58" s="16"/>
-      <c r="R58" s="16"/>
-      <c r="S58" s="16"/>
-      <c r="T58" s="16"/>
-      <c r="U58" s="16"/>
-      <c r="V58" s="16"/>
-      <c r="W58" s="16"/>
-      <c r="X58" s="16"/>
-      <c r="Y58" s="16"/>
-      <c r="Z58" s="16"/>
-      <c r="AA58" s="16"/>
-      <c r="AB58" s="16"/>
-      <c r="AC58" s="16"/>
-      <c r="AD58" s="16"/>
-      <c r="AE58" s="16"/>
-    </row>
-    <row r="59" ht="29.25" customHeight="1">
-      <c r="A59" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D59" s="7" t="s">
+      <c r="I59" s="14"/>
+      <c r="J59" s="15"/>
+      <c r="K59" s="15"/>
+      <c r="L59" s="15"/>
+      <c r="M59" s="16"/>
+      <c r="N59" s="16"/>
+      <c r="O59" s="16"/>
+      <c r="P59" s="16"/>
+      <c r="Q59" s="16"/>
+      <c r="R59" s="16"/>
+      <c r="S59" s="16"/>
+      <c r="T59" s="16"/>
+      <c r="U59" s="16"/>
+      <c r="V59" s="16"/>
+      <c r="W59" s="16"/>
+      <c r="X59" s="16"/>
+      <c r="Y59" s="16"/>
+      <c r="Z59" s="16"/>
+      <c r="AA59" s="16"/>
+      <c r="AB59" s="16"/>
+      <c r="AC59" s="16"/>
+      <c r="AD59" s="16"/>
+      <c r="AE59" s="16"/>
+    </row>
+    <row r="60" ht="29.25" customHeight="1">
+      <c r="A60" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D60" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G59" s="8">
+      <c r="E60" s="7"/>
+      <c r="F60" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G60" s="8">
         <v>46287.0</v>
       </c>
-      <c r="H59" s="8">
+      <c r="H60" s="8">
         <v>46295.0</v>
       </c>
-      <c r="I59" s="8"/>
-      <c r="J59" s="9"/>
-      <c r="K59" s="9"/>
-      <c r="L59" s="9"/>
-    </row>
-    <row r="60" ht="29.25" customHeight="1">
-      <c r="A60" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B60" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="C60" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="D60" s="13" t="s">
+      <c r="I60" s="8"/>
+      <c r="J60" s="9"/>
+      <c r="K60" s="9"/>
+      <c r="L60" s="9"/>
+    </row>
+    <row r="61" ht="29.25" customHeight="1">
+      <c r="A61" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D61" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G60" s="14">
+      <c r="E61" s="13"/>
+      <c r="F61" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="G61" s="14">
         <v>46287.0</v>
       </c>
-      <c r="H60" s="14">
+      <c r="H61" s="14">
         <v>46293.0</v>
       </c>
-      <c r="I60" s="14"/>
-      <c r="J60" s="15"/>
-      <c r="K60" s="15"/>
-      <c r="L60" s="15"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="16"/>
-      <c r="O60" s="16"/>
-      <c r="P60" s="16"/>
-      <c r="Q60" s="16"/>
-      <c r="R60" s="16"/>
-      <c r="S60" s="16"/>
-      <c r="T60" s="16"/>
-      <c r="U60" s="16"/>
-      <c r="V60" s="16"/>
-      <c r="W60" s="16"/>
-      <c r="X60" s="16"/>
-      <c r="Y60" s="16"/>
-      <c r="Z60" s="16"/>
-      <c r="AA60" s="16"/>
-      <c r="AB60" s="16"/>
-      <c r="AC60" s="16"/>
-      <c r="AD60" s="16"/>
-      <c r="AE60" s="16"/>
-    </row>
-    <row r="61" ht="29.25" customHeight="1">
-      <c r="A61" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C61" s="6" t="s">
+      <c r="I61" s="14"/>
+      <c r="J61" s="15"/>
+      <c r="K61" s="15"/>
+      <c r="L61" s="15"/>
+      <c r="M61" s="16"/>
+      <c r="N61" s="16"/>
+      <c r="O61" s="16"/>
+      <c r="P61" s="16"/>
+      <c r="Q61" s="16"/>
+      <c r="R61" s="16"/>
+      <c r="S61" s="16"/>
+      <c r="T61" s="16"/>
+      <c r="U61" s="16"/>
+      <c r="V61" s="16"/>
+      <c r="W61" s="16"/>
+      <c r="X61" s="16"/>
+      <c r="Y61" s="16"/>
+      <c r="Z61" s="16"/>
+      <c r="AA61" s="16"/>
+      <c r="AB61" s="16"/>
+      <c r="AC61" s="16"/>
+      <c r="AD61" s="16"/>
+      <c r="AE61" s="16"/>
+    </row>
+    <row r="62" ht="29.25" customHeight="1">
+      <c r="A62" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B62" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D61" s="7" t="s">
+      <c r="C62" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D62" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G61" s="8">
+      <c r="E62" s="7"/>
+      <c r="F62" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G62" s="8">
         <v>46296.0</v>
       </c>
-      <c r="H61" s="8">
+      <c r="H62" s="8">
         <v>46303.0</v>
       </c>
-      <c r="I61" s="8"/>
-      <c r="J61" s="9"/>
-      <c r="K61" s="9"/>
-      <c r="L61" s="9"/>
-    </row>
-    <row r="62" ht="29.25" customHeight="1">
-      <c r="A62" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B62" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="C62" s="12" t="s">
+      <c r="I62" s="8"/>
+      <c r="J62" s="9"/>
+      <c r="K62" s="9"/>
+      <c r="L62" s="9"/>
+    </row>
+    <row r="63" ht="29.25" customHeight="1">
+      <c r="A63" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B63" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="D62" s="13"/>
-      <c r="E62" s="13"/>
-      <c r="F62" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G62" s="14">
+      <c r="C63" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="D63" s="13"/>
+      <c r="E63" s="13"/>
+      <c r="F63" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="G63" s="14">
         <v>46303.0</v>
       </c>
-      <c r="H62" s="14">
+      <c r="H63" s="14">
         <v>46303.0</v>
       </c>
-      <c r="I62" s="14"/>
-      <c r="J62" s="15"/>
-      <c r="K62" s="15"/>
-      <c r="L62" s="15"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="16"/>
-      <c r="O62" s="16"/>
-      <c r="P62" s="16"/>
-      <c r="Q62" s="16"/>
-      <c r="R62" s="16"/>
-      <c r="S62" s="16"/>
-      <c r="T62" s="16"/>
-      <c r="U62" s="16"/>
-      <c r="V62" s="16"/>
-      <c r="W62" s="16"/>
-      <c r="X62" s="16"/>
-      <c r="Y62" s="16"/>
-      <c r="Z62" s="16"/>
-      <c r="AA62" s="16"/>
-      <c r="AB62" s="16"/>
-      <c r="AC62" s="16"/>
-      <c r="AD62" s="16"/>
-      <c r="AE62" s="16"/>
-    </row>
-    <row r="63" ht="29.25" customHeight="1">
-      <c r="A63" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C63" s="6" t="s">
+      <c r="I63" s="14"/>
+      <c r="J63" s="15"/>
+      <c r="K63" s="15"/>
+      <c r="L63" s="15"/>
+      <c r="M63" s="16"/>
+      <c r="N63" s="16"/>
+      <c r="O63" s="16"/>
+      <c r="P63" s="16"/>
+      <c r="Q63" s="16"/>
+      <c r="R63" s="16"/>
+      <c r="S63" s="16"/>
+      <c r="T63" s="16"/>
+      <c r="U63" s="16"/>
+      <c r="V63" s="16"/>
+      <c r="W63" s="16"/>
+      <c r="X63" s="16"/>
+      <c r="Y63" s="16"/>
+      <c r="Z63" s="16"/>
+      <c r="AA63" s="16"/>
+      <c r="AB63" s="16"/>
+      <c r="AC63" s="16"/>
+      <c r="AD63" s="16"/>
+      <c r="AE63" s="16"/>
+    </row>
+    <row r="64" ht="29.25" customHeight="1">
+      <c r="A64" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B64" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D63" s="7" t="s">
+      <c r="C64" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D64" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E63" s="7"/>
-      <c r="F63" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G63" s="8">
+      <c r="E64" s="7"/>
+      <c r="F64" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G64" s="8">
         <v>46305.0</v>
       </c>
-      <c r="H63" s="8">
+      <c r="H64" s="8">
         <v>46305.0</v>
       </c>
-      <c r="I63" s="8"/>
-      <c r="J63" s="9"/>
-      <c r="K63" s="9"/>
-      <c r="L63" s="9"/>
-    </row>
-    <row r="64" ht="29.25" customHeight="1">
-      <c r="A64" s="23"/>
-      <c r="B64" s="6"/>
-      <c r="C64" s="24"/>
-      <c r="D64" s="25"/>
-      <c r="E64" s="21"/>
-      <c r="F64" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="G64" s="27"/>
-      <c r="H64" s="27"/>
-      <c r="I64" s="27"/>
-      <c r="J64" s="17"/>
-      <c r="K64" s="21"/>
-      <c r="L64" s="21"/>
+      <c r="I64" s="8"/>
+      <c r="J64" s="9"/>
+      <c r="K64" s="9"/>
+      <c r="L64" s="9"/>
     </row>
     <row r="65" ht="29.25" customHeight="1">
       <c r="A65" s="23"/>
@@ -3467,20 +3503,22 @@
     <row r="69" ht="29.25" customHeight="1">
       <c r="A69" s="23"/>
       <c r="B69" s="6"/>
-      <c r="C69" s="28"/>
+      <c r="C69" s="24"/>
       <c r="D69" s="25"/>
-      <c r="E69" s="29"/>
+      <c r="E69" s="21"/>
       <c r="F69" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="G69" s="30"/>
-      <c r="H69" s="30"/>
-      <c r="I69" s="30"/>
+      <c r="G69" s="27"/>
+      <c r="H69" s="27"/>
+      <c r="I69" s="27"/>
       <c r="J69" s="17"/>
+      <c r="K69" s="21"/>
+      <c r="L69" s="21"/>
     </row>
     <row r="70" ht="29.25" customHeight="1">
-      <c r="A70" s="31"/>
-      <c r="B70" s="28"/>
+      <c r="A70" s="23"/>
+      <c r="B70" s="6"/>
       <c r="C70" s="28"/>
       <c r="D70" s="25"/>
       <c r="E70" s="29"/>
@@ -4456,7 +4494,7 @@
       <c r="G139" s="30"/>
       <c r="H139" s="30"/>
       <c r="I139" s="30"/>
-      <c r="J139" s="32"/>
+      <c r="J139" s="17"/>
     </row>
     <row r="140" ht="29.25" customHeight="1">
       <c r="A140" s="31"/>
@@ -9320,7 +9358,11 @@
       <c r="A487" s="31"/>
       <c r="B487" s="28"/>
       <c r="C487" s="28"/>
+      <c r="D487" s="25"/>
       <c r="E487" s="29"/>
+      <c r="F487" s="26" t="s">
+        <v>69</v>
+      </c>
       <c r="G487" s="30"/>
       <c r="H487" s="30"/>
       <c r="I487" s="30"/>
@@ -14886,50 +14928,60 @@
       <c r="I1043" s="30"/>
       <c r="J1043" s="32"/>
     </row>
+    <row r="1044" ht="29.25" customHeight="1">
+      <c r="A1044" s="31"/>
+      <c r="B1044" s="28"/>
+      <c r="C1044" s="28"/>
+      <c r="E1044" s="29"/>
+      <c r="G1044" s="30"/>
+      <c r="H1044" s="30"/>
+      <c r="I1044" s="30"/>
+      <c r="J1044" s="32"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D63">
+  <conditionalFormatting sqref="D2:D64">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Finalizada">
       <formula>NOT(ISERROR(SEARCH(("Finalizada"),(D2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D63">
+  <conditionalFormatting sqref="D2:D64">
     <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="En Proceso">
       <formula>NOT(ISERROR(SEARCH(("En Proceso"),(D2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D63">
+  <conditionalFormatting sqref="D2:D64">
     <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Pendiente de Revision">
       <formula>NOT(ISERROR(SEARCH(("Pendiente de Revision"),(D2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J1043">
+  <conditionalFormatting sqref="J2:J1044">
     <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="SI">
       <formula>NOT(ISERROR(SEARCH(("SI"),(J2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E1043">
+  <conditionalFormatting sqref="E2:E1044">
     <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Validado">
       <formula>NOT(ISERROR(SEARCH(("Validado"),(E2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E1043">
+  <conditionalFormatting sqref="E2:E1044">
     <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="Revision">
       <formula>NOT(ISERROR(SEARCH(("Revision"),(E2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E88">
+  <conditionalFormatting sqref="E2:E89">
     <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="Reasignado">
       <formula>NOT(ISERROR(SEARCH(("Reasignado"),(E2))))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D486">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D487">
       <formula1>"Sin Comenzar,En Proceso,Finalizada"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E1043">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E1044">
       <formula1>"_,Esperando Revision,En Revision,Reasignado,Validado"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F486">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F487">
       <formula1>"_,Ignacio,Lucia,Luciano,Gabriel,Lucía"</formula1>
     </dataValidation>
   </dataValidations>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="114">
   <si>
     <t>Etapa</t>
   </si>
@@ -53,9 +53,6 @@
   </si>
   <si>
     <t>Documentacion</t>
-  </si>
-  <si>
-    <t>Plan de Proyecto</t>
   </si>
   <si>
     <t>Finalizada</t>
@@ -212,10 +209,10 @@
     <t>Conciliar Sintesis con Cuestionarios</t>
   </si>
   <si>
-    <t>RF Perfil Cliente</t>
+    <t>Esperando Revision</t>
   </si>
   <si>
-    <t>Esperando Revision</t>
+    <t>RF Perfil Cliente</t>
   </si>
   <si>
     <t>RF Perfil Director</t>
@@ -245,6 +242,9 @@
     <t>Automatizacion de Reportes al Cliente</t>
   </si>
   <si>
+    <t>Crear plantilla de formatos de ESRE</t>
+  </si>
+  <si>
     <t>RNOF Perfil Director</t>
   </si>
   <si>
@@ -258,6 +258,12 @@
   </si>
   <si>
     <t>RNOF Perfil Tecnicos</t>
+  </si>
+  <si>
+    <t>Revisiton de RF</t>
+  </si>
+  <si>
+    <t>Revision de RNF</t>
   </si>
   <si>
     <t>Especificacion de Requerimientos</t>
@@ -285,6 +291,24 @@
   </si>
   <si>
     <t>Modelado de Casos de Uso</t>
+  </si>
+  <si>
+    <t>CU Perfil Cliente</t>
+  </si>
+  <si>
+    <t>CU Perfil Director</t>
+  </si>
+  <si>
+    <t>CU Perfil Inspector</t>
+  </si>
+  <si>
+    <t>CU Perfil Docente</t>
+  </si>
+  <si>
+    <t>CU Perfil Estudiante</t>
+  </si>
+  <si>
+    <t>CU Perfil Tecnicos</t>
   </si>
   <si>
     <t>Disenio</t>
@@ -865,17 +889,18 @@
       <c r="B2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="6" t="str">
+        <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
+        <v>Plan de Proyecto: 2026-09-20 16:36</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="F2" s="7" t="s">
         <v>16</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>17</v>
       </c>
       <c r="G2" s="8">
         <v>46277.0</v>
@@ -890,10 +915,10 @@
         <v>100.0</v>
       </c>
       <c r="K2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="9" t="s">
         <v>18</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" ht="29.25" customHeight="1">
@@ -904,16 +929,16 @@
         <v>13</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="F3" s="13" t="s">
         <v>16</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>17</v>
       </c>
       <c r="G3" s="14">
         <v>46277.0</v>
@@ -928,10 +953,10 @@
         <v>100.0</v>
       </c>
       <c r="K3" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" s="15" t="s">
         <v>18</v>
-      </c>
-      <c r="L3" s="15" t="s">
-        <v>19</v>
       </c>
       <c r="M3" s="16"/>
       <c r="N3" s="16"/>
@@ -958,19 +983,19 @@
         <v>12</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>22</v>
-      </c>
       <c r="D4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>16</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>17</v>
       </c>
       <c r="G4" s="8">
         <v>46277.0</v>
@@ -992,19 +1017,19 @@
         <v>12</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D5" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="F5" s="13" t="s">
         <v>16</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>17</v>
       </c>
       <c r="G5" s="14">
         <v>46277.0</v>
@@ -1045,19 +1070,19 @@
         <v>12</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>16</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>17</v>
       </c>
       <c r="G6" s="8">
         <v>46282.0</v>
@@ -1079,19 +1104,19 @@
         <v>12</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="F7" s="13" t="s">
         <v>16</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>17</v>
       </c>
       <c r="G7" s="8">
         <v>46282.0</v>
@@ -1129,22 +1154,22 @@
     </row>
     <row r="8" ht="29.25" customHeight="1">
       <c r="A8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="C8" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>28</v>
-      </c>
       <c r="D8" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="F8" s="13" t="s">
         <v>16</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>17</v>
       </c>
       <c r="G8" s="14">
         <v>46270.0</v>
@@ -1182,22 +1207,22 @@
     </row>
     <row r="9" ht="29.25" customHeight="1">
       <c r="A9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="11" t="s">
-        <v>27</v>
-      </c>
       <c r="C9" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="F9" s="7" t="s">
         <v>16</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>17</v>
       </c>
       <c r="G9" s="8">
         <v>46270.0</v>
@@ -1216,22 +1241,22 @@
     </row>
     <row r="10" ht="29.25" customHeight="1">
       <c r="A10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>27</v>
-      </c>
       <c r="C10" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="F10" s="13" t="s">
         <v>16</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>17</v>
       </c>
       <c r="G10" s="14">
         <v>46270.0</v>
@@ -1269,22 +1294,22 @@
     </row>
     <row r="11" ht="29.25" customHeight="1">
       <c r="A11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>27</v>
-      </c>
       <c r="C11" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="F11" s="7" t="s">
         <v>16</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>17</v>
       </c>
       <c r="G11" s="8">
         <v>46270.0</v>
@@ -1303,22 +1328,22 @@
     </row>
     <row r="12" ht="29.25" customHeight="1">
       <c r="A12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>27</v>
-      </c>
       <c r="C12" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="F12" s="13" t="s">
         <v>16</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>17</v>
       </c>
       <c r="G12" s="14">
         <v>46270.0</v>
@@ -1356,22 +1381,22 @@
     </row>
     <row r="13" ht="29.25" customHeight="1">
       <c r="A13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="11" t="s">
-        <v>27</v>
-      </c>
       <c r="C13" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>32</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>33</v>
       </c>
       <c r="G13" s="8">
         <v>46270.0</v>
@@ -1390,22 +1415,22 @@
     </row>
     <row r="14" ht="29.25" customHeight="1">
       <c r="A14" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="11" t="s">
-        <v>27</v>
-      </c>
       <c r="C14" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D14" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="13" t="s">
-        <v>16</v>
-      </c>
       <c r="F14" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G14" s="14">
         <v>46270.0</v>
@@ -1443,22 +1468,22 @@
     </row>
     <row r="15" ht="29.25" customHeight="1">
       <c r="A15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="11" t="s">
-        <v>27</v>
-      </c>
       <c r="C15" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="F15" s="7" t="s">
         <v>16</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>17</v>
       </c>
       <c r="G15" s="8">
         <v>46269.0</v>
@@ -1477,22 +1502,22 @@
     </row>
     <row r="16" ht="29.25" customHeight="1">
       <c r="A16" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="11" t="s">
-        <v>27</v>
-      </c>
       <c r="C16" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D16" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="F16" s="13" t="s">
         <v>16</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>17</v>
       </c>
       <c r="G16" s="14">
         <v>46269.0</v>
@@ -1530,22 +1555,22 @@
     </row>
     <row r="17" ht="29.25" customHeight="1">
       <c r="A17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="11" t="s">
-        <v>27</v>
-      </c>
       <c r="C17" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="F17" s="7" t="s">
         <v>16</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>17</v>
       </c>
       <c r="G17" s="8">
         <v>46274.0</v>
@@ -1564,22 +1589,22 @@
     </row>
     <row r="18" ht="29.25" customHeight="1">
       <c r="A18" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="11" t="s">
-        <v>27</v>
-      </c>
       <c r="C18" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>38</v>
       </c>
       <c r="G18" s="8">
         <v>46274.0</v>
@@ -1598,22 +1623,22 @@
     </row>
     <row r="19" ht="29.25" customHeight="1">
       <c r="A19" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="11" t="s">
-        <v>27</v>
-      </c>
       <c r="C19" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" s="13" t="s">
+      <c r="F19" s="13" t="s">
         <v>40</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>41</v>
       </c>
       <c r="G19" s="14">
         <v>46274.0</v>
@@ -1626,10 +1651,10 @@
       </c>
       <c r="J19" s="15"/>
       <c r="K19" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="L19" s="15" t="s">
         <v>42</v>
-      </c>
-      <c r="L19" s="15" t="s">
-        <v>43</v>
       </c>
       <c r="M19" s="16"/>
       <c r="N19" s="16"/>
@@ -1653,22 +1678,22 @@
     </row>
     <row r="20" ht="29.25" customHeight="1">
       <c r="A20" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="11" t="s">
-        <v>27</v>
-      </c>
       <c r="C20" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>40</v>
-      </c>
       <c r="F20" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G20" s="8">
         <v>46274.0</v>
@@ -1681,30 +1706,30 @@
       </c>
       <c r="J20" s="17"/>
       <c r="K20" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L20" s="18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" ht="29.25" customHeight="1">
       <c r="A21" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>46</v>
-      </c>
       <c r="D21" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E21" s="13" t="s">
-        <v>16</v>
-      </c>
       <c r="F21" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G21" s="14">
         <v>46274.0</v>
@@ -1720,7 +1745,7 @@
       </c>
       <c r="K21" s="15"/>
       <c r="L21" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M21" s="16"/>
       <c r="N21" s="16"/>
@@ -1744,22 +1769,22 @@
     </row>
     <row r="22" ht="29.25" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="F22" s="7" t="s">
         <v>16</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>17</v>
       </c>
       <c r="G22" s="8">
         <v>46276.0</v>
@@ -1778,22 +1803,22 @@
     </row>
     <row r="23" ht="29.25" customHeight="1">
       <c r="A23" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D23" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E23" s="13" t="s">
-        <v>16</v>
-      </c>
       <c r="F23" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G23" s="14">
         <v>46276.0</v>
@@ -1831,22 +1856,22 @@
     </row>
     <row r="24" ht="29.25" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D24" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>16</v>
-      </c>
       <c r="F24" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G24" s="8">
         <v>46271.0</v>
@@ -1865,22 +1890,22 @@
     </row>
     <row r="25" ht="29.25" customHeight="1">
       <c r="A25" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="12" t="s">
-        <v>51</v>
-      </c>
       <c r="D25" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E25" s="13" t="s">
-        <v>16</v>
-      </c>
       <c r="F25" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G25" s="14">
         <v>46271.0</v>
@@ -1918,22 +1943,22 @@
     </row>
     <row r="26" ht="29.25" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D26" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E26" s="7" t="s">
-        <v>16</v>
-      </c>
       <c r="F26" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G26" s="8">
         <v>46271.0</v>
@@ -1952,22 +1977,22 @@
     </row>
     <row r="27" ht="37.5" customHeight="1">
       <c r="A27" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" s="13" t="s">
+      <c r="F27" s="13" t="s">
         <v>54</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>55</v>
       </c>
       <c r="G27" s="14">
         <v>46274.0</v>
@@ -2005,22 +2030,22 @@
     </row>
     <row r="28" ht="37.5" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D28" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="F28" s="7" t="s">
         <v>16</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>17</v>
       </c>
       <c r="G28" s="8">
         <v>46283.0</v>
@@ -2037,22 +2062,22 @@
     </row>
     <row r="29" ht="37.5" customHeight="1">
       <c r="A29" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="11" t="s">
-        <v>27</v>
-      </c>
       <c r="C29" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D29" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>16</v>
-      </c>
       <c r="F29" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G29" s="14">
         <v>46274.0</v>
@@ -2090,22 +2115,22 @@
     </row>
     <row r="30" ht="37.5" customHeight="1">
       <c r="A30" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="11" t="s">
-        <v>27</v>
-      </c>
       <c r="C30" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D30" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="F30" s="7" t="s">
         <v>16</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>17</v>
       </c>
       <c r="G30" s="8">
         <v>46274.0</v>
@@ -2124,22 +2149,22 @@
     </row>
     <row r="31" ht="29.25" customHeight="1">
       <c r="A31" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B31" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="C31" s="12" t="s">
-        <v>59</v>
-      </c>
       <c r="D31" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E31" s="13" t="s">
-        <v>16</v>
-      </c>
       <c r="F31" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G31" s="14">
         <v>46276.0</v>
@@ -2154,7 +2179,7 @@
         <v>20.0</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L31" s="15"/>
       <c r="M31" s="16"/>
@@ -2179,22 +2204,22 @@
     </row>
     <row r="32" ht="29.25" customHeight="1">
       <c r="A32" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B32" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>59</v>
-      </c>
       <c r="D32" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E32" s="7" t="s">
-        <v>16</v>
-      </c>
       <c r="F32" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G32" s="8">
         <v>46276.0</v>
@@ -2209,28 +2234,28 @@
         <v>20.0</v>
       </c>
       <c r="K32" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L32" s="9"/>
     </row>
     <row r="33" ht="29.25" customHeight="1">
       <c r="A33" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D33" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E33" s="13" t="s">
+      <c r="F33" s="13" t="s">
         <v>16</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>17</v>
       </c>
       <c r="G33" s="14">
         <v>46282.0</v>
@@ -2238,10 +2263,12 @@
       <c r="H33" s="14">
         <v>46282.0</v>
       </c>
-      <c r="I33" s="14"/>
+      <c r="I33" s="14">
+        <v>46284.0</v>
+      </c>
       <c r="J33" s="15"/>
       <c r="K33" s="15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L33" s="15"/>
       <c r="M33" s="16"/>
@@ -2266,22 +2293,22 @@
     </row>
     <row r="34" ht="29.25" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C34" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D34" s="7" t="s">
-        <v>64</v>
-      </c>
       <c r="E34" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G34" s="8">
         <v>46283.0</v>
@@ -2292,28 +2319,28 @@
       <c r="I34" s="8"/>
       <c r="J34" s="17"/>
       <c r="K34" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L34" s="9"/>
     </row>
     <row r="35" ht="29.25" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C35" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D35" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>40</v>
-      </c>
       <c r="F35" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G35" s="8">
         <v>46285.0</v>
@@ -2322,7 +2349,7 @@
         <v>46285.0</v>
       </c>
       <c r="I35" s="8">
-        <v>46285.0</v>
+        <v>46284.0</v>
       </c>
       <c r="J35" s="17"/>
       <c r="K35" s="9"/>
@@ -2330,31 +2357,31 @@
     </row>
     <row r="36" ht="29.25" customHeight="1">
       <c r="A36" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>66</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G36" s="8">
         <v>46283.0</v>
       </c>
       <c r="H36" s="8">
-        <v>46283.0</v>
+        <v>46285.0</v>
       </c>
       <c r="I36" s="8">
-        <v>46283.0</v>
+        <v>46285.0</v>
       </c>
       <c r="J36" s="17"/>
       <c r="K36" s="9"/>
@@ -2362,22 +2389,22 @@
     </row>
     <row r="37" ht="29.25" customHeight="1">
       <c r="A37" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G37" s="14">
         <v>46283.0</v>
@@ -2385,9 +2412,7 @@
       <c r="H37" s="14">
         <v>46285.0</v>
       </c>
-      <c r="I37" s="14">
-        <v>46289.0</v>
-      </c>
+      <c r="I37" s="14"/>
       <c r="J37" s="15"/>
       <c r="K37" s="15"/>
       <c r="L37" s="15"/>
@@ -2413,20 +2438,20 @@
     </row>
     <row r="38" ht="29.25" customHeight="1">
       <c r="A38" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E38" s="7"/>
       <c r="F38" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G38" s="8">
         <v>46283.0</v>
@@ -2441,20 +2466,20 @@
     </row>
     <row r="39" ht="29.25" customHeight="1">
       <c r="A39" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E39" s="13"/>
       <c r="F39" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G39" s="14">
         <v>46283.0</v>
@@ -2488,20 +2513,20 @@
     </row>
     <row r="40" ht="29.25" customHeight="1">
       <c r="A40" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E40" s="7"/>
       <c r="F40" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G40" s="8">
         <v>46283.0</v>
@@ -2516,25 +2541,25 @@
     </row>
     <row r="41" ht="29.25" customHeight="1">
       <c r="A41" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C41" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D41" s="13" t="s">
-        <v>74</v>
-      </c>
       <c r="E41" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G41" s="14">
-        <v>46285.0</v>
+        <v>46286.0</v>
       </c>
       <c r="H41" s="14">
         <v>46289.0</v>
@@ -2565,30 +2590,32 @@
     </row>
     <row r="42" ht="29.25" customHeight="1">
       <c r="A42" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G42" s="8">
-        <v>46285.0</v>
+        <v>46284.0</v>
       </c>
       <c r="H42" s="8">
         <v>46289.0</v>
       </c>
-      <c r="I42" s="8"/>
+      <c r="I42" s="8">
+        <v>46285.0</v>
+      </c>
       <c r="J42" s="17"/>
       <c r="K42" s="21"/>
       <c r="L42" s="21"/>
@@ -2598,19 +2625,19 @@
         <v>12</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D43" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E43" s="13" t="s">
+      <c r="F43" s="13" t="s">
         <v>16</v>
-      </c>
-      <c r="F43" s="13" t="s">
-        <v>17</v>
       </c>
       <c r="G43" s="14">
         <v>46285.0</v>
@@ -2618,7 +2645,9 @@
       <c r="H43" s="14">
         <v>46285.0</v>
       </c>
-      <c r="I43" s="14"/>
+      <c r="I43" s="14">
+        <v>46285.0</v>
+      </c>
       <c r="J43" s="15"/>
       <c r="K43" s="15"/>
       <c r="L43" s="15"/>
@@ -2644,30 +2673,32 @@
     </row>
     <row r="44" ht="29.25" customHeight="1">
       <c r="A44" s="10" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="G44" s="14">
-        <v>46288.0</v>
+        <v>46285.0</v>
       </c>
       <c r="H44" s="14">
-        <v>46289.0</v>
-      </c>
-      <c r="I44" s="14"/>
+        <v>46286.0</v>
+      </c>
+      <c r="I44" s="14">
+        <v>46285.0</v>
+      </c>
       <c r="J44" s="15"/>
       <c r="K44" s="15"/>
       <c r="L44" s="15"/>
@@ -2692,205 +2723,226 @@
       <c r="AE44" s="16"/>
     </row>
     <row r="45" ht="29.25" customHeight="1">
-      <c r="A45" s="4" t="s">
-        <v>26</v>
+      <c r="A45" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C45" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F45" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G45" s="14">
+        <v>46288.0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>46289.0</v>
+      </c>
+      <c r="I45" s="14"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="15"/>
+      <c r="L45" s="15"/>
+      <c r="M45" s="16"/>
+      <c r="N45" s="16"/>
+      <c r="O45" s="16"/>
+      <c r="P45" s="16"/>
+      <c r="Q45" s="16"/>
+      <c r="R45" s="16"/>
+      <c r="S45" s="16"/>
+      <c r="T45" s="16"/>
+      <c r="U45" s="16"/>
+      <c r="V45" s="16"/>
+      <c r="W45" s="16"/>
+      <c r="X45" s="16"/>
+      <c r="Y45" s="16"/>
+      <c r="Z45" s="16"/>
+      <c r="AA45" s="16"/>
+      <c r="AB45" s="16"/>
+      <c r="AC45" s="16"/>
+      <c r="AD45" s="16"/>
+      <c r="AE45" s="16"/>
+    </row>
+    <row r="46" ht="29.25" customHeight="1">
+      <c r="A46" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="D45" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G45" s="8">
+      <c r="D46" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G46" s="8">
         <v>46288.0</v>
       </c>
-      <c r="H45" s="8">
+      <c r="H46" s="8">
         <v>46289.0</v>
       </c>
-      <c r="I45" s="8"/>
-      <c r="J45" s="17"/>
-      <c r="K45" s="9"/>
-      <c r="L45" s="9"/>
-    </row>
-    <row r="46" ht="29.25" customHeight="1">
-      <c r="A46" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B46" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C46" s="12" t="s">
+      <c r="I46" s="8"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="9"/>
+      <c r="L46" s="9"/>
+    </row>
+    <row r="47" ht="29.25" customHeight="1">
+      <c r="A47" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="D46" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G46" s="14">
+      <c r="D47" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G47" s="14">
         <v>46285.0</v>
       </c>
-      <c r="H46" s="14">
+      <c r="H47" s="14">
         <v>46289.0</v>
       </c>
-      <c r="I46" s="14"/>
-      <c r="J46" s="15"/>
-      <c r="K46" s="15"/>
-      <c r="L46" s="15"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="16"/>
-      <c r="O46" s="16"/>
-      <c r="P46" s="16"/>
-      <c r="Q46" s="16"/>
-      <c r="R46" s="16"/>
-      <c r="S46" s="16"/>
-      <c r="T46" s="16"/>
-      <c r="U46" s="16"/>
-      <c r="V46" s="16"/>
-      <c r="W46" s="16"/>
-      <c r="X46" s="16"/>
-      <c r="Y46" s="16"/>
-      <c r="Z46" s="16"/>
-      <c r="AA46" s="16"/>
-      <c r="AB46" s="16"/>
-      <c r="AC46" s="16"/>
-      <c r="AD46" s="16"/>
-      <c r="AE46" s="16"/>
-    </row>
-    <row r="47" ht="29.25" customHeight="1">
-      <c r="A47" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B47" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C47" s="22" t="s">
+      <c r="I47" s="14"/>
+      <c r="J47" s="15"/>
+      <c r="K47" s="15"/>
+      <c r="L47" s="15"/>
+      <c r="M47" s="16"/>
+      <c r="N47" s="16"/>
+      <c r="O47" s="16"/>
+      <c r="P47" s="16"/>
+      <c r="Q47" s="16"/>
+      <c r="R47" s="16"/>
+      <c r="S47" s="16"/>
+      <c r="T47" s="16"/>
+      <c r="U47" s="16"/>
+      <c r="V47" s="16"/>
+      <c r="W47" s="16"/>
+      <c r="X47" s="16"/>
+      <c r="Y47" s="16"/>
+      <c r="Z47" s="16"/>
+      <c r="AA47" s="16"/>
+      <c r="AB47" s="16"/>
+      <c r="AC47" s="16"/>
+      <c r="AD47" s="16"/>
+      <c r="AE47" s="16"/>
+    </row>
+    <row r="48" ht="29.25" customHeight="1">
+      <c r="A48" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D47" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G47" s="8">
+      <c r="D48" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G48" s="8">
         <v>46286.0</v>
       </c>
-      <c r="H47" s="8">
+      <c r="H48" s="8">
         <v>46288.0</v>
       </c>
-      <c r="I47" s="8"/>
-      <c r="J47" s="17"/>
-      <c r="K47" s="9"/>
-      <c r="L47" s="9"/>
-    </row>
-    <row r="48" ht="29.25" customHeight="1">
-      <c r="A48" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B48" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C48" s="12" t="s">
+      <c r="I48" s="8"/>
+      <c r="J48" s="17"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="9"/>
+    </row>
+    <row r="49" ht="29.25" customHeight="1">
+      <c r="A49" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="D48" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G48" s="14">
+      <c r="D49" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G49" s="14">
         <v>46286.0</v>
       </c>
-      <c r="H48" s="14">
+      <c r="H49" s="14">
         <v>46288.0</v>
       </c>
-      <c r="I48" s="14"/>
-      <c r="J48" s="15"/>
-      <c r="K48" s="15"/>
-      <c r="L48" s="15"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="16"/>
-      <c r="O48" s="16"/>
-      <c r="P48" s="16"/>
-      <c r="Q48" s="16"/>
-      <c r="R48" s="16"/>
-      <c r="S48" s="16"/>
-      <c r="T48" s="16"/>
-      <c r="U48" s="16"/>
-      <c r="V48" s="16"/>
-      <c r="W48" s="16"/>
-      <c r="X48" s="16"/>
-      <c r="Y48" s="16"/>
-      <c r="Z48" s="16"/>
-      <c r="AA48" s="16"/>
-      <c r="AB48" s="16"/>
-      <c r="AC48" s="16"/>
-      <c r="AD48" s="16"/>
-      <c r="AE48" s="16"/>
-    </row>
-    <row r="49" ht="29.25" customHeight="1">
-      <c r="A49" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B49" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C49" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="8">
-        <v>46286.0</v>
-      </c>
-      <c r="H49" s="8">
-        <v>46288.0</v>
-      </c>
-      <c r="I49" s="8"/>
-      <c r="J49" s="17"/>
-      <c r="K49" s="9"/>
-      <c r="L49" s="9"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="15"/>
+      <c r="K49" s="15"/>
+      <c r="L49" s="15"/>
+      <c r="M49" s="16"/>
+      <c r="N49" s="16"/>
+      <c r="O49" s="16"/>
+      <c r="P49" s="16"/>
+      <c r="Q49" s="16"/>
+      <c r="R49" s="16"/>
+      <c r="S49" s="16"/>
+      <c r="T49" s="16"/>
+      <c r="U49" s="16"/>
+      <c r="V49" s="16"/>
+      <c r="W49" s="16"/>
+      <c r="X49" s="16"/>
+      <c r="Y49" s="16"/>
+      <c r="Z49" s="16"/>
+      <c r="AA49" s="16"/>
+      <c r="AB49" s="16"/>
+      <c r="AC49" s="16"/>
+      <c r="AD49" s="16"/>
+      <c r="AE49" s="16"/>
     </row>
     <row r="50" ht="29.25" customHeight="1">
       <c r="A50" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B50" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="C50" s="12" t="s">
-        <v>83</v>
-      </c>
       <c r="D50" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>69</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="E50" s="13"/>
       <c r="F50" s="13" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="G50" s="14">
-        <v>46287.0</v>
+        <v>46286.0</v>
       </c>
       <c r="H50" s="14">
-        <v>46290.0</v>
+        <v>46288.0</v>
       </c>
       <c r="I50" s="14"/>
       <c r="J50" s="15"/>
@@ -2917,57 +2969,76 @@
       <c r="AE50" s="16"/>
     </row>
     <row r="51" ht="29.25" customHeight="1">
-      <c r="A51" s="4" t="s">
-        <v>26</v>
+      <c r="A51" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G51" s="8">
+        <v>57</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G51" s="14">
+        <v>46286.0</v>
+      </c>
+      <c r="H51" s="14">
         <v>46288.0</v>
       </c>
-      <c r="H51" s="8">
-        <v>46290.0</v>
-      </c>
-      <c r="I51" s="8"/>
-      <c r="J51" s="17"/>
-      <c r="K51" s="9"/>
-      <c r="L51" s="9"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="15"/>
+      <c r="K51" s="15"/>
+      <c r="L51" s="15"/>
+      <c r="M51" s="16"/>
+      <c r="N51" s="16"/>
+      <c r="O51" s="16"/>
+      <c r="P51" s="16"/>
+      <c r="Q51" s="16"/>
+      <c r="R51" s="16"/>
+      <c r="S51" s="16"/>
+      <c r="T51" s="16"/>
+      <c r="U51" s="16"/>
+      <c r="V51" s="16"/>
+      <c r="W51" s="16"/>
+      <c r="X51" s="16"/>
+      <c r="Y51" s="16"/>
+      <c r="Z51" s="16"/>
+      <c r="AA51" s="16"/>
+      <c r="AB51" s="16"/>
+      <c r="AC51" s="16"/>
+      <c r="AD51" s="16"/>
+      <c r="AE51" s="16"/>
     </row>
     <row r="52" ht="29.25" customHeight="1">
       <c r="A52" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B52" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C52" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C52" s="12" t="s">
-        <v>86</v>
-      </c>
       <c r="D52" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E52" s="13"/>
+        <v>73</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>68</v>
+      </c>
       <c r="F52" s="13" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="G52" s="14">
-        <v>46291.0</v>
+        <v>46287.0</v>
       </c>
       <c r="H52" s="14">
-        <v>46291.0</v>
+        <v>46290.0</v>
       </c>
       <c r="I52" s="14"/>
       <c r="J52" s="15"/>
@@ -2995,50 +3066,50 @@
     </row>
     <row r="53" ht="29.25" customHeight="1">
       <c r="A53" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>87</v>
+        <v>25</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>84</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G53" s="8">
-        <v>46291.0</v>
+        <v>46288.0</v>
       </c>
       <c r="H53" s="8">
-        <v>46291.0</v>
+        <v>46290.0</v>
       </c>
       <c r="I53" s="8"/>
-      <c r="J53" s="9"/>
+      <c r="J53" s="17"/>
       <c r="K53" s="9"/>
       <c r="L53" s="9"/>
     </row>
     <row r="54" ht="29.25" customHeight="1">
       <c r="A54" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>87</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E54" s="13"/>
       <c r="F54" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G54" s="14">
         <v>46291.0</v>
@@ -3072,28 +3143,28 @@
     </row>
     <row r="55" ht="29.25" customHeight="1">
       <c r="A55" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>90</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="G55" s="8">
-        <v>46286.0</v>
+        <v>46291.0</v>
       </c>
       <c r="H55" s="8">
-        <v>46293.0</v>
+        <v>46291.0</v>
       </c>
       <c r="I55" s="8"/>
       <c r="J55" s="9"/>
@@ -3102,34 +3173,30 @@
     </row>
     <row r="56" ht="29.25" customHeight="1">
       <c r="A56" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C56" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B56" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C56" s="12" t="s">
-        <v>93</v>
-      </c>
       <c r="D56" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E56" s="13" t="s">
-        <v>69</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="E56" s="13"/>
       <c r="F56" s="13" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G56" s="14">
-        <v>46289.0</v>
+        <v>46291.0</v>
       </c>
       <c r="H56" s="14">
-        <v>46289.0</v>
+        <v>46291.0</v>
       </c>
       <c r="I56" s="14"/>
       <c r="J56" s="15"/>
-      <c r="K56" s="15" t="s">
-        <v>94</v>
-      </c>
+      <c r="K56" s="15"/>
       <c r="L56" s="15"/>
       <c r="M56" s="16"/>
       <c r="N56" s="16"/>
@@ -3153,89 +3220,88 @@
     </row>
     <row r="57" ht="29.25" customHeight="1">
       <c r="A57" s="4" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>92</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="G57" s="8">
-        <v>46289.0</v>
+        <v>46286.0</v>
       </c>
       <c r="H57" s="8">
-        <v>46289.0</v>
+        <v>46293.0</v>
       </c>
       <c r="I57" s="8"/>
       <c r="J57" s="9"/>
-      <c r="K57" s="9" t="s">
-        <v>94</v>
-      </c>
+      <c r="K57" s="9"/>
       <c r="L57" s="9"/>
     </row>
     <row r="58" ht="29.25" customHeight="1">
       <c r="A58" s="4" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G58" s="8">
-        <v>46289.0</v>
-      </c>
-      <c r="H58" s="8">
-        <v>46289.0</v>
-      </c>
-      <c r="I58" s="8"/>
-      <c r="J58" s="9"/>
-      <c r="K58" s="9"/>
-      <c r="L58" s="9"/>
+        <v>93</v>
+      </c>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="14"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="15"/>
+      <c r="K58" s="15"/>
+      <c r="L58" s="15"/>
+      <c r="M58" s="16"/>
+      <c r="N58" s="16"/>
+      <c r="O58" s="16"/>
+      <c r="P58" s="16"/>
+      <c r="Q58" s="16"/>
+      <c r="R58" s="16"/>
+      <c r="S58" s="16"/>
+      <c r="T58" s="16"/>
+      <c r="U58" s="16"/>
+      <c r="V58" s="16"/>
+      <c r="W58" s="16"/>
+      <c r="X58" s="16"/>
+      <c r="Y58" s="16"/>
+      <c r="Z58" s="16"/>
+      <c r="AA58" s="16"/>
+      <c r="AB58" s="16"/>
+      <c r="AC58" s="16"/>
+      <c r="AD58" s="16"/>
+      <c r="AE58" s="16"/>
     </row>
     <row r="59" ht="29.25" customHeight="1">
-      <c r="A59" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B59" s="11" t="s">
-        <v>97</v>
+      <c r="A59" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D59" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E59" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="F59" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G59" s="14">
-        <v>46286.0</v>
-      </c>
-      <c r="H59" s="14">
-        <v>46293.0</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="D59" s="13"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14"/>
       <c r="I59" s="14"/>
       <c r="J59" s="15"/>
       <c r="K59" s="15"/>
@@ -3262,55 +3328,58 @@
     </row>
     <row r="60" ht="29.25" customHeight="1">
       <c r="A60" s="4" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G60" s="8">
-        <v>46287.0</v>
-      </c>
-      <c r="H60" s="8">
-        <v>46295.0</v>
-      </c>
-      <c r="I60" s="8"/>
-      <c r="J60" s="9"/>
-      <c r="K60" s="9"/>
-      <c r="L60" s="9"/>
+        <v>95</v>
+      </c>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="14"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="15"/>
+      <c r="K60" s="15"/>
+      <c r="L60" s="15"/>
+      <c r="M60" s="16"/>
+      <c r="N60" s="16"/>
+      <c r="O60" s="16"/>
+      <c r="P60" s="16"/>
+      <c r="Q60" s="16"/>
+      <c r="R60" s="16"/>
+      <c r="S60" s="16"/>
+      <c r="T60" s="16"/>
+      <c r="U60" s="16"/>
+      <c r="V60" s="16"/>
+      <c r="W60" s="16"/>
+      <c r="X60" s="16"/>
+      <c r="Y60" s="16"/>
+      <c r="Z60" s="16"/>
+      <c r="AA60" s="16"/>
+      <c r="AB60" s="16"/>
+      <c r="AC60" s="16"/>
+      <c r="AD60" s="16"/>
+      <c r="AE60" s="16"/>
     </row>
     <row r="61" ht="29.25" customHeight="1">
-      <c r="A61" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B61" s="11" t="s">
-        <v>99</v>
+      <c r="A61" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="D61" s="13" t="s">
-        <v>74</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="D61" s="13"/>
       <c r="E61" s="13"/>
-      <c r="F61" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G61" s="14">
-        <v>46287.0</v>
-      </c>
-      <c r="H61" s="14">
-        <v>46293.0</v>
-      </c>
+      <c r="F61" s="13"/>
+      <c r="G61" s="14"/>
+      <c r="H61" s="14"/>
       <c r="I61" s="14"/>
       <c r="J61" s="15"/>
       <c r="K61" s="15"/>
@@ -3337,53 +3406,54 @@
     </row>
     <row r="62" ht="29.25" customHeight="1">
       <c r="A62" s="4" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G62" s="8">
-        <v>46296.0</v>
-      </c>
-      <c r="H62" s="8">
-        <v>46303.0</v>
-      </c>
-      <c r="I62" s="8"/>
-      <c r="J62" s="9"/>
-      <c r="K62" s="9"/>
-      <c r="L62" s="9"/>
+        <v>97</v>
+      </c>
+      <c r="D62" s="13"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13"/>
+      <c r="G62" s="14"/>
+      <c r="H62" s="14"/>
+      <c r="I62" s="14"/>
+      <c r="J62" s="15"/>
+      <c r="K62" s="15"/>
+      <c r="L62" s="15"/>
+      <c r="M62" s="16"/>
+      <c r="N62" s="16"/>
+      <c r="O62" s="16"/>
+      <c r="P62" s="16"/>
+      <c r="Q62" s="16"/>
+      <c r="R62" s="16"/>
+      <c r="S62" s="16"/>
+      <c r="T62" s="16"/>
+      <c r="U62" s="16"/>
+      <c r="V62" s="16"/>
+      <c r="W62" s="16"/>
+      <c r="X62" s="16"/>
+      <c r="Y62" s="16"/>
+      <c r="Z62" s="16"/>
+      <c r="AA62" s="16"/>
+      <c r="AB62" s="16"/>
+      <c r="AC62" s="16"/>
+      <c r="AD62" s="16"/>
+      <c r="AE62" s="16"/>
     </row>
     <row r="63" ht="29.25" customHeight="1">
-      <c r="A63" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B63" s="11" t="s">
-        <v>102</v>
-      </c>
+      <c r="A63" s="10"/>
+      <c r="B63" s="11"/>
       <c r="C63" s="12" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D63" s="13"/>
       <c r="E63" s="13"/>
-      <c r="F63" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G63" s="14">
-        <v>46303.0</v>
-      </c>
-      <c r="H63" s="14">
-        <v>46303.0</v>
-      </c>
+      <c r="F63" s="13"/>
+      <c r="G63" s="14"/>
+      <c r="H63" s="14"/>
       <c r="I63" s="14"/>
       <c r="J63" s="15"/>
       <c r="K63" s="15"/>
@@ -3409,233 +3479,429 @@
       <c r="AE63" s="16"/>
     </row>
     <row r="64" ht="29.25" customHeight="1">
-      <c r="A64" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B64" s="5" t="s">
+      <c r="A64" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E64" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F64" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G64" s="14">
+        <v>46289.0</v>
+      </c>
+      <c r="H64" s="14">
+        <v>46289.0</v>
+      </c>
+      <c r="I64" s="14"/>
+      <c r="J64" s="15"/>
+      <c r="K64" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="L64" s="15"/>
+      <c r="M64" s="16"/>
+      <c r="N64" s="16"/>
+      <c r="O64" s="16"/>
+      <c r="P64" s="16"/>
+      <c r="Q64" s="16"/>
+      <c r="R64" s="16"/>
+      <c r="S64" s="16"/>
+      <c r="T64" s="16"/>
+      <c r="U64" s="16"/>
+      <c r="V64" s="16"/>
+      <c r="W64" s="16"/>
+      <c r="X64" s="16"/>
+      <c r="Y64" s="16"/>
+      <c r="Z64" s="16"/>
+      <c r="AA64" s="16"/>
+      <c r="AB64" s="16"/>
+      <c r="AC64" s="16"/>
+      <c r="AD64" s="16"/>
+      <c r="AE64" s="16"/>
+    </row>
+    <row r="65" ht="29.25" customHeight="1">
+      <c r="A65" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G65" s="8">
+        <v>46289.0</v>
+      </c>
+      <c r="H65" s="8">
+        <v>46289.0</v>
+      </c>
+      <c r="I65" s="8"/>
+      <c r="J65" s="9"/>
+      <c r="K65" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="L65" s="9"/>
+    </row>
+    <row r="66" ht="29.25" customHeight="1">
+      <c r="A66" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C66" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="D66" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E66" s="7"/>
+      <c r="F66" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G66" s="8">
+        <v>46289.0</v>
+      </c>
+      <c r="H66" s="8">
+        <v>46289.0</v>
+      </c>
+      <c r="I66" s="8"/>
+      <c r="J66" s="9"/>
+      <c r="K66" s="9"/>
+      <c r="L66" s="9"/>
+    </row>
+    <row r="67" ht="29.25" customHeight="1">
+      <c r="A67" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B67" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="D64" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E64" s="7"/>
-      <c r="F64" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G64" s="8">
+      <c r="C67" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F67" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G67" s="14">
+        <v>46286.0</v>
+      </c>
+      <c r="H67" s="14">
+        <v>46293.0</v>
+      </c>
+      <c r="I67" s="14"/>
+      <c r="J67" s="15"/>
+      <c r="K67" s="15"/>
+      <c r="L67" s="15"/>
+      <c r="M67" s="16"/>
+      <c r="N67" s="16"/>
+      <c r="O67" s="16"/>
+      <c r="P67" s="16"/>
+      <c r="Q67" s="16"/>
+      <c r="R67" s="16"/>
+      <c r="S67" s="16"/>
+      <c r="T67" s="16"/>
+      <c r="U67" s="16"/>
+      <c r="V67" s="16"/>
+      <c r="W67" s="16"/>
+      <c r="X67" s="16"/>
+      <c r="Y67" s="16"/>
+      <c r="Z67" s="16"/>
+      <c r="AA67" s="16"/>
+      <c r="AB67" s="16"/>
+      <c r="AC67" s="16"/>
+      <c r="AD67" s="16"/>
+      <c r="AE67" s="16"/>
+    </row>
+    <row r="68" ht="29.25" customHeight="1">
+      <c r="A68" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E68" s="7"/>
+      <c r="F68" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G68" s="8">
+        <v>46287.0</v>
+      </c>
+      <c r="H68" s="8">
+        <v>46295.0</v>
+      </c>
+      <c r="I68" s="8"/>
+      <c r="J68" s="9"/>
+      <c r="K68" s="9"/>
+      <c r="L68" s="9"/>
+    </row>
+    <row r="69" ht="29.25" customHeight="1">
+      <c r="A69" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D69" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E69" s="13"/>
+      <c r="F69" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G69" s="14">
+        <v>46287.0</v>
+      </c>
+      <c r="H69" s="14">
+        <v>46293.0</v>
+      </c>
+      <c r="I69" s="14"/>
+      <c r="J69" s="15"/>
+      <c r="K69" s="15"/>
+      <c r="L69" s="15"/>
+      <c r="M69" s="16"/>
+      <c r="N69" s="16"/>
+      <c r="O69" s="16"/>
+      <c r="P69" s="16"/>
+      <c r="Q69" s="16"/>
+      <c r="R69" s="16"/>
+      <c r="S69" s="16"/>
+      <c r="T69" s="16"/>
+      <c r="U69" s="16"/>
+      <c r="V69" s="16"/>
+      <c r="W69" s="16"/>
+      <c r="X69" s="16"/>
+      <c r="Y69" s="16"/>
+      <c r="Z69" s="16"/>
+      <c r="AA69" s="16"/>
+      <c r="AB69" s="16"/>
+      <c r="AC69" s="16"/>
+      <c r="AD69" s="16"/>
+      <c r="AE69" s="16"/>
+    </row>
+    <row r="70" ht="29.25" customHeight="1">
+      <c r="A70" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G70" s="8">
+        <v>46296.0</v>
+      </c>
+      <c r="H70" s="8">
+        <v>46303.0</v>
+      </c>
+      <c r="I70" s="8"/>
+      <c r="J70" s="9"/>
+      <c r="K70" s="9"/>
+      <c r="L70" s="9"/>
+    </row>
+    <row r="71" ht="29.25" customHeight="1">
+      <c r="A71" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="D71" s="13"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G71" s="14">
+        <v>46303.0</v>
+      </c>
+      <c r="H71" s="14">
+        <v>46303.0</v>
+      </c>
+      <c r="I71" s="14"/>
+      <c r="J71" s="15"/>
+      <c r="K71" s="15"/>
+      <c r="L71" s="15"/>
+      <c r="M71" s="16"/>
+      <c r="N71" s="16"/>
+      <c r="O71" s="16"/>
+      <c r="P71" s="16"/>
+      <c r="Q71" s="16"/>
+      <c r="R71" s="16"/>
+      <c r="S71" s="16"/>
+      <c r="T71" s="16"/>
+      <c r="U71" s="16"/>
+      <c r="V71" s="16"/>
+      <c r="W71" s="16"/>
+      <c r="X71" s="16"/>
+      <c r="Y71" s="16"/>
+      <c r="Z71" s="16"/>
+      <c r="AA71" s="16"/>
+      <c r="AB71" s="16"/>
+      <c r="AC71" s="16"/>
+      <c r="AD71" s="16"/>
+      <c r="AE71" s="16"/>
+    </row>
+    <row r="72" ht="29.25" customHeight="1">
+      <c r="A72" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E72" s="7"/>
+      <c r="F72" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G72" s="8">
         <v>46305.0</v>
       </c>
-      <c r="H64" s="8">
+      <c r="H72" s="8">
         <v>46305.0</v>
       </c>
-      <c r="I64" s="8"/>
-      <c r="J64" s="9"/>
-      <c r="K64" s="9"/>
-      <c r="L64" s="9"/>
-    </row>
-    <row r="65" ht="29.25" customHeight="1">
-      <c r="A65" s="23"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="24"/>
-      <c r="D65" s="25"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="G65" s="27"/>
-      <c r="H65" s="27"/>
-      <c r="I65" s="27"/>
-      <c r="J65" s="17"/>
-      <c r="K65" s="21"/>
-      <c r="L65" s="21"/>
-    </row>
-    <row r="66" ht="29.25" customHeight="1">
-      <c r="A66" s="23"/>
-      <c r="B66" s="6"/>
-      <c r="C66" s="24"/>
-      <c r="D66" s="25"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="G66" s="27"/>
-      <c r="H66" s="27"/>
-      <c r="I66" s="27"/>
-      <c r="J66" s="17"/>
-      <c r="K66" s="21"/>
-      <c r="L66" s="21"/>
-    </row>
-    <row r="67" ht="29.25" customHeight="1">
-      <c r="A67" s="23"/>
-      <c r="B67" s="6"/>
-      <c r="C67" s="24"/>
-      <c r="D67" s="25"/>
-      <c r="E67" s="21"/>
-      <c r="F67" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="G67" s="27"/>
-      <c r="H67" s="27"/>
-      <c r="I67" s="27"/>
-      <c r="J67" s="17"/>
-      <c r="K67" s="21"/>
-      <c r="L67" s="21"/>
-    </row>
-    <row r="68" ht="29.25" customHeight="1">
-      <c r="A68" s="23"/>
-      <c r="B68" s="6"/>
-      <c r="C68" s="24"/>
-      <c r="D68" s="25"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="G68" s="27"/>
-      <c r="H68" s="27"/>
-      <c r="I68" s="27"/>
-      <c r="J68" s="17"/>
-      <c r="K68" s="21"/>
-      <c r="L68" s="21"/>
-    </row>
-    <row r="69" ht="29.25" customHeight="1">
-      <c r="A69" s="23"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="24"/>
-      <c r="D69" s="25"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="G69" s="27"/>
-      <c r="H69" s="27"/>
-      <c r="I69" s="27"/>
-      <c r="J69" s="17"/>
-      <c r="K69" s="21"/>
-      <c r="L69" s="21"/>
-    </row>
-    <row r="70" ht="29.25" customHeight="1">
-      <c r="A70" s="23"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="28"/>
-      <c r="D70" s="25"/>
-      <c r="E70" s="29"/>
-      <c r="F70" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
-      <c r="I70" s="30"/>
-      <c r="J70" s="17"/>
-    </row>
-    <row r="71" ht="29.25" customHeight="1">
-      <c r="A71" s="31"/>
-      <c r="B71" s="28"/>
-      <c r="C71" s="28"/>
-      <c r="D71" s="25"/>
-      <c r="E71" s="29"/>
-      <c r="F71" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="G71" s="30"/>
-      <c r="H71" s="30"/>
-      <c r="I71" s="30"/>
-      <c r="J71" s="17"/>
-    </row>
-    <row r="72" ht="29.25" customHeight="1">
-      <c r="A72" s="31"/>
-      <c r="B72" s="28"/>
-      <c r="C72" s="28"/>
-      <c r="D72" s="25"/>
-      <c r="E72" s="29"/>
-      <c r="F72" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="G72" s="30"/>
-      <c r="H72" s="30"/>
-      <c r="I72" s="30"/>
-      <c r="J72" s="17"/>
+      <c r="I72" s="8"/>
+      <c r="J72" s="9"/>
+      <c r="K72" s="9"/>
+      <c r="L72" s="9"/>
     </row>
     <row r="73" ht="29.25" customHeight="1">
-      <c r="A73" s="31"/>
-      <c r="B73" s="28"/>
-      <c r="C73" s="28"/>
+      <c r="A73" s="23"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="24"/>
       <c r="D73" s="25"/>
-      <c r="E73" s="29"/>
+      <c r="E73" s="21"/>
       <c r="F73" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="G73" s="30"/>
-      <c r="H73" s="30"/>
-      <c r="I73" s="30"/>
+        <v>68</v>
+      </c>
+      <c r="G73" s="27"/>
+      <c r="H73" s="27"/>
+      <c r="I73" s="27"/>
       <c r="J73" s="17"/>
+      <c r="K73" s="21"/>
+      <c r="L73" s="21"/>
     </row>
     <row r="74" ht="29.25" customHeight="1">
-      <c r="A74" s="31"/>
-      <c r="B74" s="28"/>
-      <c r="C74" s="28"/>
+      <c r="A74" s="23"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="24"/>
       <c r="D74" s="25"/>
-      <c r="E74" s="29"/>
+      <c r="E74" s="21"/>
       <c r="F74" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="G74" s="30"/>
-      <c r="H74" s="30"/>
-      <c r="I74" s="30"/>
+        <v>68</v>
+      </c>
+      <c r="G74" s="27"/>
+      <c r="H74" s="27"/>
+      <c r="I74" s="27"/>
       <c r="J74" s="17"/>
+      <c r="K74" s="21"/>
+      <c r="L74" s="21"/>
     </row>
     <row r="75" ht="29.25" customHeight="1">
-      <c r="A75" s="31"/>
-      <c r="B75" s="28"/>
-      <c r="C75" s="28"/>
+      <c r="A75" s="23"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="24"/>
       <c r="D75" s="25"/>
-      <c r="E75" s="29"/>
+      <c r="E75" s="21"/>
       <c r="F75" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="G75" s="30"/>
-      <c r="H75" s="30"/>
-      <c r="I75" s="30"/>
+        <v>68</v>
+      </c>
+      <c r="G75" s="27"/>
+      <c r="H75" s="27"/>
+      <c r="I75" s="27"/>
       <c r="J75" s="17"/>
+      <c r="K75" s="21"/>
+      <c r="L75" s="21"/>
     </row>
     <row r="76" ht="29.25" customHeight="1">
-      <c r="A76" s="31"/>
-      <c r="B76" s="28"/>
-      <c r="C76" s="28"/>
+      <c r="A76" s="23"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="24"/>
       <c r="D76" s="25"/>
-      <c r="E76" s="29"/>
+      <c r="E76" s="21"/>
       <c r="F76" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="G76" s="30"/>
-      <c r="H76" s="30"/>
-      <c r="I76" s="30"/>
+        <v>68</v>
+      </c>
+      <c r="G76" s="27"/>
+      <c r="H76" s="27"/>
+      <c r="I76" s="27"/>
       <c r="J76" s="17"/>
+      <c r="K76" s="21"/>
+      <c r="L76" s="21"/>
     </row>
     <row r="77" ht="29.25" customHeight="1">
-      <c r="A77" s="31"/>
-      <c r="B77" s="28"/>
-      <c r="C77" s="28"/>
+      <c r="A77" s="23"/>
+      <c r="B77" s="6"/>
+      <c r="C77" s="24"/>
       <c r="D77" s="25"/>
-      <c r="E77" s="29"/>
+      <c r="E77" s="21"/>
       <c r="F77" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="G77" s="30"/>
-      <c r="H77" s="30"/>
-      <c r="I77" s="30"/>
+        <v>68</v>
+      </c>
+      <c r="G77" s="27"/>
+      <c r="H77" s="27"/>
+      <c r="I77" s="27"/>
       <c r="J77" s="17"/>
+      <c r="K77" s="21"/>
+      <c r="L77" s="21"/>
     </row>
     <row r="78" ht="29.25" customHeight="1">
-      <c r="A78" s="31"/>
-      <c r="B78" s="28"/>
+      <c r="A78" s="23"/>
+      <c r="B78" s="6"/>
       <c r="C78" s="28"/>
       <c r="D78" s="25"/>
       <c r="E78" s="29"/>
       <c r="F78" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G78" s="30"/>
       <c r="H78" s="30"/>
@@ -3649,7 +3915,7 @@
       <c r="D79" s="25"/>
       <c r="E79" s="29"/>
       <c r="F79" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G79" s="30"/>
       <c r="H79" s="30"/>
@@ -3663,7 +3929,7 @@
       <c r="D80" s="25"/>
       <c r="E80" s="29"/>
       <c r="F80" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G80" s="30"/>
       <c r="H80" s="30"/>
@@ -3677,7 +3943,7 @@
       <c r="D81" s="25"/>
       <c r="E81" s="29"/>
       <c r="F81" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G81" s="30"/>
       <c r="H81" s="30"/>
@@ -3691,7 +3957,7 @@
       <c r="D82" s="25"/>
       <c r="E82" s="29"/>
       <c r="F82" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G82" s="30"/>
       <c r="H82" s="30"/>
@@ -3705,7 +3971,7 @@
       <c r="D83" s="25"/>
       <c r="E83" s="29"/>
       <c r="F83" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G83" s="30"/>
       <c r="H83" s="30"/>
@@ -3719,7 +3985,7 @@
       <c r="D84" s="25"/>
       <c r="E84" s="29"/>
       <c r="F84" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G84" s="30"/>
       <c r="H84" s="30"/>
@@ -3733,7 +3999,7 @@
       <c r="D85" s="25"/>
       <c r="E85" s="29"/>
       <c r="F85" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G85" s="30"/>
       <c r="H85" s="30"/>
@@ -3747,7 +4013,7 @@
       <c r="D86" s="25"/>
       <c r="E86" s="29"/>
       <c r="F86" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G86" s="30"/>
       <c r="H86" s="30"/>
@@ -3761,7 +4027,7 @@
       <c r="D87" s="25"/>
       <c r="E87" s="29"/>
       <c r="F87" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G87" s="30"/>
       <c r="H87" s="30"/>
@@ -3775,7 +4041,7 @@
       <c r="D88" s="25"/>
       <c r="E88" s="29"/>
       <c r="F88" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G88" s="30"/>
       <c r="H88" s="30"/>
@@ -3789,7 +4055,7 @@
       <c r="D89" s="25"/>
       <c r="E89" s="29"/>
       <c r="F89" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G89" s="30"/>
       <c r="H89" s="30"/>
@@ -3803,7 +4069,7 @@
       <c r="D90" s="25"/>
       <c r="E90" s="29"/>
       <c r="F90" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G90" s="30"/>
       <c r="H90" s="30"/>
@@ -3817,7 +4083,7 @@
       <c r="D91" s="25"/>
       <c r="E91" s="29"/>
       <c r="F91" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G91" s="30"/>
       <c r="H91" s="30"/>
@@ -3831,7 +4097,7 @@
       <c r="D92" s="25"/>
       <c r="E92" s="29"/>
       <c r="F92" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G92" s="30"/>
       <c r="H92" s="30"/>
@@ -3845,7 +4111,7 @@
       <c r="D93" s="25"/>
       <c r="E93" s="29"/>
       <c r="F93" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G93" s="30"/>
       <c r="H93" s="30"/>
@@ -3859,7 +4125,7 @@
       <c r="D94" s="25"/>
       <c r="E94" s="29"/>
       <c r="F94" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G94" s="30"/>
       <c r="H94" s="30"/>
@@ -3873,7 +4139,7 @@
       <c r="D95" s="25"/>
       <c r="E95" s="29"/>
       <c r="F95" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G95" s="30"/>
       <c r="H95" s="30"/>
@@ -3887,7 +4153,7 @@
       <c r="D96" s="25"/>
       <c r="E96" s="29"/>
       <c r="F96" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G96" s="30"/>
       <c r="H96" s="30"/>
@@ -3901,7 +4167,7 @@
       <c r="D97" s="25"/>
       <c r="E97" s="29"/>
       <c r="F97" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G97" s="30"/>
       <c r="H97" s="30"/>
@@ -3915,7 +4181,7 @@
       <c r="D98" s="25"/>
       <c r="E98" s="29"/>
       <c r="F98" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G98" s="30"/>
       <c r="H98" s="30"/>
@@ -3929,7 +4195,7 @@
       <c r="D99" s="25"/>
       <c r="E99" s="29"/>
       <c r="F99" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G99" s="30"/>
       <c r="H99" s="30"/>
@@ -3943,7 +4209,7 @@
       <c r="D100" s="25"/>
       <c r="E100" s="29"/>
       <c r="F100" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G100" s="30"/>
       <c r="H100" s="30"/>
@@ -3957,7 +4223,7 @@
       <c r="D101" s="25"/>
       <c r="E101" s="29"/>
       <c r="F101" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G101" s="30"/>
       <c r="H101" s="30"/>
@@ -3971,7 +4237,7 @@
       <c r="D102" s="25"/>
       <c r="E102" s="29"/>
       <c r="F102" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G102" s="30"/>
       <c r="H102" s="30"/>
@@ -3985,7 +4251,7 @@
       <c r="D103" s="25"/>
       <c r="E103" s="29"/>
       <c r="F103" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G103" s="30"/>
       <c r="H103" s="30"/>
@@ -3999,7 +4265,7 @@
       <c r="D104" s="25"/>
       <c r="E104" s="29"/>
       <c r="F104" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G104" s="30"/>
       <c r="H104" s="30"/>
@@ -4013,7 +4279,7 @@
       <c r="D105" s="25"/>
       <c r="E105" s="29"/>
       <c r="F105" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G105" s="30"/>
       <c r="H105" s="30"/>
@@ -4027,7 +4293,7 @@
       <c r="D106" s="25"/>
       <c r="E106" s="29"/>
       <c r="F106" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G106" s="30"/>
       <c r="H106" s="30"/>
@@ -4041,7 +4307,7 @@
       <c r="D107" s="25"/>
       <c r="E107" s="29"/>
       <c r="F107" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G107" s="30"/>
       <c r="H107" s="30"/>
@@ -4055,7 +4321,7 @@
       <c r="D108" s="25"/>
       <c r="E108" s="29"/>
       <c r="F108" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G108" s="30"/>
       <c r="H108" s="30"/>
@@ -4069,7 +4335,7 @@
       <c r="D109" s="25"/>
       <c r="E109" s="29"/>
       <c r="F109" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G109" s="30"/>
       <c r="H109" s="30"/>
@@ -4083,7 +4349,7 @@
       <c r="D110" s="25"/>
       <c r="E110" s="29"/>
       <c r="F110" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G110" s="30"/>
       <c r="H110" s="30"/>
@@ -4097,7 +4363,7 @@
       <c r="D111" s="25"/>
       <c r="E111" s="29"/>
       <c r="F111" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G111" s="30"/>
       <c r="H111" s="30"/>
@@ -4111,7 +4377,7 @@
       <c r="D112" s="25"/>
       <c r="E112" s="29"/>
       <c r="F112" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G112" s="30"/>
       <c r="H112" s="30"/>
@@ -4125,7 +4391,7 @@
       <c r="D113" s="25"/>
       <c r="E113" s="29"/>
       <c r="F113" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G113" s="30"/>
       <c r="H113" s="30"/>
@@ -4139,7 +4405,7 @@
       <c r="D114" s="25"/>
       <c r="E114" s="29"/>
       <c r="F114" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G114" s="30"/>
       <c r="H114" s="30"/>
@@ -4153,7 +4419,7 @@
       <c r="D115" s="25"/>
       <c r="E115" s="29"/>
       <c r="F115" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G115" s="30"/>
       <c r="H115" s="30"/>
@@ -4167,7 +4433,7 @@
       <c r="D116" s="25"/>
       <c r="E116" s="29"/>
       <c r="F116" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G116" s="30"/>
       <c r="H116" s="30"/>
@@ -4181,7 +4447,7 @@
       <c r="D117" s="25"/>
       <c r="E117" s="29"/>
       <c r="F117" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G117" s="30"/>
       <c r="H117" s="30"/>
@@ -4195,7 +4461,7 @@
       <c r="D118" s="25"/>
       <c r="E118" s="29"/>
       <c r="F118" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G118" s="30"/>
       <c r="H118" s="30"/>
@@ -4209,7 +4475,7 @@
       <c r="D119" s="25"/>
       <c r="E119" s="29"/>
       <c r="F119" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G119" s="30"/>
       <c r="H119" s="30"/>
@@ -4223,7 +4489,7 @@
       <c r="D120" s="25"/>
       <c r="E120" s="29"/>
       <c r="F120" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G120" s="30"/>
       <c r="H120" s="30"/>
@@ -4237,7 +4503,7 @@
       <c r="D121" s="25"/>
       <c r="E121" s="29"/>
       <c r="F121" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G121" s="30"/>
       <c r="H121" s="30"/>
@@ -4251,7 +4517,7 @@
       <c r="D122" s="25"/>
       <c r="E122" s="29"/>
       <c r="F122" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G122" s="30"/>
       <c r="H122" s="30"/>
@@ -4265,7 +4531,7 @@
       <c r="D123" s="25"/>
       <c r="E123" s="29"/>
       <c r="F123" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G123" s="30"/>
       <c r="H123" s="30"/>
@@ -4279,7 +4545,7 @@
       <c r="D124" s="25"/>
       <c r="E124" s="29"/>
       <c r="F124" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G124" s="30"/>
       <c r="H124" s="30"/>
@@ -4293,7 +4559,7 @@
       <c r="D125" s="25"/>
       <c r="E125" s="29"/>
       <c r="F125" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G125" s="30"/>
       <c r="H125" s="30"/>
@@ -4307,7 +4573,7 @@
       <c r="D126" s="25"/>
       <c r="E126" s="29"/>
       <c r="F126" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G126" s="30"/>
       <c r="H126" s="30"/>
@@ -4321,7 +4587,7 @@
       <c r="D127" s="25"/>
       <c r="E127" s="29"/>
       <c r="F127" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G127" s="30"/>
       <c r="H127" s="30"/>
@@ -4335,7 +4601,7 @@
       <c r="D128" s="25"/>
       <c r="E128" s="29"/>
       <c r="F128" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G128" s="30"/>
       <c r="H128" s="30"/>
@@ -4349,7 +4615,7 @@
       <c r="D129" s="25"/>
       <c r="E129" s="29"/>
       <c r="F129" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G129" s="30"/>
       <c r="H129" s="30"/>
@@ -4363,7 +4629,7 @@
       <c r="D130" s="25"/>
       <c r="E130" s="29"/>
       <c r="F130" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G130" s="30"/>
       <c r="H130" s="30"/>
@@ -4377,7 +4643,7 @@
       <c r="D131" s="25"/>
       <c r="E131" s="29"/>
       <c r="F131" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G131" s="30"/>
       <c r="H131" s="30"/>
@@ -4391,7 +4657,7 @@
       <c r="D132" s="25"/>
       <c r="E132" s="29"/>
       <c r="F132" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G132" s="30"/>
       <c r="H132" s="30"/>
@@ -4405,7 +4671,7 @@
       <c r="D133" s="25"/>
       <c r="E133" s="29"/>
       <c r="F133" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G133" s="30"/>
       <c r="H133" s="30"/>
@@ -4419,7 +4685,7 @@
       <c r="D134" s="25"/>
       <c r="E134" s="29"/>
       <c r="F134" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G134" s="30"/>
       <c r="H134" s="30"/>
@@ -4433,7 +4699,7 @@
       <c r="D135" s="25"/>
       <c r="E135" s="29"/>
       <c r="F135" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G135" s="30"/>
       <c r="H135" s="30"/>
@@ -4447,7 +4713,7 @@
       <c r="D136" s="25"/>
       <c r="E136" s="29"/>
       <c r="F136" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G136" s="30"/>
       <c r="H136" s="30"/>
@@ -4461,7 +4727,7 @@
       <c r="D137" s="25"/>
       <c r="E137" s="29"/>
       <c r="F137" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G137" s="30"/>
       <c r="H137" s="30"/>
@@ -4475,7 +4741,7 @@
       <c r="D138" s="25"/>
       <c r="E138" s="29"/>
       <c r="F138" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G138" s="30"/>
       <c r="H138" s="30"/>
@@ -4489,7 +4755,7 @@
       <c r="D139" s="25"/>
       <c r="E139" s="29"/>
       <c r="F139" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G139" s="30"/>
       <c r="H139" s="30"/>
@@ -4503,12 +4769,12 @@
       <c r="D140" s="25"/>
       <c r="E140" s="29"/>
       <c r="F140" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G140" s="30"/>
       <c r="H140" s="30"/>
       <c r="I140" s="30"/>
-      <c r="J140" s="32"/>
+      <c r="J140" s="17"/>
     </row>
     <row r="141" ht="29.25" customHeight="1">
       <c r="A141" s="31"/>
@@ -4517,12 +4783,12 @@
       <c r="D141" s="25"/>
       <c r="E141" s="29"/>
       <c r="F141" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G141" s="30"/>
       <c r="H141" s="30"/>
       <c r="I141" s="30"/>
-      <c r="J141" s="32"/>
+      <c r="J141" s="17"/>
     </row>
     <row r="142" ht="29.25" customHeight="1">
       <c r="A142" s="31"/>
@@ -4531,12 +4797,12 @@
       <c r="D142" s="25"/>
       <c r="E142" s="29"/>
       <c r="F142" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G142" s="30"/>
       <c r="H142" s="30"/>
       <c r="I142" s="30"/>
-      <c r="J142" s="32"/>
+      <c r="J142" s="17"/>
     </row>
     <row r="143" ht="29.25" customHeight="1">
       <c r="A143" s="31"/>
@@ -4545,12 +4811,12 @@
       <c r="D143" s="25"/>
       <c r="E143" s="29"/>
       <c r="F143" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G143" s="30"/>
       <c r="H143" s="30"/>
       <c r="I143" s="30"/>
-      <c r="J143" s="32"/>
+      <c r="J143" s="17"/>
     </row>
     <row r="144" ht="29.25" customHeight="1">
       <c r="A144" s="31"/>
@@ -4559,12 +4825,12 @@
       <c r="D144" s="25"/>
       <c r="E144" s="29"/>
       <c r="F144" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G144" s="30"/>
       <c r="H144" s="30"/>
       <c r="I144" s="30"/>
-      <c r="J144" s="32"/>
+      <c r="J144" s="17"/>
     </row>
     <row r="145" ht="29.25" customHeight="1">
       <c r="A145" s="31"/>
@@ -4573,12 +4839,12 @@
       <c r="D145" s="25"/>
       <c r="E145" s="29"/>
       <c r="F145" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G145" s="30"/>
       <c r="H145" s="30"/>
       <c r="I145" s="30"/>
-      <c r="J145" s="32"/>
+      <c r="J145" s="17"/>
     </row>
     <row r="146" ht="29.25" customHeight="1">
       <c r="A146" s="31"/>
@@ -4587,12 +4853,12 @@
       <c r="D146" s="25"/>
       <c r="E146" s="29"/>
       <c r="F146" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G146" s="30"/>
       <c r="H146" s="30"/>
       <c r="I146" s="30"/>
-      <c r="J146" s="32"/>
+      <c r="J146" s="17"/>
     </row>
     <row r="147" ht="29.25" customHeight="1">
       <c r="A147" s="31"/>
@@ -4601,12 +4867,12 @@
       <c r="D147" s="25"/>
       <c r="E147" s="29"/>
       <c r="F147" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G147" s="30"/>
       <c r="H147" s="30"/>
       <c r="I147" s="30"/>
-      <c r="J147" s="32"/>
+      <c r="J147" s="17"/>
     </row>
     <row r="148" ht="29.25" customHeight="1">
       <c r="A148" s="31"/>
@@ -4615,7 +4881,7 @@
       <c r="D148" s="25"/>
       <c r="E148" s="29"/>
       <c r="F148" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G148" s="30"/>
       <c r="H148" s="30"/>
@@ -4629,7 +4895,7 @@
       <c r="D149" s="25"/>
       <c r="E149" s="29"/>
       <c r="F149" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G149" s="30"/>
       <c r="H149" s="30"/>
@@ -4643,7 +4909,7 @@
       <c r="D150" s="25"/>
       <c r="E150" s="29"/>
       <c r="F150" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G150" s="30"/>
       <c r="H150" s="30"/>
@@ -4657,7 +4923,7 @@
       <c r="D151" s="25"/>
       <c r="E151" s="29"/>
       <c r="F151" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G151" s="30"/>
       <c r="H151" s="30"/>
@@ -4671,7 +4937,7 @@
       <c r="D152" s="25"/>
       <c r="E152" s="29"/>
       <c r="F152" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G152" s="30"/>
       <c r="H152" s="30"/>
@@ -4685,7 +4951,7 @@
       <c r="D153" s="25"/>
       <c r="E153" s="29"/>
       <c r="F153" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G153" s="30"/>
       <c r="H153" s="30"/>
@@ -4699,7 +4965,7 @@
       <c r="D154" s="25"/>
       <c r="E154" s="29"/>
       <c r="F154" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G154" s="30"/>
       <c r="H154" s="30"/>
@@ -4713,7 +4979,7 @@
       <c r="D155" s="25"/>
       <c r="E155" s="29"/>
       <c r="F155" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G155" s="30"/>
       <c r="H155" s="30"/>
@@ -4727,7 +4993,7 @@
       <c r="D156" s="25"/>
       <c r="E156" s="29"/>
       <c r="F156" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G156" s="30"/>
       <c r="H156" s="30"/>
@@ -4741,7 +5007,7 @@
       <c r="D157" s="25"/>
       <c r="E157" s="29"/>
       <c r="F157" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G157" s="30"/>
       <c r="H157" s="30"/>
@@ -4755,7 +5021,7 @@
       <c r="D158" s="25"/>
       <c r="E158" s="29"/>
       <c r="F158" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G158" s="30"/>
       <c r="H158" s="30"/>
@@ -4769,7 +5035,7 @@
       <c r="D159" s="25"/>
       <c r="E159" s="29"/>
       <c r="F159" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G159" s="30"/>
       <c r="H159" s="30"/>
@@ -4783,7 +5049,7 @@
       <c r="D160" s="25"/>
       <c r="E160" s="29"/>
       <c r="F160" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G160" s="30"/>
       <c r="H160" s="30"/>
@@ -4797,7 +5063,7 @@
       <c r="D161" s="25"/>
       <c r="E161" s="29"/>
       <c r="F161" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G161" s="30"/>
       <c r="H161" s="30"/>
@@ -4811,7 +5077,7 @@
       <c r="D162" s="25"/>
       <c r="E162" s="29"/>
       <c r="F162" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G162" s="30"/>
       <c r="H162" s="30"/>
@@ -4825,7 +5091,7 @@
       <c r="D163" s="25"/>
       <c r="E163" s="29"/>
       <c r="F163" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G163" s="30"/>
       <c r="H163" s="30"/>
@@ -4839,7 +5105,7 @@
       <c r="D164" s="25"/>
       <c r="E164" s="29"/>
       <c r="F164" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G164" s="30"/>
       <c r="H164" s="30"/>
@@ -4853,7 +5119,7 @@
       <c r="D165" s="25"/>
       <c r="E165" s="29"/>
       <c r="F165" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G165" s="30"/>
       <c r="H165" s="30"/>
@@ -4867,7 +5133,7 @@
       <c r="D166" s="25"/>
       <c r="E166" s="29"/>
       <c r="F166" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G166" s="30"/>
       <c r="H166" s="30"/>
@@ -4881,7 +5147,7 @@
       <c r="D167" s="25"/>
       <c r="E167" s="29"/>
       <c r="F167" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G167" s="30"/>
       <c r="H167" s="30"/>
@@ -4895,7 +5161,7 @@
       <c r="D168" s="25"/>
       <c r="E168" s="29"/>
       <c r="F168" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G168" s="30"/>
       <c r="H168" s="30"/>
@@ -4909,7 +5175,7 @@
       <c r="D169" s="25"/>
       <c r="E169" s="29"/>
       <c r="F169" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G169" s="30"/>
       <c r="H169" s="30"/>
@@ -4923,7 +5189,7 @@
       <c r="D170" s="25"/>
       <c r="E170" s="29"/>
       <c r="F170" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G170" s="30"/>
       <c r="H170" s="30"/>
@@ -4937,7 +5203,7 @@
       <c r="D171" s="25"/>
       <c r="E171" s="29"/>
       <c r="F171" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G171" s="30"/>
       <c r="H171" s="30"/>
@@ -4951,7 +5217,7 @@
       <c r="D172" s="25"/>
       <c r="E172" s="29"/>
       <c r="F172" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G172" s="30"/>
       <c r="H172" s="30"/>
@@ -4965,7 +5231,7 @@
       <c r="D173" s="25"/>
       <c r="E173" s="29"/>
       <c r="F173" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G173" s="30"/>
       <c r="H173" s="30"/>
@@ -4979,7 +5245,7 @@
       <c r="D174" s="25"/>
       <c r="E174" s="29"/>
       <c r="F174" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G174" s="30"/>
       <c r="H174" s="30"/>
@@ -4993,7 +5259,7 @@
       <c r="D175" s="25"/>
       <c r="E175" s="29"/>
       <c r="F175" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G175" s="30"/>
       <c r="H175" s="30"/>
@@ -5007,7 +5273,7 @@
       <c r="D176" s="25"/>
       <c r="E176" s="29"/>
       <c r="F176" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G176" s="30"/>
       <c r="H176" s="30"/>
@@ -5021,7 +5287,7 @@
       <c r="D177" s="25"/>
       <c r="E177" s="29"/>
       <c r="F177" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G177" s="30"/>
       <c r="H177" s="30"/>
@@ -5035,7 +5301,7 @@
       <c r="D178" s="25"/>
       <c r="E178" s="29"/>
       <c r="F178" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G178" s="30"/>
       <c r="H178" s="30"/>
@@ -5049,7 +5315,7 @@
       <c r="D179" s="25"/>
       <c r="E179" s="29"/>
       <c r="F179" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G179" s="30"/>
       <c r="H179" s="30"/>
@@ -5063,7 +5329,7 @@
       <c r="D180" s="25"/>
       <c r="E180" s="29"/>
       <c r="F180" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G180" s="30"/>
       <c r="H180" s="30"/>
@@ -5077,7 +5343,7 @@
       <c r="D181" s="25"/>
       <c r="E181" s="29"/>
       <c r="F181" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G181" s="30"/>
       <c r="H181" s="30"/>
@@ -5091,7 +5357,7 @@
       <c r="D182" s="25"/>
       <c r="E182" s="29"/>
       <c r="F182" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G182" s="30"/>
       <c r="H182" s="30"/>
@@ -5105,7 +5371,7 @@
       <c r="D183" s="25"/>
       <c r="E183" s="29"/>
       <c r="F183" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G183" s="30"/>
       <c r="H183" s="30"/>
@@ -5119,7 +5385,7 @@
       <c r="D184" s="25"/>
       <c r="E184" s="29"/>
       <c r="F184" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G184" s="30"/>
       <c r="H184" s="30"/>
@@ -5133,7 +5399,7 @@
       <c r="D185" s="25"/>
       <c r="E185" s="29"/>
       <c r="F185" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G185" s="30"/>
       <c r="H185" s="30"/>
@@ -5147,7 +5413,7 @@
       <c r="D186" s="25"/>
       <c r="E186" s="29"/>
       <c r="F186" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G186" s="30"/>
       <c r="H186" s="30"/>
@@ -5161,7 +5427,7 @@
       <c r="D187" s="25"/>
       <c r="E187" s="29"/>
       <c r="F187" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G187" s="30"/>
       <c r="H187" s="30"/>
@@ -5175,7 +5441,7 @@
       <c r="D188" s="25"/>
       <c r="E188" s="29"/>
       <c r="F188" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G188" s="30"/>
       <c r="H188" s="30"/>
@@ -5189,7 +5455,7 @@
       <c r="D189" s="25"/>
       <c r="E189" s="29"/>
       <c r="F189" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G189" s="30"/>
       <c r="H189" s="30"/>
@@ -5203,7 +5469,7 @@
       <c r="D190" s="25"/>
       <c r="E190" s="29"/>
       <c r="F190" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G190" s="30"/>
       <c r="H190" s="30"/>
@@ -5217,7 +5483,7 @@
       <c r="D191" s="25"/>
       <c r="E191" s="29"/>
       <c r="F191" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G191" s="30"/>
       <c r="H191" s="30"/>
@@ -5231,7 +5497,7 @@
       <c r="D192" s="25"/>
       <c r="E192" s="29"/>
       <c r="F192" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G192" s="30"/>
       <c r="H192" s="30"/>
@@ -5245,7 +5511,7 @@
       <c r="D193" s="25"/>
       <c r="E193" s="29"/>
       <c r="F193" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G193" s="30"/>
       <c r="H193" s="30"/>
@@ -5259,7 +5525,7 @@
       <c r="D194" s="25"/>
       <c r="E194" s="29"/>
       <c r="F194" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G194" s="30"/>
       <c r="H194" s="30"/>
@@ -5273,7 +5539,7 @@
       <c r="D195" s="25"/>
       <c r="E195" s="29"/>
       <c r="F195" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G195" s="30"/>
       <c r="H195" s="30"/>
@@ -5287,7 +5553,7 @@
       <c r="D196" s="25"/>
       <c r="E196" s="29"/>
       <c r="F196" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G196" s="30"/>
       <c r="H196" s="30"/>
@@ -5301,7 +5567,7 @@
       <c r="D197" s="25"/>
       <c r="E197" s="29"/>
       <c r="F197" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G197" s="30"/>
       <c r="H197" s="30"/>
@@ -5315,7 +5581,7 @@
       <c r="D198" s="25"/>
       <c r="E198" s="29"/>
       <c r="F198" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G198" s="30"/>
       <c r="H198" s="30"/>
@@ -5329,7 +5595,7 @@
       <c r="D199" s="25"/>
       <c r="E199" s="29"/>
       <c r="F199" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G199" s="30"/>
       <c r="H199" s="30"/>
@@ -5343,7 +5609,7 @@
       <c r="D200" s="25"/>
       <c r="E200" s="29"/>
       <c r="F200" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G200" s="30"/>
       <c r="H200" s="30"/>
@@ -5357,7 +5623,7 @@
       <c r="D201" s="25"/>
       <c r="E201" s="29"/>
       <c r="F201" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G201" s="30"/>
       <c r="H201" s="30"/>
@@ -5371,7 +5637,7 @@
       <c r="D202" s="25"/>
       <c r="E202" s="29"/>
       <c r="F202" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G202" s="30"/>
       <c r="H202" s="30"/>
@@ -5385,7 +5651,7 @@
       <c r="D203" s="25"/>
       <c r="E203" s="29"/>
       <c r="F203" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G203" s="30"/>
       <c r="H203" s="30"/>
@@ -5399,7 +5665,7 @@
       <c r="D204" s="25"/>
       <c r="E204" s="29"/>
       <c r="F204" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G204" s="30"/>
       <c r="H204" s="30"/>
@@ -5413,7 +5679,7 @@
       <c r="D205" s="25"/>
       <c r="E205" s="29"/>
       <c r="F205" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G205" s="30"/>
       <c r="H205" s="30"/>
@@ -5427,7 +5693,7 @@
       <c r="D206" s="25"/>
       <c r="E206" s="29"/>
       <c r="F206" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G206" s="30"/>
       <c r="H206" s="30"/>
@@ -5441,7 +5707,7 @@
       <c r="D207" s="25"/>
       <c r="E207" s="29"/>
       <c r="F207" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G207" s="30"/>
       <c r="H207" s="30"/>
@@ -5455,7 +5721,7 @@
       <c r="D208" s="25"/>
       <c r="E208" s="29"/>
       <c r="F208" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G208" s="30"/>
       <c r="H208" s="30"/>
@@ -5469,7 +5735,7 @@
       <c r="D209" s="25"/>
       <c r="E209" s="29"/>
       <c r="F209" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G209" s="30"/>
       <c r="H209" s="30"/>
@@ -5483,7 +5749,7 @@
       <c r="D210" s="25"/>
       <c r="E210" s="29"/>
       <c r="F210" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G210" s="30"/>
       <c r="H210" s="30"/>
@@ -5497,7 +5763,7 @@
       <c r="D211" s="25"/>
       <c r="E211" s="29"/>
       <c r="F211" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G211" s="30"/>
       <c r="H211" s="30"/>
@@ -5511,7 +5777,7 @@
       <c r="D212" s="25"/>
       <c r="E212" s="29"/>
       <c r="F212" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G212" s="30"/>
       <c r="H212" s="30"/>
@@ -5525,7 +5791,7 @@
       <c r="D213" s="25"/>
       <c r="E213" s="29"/>
       <c r="F213" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G213" s="30"/>
       <c r="H213" s="30"/>
@@ -5539,7 +5805,7 @@
       <c r="D214" s="25"/>
       <c r="E214" s="29"/>
       <c r="F214" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G214" s="30"/>
       <c r="H214" s="30"/>
@@ -5553,7 +5819,7 @@
       <c r="D215" s="25"/>
       <c r="E215" s="29"/>
       <c r="F215" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G215" s="30"/>
       <c r="H215" s="30"/>
@@ -5567,7 +5833,7 @@
       <c r="D216" s="25"/>
       <c r="E216" s="29"/>
       <c r="F216" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G216" s="30"/>
       <c r="H216" s="30"/>
@@ -5581,7 +5847,7 @@
       <c r="D217" s="25"/>
       <c r="E217" s="29"/>
       <c r="F217" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G217" s="30"/>
       <c r="H217" s="30"/>
@@ -5595,7 +5861,7 @@
       <c r="D218" s="25"/>
       <c r="E218" s="29"/>
       <c r="F218" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G218" s="30"/>
       <c r="H218" s="30"/>
@@ -5609,7 +5875,7 @@
       <c r="D219" s="25"/>
       <c r="E219" s="29"/>
       <c r="F219" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G219" s="30"/>
       <c r="H219" s="30"/>
@@ -5623,7 +5889,7 @@
       <c r="D220" s="25"/>
       <c r="E220" s="29"/>
       <c r="F220" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G220" s="30"/>
       <c r="H220" s="30"/>
@@ -5637,7 +5903,7 @@
       <c r="D221" s="25"/>
       <c r="E221" s="29"/>
       <c r="F221" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G221" s="30"/>
       <c r="H221" s="30"/>
@@ -5651,7 +5917,7 @@
       <c r="D222" s="25"/>
       <c r="E222" s="29"/>
       <c r="F222" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G222" s="30"/>
       <c r="H222" s="30"/>
@@ -5665,7 +5931,7 @@
       <c r="D223" s="25"/>
       <c r="E223" s="29"/>
       <c r="F223" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G223" s="30"/>
       <c r="H223" s="30"/>
@@ -5679,7 +5945,7 @@
       <c r="D224" s="25"/>
       <c r="E224" s="29"/>
       <c r="F224" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G224" s="30"/>
       <c r="H224" s="30"/>
@@ -5693,7 +5959,7 @@
       <c r="D225" s="25"/>
       <c r="E225" s="29"/>
       <c r="F225" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G225" s="30"/>
       <c r="H225" s="30"/>
@@ -5707,7 +5973,7 @@
       <c r="D226" s="25"/>
       <c r="E226" s="29"/>
       <c r="F226" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G226" s="30"/>
       <c r="H226" s="30"/>
@@ -5721,7 +5987,7 @@
       <c r="D227" s="25"/>
       <c r="E227" s="29"/>
       <c r="F227" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G227" s="30"/>
       <c r="H227" s="30"/>
@@ -5735,7 +6001,7 @@
       <c r="D228" s="25"/>
       <c r="E228" s="29"/>
       <c r="F228" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G228" s="30"/>
       <c r="H228" s="30"/>
@@ -5749,7 +6015,7 @@
       <c r="D229" s="25"/>
       <c r="E229" s="29"/>
       <c r="F229" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G229" s="30"/>
       <c r="H229" s="30"/>
@@ -5763,7 +6029,7 @@
       <c r="D230" s="25"/>
       <c r="E230" s="29"/>
       <c r="F230" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G230" s="30"/>
       <c r="H230" s="30"/>
@@ -5777,7 +6043,7 @@
       <c r="D231" s="25"/>
       <c r="E231" s="29"/>
       <c r="F231" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G231" s="30"/>
       <c r="H231" s="30"/>
@@ -5791,7 +6057,7 @@
       <c r="D232" s="25"/>
       <c r="E232" s="29"/>
       <c r="F232" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G232" s="30"/>
       <c r="H232" s="30"/>
@@ -5805,7 +6071,7 @@
       <c r="D233" s="25"/>
       <c r="E233" s="29"/>
       <c r="F233" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G233" s="30"/>
       <c r="H233" s="30"/>
@@ -5819,7 +6085,7 @@
       <c r="D234" s="25"/>
       <c r="E234" s="29"/>
       <c r="F234" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G234" s="30"/>
       <c r="H234" s="30"/>
@@ -5833,7 +6099,7 @@
       <c r="D235" s="25"/>
       <c r="E235" s="29"/>
       <c r="F235" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G235" s="30"/>
       <c r="H235" s="30"/>
@@ -5847,7 +6113,7 @@
       <c r="D236" s="25"/>
       <c r="E236" s="29"/>
       <c r="F236" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G236" s="30"/>
       <c r="H236" s="30"/>
@@ -5861,7 +6127,7 @@
       <c r="D237" s="25"/>
       <c r="E237" s="29"/>
       <c r="F237" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G237" s="30"/>
       <c r="H237" s="30"/>
@@ -5875,7 +6141,7 @@
       <c r="D238" s="25"/>
       <c r="E238" s="29"/>
       <c r="F238" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G238" s="30"/>
       <c r="H238" s="30"/>
@@ -5889,7 +6155,7 @@
       <c r="D239" s="25"/>
       <c r="E239" s="29"/>
       <c r="F239" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G239" s="30"/>
       <c r="H239" s="30"/>
@@ -5903,7 +6169,7 @@
       <c r="D240" s="25"/>
       <c r="E240" s="29"/>
       <c r="F240" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G240" s="30"/>
       <c r="H240" s="30"/>
@@ -5917,7 +6183,7 @@
       <c r="D241" s="25"/>
       <c r="E241" s="29"/>
       <c r="F241" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G241" s="30"/>
       <c r="H241" s="30"/>
@@ -5931,7 +6197,7 @@
       <c r="D242" s="25"/>
       <c r="E242" s="29"/>
       <c r="F242" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G242" s="30"/>
       <c r="H242" s="30"/>
@@ -5945,7 +6211,7 @@
       <c r="D243" s="25"/>
       <c r="E243" s="29"/>
       <c r="F243" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G243" s="30"/>
       <c r="H243" s="30"/>
@@ -5959,7 +6225,7 @@
       <c r="D244" s="25"/>
       <c r="E244" s="29"/>
       <c r="F244" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G244" s="30"/>
       <c r="H244" s="30"/>
@@ -5973,7 +6239,7 @@
       <c r="D245" s="25"/>
       <c r="E245" s="29"/>
       <c r="F245" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G245" s="30"/>
       <c r="H245" s="30"/>
@@ -5987,7 +6253,7 @@
       <c r="D246" s="25"/>
       <c r="E246" s="29"/>
       <c r="F246" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G246" s="30"/>
       <c r="H246" s="30"/>
@@ -6001,7 +6267,7 @@
       <c r="D247" s="25"/>
       <c r="E247" s="29"/>
       <c r="F247" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G247" s="30"/>
       <c r="H247" s="30"/>
@@ -6015,7 +6281,7 @@
       <c r="D248" s="25"/>
       <c r="E248" s="29"/>
       <c r="F248" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G248" s="30"/>
       <c r="H248" s="30"/>
@@ -6029,7 +6295,7 @@
       <c r="D249" s="25"/>
       <c r="E249" s="29"/>
       <c r="F249" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G249" s="30"/>
       <c r="H249" s="30"/>
@@ -6043,7 +6309,7 @@
       <c r="D250" s="25"/>
       <c r="E250" s="29"/>
       <c r="F250" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G250" s="30"/>
       <c r="H250" s="30"/>
@@ -6057,7 +6323,7 @@
       <c r="D251" s="25"/>
       <c r="E251" s="29"/>
       <c r="F251" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G251" s="30"/>
       <c r="H251" s="30"/>
@@ -6071,7 +6337,7 @@
       <c r="D252" s="25"/>
       <c r="E252" s="29"/>
       <c r="F252" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G252" s="30"/>
       <c r="H252" s="30"/>
@@ -6085,7 +6351,7 @@
       <c r="D253" s="25"/>
       <c r="E253" s="29"/>
       <c r="F253" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G253" s="30"/>
       <c r="H253" s="30"/>
@@ -6099,7 +6365,7 @@
       <c r="D254" s="25"/>
       <c r="E254" s="29"/>
       <c r="F254" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G254" s="30"/>
       <c r="H254" s="30"/>
@@ -6113,7 +6379,7 @@
       <c r="D255" s="25"/>
       <c r="E255" s="29"/>
       <c r="F255" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G255" s="30"/>
       <c r="H255" s="30"/>
@@ -6127,7 +6393,7 @@
       <c r="D256" s="25"/>
       <c r="E256" s="29"/>
       <c r="F256" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G256" s="30"/>
       <c r="H256" s="30"/>
@@ -6141,7 +6407,7 @@
       <c r="D257" s="25"/>
       <c r="E257" s="29"/>
       <c r="F257" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G257" s="30"/>
       <c r="H257" s="30"/>
@@ -6155,7 +6421,7 @@
       <c r="D258" s="25"/>
       <c r="E258" s="29"/>
       <c r="F258" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G258" s="30"/>
       <c r="H258" s="30"/>
@@ -6169,7 +6435,7 @@
       <c r="D259" s="25"/>
       <c r="E259" s="29"/>
       <c r="F259" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G259" s="30"/>
       <c r="H259" s="30"/>
@@ -6183,7 +6449,7 @@
       <c r="D260" s="25"/>
       <c r="E260" s="29"/>
       <c r="F260" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G260" s="30"/>
       <c r="H260" s="30"/>
@@ -6197,7 +6463,7 @@
       <c r="D261" s="25"/>
       <c r="E261" s="29"/>
       <c r="F261" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G261" s="30"/>
       <c r="H261" s="30"/>
@@ -6211,7 +6477,7 @@
       <c r="D262" s="25"/>
       <c r="E262" s="29"/>
       <c r="F262" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G262" s="30"/>
       <c r="H262" s="30"/>
@@ -6225,7 +6491,7 @@
       <c r="D263" s="25"/>
       <c r="E263" s="29"/>
       <c r="F263" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G263" s="30"/>
       <c r="H263" s="30"/>
@@ -6239,7 +6505,7 @@
       <c r="D264" s="25"/>
       <c r="E264" s="29"/>
       <c r="F264" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G264" s="30"/>
       <c r="H264" s="30"/>
@@ -6253,7 +6519,7 @@
       <c r="D265" s="25"/>
       <c r="E265" s="29"/>
       <c r="F265" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G265" s="30"/>
       <c r="H265" s="30"/>
@@ -6267,7 +6533,7 @@
       <c r="D266" s="25"/>
       <c r="E266" s="29"/>
       <c r="F266" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G266" s="30"/>
       <c r="H266" s="30"/>
@@ -6281,7 +6547,7 @@
       <c r="D267" s="25"/>
       <c r="E267" s="29"/>
       <c r="F267" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G267" s="30"/>
       <c r="H267" s="30"/>
@@ -6295,7 +6561,7 @@
       <c r="D268" s="25"/>
       <c r="E268" s="29"/>
       <c r="F268" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G268" s="30"/>
       <c r="H268" s="30"/>
@@ -6309,7 +6575,7 @@
       <c r="D269" s="25"/>
       <c r="E269" s="29"/>
       <c r="F269" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G269" s="30"/>
       <c r="H269" s="30"/>
@@ -6323,7 +6589,7 @@
       <c r="D270" s="25"/>
       <c r="E270" s="29"/>
       <c r="F270" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G270" s="30"/>
       <c r="H270" s="30"/>
@@ -6337,7 +6603,7 @@
       <c r="D271" s="25"/>
       <c r="E271" s="29"/>
       <c r="F271" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G271" s="30"/>
       <c r="H271" s="30"/>
@@ -6351,7 +6617,7 @@
       <c r="D272" s="25"/>
       <c r="E272" s="29"/>
       <c r="F272" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G272" s="30"/>
       <c r="H272" s="30"/>
@@ -6365,7 +6631,7 @@
       <c r="D273" s="25"/>
       <c r="E273" s="29"/>
       <c r="F273" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G273" s="30"/>
       <c r="H273" s="30"/>
@@ -6379,7 +6645,7 @@
       <c r="D274" s="25"/>
       <c r="E274" s="29"/>
       <c r="F274" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G274" s="30"/>
       <c r="H274" s="30"/>
@@ -6393,7 +6659,7 @@
       <c r="D275" s="25"/>
       <c r="E275" s="29"/>
       <c r="F275" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G275" s="30"/>
       <c r="H275" s="30"/>
@@ -6407,7 +6673,7 @@
       <c r="D276" s="25"/>
       <c r="E276" s="29"/>
       <c r="F276" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G276" s="30"/>
       <c r="H276" s="30"/>
@@ -6421,7 +6687,7 @@
       <c r="D277" s="25"/>
       <c r="E277" s="29"/>
       <c r="F277" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G277" s="30"/>
       <c r="H277" s="30"/>
@@ -6435,7 +6701,7 @@
       <c r="D278" s="25"/>
       <c r="E278" s="29"/>
       <c r="F278" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G278" s="30"/>
       <c r="H278" s="30"/>
@@ -6449,7 +6715,7 @@
       <c r="D279" s="25"/>
       <c r="E279" s="29"/>
       <c r="F279" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G279" s="30"/>
       <c r="H279" s="30"/>
@@ -6463,7 +6729,7 @@
       <c r="D280" s="25"/>
       <c r="E280" s="29"/>
       <c r="F280" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G280" s="30"/>
       <c r="H280" s="30"/>
@@ -6477,7 +6743,7 @@
       <c r="D281" s="25"/>
       <c r="E281" s="29"/>
       <c r="F281" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G281" s="30"/>
       <c r="H281" s="30"/>
@@ -6491,7 +6757,7 @@
       <c r="D282" s="25"/>
       <c r="E282" s="29"/>
       <c r="F282" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G282" s="30"/>
       <c r="H282" s="30"/>
@@ -6505,7 +6771,7 @@
       <c r="D283" s="25"/>
       <c r="E283" s="29"/>
       <c r="F283" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G283" s="30"/>
       <c r="H283" s="30"/>
@@ -6519,7 +6785,7 @@
       <c r="D284" s="25"/>
       <c r="E284" s="29"/>
       <c r="F284" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G284" s="30"/>
       <c r="H284" s="30"/>
@@ -6533,7 +6799,7 @@
       <c r="D285" s="25"/>
       <c r="E285" s="29"/>
       <c r="F285" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G285" s="30"/>
       <c r="H285" s="30"/>
@@ -6547,7 +6813,7 @@
       <c r="D286" s="25"/>
       <c r="E286" s="29"/>
       <c r="F286" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G286" s="30"/>
       <c r="H286" s="30"/>
@@ -6561,7 +6827,7 @@
       <c r="D287" s="25"/>
       <c r="E287" s="29"/>
       <c r="F287" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G287" s="30"/>
       <c r="H287" s="30"/>
@@ -6575,7 +6841,7 @@
       <c r="D288" s="25"/>
       <c r="E288" s="29"/>
       <c r="F288" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G288" s="30"/>
       <c r="H288" s="30"/>
@@ -6589,7 +6855,7 @@
       <c r="D289" s="25"/>
       <c r="E289" s="29"/>
       <c r="F289" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G289" s="30"/>
       <c r="H289" s="30"/>
@@ -6603,7 +6869,7 @@
       <c r="D290" s="25"/>
       <c r="E290" s="29"/>
       <c r="F290" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G290" s="30"/>
       <c r="H290" s="30"/>
@@ -6617,7 +6883,7 @@
       <c r="D291" s="25"/>
       <c r="E291" s="29"/>
       <c r="F291" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G291" s="30"/>
       <c r="H291" s="30"/>
@@ -6631,7 +6897,7 @@
       <c r="D292" s="25"/>
       <c r="E292" s="29"/>
       <c r="F292" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G292" s="30"/>
       <c r="H292" s="30"/>
@@ -6645,7 +6911,7 @@
       <c r="D293" s="25"/>
       <c r="E293" s="29"/>
       <c r="F293" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G293" s="30"/>
       <c r="H293" s="30"/>
@@ -6659,7 +6925,7 @@
       <c r="D294" s="25"/>
       <c r="E294" s="29"/>
       <c r="F294" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G294" s="30"/>
       <c r="H294" s="30"/>
@@ -6673,7 +6939,7 @@
       <c r="D295" s="25"/>
       <c r="E295" s="29"/>
       <c r="F295" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G295" s="30"/>
       <c r="H295" s="30"/>
@@ -6687,7 +6953,7 @@
       <c r="D296" s="25"/>
       <c r="E296" s="29"/>
       <c r="F296" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G296" s="30"/>
       <c r="H296" s="30"/>
@@ -6701,7 +6967,7 @@
       <c r="D297" s="25"/>
       <c r="E297" s="29"/>
       <c r="F297" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G297" s="30"/>
       <c r="H297" s="30"/>
@@ -6715,7 +6981,7 @@
       <c r="D298" s="25"/>
       <c r="E298" s="29"/>
       <c r="F298" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G298" s="30"/>
       <c r="H298" s="30"/>
@@ -6729,7 +6995,7 @@
       <c r="D299" s="25"/>
       <c r="E299" s="29"/>
       <c r="F299" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G299" s="30"/>
       <c r="H299" s="30"/>
@@ -6743,7 +7009,7 @@
       <c r="D300" s="25"/>
       <c r="E300" s="29"/>
       <c r="F300" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G300" s="30"/>
       <c r="H300" s="30"/>
@@ -6757,7 +7023,7 @@
       <c r="D301" s="25"/>
       <c r="E301" s="29"/>
       <c r="F301" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G301" s="30"/>
       <c r="H301" s="30"/>
@@ -6771,7 +7037,7 @@
       <c r="D302" s="25"/>
       <c r="E302" s="29"/>
       <c r="F302" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G302" s="30"/>
       <c r="H302" s="30"/>
@@ -6785,7 +7051,7 @@
       <c r="D303" s="25"/>
       <c r="E303" s="29"/>
       <c r="F303" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G303" s="30"/>
       <c r="H303" s="30"/>
@@ -6799,7 +7065,7 @@
       <c r="D304" s="25"/>
       <c r="E304" s="29"/>
       <c r="F304" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G304" s="30"/>
       <c r="H304" s="30"/>
@@ -6813,7 +7079,7 @@
       <c r="D305" s="25"/>
       <c r="E305" s="29"/>
       <c r="F305" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G305" s="30"/>
       <c r="H305" s="30"/>
@@ -6827,7 +7093,7 @@
       <c r="D306" s="25"/>
       <c r="E306" s="29"/>
       <c r="F306" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G306" s="30"/>
       <c r="H306" s="30"/>
@@ -6841,7 +7107,7 @@
       <c r="D307" s="25"/>
       <c r="E307" s="29"/>
       <c r="F307" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G307" s="30"/>
       <c r="H307" s="30"/>
@@ -6855,7 +7121,7 @@
       <c r="D308" s="25"/>
       <c r="E308" s="29"/>
       <c r="F308" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G308" s="30"/>
       <c r="H308" s="30"/>
@@ -6869,7 +7135,7 @@
       <c r="D309" s="25"/>
       <c r="E309" s="29"/>
       <c r="F309" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G309" s="30"/>
       <c r="H309" s="30"/>
@@ -6883,7 +7149,7 @@
       <c r="D310" s="25"/>
       <c r="E310" s="29"/>
       <c r="F310" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G310" s="30"/>
       <c r="H310" s="30"/>
@@ -6897,7 +7163,7 @@
       <c r="D311" s="25"/>
       <c r="E311" s="29"/>
       <c r="F311" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G311" s="30"/>
       <c r="H311" s="30"/>
@@ -6911,7 +7177,7 @@
       <c r="D312" s="25"/>
       <c r="E312" s="29"/>
       <c r="F312" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G312" s="30"/>
       <c r="H312" s="30"/>
@@ -6925,7 +7191,7 @@
       <c r="D313" s="25"/>
       <c r="E313" s="29"/>
       <c r="F313" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G313" s="30"/>
       <c r="H313" s="30"/>
@@ -6939,7 +7205,7 @@
       <c r="D314" s="25"/>
       <c r="E314" s="29"/>
       <c r="F314" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G314" s="30"/>
       <c r="H314" s="30"/>
@@ -6953,7 +7219,7 @@
       <c r="D315" s="25"/>
       <c r="E315" s="29"/>
       <c r="F315" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G315" s="30"/>
       <c r="H315" s="30"/>
@@ -6967,7 +7233,7 @@
       <c r="D316" s="25"/>
       <c r="E316" s="29"/>
       <c r="F316" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G316" s="30"/>
       <c r="H316" s="30"/>
@@ -6981,7 +7247,7 @@
       <c r="D317" s="25"/>
       <c r="E317" s="29"/>
       <c r="F317" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G317" s="30"/>
       <c r="H317" s="30"/>
@@ -6995,7 +7261,7 @@
       <c r="D318" s="25"/>
       <c r="E318" s="29"/>
       <c r="F318" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G318" s="30"/>
       <c r="H318" s="30"/>
@@ -7009,7 +7275,7 @@
       <c r="D319" s="25"/>
       <c r="E319" s="29"/>
       <c r="F319" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G319" s="30"/>
       <c r="H319" s="30"/>
@@ -7023,7 +7289,7 @@
       <c r="D320" s="25"/>
       <c r="E320" s="29"/>
       <c r="F320" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G320" s="30"/>
       <c r="H320" s="30"/>
@@ -7037,7 +7303,7 @@
       <c r="D321" s="25"/>
       <c r="E321" s="29"/>
       <c r="F321" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G321" s="30"/>
       <c r="H321" s="30"/>
@@ -7051,7 +7317,7 @@
       <c r="D322" s="25"/>
       <c r="E322" s="29"/>
       <c r="F322" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G322" s="30"/>
       <c r="H322" s="30"/>
@@ -7065,7 +7331,7 @@
       <c r="D323" s="25"/>
       <c r="E323" s="29"/>
       <c r="F323" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G323" s="30"/>
       <c r="H323" s="30"/>
@@ -7079,7 +7345,7 @@
       <c r="D324" s="25"/>
       <c r="E324" s="29"/>
       <c r="F324" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G324" s="30"/>
       <c r="H324" s="30"/>
@@ -7093,7 +7359,7 @@
       <c r="D325" s="25"/>
       <c r="E325" s="29"/>
       <c r="F325" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G325" s="30"/>
       <c r="H325" s="30"/>
@@ -7107,7 +7373,7 @@
       <c r="D326" s="25"/>
       <c r="E326" s="29"/>
       <c r="F326" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G326" s="30"/>
       <c r="H326" s="30"/>
@@ -7121,7 +7387,7 @@
       <c r="D327" s="25"/>
       <c r="E327" s="29"/>
       <c r="F327" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G327" s="30"/>
       <c r="H327" s="30"/>
@@ -7135,7 +7401,7 @@
       <c r="D328" s="25"/>
       <c r="E328" s="29"/>
       <c r="F328" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G328" s="30"/>
       <c r="H328" s="30"/>
@@ -7149,7 +7415,7 @@
       <c r="D329" s="25"/>
       <c r="E329" s="29"/>
       <c r="F329" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G329" s="30"/>
       <c r="H329" s="30"/>
@@ -7163,7 +7429,7 @@
       <c r="D330" s="25"/>
       <c r="E330" s="29"/>
       <c r="F330" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G330" s="30"/>
       <c r="H330" s="30"/>
@@ -7177,7 +7443,7 @@
       <c r="D331" s="25"/>
       <c r="E331" s="29"/>
       <c r="F331" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G331" s="30"/>
       <c r="H331" s="30"/>
@@ -7191,7 +7457,7 @@
       <c r="D332" s="25"/>
       <c r="E332" s="29"/>
       <c r="F332" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G332" s="30"/>
       <c r="H332" s="30"/>
@@ -7205,7 +7471,7 @@
       <c r="D333" s="25"/>
       <c r="E333" s="29"/>
       <c r="F333" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G333" s="30"/>
       <c r="H333" s="30"/>
@@ -7219,7 +7485,7 @@
       <c r="D334" s="25"/>
       <c r="E334" s="29"/>
       <c r="F334" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G334" s="30"/>
       <c r="H334" s="30"/>
@@ -7233,7 +7499,7 @@
       <c r="D335" s="25"/>
       <c r="E335" s="29"/>
       <c r="F335" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G335" s="30"/>
       <c r="H335" s="30"/>
@@ -7247,7 +7513,7 @@
       <c r="D336" s="25"/>
       <c r="E336" s="29"/>
       <c r="F336" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G336" s="30"/>
       <c r="H336" s="30"/>
@@ -7261,7 +7527,7 @@
       <c r="D337" s="25"/>
       <c r="E337" s="29"/>
       <c r="F337" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G337" s="30"/>
       <c r="H337" s="30"/>
@@ -7275,7 +7541,7 @@
       <c r="D338" s="25"/>
       <c r="E338" s="29"/>
       <c r="F338" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G338" s="30"/>
       <c r="H338" s="30"/>
@@ -7289,7 +7555,7 @@
       <c r="D339" s="25"/>
       <c r="E339" s="29"/>
       <c r="F339" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G339" s="30"/>
       <c r="H339" s="30"/>
@@ -7303,7 +7569,7 @@
       <c r="D340" s="25"/>
       <c r="E340" s="29"/>
       <c r="F340" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G340" s="30"/>
       <c r="H340" s="30"/>
@@ -7317,7 +7583,7 @@
       <c r="D341" s="25"/>
       <c r="E341" s="29"/>
       <c r="F341" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G341" s="30"/>
       <c r="H341" s="30"/>
@@ -7331,7 +7597,7 @@
       <c r="D342" s="25"/>
       <c r="E342" s="29"/>
       <c r="F342" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G342" s="30"/>
       <c r="H342" s="30"/>
@@ -7345,7 +7611,7 @@
       <c r="D343" s="25"/>
       <c r="E343" s="29"/>
       <c r="F343" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G343" s="30"/>
       <c r="H343" s="30"/>
@@ -7359,7 +7625,7 @@
       <c r="D344" s="25"/>
       <c r="E344" s="29"/>
       <c r="F344" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G344" s="30"/>
       <c r="H344" s="30"/>
@@ -7373,7 +7639,7 @@
       <c r="D345" s="25"/>
       <c r="E345" s="29"/>
       <c r="F345" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G345" s="30"/>
       <c r="H345" s="30"/>
@@ -7387,7 +7653,7 @@
       <c r="D346" s="25"/>
       <c r="E346" s="29"/>
       <c r="F346" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G346" s="30"/>
       <c r="H346" s="30"/>
@@ -7401,7 +7667,7 @@
       <c r="D347" s="25"/>
       <c r="E347" s="29"/>
       <c r="F347" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G347" s="30"/>
       <c r="H347" s="30"/>
@@ -7415,7 +7681,7 @@
       <c r="D348" s="25"/>
       <c r="E348" s="29"/>
       <c r="F348" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G348" s="30"/>
       <c r="H348" s="30"/>
@@ -7429,7 +7695,7 @@
       <c r="D349" s="25"/>
       <c r="E349" s="29"/>
       <c r="F349" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G349" s="30"/>
       <c r="H349" s="30"/>
@@ -7443,7 +7709,7 @@
       <c r="D350" s="25"/>
       <c r="E350" s="29"/>
       <c r="F350" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G350" s="30"/>
       <c r="H350" s="30"/>
@@ -7457,7 +7723,7 @@
       <c r="D351" s="25"/>
       <c r="E351" s="29"/>
       <c r="F351" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G351" s="30"/>
       <c r="H351" s="30"/>
@@ -7471,7 +7737,7 @@
       <c r="D352" s="25"/>
       <c r="E352" s="29"/>
       <c r="F352" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G352" s="30"/>
       <c r="H352" s="30"/>
@@ -7485,7 +7751,7 @@
       <c r="D353" s="25"/>
       <c r="E353" s="29"/>
       <c r="F353" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G353" s="30"/>
       <c r="H353" s="30"/>
@@ -7499,7 +7765,7 @@
       <c r="D354" s="25"/>
       <c r="E354" s="29"/>
       <c r="F354" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G354" s="30"/>
       <c r="H354" s="30"/>
@@ -7513,7 +7779,7 @@
       <c r="D355" s="25"/>
       <c r="E355" s="29"/>
       <c r="F355" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G355" s="30"/>
       <c r="H355" s="30"/>
@@ -7527,7 +7793,7 @@
       <c r="D356" s="25"/>
       <c r="E356" s="29"/>
       <c r="F356" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G356" s="30"/>
       <c r="H356" s="30"/>
@@ -7541,7 +7807,7 @@
       <c r="D357" s="25"/>
       <c r="E357" s="29"/>
       <c r="F357" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G357" s="30"/>
       <c r="H357" s="30"/>
@@ -7555,7 +7821,7 @@
       <c r="D358" s="25"/>
       <c r="E358" s="29"/>
       <c r="F358" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G358" s="30"/>
       <c r="H358" s="30"/>
@@ -7569,7 +7835,7 @@
       <c r="D359" s="25"/>
       <c r="E359" s="29"/>
       <c r="F359" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G359" s="30"/>
       <c r="H359" s="30"/>
@@ -7583,7 +7849,7 @@
       <c r="D360" s="25"/>
       <c r="E360" s="29"/>
       <c r="F360" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G360" s="30"/>
       <c r="H360" s="30"/>
@@ -7597,7 +7863,7 @@
       <c r="D361" s="25"/>
       <c r="E361" s="29"/>
       <c r="F361" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G361" s="30"/>
       <c r="H361" s="30"/>
@@ -7611,7 +7877,7 @@
       <c r="D362" s="25"/>
       <c r="E362" s="29"/>
       <c r="F362" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G362" s="30"/>
       <c r="H362" s="30"/>
@@ -7625,7 +7891,7 @@
       <c r="D363" s="25"/>
       <c r="E363" s="29"/>
       <c r="F363" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G363" s="30"/>
       <c r="H363" s="30"/>
@@ -7639,7 +7905,7 @@
       <c r="D364" s="25"/>
       <c r="E364" s="29"/>
       <c r="F364" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G364" s="30"/>
       <c r="H364" s="30"/>
@@ -7653,7 +7919,7 @@
       <c r="D365" s="25"/>
       <c r="E365" s="29"/>
       <c r="F365" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G365" s="30"/>
       <c r="H365" s="30"/>
@@ -7667,7 +7933,7 @@
       <c r="D366" s="25"/>
       <c r="E366" s="29"/>
       <c r="F366" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G366" s="30"/>
       <c r="H366" s="30"/>
@@ -7681,7 +7947,7 @@
       <c r="D367" s="25"/>
       <c r="E367" s="29"/>
       <c r="F367" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G367" s="30"/>
       <c r="H367" s="30"/>
@@ -7695,7 +7961,7 @@
       <c r="D368" s="25"/>
       <c r="E368" s="29"/>
       <c r="F368" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G368" s="30"/>
       <c r="H368" s="30"/>
@@ -7709,7 +7975,7 @@
       <c r="D369" s="25"/>
       <c r="E369" s="29"/>
       <c r="F369" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G369" s="30"/>
       <c r="H369" s="30"/>
@@ -7723,7 +7989,7 @@
       <c r="D370" s="25"/>
       <c r="E370" s="29"/>
       <c r="F370" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G370" s="30"/>
       <c r="H370" s="30"/>
@@ -7737,7 +8003,7 @@
       <c r="D371" s="25"/>
       <c r="E371" s="29"/>
       <c r="F371" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G371" s="30"/>
       <c r="H371" s="30"/>
@@ -7751,7 +8017,7 @@
       <c r="D372" s="25"/>
       <c r="E372" s="29"/>
       <c r="F372" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G372" s="30"/>
       <c r="H372" s="30"/>
@@ -7765,7 +8031,7 @@
       <c r="D373" s="25"/>
       <c r="E373" s="29"/>
       <c r="F373" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G373" s="30"/>
       <c r="H373" s="30"/>
@@ -7779,7 +8045,7 @@
       <c r="D374" s="25"/>
       <c r="E374" s="29"/>
       <c r="F374" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G374" s="30"/>
       <c r="H374" s="30"/>
@@ -7793,7 +8059,7 @@
       <c r="D375" s="25"/>
       <c r="E375" s="29"/>
       <c r="F375" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G375" s="30"/>
       <c r="H375" s="30"/>
@@ -7807,7 +8073,7 @@
       <c r="D376" s="25"/>
       <c r="E376" s="29"/>
       <c r="F376" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G376" s="30"/>
       <c r="H376" s="30"/>
@@ -7821,7 +8087,7 @@
       <c r="D377" s="25"/>
       <c r="E377" s="29"/>
       <c r="F377" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G377" s="30"/>
       <c r="H377" s="30"/>
@@ -7835,7 +8101,7 @@
       <c r="D378" s="25"/>
       <c r="E378" s="29"/>
       <c r="F378" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G378" s="30"/>
       <c r="H378" s="30"/>
@@ -7849,7 +8115,7 @@
       <c r="D379" s="25"/>
       <c r="E379" s="29"/>
       <c r="F379" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G379" s="30"/>
       <c r="H379" s="30"/>
@@ -7863,7 +8129,7 @@
       <c r="D380" s="25"/>
       <c r="E380" s="29"/>
       <c r="F380" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G380" s="30"/>
       <c r="H380" s="30"/>
@@ -7877,7 +8143,7 @@
       <c r="D381" s="25"/>
       <c r="E381" s="29"/>
       <c r="F381" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G381" s="30"/>
       <c r="H381" s="30"/>
@@ -7891,7 +8157,7 @@
       <c r="D382" s="25"/>
       <c r="E382" s="29"/>
       <c r="F382" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G382" s="30"/>
       <c r="H382" s="30"/>
@@ -7905,7 +8171,7 @@
       <c r="D383" s="25"/>
       <c r="E383" s="29"/>
       <c r="F383" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G383" s="30"/>
       <c r="H383" s="30"/>
@@ -7919,7 +8185,7 @@
       <c r="D384" s="25"/>
       <c r="E384" s="29"/>
       <c r="F384" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G384" s="30"/>
       <c r="H384" s="30"/>
@@ -7933,7 +8199,7 @@
       <c r="D385" s="25"/>
       <c r="E385" s="29"/>
       <c r="F385" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G385" s="30"/>
       <c r="H385" s="30"/>
@@ -7947,7 +8213,7 @@
       <c r="D386" s="25"/>
       <c r="E386" s="29"/>
       <c r="F386" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G386" s="30"/>
       <c r="H386" s="30"/>
@@ -7961,7 +8227,7 @@
       <c r="D387" s="25"/>
       <c r="E387" s="29"/>
       <c r="F387" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G387" s="30"/>
       <c r="H387" s="30"/>
@@ -7975,7 +8241,7 @@
       <c r="D388" s="25"/>
       <c r="E388" s="29"/>
       <c r="F388" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G388" s="30"/>
       <c r="H388" s="30"/>
@@ -7989,7 +8255,7 @@
       <c r="D389" s="25"/>
       <c r="E389" s="29"/>
       <c r="F389" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G389" s="30"/>
       <c r="H389" s="30"/>
@@ -8003,7 +8269,7 @@
       <c r="D390" s="25"/>
       <c r="E390" s="29"/>
       <c r="F390" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G390" s="30"/>
       <c r="H390" s="30"/>
@@ -8017,7 +8283,7 @@
       <c r="D391" s="25"/>
       <c r="E391" s="29"/>
       <c r="F391" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G391" s="30"/>
       <c r="H391" s="30"/>
@@ -8031,7 +8297,7 @@
       <c r="D392" s="25"/>
       <c r="E392" s="29"/>
       <c r="F392" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G392" s="30"/>
       <c r="H392" s="30"/>
@@ -8045,7 +8311,7 @@
       <c r="D393" s="25"/>
       <c r="E393" s="29"/>
       <c r="F393" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G393" s="30"/>
       <c r="H393" s="30"/>
@@ -8059,7 +8325,7 @@
       <c r="D394" s="25"/>
       <c r="E394" s="29"/>
       <c r="F394" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G394" s="30"/>
       <c r="H394" s="30"/>
@@ -8073,7 +8339,7 @@
       <c r="D395" s="25"/>
       <c r="E395" s="29"/>
       <c r="F395" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G395" s="30"/>
       <c r="H395" s="30"/>
@@ -8087,7 +8353,7 @@
       <c r="D396" s="25"/>
       <c r="E396" s="29"/>
       <c r="F396" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G396" s="30"/>
       <c r="H396" s="30"/>
@@ -8101,7 +8367,7 @@
       <c r="D397" s="25"/>
       <c r="E397" s="29"/>
       <c r="F397" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G397" s="30"/>
       <c r="H397" s="30"/>
@@ -8115,7 +8381,7 @@
       <c r="D398" s="25"/>
       <c r="E398" s="29"/>
       <c r="F398" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G398" s="30"/>
       <c r="H398" s="30"/>
@@ -8129,7 +8395,7 @@
       <c r="D399" s="25"/>
       <c r="E399" s="29"/>
       <c r="F399" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G399" s="30"/>
       <c r="H399" s="30"/>
@@ -8143,7 +8409,7 @@
       <c r="D400" s="25"/>
       <c r="E400" s="29"/>
       <c r="F400" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G400" s="30"/>
       <c r="H400" s="30"/>
@@ -8157,7 +8423,7 @@
       <c r="D401" s="25"/>
       <c r="E401" s="29"/>
       <c r="F401" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G401" s="30"/>
       <c r="H401" s="30"/>
@@ -8171,7 +8437,7 @@
       <c r="D402" s="25"/>
       <c r="E402" s="29"/>
       <c r="F402" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G402" s="30"/>
       <c r="H402" s="30"/>
@@ -8185,7 +8451,7 @@
       <c r="D403" s="25"/>
       <c r="E403" s="29"/>
       <c r="F403" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G403" s="30"/>
       <c r="H403" s="30"/>
@@ -8199,7 +8465,7 @@
       <c r="D404" s="25"/>
       <c r="E404" s="29"/>
       <c r="F404" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G404" s="30"/>
       <c r="H404" s="30"/>
@@ -8213,7 +8479,7 @@
       <c r="D405" s="25"/>
       <c r="E405" s="29"/>
       <c r="F405" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G405" s="30"/>
       <c r="H405" s="30"/>
@@ -8227,7 +8493,7 @@
       <c r="D406" s="25"/>
       <c r="E406" s="29"/>
       <c r="F406" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G406" s="30"/>
       <c r="H406" s="30"/>
@@ -8241,7 +8507,7 @@
       <c r="D407" s="25"/>
       <c r="E407" s="29"/>
       <c r="F407" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G407" s="30"/>
       <c r="H407" s="30"/>
@@ -8255,7 +8521,7 @@
       <c r="D408" s="25"/>
       <c r="E408" s="29"/>
       <c r="F408" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G408" s="30"/>
       <c r="H408" s="30"/>
@@ -8269,7 +8535,7 @@
       <c r="D409" s="25"/>
       <c r="E409" s="29"/>
       <c r="F409" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G409" s="30"/>
       <c r="H409" s="30"/>
@@ -8283,7 +8549,7 @@
       <c r="D410" s="25"/>
       <c r="E410" s="29"/>
       <c r="F410" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G410" s="30"/>
       <c r="H410" s="30"/>
@@ -8297,7 +8563,7 @@
       <c r="D411" s="25"/>
       <c r="E411" s="29"/>
       <c r="F411" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G411" s="30"/>
       <c r="H411" s="30"/>
@@ -8311,7 +8577,7 @@
       <c r="D412" s="25"/>
       <c r="E412" s="29"/>
       <c r="F412" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G412" s="30"/>
       <c r="H412" s="30"/>
@@ -8325,7 +8591,7 @@
       <c r="D413" s="25"/>
       <c r="E413" s="29"/>
       <c r="F413" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G413" s="30"/>
       <c r="H413" s="30"/>
@@ -8339,7 +8605,7 @@
       <c r="D414" s="25"/>
       <c r="E414" s="29"/>
       <c r="F414" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G414" s="30"/>
       <c r="H414" s="30"/>
@@ -8353,7 +8619,7 @@
       <c r="D415" s="25"/>
       <c r="E415" s="29"/>
       <c r="F415" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G415" s="30"/>
       <c r="H415" s="30"/>
@@ -8367,7 +8633,7 @@
       <c r="D416" s="25"/>
       <c r="E416" s="29"/>
       <c r="F416" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G416" s="30"/>
       <c r="H416" s="30"/>
@@ -8381,7 +8647,7 @@
       <c r="D417" s="25"/>
       <c r="E417" s="29"/>
       <c r="F417" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G417" s="30"/>
       <c r="H417" s="30"/>
@@ -8395,7 +8661,7 @@
       <c r="D418" s="25"/>
       <c r="E418" s="29"/>
       <c r="F418" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G418" s="30"/>
       <c r="H418" s="30"/>
@@ -8409,7 +8675,7 @@
       <c r="D419" s="25"/>
       <c r="E419" s="29"/>
       <c r="F419" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G419" s="30"/>
       <c r="H419" s="30"/>
@@ -8423,7 +8689,7 @@
       <c r="D420" s="25"/>
       <c r="E420" s="29"/>
       <c r="F420" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G420" s="30"/>
       <c r="H420" s="30"/>
@@ -8437,7 +8703,7 @@
       <c r="D421" s="25"/>
       <c r="E421" s="29"/>
       <c r="F421" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G421" s="30"/>
       <c r="H421" s="30"/>
@@ -8451,7 +8717,7 @@
       <c r="D422" s="25"/>
       <c r="E422" s="29"/>
       <c r="F422" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G422" s="30"/>
       <c r="H422" s="30"/>
@@ -8465,7 +8731,7 @@
       <c r="D423" s="25"/>
       <c r="E423" s="29"/>
       <c r="F423" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G423" s="30"/>
       <c r="H423" s="30"/>
@@ -8479,7 +8745,7 @@
       <c r="D424" s="25"/>
       <c r="E424" s="29"/>
       <c r="F424" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G424" s="30"/>
       <c r="H424" s="30"/>
@@ -8493,7 +8759,7 @@
       <c r="D425" s="25"/>
       <c r="E425" s="29"/>
       <c r="F425" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G425" s="30"/>
       <c r="H425" s="30"/>
@@ -8507,7 +8773,7 @@
       <c r="D426" s="25"/>
       <c r="E426" s="29"/>
       <c r="F426" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G426" s="30"/>
       <c r="H426" s="30"/>
@@ -8521,7 +8787,7 @@
       <c r="D427" s="25"/>
       <c r="E427" s="29"/>
       <c r="F427" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G427" s="30"/>
       <c r="H427" s="30"/>
@@ -8535,7 +8801,7 @@
       <c r="D428" s="25"/>
       <c r="E428" s="29"/>
       <c r="F428" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G428" s="30"/>
       <c r="H428" s="30"/>
@@ -8549,7 +8815,7 @@
       <c r="D429" s="25"/>
       <c r="E429" s="29"/>
       <c r="F429" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G429" s="30"/>
       <c r="H429" s="30"/>
@@ -8563,7 +8829,7 @@
       <c r="D430" s="25"/>
       <c r="E430" s="29"/>
       <c r="F430" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G430" s="30"/>
       <c r="H430" s="30"/>
@@ -8577,7 +8843,7 @@
       <c r="D431" s="25"/>
       <c r="E431" s="29"/>
       <c r="F431" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G431" s="30"/>
       <c r="H431" s="30"/>
@@ -8591,7 +8857,7 @@
       <c r="D432" s="25"/>
       <c r="E432" s="29"/>
       <c r="F432" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G432" s="30"/>
       <c r="H432" s="30"/>
@@ -8605,7 +8871,7 @@
       <c r="D433" s="25"/>
       <c r="E433" s="29"/>
       <c r="F433" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G433" s="30"/>
       <c r="H433" s="30"/>
@@ -8619,7 +8885,7 @@
       <c r="D434" s="25"/>
       <c r="E434" s="29"/>
       <c r="F434" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G434" s="30"/>
       <c r="H434" s="30"/>
@@ -8633,7 +8899,7 @@
       <c r="D435" s="25"/>
       <c r="E435" s="29"/>
       <c r="F435" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G435" s="30"/>
       <c r="H435" s="30"/>
@@ -8647,7 +8913,7 @@
       <c r="D436" s="25"/>
       <c r="E436" s="29"/>
       <c r="F436" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G436" s="30"/>
       <c r="H436" s="30"/>
@@ -8661,7 +8927,7 @@
       <c r="D437" s="25"/>
       <c r="E437" s="29"/>
       <c r="F437" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G437" s="30"/>
       <c r="H437" s="30"/>
@@ -8675,7 +8941,7 @@
       <c r="D438" s="25"/>
       <c r="E438" s="29"/>
       <c r="F438" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G438" s="30"/>
       <c r="H438" s="30"/>
@@ -8689,7 +8955,7 @@
       <c r="D439" s="25"/>
       <c r="E439" s="29"/>
       <c r="F439" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G439" s="30"/>
       <c r="H439" s="30"/>
@@ -8703,7 +8969,7 @@
       <c r="D440" s="25"/>
       <c r="E440" s="29"/>
       <c r="F440" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G440" s="30"/>
       <c r="H440" s="30"/>
@@ -8717,7 +8983,7 @@
       <c r="D441" s="25"/>
       <c r="E441" s="29"/>
       <c r="F441" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G441" s="30"/>
       <c r="H441" s="30"/>
@@ -8731,7 +8997,7 @@
       <c r="D442" s="25"/>
       <c r="E442" s="29"/>
       <c r="F442" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G442" s="30"/>
       <c r="H442" s="30"/>
@@ -8745,7 +9011,7 @@
       <c r="D443" s="25"/>
       <c r="E443" s="29"/>
       <c r="F443" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G443" s="30"/>
       <c r="H443" s="30"/>
@@ -8759,7 +9025,7 @@
       <c r="D444" s="25"/>
       <c r="E444" s="29"/>
       <c r="F444" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G444" s="30"/>
       <c r="H444" s="30"/>
@@ -8773,7 +9039,7 @@
       <c r="D445" s="25"/>
       <c r="E445" s="29"/>
       <c r="F445" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G445" s="30"/>
       <c r="H445" s="30"/>
@@ -8787,7 +9053,7 @@
       <c r="D446" s="25"/>
       <c r="E446" s="29"/>
       <c r="F446" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G446" s="30"/>
       <c r="H446" s="30"/>
@@ -8801,7 +9067,7 @@
       <c r="D447" s="25"/>
       <c r="E447" s="29"/>
       <c r="F447" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G447" s="30"/>
       <c r="H447" s="30"/>
@@ -8815,7 +9081,7 @@
       <c r="D448" s="25"/>
       <c r="E448" s="29"/>
       <c r="F448" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G448" s="30"/>
       <c r="H448" s="30"/>
@@ -8829,7 +9095,7 @@
       <c r="D449" s="25"/>
       <c r="E449" s="29"/>
       <c r="F449" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G449" s="30"/>
       <c r="H449" s="30"/>
@@ -8843,7 +9109,7 @@
       <c r="D450" s="25"/>
       <c r="E450" s="29"/>
       <c r="F450" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G450" s="30"/>
       <c r="H450" s="30"/>
@@ -8857,7 +9123,7 @@
       <c r="D451" s="25"/>
       <c r="E451" s="29"/>
       <c r="F451" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G451" s="30"/>
       <c r="H451" s="30"/>
@@ -8871,7 +9137,7 @@
       <c r="D452" s="25"/>
       <c r="E452" s="29"/>
       <c r="F452" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G452" s="30"/>
       <c r="H452" s="30"/>
@@ -8885,7 +9151,7 @@
       <c r="D453" s="25"/>
       <c r="E453" s="29"/>
       <c r="F453" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G453" s="30"/>
       <c r="H453" s="30"/>
@@ -8899,7 +9165,7 @@
       <c r="D454" s="25"/>
       <c r="E454" s="29"/>
       <c r="F454" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G454" s="30"/>
       <c r="H454" s="30"/>
@@ -8913,7 +9179,7 @@
       <c r="D455" s="25"/>
       <c r="E455" s="29"/>
       <c r="F455" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G455" s="30"/>
       <c r="H455" s="30"/>
@@ -8927,7 +9193,7 @@
       <c r="D456" s="25"/>
       <c r="E456" s="29"/>
       <c r="F456" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G456" s="30"/>
       <c r="H456" s="30"/>
@@ -8941,7 +9207,7 @@
       <c r="D457" s="25"/>
       <c r="E457" s="29"/>
       <c r="F457" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G457" s="30"/>
       <c r="H457" s="30"/>
@@ -8955,7 +9221,7 @@
       <c r="D458" s="25"/>
       <c r="E458" s="29"/>
       <c r="F458" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G458" s="30"/>
       <c r="H458" s="30"/>
@@ -8969,7 +9235,7 @@
       <c r="D459" s="25"/>
       <c r="E459" s="29"/>
       <c r="F459" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G459" s="30"/>
       <c r="H459" s="30"/>
@@ -8983,7 +9249,7 @@
       <c r="D460" s="25"/>
       <c r="E460" s="29"/>
       <c r="F460" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G460" s="30"/>
       <c r="H460" s="30"/>
@@ -8997,7 +9263,7 @@
       <c r="D461" s="25"/>
       <c r="E461" s="29"/>
       <c r="F461" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G461" s="30"/>
       <c r="H461" s="30"/>
@@ -9011,7 +9277,7 @@
       <c r="D462" s="25"/>
       <c r="E462" s="29"/>
       <c r="F462" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G462" s="30"/>
       <c r="H462" s="30"/>
@@ -9025,7 +9291,7 @@
       <c r="D463" s="25"/>
       <c r="E463" s="29"/>
       <c r="F463" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G463" s="30"/>
       <c r="H463" s="30"/>
@@ -9039,7 +9305,7 @@
       <c r="D464" s="25"/>
       <c r="E464" s="29"/>
       <c r="F464" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G464" s="30"/>
       <c r="H464" s="30"/>
@@ -9053,7 +9319,7 @@
       <c r="D465" s="25"/>
       <c r="E465" s="29"/>
       <c r="F465" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G465" s="30"/>
       <c r="H465" s="30"/>
@@ -9067,7 +9333,7 @@
       <c r="D466" s="25"/>
       <c r="E466" s="29"/>
       <c r="F466" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G466" s="30"/>
       <c r="H466" s="30"/>
@@ -9081,7 +9347,7 @@
       <c r="D467" s="25"/>
       <c r="E467" s="29"/>
       <c r="F467" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G467" s="30"/>
       <c r="H467" s="30"/>
@@ -9095,7 +9361,7 @@
       <c r="D468" s="25"/>
       <c r="E468" s="29"/>
       <c r="F468" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G468" s="30"/>
       <c r="H468" s="30"/>
@@ -9109,7 +9375,7 @@
       <c r="D469" s="25"/>
       <c r="E469" s="29"/>
       <c r="F469" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G469" s="30"/>
       <c r="H469" s="30"/>
@@ -9123,7 +9389,7 @@
       <c r="D470" s="25"/>
       <c r="E470" s="29"/>
       <c r="F470" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G470" s="30"/>
       <c r="H470" s="30"/>
@@ -9137,7 +9403,7 @@
       <c r="D471" s="25"/>
       <c r="E471" s="29"/>
       <c r="F471" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G471" s="30"/>
       <c r="H471" s="30"/>
@@ -9151,7 +9417,7 @@
       <c r="D472" s="25"/>
       <c r="E472" s="29"/>
       <c r="F472" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G472" s="30"/>
       <c r="H472" s="30"/>
@@ -9165,7 +9431,7 @@
       <c r="D473" s="25"/>
       <c r="E473" s="29"/>
       <c r="F473" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G473" s="30"/>
       <c r="H473" s="30"/>
@@ -9179,7 +9445,7 @@
       <c r="D474" s="25"/>
       <c r="E474" s="29"/>
       <c r="F474" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G474" s="30"/>
       <c r="H474" s="30"/>
@@ -9193,7 +9459,7 @@
       <c r="D475" s="25"/>
       <c r="E475" s="29"/>
       <c r="F475" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G475" s="30"/>
       <c r="H475" s="30"/>
@@ -9207,7 +9473,7 @@
       <c r="D476" s="25"/>
       <c r="E476" s="29"/>
       <c r="F476" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G476" s="30"/>
       <c r="H476" s="30"/>
@@ -9221,7 +9487,7 @@
       <c r="D477" s="25"/>
       <c r="E477" s="29"/>
       <c r="F477" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G477" s="30"/>
       <c r="H477" s="30"/>
@@ -9235,7 +9501,7 @@
       <c r="D478" s="25"/>
       <c r="E478" s="29"/>
       <c r="F478" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G478" s="30"/>
       <c r="H478" s="30"/>
@@ -9249,7 +9515,7 @@
       <c r="D479" s="25"/>
       <c r="E479" s="29"/>
       <c r="F479" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G479" s="30"/>
       <c r="H479" s="30"/>
@@ -9263,7 +9529,7 @@
       <c r="D480" s="25"/>
       <c r="E480" s="29"/>
       <c r="F480" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G480" s="30"/>
       <c r="H480" s="30"/>
@@ -9277,7 +9543,7 @@
       <c r="D481" s="25"/>
       <c r="E481" s="29"/>
       <c r="F481" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G481" s="30"/>
       <c r="H481" s="30"/>
@@ -9291,7 +9557,7 @@
       <c r="D482" s="25"/>
       <c r="E482" s="29"/>
       <c r="F482" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G482" s="30"/>
       <c r="H482" s="30"/>
@@ -9305,7 +9571,7 @@
       <c r="D483" s="25"/>
       <c r="E483" s="29"/>
       <c r="F483" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G483" s="30"/>
       <c r="H483" s="30"/>
@@ -9319,7 +9585,7 @@
       <c r="D484" s="25"/>
       <c r="E484" s="29"/>
       <c r="F484" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G484" s="30"/>
       <c r="H484" s="30"/>
@@ -9333,7 +9599,7 @@
       <c r="D485" s="25"/>
       <c r="E485" s="29"/>
       <c r="F485" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G485" s="30"/>
       <c r="H485" s="30"/>
@@ -9347,7 +9613,7 @@
       <c r="D486" s="25"/>
       <c r="E486" s="29"/>
       <c r="F486" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G486" s="30"/>
       <c r="H486" s="30"/>
@@ -9361,7 +9627,7 @@
       <c r="D487" s="25"/>
       <c r="E487" s="29"/>
       <c r="F487" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G487" s="30"/>
       <c r="H487" s="30"/>
@@ -9372,7 +9638,11 @@
       <c r="A488" s="31"/>
       <c r="B488" s="28"/>
       <c r="C488" s="28"/>
+      <c r="D488" s="25"/>
       <c r="E488" s="29"/>
+      <c r="F488" s="26" t="s">
+        <v>68</v>
+      </c>
       <c r="G488" s="30"/>
       <c r="H488" s="30"/>
       <c r="I488" s="30"/>
@@ -9382,7 +9652,11 @@
       <c r="A489" s="31"/>
       <c r="B489" s="28"/>
       <c r="C489" s="28"/>
+      <c r="D489" s="25"/>
       <c r="E489" s="29"/>
+      <c r="F489" s="26" t="s">
+        <v>68</v>
+      </c>
       <c r="G489" s="30"/>
       <c r="H489" s="30"/>
       <c r="I489" s="30"/>
@@ -9392,7 +9666,11 @@
       <c r="A490" s="31"/>
       <c r="B490" s="28"/>
       <c r="C490" s="28"/>
+      <c r="D490" s="25"/>
       <c r="E490" s="29"/>
+      <c r="F490" s="26" t="s">
+        <v>68</v>
+      </c>
       <c r="G490" s="30"/>
       <c r="H490" s="30"/>
       <c r="I490" s="30"/>
@@ -9402,7 +9680,11 @@
       <c r="A491" s="31"/>
       <c r="B491" s="28"/>
       <c r="C491" s="28"/>
+      <c r="D491" s="25"/>
       <c r="E491" s="29"/>
+      <c r="F491" s="26" t="s">
+        <v>68</v>
+      </c>
       <c r="G491" s="30"/>
       <c r="H491" s="30"/>
       <c r="I491" s="30"/>
@@ -9412,7 +9694,11 @@
       <c r="A492" s="31"/>
       <c r="B492" s="28"/>
       <c r="C492" s="28"/>
+      <c r="D492" s="25"/>
       <c r="E492" s="29"/>
+      <c r="F492" s="26" t="s">
+        <v>68</v>
+      </c>
       <c r="G492" s="30"/>
       <c r="H492" s="30"/>
       <c r="I492" s="30"/>
@@ -9422,7 +9708,11 @@
       <c r="A493" s="31"/>
       <c r="B493" s="28"/>
       <c r="C493" s="28"/>
+      <c r="D493" s="25"/>
       <c r="E493" s="29"/>
+      <c r="F493" s="26" t="s">
+        <v>68</v>
+      </c>
       <c r="G493" s="30"/>
       <c r="H493" s="30"/>
       <c r="I493" s="30"/>
@@ -9432,7 +9722,11 @@
       <c r="A494" s="31"/>
       <c r="B494" s="28"/>
       <c r="C494" s="28"/>
+      <c r="D494" s="25"/>
       <c r="E494" s="29"/>
+      <c r="F494" s="26" t="s">
+        <v>68</v>
+      </c>
       <c r="G494" s="30"/>
       <c r="H494" s="30"/>
       <c r="I494" s="30"/>
@@ -9442,7 +9736,11 @@
       <c r="A495" s="31"/>
       <c r="B495" s="28"/>
       <c r="C495" s="28"/>
+      <c r="D495" s="25"/>
       <c r="E495" s="29"/>
+      <c r="F495" s="26" t="s">
+        <v>68</v>
+      </c>
       <c r="G495" s="30"/>
       <c r="H495" s="30"/>
       <c r="I495" s="30"/>
@@ -14938,50 +15236,130 @@
       <c r="I1044" s="30"/>
       <c r="J1044" s="32"/>
     </row>
+    <row r="1045" ht="29.25" customHeight="1">
+      <c r="A1045" s="31"/>
+      <c r="B1045" s="28"/>
+      <c r="C1045" s="28"/>
+      <c r="E1045" s="29"/>
+      <c r="G1045" s="30"/>
+      <c r="H1045" s="30"/>
+      <c r="I1045" s="30"/>
+      <c r="J1045" s="32"/>
+    </row>
+    <row r="1046" ht="29.25" customHeight="1">
+      <c r="A1046" s="31"/>
+      <c r="B1046" s="28"/>
+      <c r="C1046" s="28"/>
+      <c r="E1046" s="29"/>
+      <c r="G1046" s="30"/>
+      <c r="H1046" s="30"/>
+      <c r="I1046" s="30"/>
+      <c r="J1046" s="32"/>
+    </row>
+    <row r="1047" ht="29.25" customHeight="1">
+      <c r="A1047" s="31"/>
+      <c r="B1047" s="28"/>
+      <c r="C1047" s="28"/>
+      <c r="E1047" s="29"/>
+      <c r="G1047" s="30"/>
+      <c r="H1047" s="30"/>
+      <c r="I1047" s="30"/>
+      <c r="J1047" s="32"/>
+    </row>
+    <row r="1048" ht="29.25" customHeight="1">
+      <c r="A1048" s="31"/>
+      <c r="B1048" s="28"/>
+      <c r="C1048" s="28"/>
+      <c r="E1048" s="29"/>
+      <c r="G1048" s="30"/>
+      <c r="H1048" s="30"/>
+      <c r="I1048" s="30"/>
+      <c r="J1048" s="32"/>
+    </row>
+    <row r="1049" ht="29.25" customHeight="1">
+      <c r="A1049" s="31"/>
+      <c r="B1049" s="28"/>
+      <c r="C1049" s="28"/>
+      <c r="E1049" s="29"/>
+      <c r="G1049" s="30"/>
+      <c r="H1049" s="30"/>
+      <c r="I1049" s="30"/>
+      <c r="J1049" s="32"/>
+    </row>
+    <row r="1050" ht="29.25" customHeight="1">
+      <c r="A1050" s="31"/>
+      <c r="B1050" s="28"/>
+      <c r="C1050" s="28"/>
+      <c r="E1050" s="29"/>
+      <c r="G1050" s="30"/>
+      <c r="H1050" s="30"/>
+      <c r="I1050" s="30"/>
+      <c r="J1050" s="32"/>
+    </row>
+    <row r="1051" ht="29.25" customHeight="1">
+      <c r="A1051" s="31"/>
+      <c r="B1051" s="28"/>
+      <c r="C1051" s="28"/>
+      <c r="E1051" s="29"/>
+      <c r="G1051" s="30"/>
+      <c r="H1051" s="30"/>
+      <c r="I1051" s="30"/>
+      <c r="J1051" s="32"/>
+    </row>
+    <row r="1052" ht="29.25" customHeight="1">
+      <c r="A1052" s="31"/>
+      <c r="B1052" s="28"/>
+      <c r="C1052" s="28"/>
+      <c r="E1052" s="29"/>
+      <c r="G1052" s="30"/>
+      <c r="H1052" s="30"/>
+      <c r="I1052" s="30"/>
+      <c r="J1052" s="32"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D64">
+  <conditionalFormatting sqref="D2:D72">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Finalizada">
       <formula>NOT(ISERROR(SEARCH(("Finalizada"),(D2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D64">
+  <conditionalFormatting sqref="D2:D72">
     <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="En Proceso">
       <formula>NOT(ISERROR(SEARCH(("En Proceso"),(D2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D64">
+  <conditionalFormatting sqref="D2:D72">
     <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Pendiente de Revision">
       <formula>NOT(ISERROR(SEARCH(("Pendiente de Revision"),(D2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J1044">
+  <conditionalFormatting sqref="J2:J1052">
     <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="SI">
       <formula>NOT(ISERROR(SEARCH(("SI"),(J2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E1044">
+  <conditionalFormatting sqref="E2:E1052">
     <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Validado">
       <formula>NOT(ISERROR(SEARCH(("Validado"),(E2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E1044">
+  <conditionalFormatting sqref="E2:E1052">
     <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="Revision">
       <formula>NOT(ISERROR(SEARCH(("Revision"),(E2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E89">
+  <conditionalFormatting sqref="E2:E97">
     <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="Reasignado">
       <formula>NOT(ISERROR(SEARCH(("Reasignado"),(E2))))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D487">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D495">
       <formula1>"Sin Comenzar,En Proceso,Finalizada"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E1044">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E1052">
       <formula1>"_,Esperando Revision,En Revision,Reasignado,Validado"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F487">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F495">
       <formula1>"_,Ignacio,Lucia,Luciano,Gabriel,Lucía"</formula1>
     </dataValidation>
   </dataValidations>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="113">
   <si>
     <t>Etapa</t>
   </si>
@@ -122,9 +122,6 @@
   </si>
   <si>
     <t>Responder Cuestionario a Directores</t>
-  </si>
-  <si>
-    <t>Lucía</t>
   </si>
   <si>
     <t>Sintesis Entrevistas</t>
@@ -860,7 +857,7 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
@@ -891,7 +888,7 @@
       </c>
       <c r="C2" s="6" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-09-20 16:36</v>
+        <v>Plan de Proyecto: 2026-09-20 16:53</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>14</v>
@@ -1604,7 +1601,7 @@
         <v>15</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G18" s="8">
         <v>46274.0</v>
@@ -1629,16 +1626,16 @@
         <v>26</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E19" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19" s="13" t="s">
         <v>39</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>40</v>
       </c>
       <c r="G19" s="14">
         <v>46274.0</v>
@@ -1651,10 +1648,10 @@
       </c>
       <c r="J19" s="15"/>
       <c r="K19" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="L19" s="15" t="s">
         <v>41</v>
-      </c>
-      <c r="L19" s="15" t="s">
-        <v>42</v>
       </c>
       <c r="M19" s="16"/>
       <c r="N19" s="16"/>
@@ -1684,13 +1681,13 @@
         <v>26</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>32</v>
@@ -1706,10 +1703,10 @@
       </c>
       <c r="J20" s="17"/>
       <c r="K20" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L20" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" ht="29.25" customHeight="1">
@@ -1717,10 +1714,10 @@
         <v>25</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="12" t="s">
         <v>44</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>45</v>
       </c>
       <c r="D21" s="13" t="s">
         <v>14</v>
@@ -1745,7 +1742,7 @@
       </c>
       <c r="K21" s="15"/>
       <c r="L21" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M21" s="16"/>
       <c r="N21" s="16"/>
@@ -1772,10 +1769,10 @@
         <v>25</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>14</v>
@@ -1806,10 +1803,10 @@
         <v>25</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>14</v>
@@ -1818,7 +1815,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G23" s="14">
         <v>46276.0</v>
@@ -1859,10 +1856,10 @@
         <v>25</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>14</v>
@@ -1893,10 +1890,10 @@
         <v>25</v>
       </c>
       <c r="B25" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="12" t="s">
         <v>49</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>50</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>14</v>
@@ -1905,7 +1902,7 @@
         <v>15</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G25" s="14">
         <v>46271.0</v>
@@ -1946,10 +1943,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>14</v>
@@ -1983,16 +1980,16 @@
         <v>12</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E27" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F27" s="13" t="s">
         <v>53</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>54</v>
       </c>
       <c r="G27" s="14">
         <v>46274.0</v>
@@ -2036,7 +2033,7 @@
         <v>12</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>14</v>
@@ -2068,7 +2065,7 @@
         <v>26</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>14</v>
@@ -2121,7 +2118,7 @@
         <v>26</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>14</v>
@@ -2152,10 +2149,10 @@
         <v>25</v>
       </c>
       <c r="B31" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" s="12" t="s">
         <v>57</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>58</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>14</v>
@@ -2164,7 +2161,7 @@
         <v>15</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G31" s="14">
         <v>46276.0</v>
@@ -2179,7 +2176,7 @@
         <v>20.0</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L31" s="15"/>
       <c r="M31" s="16"/>
@@ -2207,10 +2204,10 @@
         <v>25</v>
       </c>
       <c r="B32" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>14</v>
@@ -2219,7 +2216,7 @@
         <v>15</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G32" s="8">
         <v>46276.0</v>
@@ -2234,7 +2231,7 @@
         <v>20.0</v>
       </c>
       <c r="K32" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L32" s="9"/>
     </row>
@@ -2243,10 +2240,10 @@
         <v>25</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>14</v>
@@ -2268,7 +2265,7 @@
       </c>
       <c r="J33" s="15"/>
       <c r="K33" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L33" s="15"/>
       <c r="M33" s="16"/>
@@ -2296,16 +2293,16 @@
         <v>25</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C34" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D34" s="7" t="s">
-        <v>63</v>
-      </c>
       <c r="E34" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>32</v>
@@ -2319,7 +2316,7 @@
       <c r="I34" s="8"/>
       <c r="J34" s="17"/>
       <c r="K34" s="20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L34" s="9"/>
     </row>
@@ -2328,16 +2325,16 @@
         <v>25</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>16</v>
@@ -2360,16 +2357,16 @@
         <v>25</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>16</v>
@@ -2392,19 +2389,19 @@
         <v>25</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G37" s="14">
         <v>46283.0</v>
@@ -2441,17 +2438,17 @@
         <v>25</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E38" s="7"/>
       <c r="F38" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G38" s="8">
         <v>46283.0</v>
@@ -2469,17 +2466,17 @@
         <v>25</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E39" s="13"/>
       <c r="F39" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G39" s="14">
         <v>46283.0</v>
@@ -2516,17 +2513,17 @@
         <v>25</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E40" s="7"/>
       <c r="F40" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G40" s="8">
         <v>46283.0</v>
@@ -2544,16 +2541,16 @@
         <v>25</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C41" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D41" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D41" s="13" t="s">
-        <v>73</v>
-      </c>
       <c r="E41" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F41" s="13" t="s">
         <v>16</v>
@@ -2593,16 +2590,16 @@
         <v>25</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>16</v>
@@ -2628,7 +2625,7 @@
         <v>20</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D43" s="13" t="s">
         <v>14</v>
@@ -2679,13 +2676,13 @@
         <v>20</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D44" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F44" s="13" t="s">
         <v>16</v>
@@ -2727,19 +2724,19 @@
         <v>25</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G45" s="14">
         <v>46288.0</v>
@@ -2776,17 +2773,17 @@
         <v>25</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E46" s="7"/>
       <c r="F46" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G46" s="8">
         <v>46288.0</v>
@@ -2804,17 +2801,17 @@
         <v>25</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E47" s="13"/>
       <c r="F47" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G47" s="14">
         <v>46285.0</v>
@@ -2851,17 +2848,17 @@
         <v>25</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E48" s="7"/>
       <c r="F48" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G48" s="8">
         <v>46286.0</v>
@@ -2879,13 +2876,13 @@
         <v>25</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E49" s="13"/>
       <c r="F49" s="13" t="s">
@@ -2926,13 +2923,13 @@
         <v>25</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E50" s="13"/>
       <c r="F50" s="13" t="s">
@@ -2973,17 +2970,17 @@
         <v>25</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E51" s="13"/>
       <c r="F51" s="13" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G51" s="14">
         <v>46286.0</v>
@@ -3020,19 +3017,19 @@
         <v>25</v>
       </c>
       <c r="B52" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C52" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="C52" s="12" t="s">
-        <v>85</v>
-      </c>
       <c r="D52" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G52" s="14">
         <v>46287.0</v>
@@ -3069,16 +3066,16 @@
         <v>25</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>32</v>
@@ -3099,13 +3096,13 @@
         <v>25</v>
       </c>
       <c r="B54" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C54" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="C54" s="12" t="s">
-        <v>88</v>
-      </c>
       <c r="D54" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E54" s="13"/>
       <c r="F54" s="13" t="s">
@@ -3146,16 +3143,16 @@
         <v>25</v>
       </c>
       <c r="B55" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C55" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="C55" s="6" t="s">
-        <v>90</v>
-      </c>
       <c r="D55" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F55" s="7" t="s">
         <v>16</v>
@@ -3176,13 +3173,13 @@
         <v>25</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E56" s="13"/>
       <c r="F56" s="13" t="s">
@@ -3223,19 +3220,19 @@
         <v>25</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G57" s="8">
         <v>46286.0</v>
@@ -3253,10 +3250,10 @@
         <v>25</v>
       </c>
       <c r="B58" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C58" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>93</v>
       </c>
       <c r="D58" s="13"/>
       <c r="E58" s="13"/>
@@ -3292,10 +3289,10 @@
         <v>25</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D59" s="13"/>
       <c r="E59" s="13"/>
@@ -3331,10 +3328,10 @@
         <v>25</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D60" s="13"/>
       <c r="E60" s="13"/>
@@ -3370,10 +3367,10 @@
         <v>25</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D61" s="13"/>
       <c r="E61" s="13"/>
@@ -3409,10 +3406,10 @@
         <v>25</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D62" s="13"/>
       <c r="E62" s="13"/>
@@ -3447,7 +3444,7 @@
       <c r="A63" s="10"/>
       <c r="B63" s="11"/>
       <c r="C63" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D63" s="13"/>
       <c r="E63" s="13"/>
@@ -3480,19 +3477,19 @@
     </row>
     <row r="64" ht="29.25" customHeight="1">
       <c r="A64" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B64" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B64" s="11" t="s">
+      <c r="C64" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="C64" s="12" t="s">
-        <v>101</v>
-      </c>
       <c r="D64" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F64" s="13" t="s">
         <v>32</v>
@@ -3506,7 +3503,7 @@
       <c r="I64" s="14"/>
       <c r="J64" s="15"/>
       <c r="K64" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L64" s="15"/>
       <c r="M64" s="16"/>
@@ -3531,19 +3528,19 @@
     </row>
     <row r="65" ht="29.25" customHeight="1">
       <c r="A65" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B65" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="C65" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C65" s="6" t="s">
-        <v>101</v>
-      </c>
       <c r="D65" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F65" s="7" t="s">
         <v>16</v>
@@ -3557,22 +3554,22 @@
       <c r="I65" s="8"/>
       <c r="J65" s="9"/>
       <c r="K65" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L65" s="9"/>
     </row>
     <row r="66" ht="29.25" customHeight="1">
       <c r="A66" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B66" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C66" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C66" s="6" t="s">
-        <v>104</v>
-      </c>
       <c r="D66" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E66" s="7"/>
       <c r="F66" s="7" t="s">
@@ -3591,22 +3588,22 @@
     </row>
     <row r="67" ht="29.25" customHeight="1">
       <c r="A67" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G67" s="14">
         <v>46286.0</v>
@@ -3640,20 +3637,20 @@
     </row>
     <row r="68" ht="29.25" customHeight="1">
       <c r="A68" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E68" s="7"/>
       <c r="F68" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G68" s="8">
         <v>46287.0</v>
@@ -3668,20 +3665,20 @@
     </row>
     <row r="69" ht="29.25" customHeight="1">
       <c r="A69" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E69" s="13"/>
       <c r="F69" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G69" s="14">
         <v>46287.0</v>
@@ -3715,20 +3712,20 @@
     </row>
     <row r="70" ht="29.25" customHeight="1">
       <c r="A70" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B70" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C70" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C70" s="6" t="s">
-        <v>109</v>
-      </c>
       <c r="D70" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E70" s="7"/>
       <c r="F70" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G70" s="8">
         <v>46296.0</v>
@@ -3743,18 +3740,18 @@
     </row>
     <row r="71" ht="29.25" customHeight="1">
       <c r="A71" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B71" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C71" s="12" t="s">
         <v>110</v>
-      </c>
-      <c r="C71" s="12" t="s">
-        <v>111</v>
       </c>
       <c r="D71" s="13"/>
       <c r="E71" s="13"/>
       <c r="F71" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G71" s="14">
         <v>46303.0</v>
@@ -3788,20 +3785,20 @@
     </row>
     <row r="72" ht="29.25" customHeight="1">
       <c r="A72" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B72" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C72" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="C72" s="6" t="s">
-        <v>113</v>
-      </c>
       <c r="D72" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E72" s="7"/>
       <c r="F72" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G72" s="8">
         <v>46305.0</v>
@@ -3821,7 +3818,7 @@
       <c r="D73" s="25"/>
       <c r="E73" s="21"/>
       <c r="F73" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G73" s="27"/>
       <c r="H73" s="27"/>
@@ -3837,7 +3834,7 @@
       <c r="D74" s="25"/>
       <c r="E74" s="21"/>
       <c r="F74" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G74" s="27"/>
       <c r="H74" s="27"/>
@@ -3853,7 +3850,7 @@
       <c r="D75" s="25"/>
       <c r="E75" s="21"/>
       <c r="F75" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G75" s="27"/>
       <c r="H75" s="27"/>
@@ -3869,7 +3866,7 @@
       <c r="D76" s="25"/>
       <c r="E76" s="21"/>
       <c r="F76" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G76" s="27"/>
       <c r="H76" s="27"/>
@@ -3885,7 +3882,7 @@
       <c r="D77" s="25"/>
       <c r="E77" s="21"/>
       <c r="F77" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G77" s="27"/>
       <c r="H77" s="27"/>
@@ -3901,7 +3898,7 @@
       <c r="D78" s="25"/>
       <c r="E78" s="29"/>
       <c r="F78" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G78" s="30"/>
       <c r="H78" s="30"/>
@@ -3915,7 +3912,7 @@
       <c r="D79" s="25"/>
       <c r="E79" s="29"/>
       <c r="F79" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G79" s="30"/>
       <c r="H79" s="30"/>
@@ -3929,7 +3926,7 @@
       <c r="D80" s="25"/>
       <c r="E80" s="29"/>
       <c r="F80" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G80" s="30"/>
       <c r="H80" s="30"/>
@@ -3943,7 +3940,7 @@
       <c r="D81" s="25"/>
       <c r="E81" s="29"/>
       <c r="F81" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G81" s="30"/>
       <c r="H81" s="30"/>
@@ -3957,7 +3954,7 @@
       <c r="D82" s="25"/>
       <c r="E82" s="29"/>
       <c r="F82" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G82" s="30"/>
       <c r="H82" s="30"/>
@@ -3971,7 +3968,7 @@
       <c r="D83" s="25"/>
       <c r="E83" s="29"/>
       <c r="F83" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G83" s="30"/>
       <c r="H83" s="30"/>
@@ -3985,7 +3982,7 @@
       <c r="D84" s="25"/>
       <c r="E84" s="29"/>
       <c r="F84" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G84" s="30"/>
       <c r="H84" s="30"/>
@@ -3999,7 +3996,7 @@
       <c r="D85" s="25"/>
       <c r="E85" s="29"/>
       <c r="F85" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G85" s="30"/>
       <c r="H85" s="30"/>
@@ -4013,7 +4010,7 @@
       <c r="D86" s="25"/>
       <c r="E86" s="29"/>
       <c r="F86" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G86" s="30"/>
       <c r="H86" s="30"/>
@@ -4027,7 +4024,7 @@
       <c r="D87" s="25"/>
       <c r="E87" s="29"/>
       <c r="F87" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G87" s="30"/>
       <c r="H87" s="30"/>
@@ -4041,7 +4038,7 @@
       <c r="D88" s="25"/>
       <c r="E88" s="29"/>
       <c r="F88" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G88" s="30"/>
       <c r="H88" s="30"/>
@@ -4055,7 +4052,7 @@
       <c r="D89" s="25"/>
       <c r="E89" s="29"/>
       <c r="F89" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G89" s="30"/>
       <c r="H89" s="30"/>
@@ -4069,7 +4066,7 @@
       <c r="D90" s="25"/>
       <c r="E90" s="29"/>
       <c r="F90" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G90" s="30"/>
       <c r="H90" s="30"/>
@@ -4083,7 +4080,7 @@
       <c r="D91" s="25"/>
       <c r="E91" s="29"/>
       <c r="F91" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G91" s="30"/>
       <c r="H91" s="30"/>
@@ -4097,7 +4094,7 @@
       <c r="D92" s="25"/>
       <c r="E92" s="29"/>
       <c r="F92" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G92" s="30"/>
       <c r="H92" s="30"/>
@@ -4111,7 +4108,7 @@
       <c r="D93" s="25"/>
       <c r="E93" s="29"/>
       <c r="F93" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G93" s="30"/>
       <c r="H93" s="30"/>
@@ -4125,7 +4122,7 @@
       <c r="D94" s="25"/>
       <c r="E94" s="29"/>
       <c r="F94" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G94" s="30"/>
       <c r="H94" s="30"/>
@@ -4139,7 +4136,7 @@
       <c r="D95" s="25"/>
       <c r="E95" s="29"/>
       <c r="F95" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G95" s="30"/>
       <c r="H95" s="30"/>
@@ -4153,7 +4150,7 @@
       <c r="D96" s="25"/>
       <c r="E96" s="29"/>
       <c r="F96" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G96" s="30"/>
       <c r="H96" s="30"/>
@@ -4167,7 +4164,7 @@
       <c r="D97" s="25"/>
       <c r="E97" s="29"/>
       <c r="F97" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G97" s="30"/>
       <c r="H97" s="30"/>
@@ -4181,7 +4178,7 @@
       <c r="D98" s="25"/>
       <c r="E98" s="29"/>
       <c r="F98" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G98" s="30"/>
       <c r="H98" s="30"/>
@@ -4195,7 +4192,7 @@
       <c r="D99" s="25"/>
       <c r="E99" s="29"/>
       <c r="F99" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G99" s="30"/>
       <c r="H99" s="30"/>
@@ -4209,7 +4206,7 @@
       <c r="D100" s="25"/>
       <c r="E100" s="29"/>
       <c r="F100" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G100" s="30"/>
       <c r="H100" s="30"/>
@@ -4223,7 +4220,7 @@
       <c r="D101" s="25"/>
       <c r="E101" s="29"/>
       <c r="F101" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G101" s="30"/>
       <c r="H101" s="30"/>
@@ -4237,7 +4234,7 @@
       <c r="D102" s="25"/>
       <c r="E102" s="29"/>
       <c r="F102" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G102" s="30"/>
       <c r="H102" s="30"/>
@@ -4251,7 +4248,7 @@
       <c r="D103" s="25"/>
       <c r="E103" s="29"/>
       <c r="F103" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G103" s="30"/>
       <c r="H103" s="30"/>
@@ -4265,7 +4262,7 @@
       <c r="D104" s="25"/>
       <c r="E104" s="29"/>
       <c r="F104" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G104" s="30"/>
       <c r="H104" s="30"/>
@@ -4279,7 +4276,7 @@
       <c r="D105" s="25"/>
       <c r="E105" s="29"/>
       <c r="F105" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G105" s="30"/>
       <c r="H105" s="30"/>
@@ -4293,7 +4290,7 @@
       <c r="D106" s="25"/>
       <c r="E106" s="29"/>
       <c r="F106" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G106" s="30"/>
       <c r="H106" s="30"/>
@@ -4307,7 +4304,7 @@
       <c r="D107" s="25"/>
       <c r="E107" s="29"/>
       <c r="F107" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G107" s="30"/>
       <c r="H107" s="30"/>
@@ -4321,7 +4318,7 @@
       <c r="D108" s="25"/>
       <c r="E108" s="29"/>
       <c r="F108" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G108" s="30"/>
       <c r="H108" s="30"/>
@@ -4335,7 +4332,7 @@
       <c r="D109" s="25"/>
       <c r="E109" s="29"/>
       <c r="F109" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G109" s="30"/>
       <c r="H109" s="30"/>
@@ -4349,7 +4346,7 @@
       <c r="D110" s="25"/>
       <c r="E110" s="29"/>
       <c r="F110" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G110" s="30"/>
       <c r="H110" s="30"/>
@@ -4363,7 +4360,7 @@
       <c r="D111" s="25"/>
       <c r="E111" s="29"/>
       <c r="F111" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G111" s="30"/>
       <c r="H111" s="30"/>
@@ -4377,7 +4374,7 @@
       <c r="D112" s="25"/>
       <c r="E112" s="29"/>
       <c r="F112" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G112" s="30"/>
       <c r="H112" s="30"/>
@@ -4391,7 +4388,7 @@
       <c r="D113" s="25"/>
       <c r="E113" s="29"/>
       <c r="F113" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G113" s="30"/>
       <c r="H113" s="30"/>
@@ -4405,7 +4402,7 @@
       <c r="D114" s="25"/>
       <c r="E114" s="29"/>
       <c r="F114" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G114" s="30"/>
       <c r="H114" s="30"/>
@@ -4419,7 +4416,7 @@
       <c r="D115" s="25"/>
       <c r="E115" s="29"/>
       <c r="F115" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G115" s="30"/>
       <c r="H115" s="30"/>
@@ -4433,7 +4430,7 @@
       <c r="D116" s="25"/>
       <c r="E116" s="29"/>
       <c r="F116" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G116" s="30"/>
       <c r="H116" s="30"/>
@@ -4447,7 +4444,7 @@
       <c r="D117" s="25"/>
       <c r="E117" s="29"/>
       <c r="F117" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G117" s="30"/>
       <c r="H117" s="30"/>
@@ -4461,7 +4458,7 @@
       <c r="D118" s="25"/>
       <c r="E118" s="29"/>
       <c r="F118" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G118" s="30"/>
       <c r="H118" s="30"/>
@@ -4475,7 +4472,7 @@
       <c r="D119" s="25"/>
       <c r="E119" s="29"/>
       <c r="F119" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G119" s="30"/>
       <c r="H119" s="30"/>
@@ -4489,7 +4486,7 @@
       <c r="D120" s="25"/>
       <c r="E120" s="29"/>
       <c r="F120" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G120" s="30"/>
       <c r="H120" s="30"/>
@@ -4503,7 +4500,7 @@
       <c r="D121" s="25"/>
       <c r="E121" s="29"/>
       <c r="F121" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G121" s="30"/>
       <c r="H121" s="30"/>
@@ -4517,7 +4514,7 @@
       <c r="D122" s="25"/>
       <c r="E122" s="29"/>
       <c r="F122" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G122" s="30"/>
       <c r="H122" s="30"/>
@@ -4531,7 +4528,7 @@
       <c r="D123" s="25"/>
       <c r="E123" s="29"/>
       <c r="F123" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G123" s="30"/>
       <c r="H123" s="30"/>
@@ -4545,7 +4542,7 @@
       <c r="D124" s="25"/>
       <c r="E124" s="29"/>
       <c r="F124" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G124" s="30"/>
       <c r="H124" s="30"/>
@@ -4559,7 +4556,7 @@
       <c r="D125" s="25"/>
       <c r="E125" s="29"/>
       <c r="F125" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G125" s="30"/>
       <c r="H125" s="30"/>
@@ -4573,7 +4570,7 @@
       <c r="D126" s="25"/>
       <c r="E126" s="29"/>
       <c r="F126" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G126" s="30"/>
       <c r="H126" s="30"/>
@@ -4587,7 +4584,7 @@
       <c r="D127" s="25"/>
       <c r="E127" s="29"/>
       <c r="F127" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G127" s="30"/>
       <c r="H127" s="30"/>
@@ -4601,7 +4598,7 @@
       <c r="D128" s="25"/>
       <c r="E128" s="29"/>
       <c r="F128" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G128" s="30"/>
       <c r="H128" s="30"/>
@@ -4615,7 +4612,7 @@
       <c r="D129" s="25"/>
       <c r="E129" s="29"/>
       <c r="F129" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G129" s="30"/>
       <c r="H129" s="30"/>
@@ -4629,7 +4626,7 @@
       <c r="D130" s="25"/>
       <c r="E130" s="29"/>
       <c r="F130" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G130" s="30"/>
       <c r="H130" s="30"/>
@@ -4643,7 +4640,7 @@
       <c r="D131" s="25"/>
       <c r="E131" s="29"/>
       <c r="F131" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G131" s="30"/>
       <c r="H131" s="30"/>
@@ -4657,7 +4654,7 @@
       <c r="D132" s="25"/>
       <c r="E132" s="29"/>
       <c r="F132" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G132" s="30"/>
       <c r="H132" s="30"/>
@@ -4671,7 +4668,7 @@
       <c r="D133" s="25"/>
       <c r="E133" s="29"/>
       <c r="F133" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G133" s="30"/>
       <c r="H133" s="30"/>
@@ -4685,7 +4682,7 @@
       <c r="D134" s="25"/>
       <c r="E134" s="29"/>
       <c r="F134" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G134" s="30"/>
       <c r="H134" s="30"/>
@@ -4699,7 +4696,7 @@
       <c r="D135" s="25"/>
       <c r="E135" s="29"/>
       <c r="F135" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G135" s="30"/>
       <c r="H135" s="30"/>
@@ -4713,7 +4710,7 @@
       <c r="D136" s="25"/>
       <c r="E136" s="29"/>
       <c r="F136" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G136" s="30"/>
       <c r="H136" s="30"/>
@@ -4727,7 +4724,7 @@
       <c r="D137" s="25"/>
       <c r="E137" s="29"/>
       <c r="F137" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G137" s="30"/>
       <c r="H137" s="30"/>
@@ -4741,7 +4738,7 @@
       <c r="D138" s="25"/>
       <c r="E138" s="29"/>
       <c r="F138" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G138" s="30"/>
       <c r="H138" s="30"/>
@@ -4755,7 +4752,7 @@
       <c r="D139" s="25"/>
       <c r="E139" s="29"/>
       <c r="F139" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G139" s="30"/>
       <c r="H139" s="30"/>
@@ -4769,7 +4766,7 @@
       <c r="D140" s="25"/>
       <c r="E140" s="29"/>
       <c r="F140" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G140" s="30"/>
       <c r="H140" s="30"/>
@@ -4783,7 +4780,7 @@
       <c r="D141" s="25"/>
       <c r="E141" s="29"/>
       <c r="F141" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G141" s="30"/>
       <c r="H141" s="30"/>
@@ -4797,7 +4794,7 @@
       <c r="D142" s="25"/>
       <c r="E142" s="29"/>
       <c r="F142" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G142" s="30"/>
       <c r="H142" s="30"/>
@@ -4811,7 +4808,7 @@
       <c r="D143" s="25"/>
       <c r="E143" s="29"/>
       <c r="F143" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G143" s="30"/>
       <c r="H143" s="30"/>
@@ -4825,7 +4822,7 @@
       <c r="D144" s="25"/>
       <c r="E144" s="29"/>
       <c r="F144" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G144" s="30"/>
       <c r="H144" s="30"/>
@@ -4839,7 +4836,7 @@
       <c r="D145" s="25"/>
       <c r="E145" s="29"/>
       <c r="F145" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G145" s="30"/>
       <c r="H145" s="30"/>
@@ -4853,7 +4850,7 @@
       <c r="D146" s="25"/>
       <c r="E146" s="29"/>
       <c r="F146" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G146" s="30"/>
       <c r="H146" s="30"/>
@@ -4867,7 +4864,7 @@
       <c r="D147" s="25"/>
       <c r="E147" s="29"/>
       <c r="F147" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G147" s="30"/>
       <c r="H147" s="30"/>
@@ -4881,7 +4878,7 @@
       <c r="D148" s="25"/>
       <c r="E148" s="29"/>
       <c r="F148" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G148" s="30"/>
       <c r="H148" s="30"/>
@@ -4895,7 +4892,7 @@
       <c r="D149" s="25"/>
       <c r="E149" s="29"/>
       <c r="F149" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G149" s="30"/>
       <c r="H149" s="30"/>
@@ -4909,7 +4906,7 @@
       <c r="D150" s="25"/>
       <c r="E150" s="29"/>
       <c r="F150" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G150" s="30"/>
       <c r="H150" s="30"/>
@@ -4923,7 +4920,7 @@
       <c r="D151" s="25"/>
       <c r="E151" s="29"/>
       <c r="F151" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G151" s="30"/>
       <c r="H151" s="30"/>
@@ -4937,7 +4934,7 @@
       <c r="D152" s="25"/>
       <c r="E152" s="29"/>
       <c r="F152" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G152" s="30"/>
       <c r="H152" s="30"/>
@@ -4951,7 +4948,7 @@
       <c r="D153" s="25"/>
       <c r="E153" s="29"/>
       <c r="F153" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G153" s="30"/>
       <c r="H153" s="30"/>
@@ -4965,7 +4962,7 @@
       <c r="D154" s="25"/>
       <c r="E154" s="29"/>
       <c r="F154" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G154" s="30"/>
       <c r="H154" s="30"/>
@@ -4979,7 +4976,7 @@
       <c r="D155" s="25"/>
       <c r="E155" s="29"/>
       <c r="F155" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G155" s="30"/>
       <c r="H155" s="30"/>
@@ -4993,7 +4990,7 @@
       <c r="D156" s="25"/>
       <c r="E156" s="29"/>
       <c r="F156" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G156" s="30"/>
       <c r="H156" s="30"/>
@@ -5007,7 +5004,7 @@
       <c r="D157" s="25"/>
       <c r="E157" s="29"/>
       <c r="F157" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G157" s="30"/>
       <c r="H157" s="30"/>
@@ -5021,7 +5018,7 @@
       <c r="D158" s="25"/>
       <c r="E158" s="29"/>
       <c r="F158" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G158" s="30"/>
       <c r="H158" s="30"/>
@@ -5035,7 +5032,7 @@
       <c r="D159" s="25"/>
       <c r="E159" s="29"/>
       <c r="F159" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G159" s="30"/>
       <c r="H159" s="30"/>
@@ -5049,7 +5046,7 @@
       <c r="D160" s="25"/>
       <c r="E160" s="29"/>
       <c r="F160" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G160" s="30"/>
       <c r="H160" s="30"/>
@@ -5063,7 +5060,7 @@
       <c r="D161" s="25"/>
       <c r="E161" s="29"/>
       <c r="F161" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G161" s="30"/>
       <c r="H161" s="30"/>
@@ -5077,7 +5074,7 @@
       <c r="D162" s="25"/>
       <c r="E162" s="29"/>
       <c r="F162" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G162" s="30"/>
       <c r="H162" s="30"/>
@@ -5091,7 +5088,7 @@
       <c r="D163" s="25"/>
       <c r="E163" s="29"/>
       <c r="F163" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G163" s="30"/>
       <c r="H163" s="30"/>
@@ -5105,7 +5102,7 @@
       <c r="D164" s="25"/>
       <c r="E164" s="29"/>
       <c r="F164" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G164" s="30"/>
       <c r="H164" s="30"/>
@@ -5119,7 +5116,7 @@
       <c r="D165" s="25"/>
       <c r="E165" s="29"/>
       <c r="F165" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G165" s="30"/>
       <c r="H165" s="30"/>
@@ -5133,7 +5130,7 @@
       <c r="D166" s="25"/>
       <c r="E166" s="29"/>
       <c r="F166" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G166" s="30"/>
       <c r="H166" s="30"/>
@@ -5147,7 +5144,7 @@
       <c r="D167" s="25"/>
       <c r="E167" s="29"/>
       <c r="F167" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G167" s="30"/>
       <c r="H167" s="30"/>
@@ -5161,7 +5158,7 @@
       <c r="D168" s="25"/>
       <c r="E168" s="29"/>
       <c r="F168" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G168" s="30"/>
       <c r="H168" s="30"/>
@@ -5175,7 +5172,7 @@
       <c r="D169" s="25"/>
       <c r="E169" s="29"/>
       <c r="F169" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G169" s="30"/>
       <c r="H169" s="30"/>
@@ -5189,7 +5186,7 @@
       <c r="D170" s="25"/>
       <c r="E170" s="29"/>
       <c r="F170" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G170" s="30"/>
       <c r="H170" s="30"/>
@@ -5203,7 +5200,7 @@
       <c r="D171" s="25"/>
       <c r="E171" s="29"/>
       <c r="F171" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G171" s="30"/>
       <c r="H171" s="30"/>
@@ -5217,7 +5214,7 @@
       <c r="D172" s="25"/>
       <c r="E172" s="29"/>
       <c r="F172" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G172" s="30"/>
       <c r="H172" s="30"/>
@@ -5231,7 +5228,7 @@
       <c r="D173" s="25"/>
       <c r="E173" s="29"/>
       <c r="F173" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G173" s="30"/>
       <c r="H173" s="30"/>
@@ -5245,7 +5242,7 @@
       <c r="D174" s="25"/>
       <c r="E174" s="29"/>
       <c r="F174" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G174" s="30"/>
       <c r="H174" s="30"/>
@@ -5259,7 +5256,7 @@
       <c r="D175" s="25"/>
       <c r="E175" s="29"/>
       <c r="F175" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G175" s="30"/>
       <c r="H175" s="30"/>
@@ -5273,7 +5270,7 @@
       <c r="D176" s="25"/>
       <c r="E176" s="29"/>
       <c r="F176" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G176" s="30"/>
       <c r="H176" s="30"/>
@@ -5287,7 +5284,7 @@
       <c r="D177" s="25"/>
       <c r="E177" s="29"/>
       <c r="F177" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G177" s="30"/>
       <c r="H177" s="30"/>
@@ -5301,7 +5298,7 @@
       <c r="D178" s="25"/>
       <c r="E178" s="29"/>
       <c r="F178" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G178" s="30"/>
       <c r="H178" s="30"/>
@@ -5315,7 +5312,7 @@
       <c r="D179" s="25"/>
       <c r="E179" s="29"/>
       <c r="F179" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G179" s="30"/>
       <c r="H179" s="30"/>
@@ -5329,7 +5326,7 @@
       <c r="D180" s="25"/>
       <c r="E180" s="29"/>
       <c r="F180" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G180" s="30"/>
       <c r="H180" s="30"/>
@@ -5343,7 +5340,7 @@
       <c r="D181" s="25"/>
       <c r="E181" s="29"/>
       <c r="F181" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G181" s="30"/>
       <c r="H181" s="30"/>
@@ -5357,7 +5354,7 @@
       <c r="D182" s="25"/>
       <c r="E182" s="29"/>
       <c r="F182" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G182" s="30"/>
       <c r="H182" s="30"/>
@@ -5371,7 +5368,7 @@
       <c r="D183" s="25"/>
       <c r="E183" s="29"/>
       <c r="F183" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G183" s="30"/>
       <c r="H183" s="30"/>
@@ -5385,7 +5382,7 @@
       <c r="D184" s="25"/>
       <c r="E184" s="29"/>
       <c r="F184" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G184" s="30"/>
       <c r="H184" s="30"/>
@@ -5399,7 +5396,7 @@
       <c r="D185" s="25"/>
       <c r="E185" s="29"/>
       <c r="F185" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G185" s="30"/>
       <c r="H185" s="30"/>
@@ -5413,7 +5410,7 @@
       <c r="D186" s="25"/>
       <c r="E186" s="29"/>
       <c r="F186" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G186" s="30"/>
       <c r="H186" s="30"/>
@@ -5427,7 +5424,7 @@
       <c r="D187" s="25"/>
       <c r="E187" s="29"/>
       <c r="F187" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G187" s="30"/>
       <c r="H187" s="30"/>
@@ -5441,7 +5438,7 @@
       <c r="D188" s="25"/>
       <c r="E188" s="29"/>
       <c r="F188" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G188" s="30"/>
       <c r="H188" s="30"/>
@@ -5455,7 +5452,7 @@
       <c r="D189" s="25"/>
       <c r="E189" s="29"/>
       <c r="F189" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G189" s="30"/>
       <c r="H189" s="30"/>
@@ -5469,7 +5466,7 @@
       <c r="D190" s="25"/>
       <c r="E190" s="29"/>
       <c r="F190" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G190" s="30"/>
       <c r="H190" s="30"/>
@@ -5483,7 +5480,7 @@
       <c r="D191" s="25"/>
       <c r="E191" s="29"/>
       <c r="F191" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G191" s="30"/>
       <c r="H191" s="30"/>
@@ -5497,7 +5494,7 @@
       <c r="D192" s="25"/>
       <c r="E192" s="29"/>
       <c r="F192" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G192" s="30"/>
       <c r="H192" s="30"/>
@@ -5511,7 +5508,7 @@
       <c r="D193" s="25"/>
       <c r="E193" s="29"/>
       <c r="F193" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G193" s="30"/>
       <c r="H193" s="30"/>
@@ -5525,7 +5522,7 @@
       <c r="D194" s="25"/>
       <c r="E194" s="29"/>
       <c r="F194" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G194" s="30"/>
       <c r="H194" s="30"/>
@@ -5539,7 +5536,7 @@
       <c r="D195" s="25"/>
       <c r="E195" s="29"/>
       <c r="F195" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G195" s="30"/>
       <c r="H195" s="30"/>
@@ -5553,7 +5550,7 @@
       <c r="D196" s="25"/>
       <c r="E196" s="29"/>
       <c r="F196" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G196" s="30"/>
       <c r="H196" s="30"/>
@@ -5567,7 +5564,7 @@
       <c r="D197" s="25"/>
       <c r="E197" s="29"/>
       <c r="F197" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G197" s="30"/>
       <c r="H197" s="30"/>
@@ -5581,7 +5578,7 @@
       <c r="D198" s="25"/>
       <c r="E198" s="29"/>
       <c r="F198" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G198" s="30"/>
       <c r="H198" s="30"/>
@@ -5595,7 +5592,7 @@
       <c r="D199" s="25"/>
       <c r="E199" s="29"/>
       <c r="F199" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G199" s="30"/>
       <c r="H199" s="30"/>
@@ -5609,7 +5606,7 @@
       <c r="D200" s="25"/>
       <c r="E200" s="29"/>
       <c r="F200" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G200" s="30"/>
       <c r="H200" s="30"/>
@@ -5623,7 +5620,7 @@
       <c r="D201" s="25"/>
       <c r="E201" s="29"/>
       <c r="F201" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G201" s="30"/>
       <c r="H201" s="30"/>
@@ -5637,7 +5634,7 @@
       <c r="D202" s="25"/>
       <c r="E202" s="29"/>
       <c r="F202" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G202" s="30"/>
       <c r="H202" s="30"/>
@@ -5651,7 +5648,7 @@
       <c r="D203" s="25"/>
       <c r="E203" s="29"/>
       <c r="F203" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G203" s="30"/>
       <c r="H203" s="30"/>
@@ -5665,7 +5662,7 @@
       <c r="D204" s="25"/>
       <c r="E204" s="29"/>
       <c r="F204" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G204" s="30"/>
       <c r="H204" s="30"/>
@@ -5679,7 +5676,7 @@
       <c r="D205" s="25"/>
       <c r="E205" s="29"/>
       <c r="F205" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G205" s="30"/>
       <c r="H205" s="30"/>
@@ -5693,7 +5690,7 @@
       <c r="D206" s="25"/>
       <c r="E206" s="29"/>
       <c r="F206" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G206" s="30"/>
       <c r="H206" s="30"/>
@@ -5707,7 +5704,7 @@
       <c r="D207" s="25"/>
       <c r="E207" s="29"/>
       <c r="F207" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G207" s="30"/>
       <c r="H207" s="30"/>
@@ -5721,7 +5718,7 @@
       <c r="D208" s="25"/>
       <c r="E208" s="29"/>
       <c r="F208" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G208" s="30"/>
       <c r="H208" s="30"/>
@@ -5735,7 +5732,7 @@
       <c r="D209" s="25"/>
       <c r="E209" s="29"/>
       <c r="F209" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G209" s="30"/>
       <c r="H209" s="30"/>
@@ -5749,7 +5746,7 @@
       <c r="D210" s="25"/>
       <c r="E210" s="29"/>
       <c r="F210" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G210" s="30"/>
       <c r="H210" s="30"/>
@@ -5763,7 +5760,7 @@
       <c r="D211" s="25"/>
       <c r="E211" s="29"/>
       <c r="F211" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G211" s="30"/>
       <c r="H211" s="30"/>
@@ -5777,7 +5774,7 @@
       <c r="D212" s="25"/>
       <c r="E212" s="29"/>
       <c r="F212" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G212" s="30"/>
       <c r="H212" s="30"/>
@@ -5791,7 +5788,7 @@
       <c r="D213" s="25"/>
       <c r="E213" s="29"/>
       <c r="F213" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G213" s="30"/>
       <c r="H213" s="30"/>
@@ -5805,7 +5802,7 @@
       <c r="D214" s="25"/>
       <c r="E214" s="29"/>
       <c r="F214" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G214" s="30"/>
       <c r="H214" s="30"/>
@@ -5819,7 +5816,7 @@
       <c r="D215" s="25"/>
       <c r="E215" s="29"/>
       <c r="F215" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G215" s="30"/>
       <c r="H215" s="30"/>
@@ -5833,7 +5830,7 @@
       <c r="D216" s="25"/>
       <c r="E216" s="29"/>
       <c r="F216" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G216" s="30"/>
       <c r="H216" s="30"/>
@@ -5847,7 +5844,7 @@
       <c r="D217" s="25"/>
       <c r="E217" s="29"/>
       <c r="F217" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G217" s="30"/>
       <c r="H217" s="30"/>
@@ -5861,7 +5858,7 @@
       <c r="D218" s="25"/>
       <c r="E218" s="29"/>
       <c r="F218" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G218" s="30"/>
       <c r="H218" s="30"/>
@@ -5875,7 +5872,7 @@
       <c r="D219" s="25"/>
       <c r="E219" s="29"/>
       <c r="F219" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G219" s="30"/>
       <c r="H219" s="30"/>
@@ -5889,7 +5886,7 @@
       <c r="D220" s="25"/>
       <c r="E220" s="29"/>
       <c r="F220" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G220" s="30"/>
       <c r="H220" s="30"/>
@@ -5903,7 +5900,7 @@
       <c r="D221" s="25"/>
       <c r="E221" s="29"/>
       <c r="F221" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G221" s="30"/>
       <c r="H221" s="30"/>
@@ -5917,7 +5914,7 @@
       <c r="D222" s="25"/>
       <c r="E222" s="29"/>
       <c r="F222" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G222" s="30"/>
       <c r="H222" s="30"/>
@@ -5931,7 +5928,7 @@
       <c r="D223" s="25"/>
       <c r="E223" s="29"/>
       <c r="F223" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G223" s="30"/>
       <c r="H223" s="30"/>
@@ -5945,7 +5942,7 @@
       <c r="D224" s="25"/>
       <c r="E224" s="29"/>
       <c r="F224" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G224" s="30"/>
       <c r="H224" s="30"/>
@@ -5959,7 +5956,7 @@
       <c r="D225" s="25"/>
       <c r="E225" s="29"/>
       <c r="F225" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G225" s="30"/>
       <c r="H225" s="30"/>
@@ -5973,7 +5970,7 @@
       <c r="D226" s="25"/>
       <c r="E226" s="29"/>
       <c r="F226" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G226" s="30"/>
       <c r="H226" s="30"/>
@@ -5987,7 +5984,7 @@
       <c r="D227" s="25"/>
       <c r="E227" s="29"/>
       <c r="F227" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G227" s="30"/>
       <c r="H227" s="30"/>
@@ -6001,7 +5998,7 @@
       <c r="D228" s="25"/>
       <c r="E228" s="29"/>
       <c r="F228" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G228" s="30"/>
       <c r="H228" s="30"/>
@@ -6015,7 +6012,7 @@
       <c r="D229" s="25"/>
       <c r="E229" s="29"/>
       <c r="F229" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G229" s="30"/>
       <c r="H229" s="30"/>
@@ -6029,7 +6026,7 @@
       <c r="D230" s="25"/>
       <c r="E230" s="29"/>
       <c r="F230" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G230" s="30"/>
       <c r="H230" s="30"/>
@@ -6043,7 +6040,7 @@
       <c r="D231" s="25"/>
       <c r="E231" s="29"/>
       <c r="F231" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G231" s="30"/>
       <c r="H231" s="30"/>
@@ -6057,7 +6054,7 @@
       <c r="D232" s="25"/>
       <c r="E232" s="29"/>
       <c r="F232" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G232" s="30"/>
       <c r="H232" s="30"/>
@@ -6071,7 +6068,7 @@
       <c r="D233" s="25"/>
       <c r="E233" s="29"/>
       <c r="F233" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G233" s="30"/>
       <c r="H233" s="30"/>
@@ -6085,7 +6082,7 @@
       <c r="D234" s="25"/>
       <c r="E234" s="29"/>
       <c r="F234" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G234" s="30"/>
       <c r="H234" s="30"/>
@@ -6099,7 +6096,7 @@
       <c r="D235" s="25"/>
       <c r="E235" s="29"/>
       <c r="F235" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G235" s="30"/>
       <c r="H235" s="30"/>
@@ -6113,7 +6110,7 @@
       <c r="D236" s="25"/>
       <c r="E236" s="29"/>
       <c r="F236" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G236" s="30"/>
       <c r="H236" s="30"/>
@@ -6127,7 +6124,7 @@
       <c r="D237" s="25"/>
       <c r="E237" s="29"/>
       <c r="F237" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G237" s="30"/>
       <c r="H237" s="30"/>
@@ -6141,7 +6138,7 @@
       <c r="D238" s="25"/>
       <c r="E238" s="29"/>
       <c r="F238" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G238" s="30"/>
       <c r="H238" s="30"/>
@@ -6155,7 +6152,7 @@
       <c r="D239" s="25"/>
       <c r="E239" s="29"/>
       <c r="F239" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G239" s="30"/>
       <c r="H239" s="30"/>
@@ -6169,7 +6166,7 @@
       <c r="D240" s="25"/>
       <c r="E240" s="29"/>
       <c r="F240" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G240" s="30"/>
       <c r="H240" s="30"/>
@@ -6183,7 +6180,7 @@
       <c r="D241" s="25"/>
       <c r="E241" s="29"/>
       <c r="F241" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G241" s="30"/>
       <c r="H241" s="30"/>
@@ -6197,7 +6194,7 @@
       <c r="D242" s="25"/>
       <c r="E242" s="29"/>
       <c r="F242" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G242" s="30"/>
       <c r="H242" s="30"/>
@@ -6211,7 +6208,7 @@
       <c r="D243" s="25"/>
       <c r="E243" s="29"/>
       <c r="F243" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G243" s="30"/>
       <c r="H243" s="30"/>
@@ -6225,7 +6222,7 @@
       <c r="D244" s="25"/>
       <c r="E244" s="29"/>
       <c r="F244" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G244" s="30"/>
       <c r="H244" s="30"/>
@@ -6239,7 +6236,7 @@
       <c r="D245" s="25"/>
       <c r="E245" s="29"/>
       <c r="F245" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G245" s="30"/>
       <c r="H245" s="30"/>
@@ -6253,7 +6250,7 @@
       <c r="D246" s="25"/>
       <c r="E246" s="29"/>
       <c r="F246" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G246" s="30"/>
       <c r="H246" s="30"/>
@@ -6267,7 +6264,7 @@
       <c r="D247" s="25"/>
       <c r="E247" s="29"/>
       <c r="F247" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G247" s="30"/>
       <c r="H247" s="30"/>
@@ -6281,7 +6278,7 @@
       <c r="D248" s="25"/>
       <c r="E248" s="29"/>
       <c r="F248" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G248" s="30"/>
       <c r="H248" s="30"/>
@@ -6295,7 +6292,7 @@
       <c r="D249" s="25"/>
       <c r="E249" s="29"/>
       <c r="F249" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G249" s="30"/>
       <c r="H249" s="30"/>
@@ -6309,7 +6306,7 @@
       <c r="D250" s="25"/>
       <c r="E250" s="29"/>
       <c r="F250" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G250" s="30"/>
       <c r="H250" s="30"/>
@@ -6323,7 +6320,7 @@
       <c r="D251" s="25"/>
       <c r="E251" s="29"/>
       <c r="F251" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G251" s="30"/>
       <c r="H251" s="30"/>
@@ -6337,7 +6334,7 @@
       <c r="D252" s="25"/>
       <c r="E252" s="29"/>
       <c r="F252" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G252" s="30"/>
       <c r="H252" s="30"/>
@@ -6351,7 +6348,7 @@
       <c r="D253" s="25"/>
       <c r="E253" s="29"/>
       <c r="F253" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G253" s="30"/>
       <c r="H253" s="30"/>
@@ -6365,7 +6362,7 @@
       <c r="D254" s="25"/>
       <c r="E254" s="29"/>
       <c r="F254" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G254" s="30"/>
       <c r="H254" s="30"/>
@@ -6379,7 +6376,7 @@
       <c r="D255" s="25"/>
       <c r="E255" s="29"/>
       <c r="F255" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G255" s="30"/>
       <c r="H255" s="30"/>
@@ -6393,7 +6390,7 @@
       <c r="D256" s="25"/>
       <c r="E256" s="29"/>
       <c r="F256" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G256" s="30"/>
       <c r="H256" s="30"/>
@@ -6407,7 +6404,7 @@
       <c r="D257" s="25"/>
       <c r="E257" s="29"/>
       <c r="F257" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G257" s="30"/>
       <c r="H257" s="30"/>
@@ -6421,7 +6418,7 @@
       <c r="D258" s="25"/>
       <c r="E258" s="29"/>
       <c r="F258" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G258" s="30"/>
       <c r="H258" s="30"/>
@@ -6435,7 +6432,7 @@
       <c r="D259" s="25"/>
       <c r="E259" s="29"/>
       <c r="F259" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G259" s="30"/>
       <c r="H259" s="30"/>
@@ -6449,7 +6446,7 @@
       <c r="D260" s="25"/>
       <c r="E260" s="29"/>
       <c r="F260" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G260" s="30"/>
       <c r="H260" s="30"/>
@@ -6463,7 +6460,7 @@
       <c r="D261" s="25"/>
       <c r="E261" s="29"/>
       <c r="F261" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G261" s="30"/>
       <c r="H261" s="30"/>
@@ -6477,7 +6474,7 @@
       <c r="D262" s="25"/>
       <c r="E262" s="29"/>
       <c r="F262" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G262" s="30"/>
       <c r="H262" s="30"/>
@@ -6491,7 +6488,7 @@
       <c r="D263" s="25"/>
       <c r="E263" s="29"/>
       <c r="F263" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G263" s="30"/>
       <c r="H263" s="30"/>
@@ -6505,7 +6502,7 @@
       <c r="D264" s="25"/>
       <c r="E264" s="29"/>
       <c r="F264" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G264" s="30"/>
       <c r="H264" s="30"/>
@@ -6519,7 +6516,7 @@
       <c r="D265" s="25"/>
       <c r="E265" s="29"/>
       <c r="F265" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G265" s="30"/>
       <c r="H265" s="30"/>
@@ -6533,7 +6530,7 @@
       <c r="D266" s="25"/>
       <c r="E266" s="29"/>
       <c r="F266" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G266" s="30"/>
       <c r="H266" s="30"/>
@@ -6547,7 +6544,7 @@
       <c r="D267" s="25"/>
       <c r="E267" s="29"/>
       <c r="F267" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G267" s="30"/>
       <c r="H267" s="30"/>
@@ -6561,7 +6558,7 @@
       <c r="D268" s="25"/>
       <c r="E268" s="29"/>
       <c r="F268" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G268" s="30"/>
       <c r="H268" s="30"/>
@@ -6575,7 +6572,7 @@
       <c r="D269" s="25"/>
       <c r="E269" s="29"/>
       <c r="F269" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G269" s="30"/>
       <c r="H269" s="30"/>
@@ -6589,7 +6586,7 @@
       <c r="D270" s="25"/>
       <c r="E270" s="29"/>
       <c r="F270" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G270" s="30"/>
       <c r="H270" s="30"/>
@@ -6603,7 +6600,7 @@
       <c r="D271" s="25"/>
       <c r="E271" s="29"/>
       <c r="F271" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G271" s="30"/>
       <c r="H271" s="30"/>
@@ -6617,7 +6614,7 @@
       <c r="D272" s="25"/>
       <c r="E272" s="29"/>
       <c r="F272" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G272" s="30"/>
       <c r="H272" s="30"/>
@@ -6631,7 +6628,7 @@
       <c r="D273" s="25"/>
       <c r="E273" s="29"/>
       <c r="F273" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G273" s="30"/>
       <c r="H273" s="30"/>
@@ -6645,7 +6642,7 @@
       <c r="D274" s="25"/>
       <c r="E274" s="29"/>
       <c r="F274" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G274" s="30"/>
       <c r="H274" s="30"/>
@@ -6659,7 +6656,7 @@
       <c r="D275" s="25"/>
       <c r="E275" s="29"/>
       <c r="F275" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G275" s="30"/>
       <c r="H275" s="30"/>
@@ -6673,7 +6670,7 @@
       <c r="D276" s="25"/>
       <c r="E276" s="29"/>
       <c r="F276" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G276" s="30"/>
       <c r="H276" s="30"/>
@@ -6687,7 +6684,7 @@
       <c r="D277" s="25"/>
       <c r="E277" s="29"/>
       <c r="F277" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G277" s="30"/>
       <c r="H277" s="30"/>
@@ -6701,7 +6698,7 @@
       <c r="D278" s="25"/>
       <c r="E278" s="29"/>
       <c r="F278" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G278" s="30"/>
       <c r="H278" s="30"/>
@@ -6715,7 +6712,7 @@
       <c r="D279" s="25"/>
       <c r="E279" s="29"/>
       <c r="F279" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G279" s="30"/>
       <c r="H279" s="30"/>
@@ -6729,7 +6726,7 @@
       <c r="D280" s="25"/>
       <c r="E280" s="29"/>
       <c r="F280" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G280" s="30"/>
       <c r="H280" s="30"/>
@@ -6743,7 +6740,7 @@
       <c r="D281" s="25"/>
       <c r="E281" s="29"/>
       <c r="F281" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G281" s="30"/>
       <c r="H281" s="30"/>
@@ -6757,7 +6754,7 @@
       <c r="D282" s="25"/>
       <c r="E282" s="29"/>
       <c r="F282" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G282" s="30"/>
       <c r="H282" s="30"/>
@@ -6771,7 +6768,7 @@
       <c r="D283" s="25"/>
       <c r="E283" s="29"/>
       <c r="F283" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G283" s="30"/>
       <c r="H283" s="30"/>
@@ -6785,7 +6782,7 @@
       <c r="D284" s="25"/>
       <c r="E284" s="29"/>
       <c r="F284" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G284" s="30"/>
       <c r="H284" s="30"/>
@@ -6799,7 +6796,7 @@
       <c r="D285" s="25"/>
       <c r="E285" s="29"/>
       <c r="F285" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G285" s="30"/>
       <c r="H285" s="30"/>
@@ -6813,7 +6810,7 @@
       <c r="D286" s="25"/>
       <c r="E286" s="29"/>
       <c r="F286" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G286" s="30"/>
       <c r="H286" s="30"/>
@@ -6827,7 +6824,7 @@
       <c r="D287" s="25"/>
       <c r="E287" s="29"/>
       <c r="F287" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G287" s="30"/>
       <c r="H287" s="30"/>
@@ -6841,7 +6838,7 @@
       <c r="D288" s="25"/>
       <c r="E288" s="29"/>
       <c r="F288" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G288" s="30"/>
       <c r="H288" s="30"/>
@@ -6855,7 +6852,7 @@
       <c r="D289" s="25"/>
       <c r="E289" s="29"/>
       <c r="F289" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G289" s="30"/>
       <c r="H289" s="30"/>
@@ -6869,7 +6866,7 @@
       <c r="D290" s="25"/>
       <c r="E290" s="29"/>
       <c r="F290" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G290" s="30"/>
       <c r="H290" s="30"/>
@@ -6883,7 +6880,7 @@
       <c r="D291" s="25"/>
       <c r="E291" s="29"/>
       <c r="F291" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G291" s="30"/>
       <c r="H291" s="30"/>
@@ -6897,7 +6894,7 @@
       <c r="D292" s="25"/>
       <c r="E292" s="29"/>
       <c r="F292" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G292" s="30"/>
       <c r="H292" s="30"/>
@@ -6911,7 +6908,7 @@
       <c r="D293" s="25"/>
       <c r="E293" s="29"/>
       <c r="F293" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G293" s="30"/>
       <c r="H293" s="30"/>
@@ -6925,7 +6922,7 @@
       <c r="D294" s="25"/>
       <c r="E294" s="29"/>
       <c r="F294" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G294" s="30"/>
       <c r="H294" s="30"/>
@@ -6939,7 +6936,7 @@
       <c r="D295" s="25"/>
       <c r="E295" s="29"/>
       <c r="F295" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G295" s="30"/>
       <c r="H295" s="30"/>
@@ -6953,7 +6950,7 @@
       <c r="D296" s="25"/>
       <c r="E296" s="29"/>
       <c r="F296" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G296" s="30"/>
       <c r="H296" s="30"/>
@@ -6967,7 +6964,7 @@
       <c r="D297" s="25"/>
       <c r="E297" s="29"/>
       <c r="F297" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G297" s="30"/>
       <c r="H297" s="30"/>
@@ -6981,7 +6978,7 @@
       <c r="D298" s="25"/>
       <c r="E298" s="29"/>
       <c r="F298" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G298" s="30"/>
       <c r="H298" s="30"/>
@@ -6995,7 +6992,7 @@
       <c r="D299" s="25"/>
       <c r="E299" s="29"/>
       <c r="F299" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G299" s="30"/>
       <c r="H299" s="30"/>
@@ -7009,7 +7006,7 @@
       <c r="D300" s="25"/>
       <c r="E300" s="29"/>
       <c r="F300" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G300" s="30"/>
       <c r="H300" s="30"/>
@@ -7023,7 +7020,7 @@
       <c r="D301" s="25"/>
       <c r="E301" s="29"/>
       <c r="F301" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G301" s="30"/>
       <c r="H301" s="30"/>
@@ -7037,7 +7034,7 @@
       <c r="D302" s="25"/>
       <c r="E302" s="29"/>
       <c r="F302" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G302" s="30"/>
       <c r="H302" s="30"/>
@@ -7051,7 +7048,7 @@
       <c r="D303" s="25"/>
       <c r="E303" s="29"/>
       <c r="F303" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G303" s="30"/>
       <c r="H303" s="30"/>
@@ -7065,7 +7062,7 @@
       <c r="D304" s="25"/>
       <c r="E304" s="29"/>
       <c r="F304" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G304" s="30"/>
       <c r="H304" s="30"/>
@@ -7079,7 +7076,7 @@
       <c r="D305" s="25"/>
       <c r="E305" s="29"/>
       <c r="F305" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G305" s="30"/>
       <c r="H305" s="30"/>
@@ -7093,7 +7090,7 @@
       <c r="D306" s="25"/>
       <c r="E306" s="29"/>
       <c r="F306" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G306" s="30"/>
       <c r="H306" s="30"/>
@@ -7107,7 +7104,7 @@
       <c r="D307" s="25"/>
       <c r="E307" s="29"/>
       <c r="F307" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G307" s="30"/>
       <c r="H307" s="30"/>
@@ -7121,7 +7118,7 @@
       <c r="D308" s="25"/>
       <c r="E308" s="29"/>
       <c r="F308" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G308" s="30"/>
       <c r="H308" s="30"/>
@@ -7135,7 +7132,7 @@
       <c r="D309" s="25"/>
       <c r="E309" s="29"/>
       <c r="F309" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G309" s="30"/>
       <c r="H309" s="30"/>
@@ -7149,7 +7146,7 @@
       <c r="D310" s="25"/>
       <c r="E310" s="29"/>
       <c r="F310" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G310" s="30"/>
       <c r="H310" s="30"/>
@@ -7163,7 +7160,7 @@
       <c r="D311" s="25"/>
       <c r="E311" s="29"/>
       <c r="F311" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G311" s="30"/>
       <c r="H311" s="30"/>
@@ -7177,7 +7174,7 @@
       <c r="D312" s="25"/>
       <c r="E312" s="29"/>
       <c r="F312" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G312" s="30"/>
       <c r="H312" s="30"/>
@@ -7191,7 +7188,7 @@
       <c r="D313" s="25"/>
       <c r="E313" s="29"/>
       <c r="F313" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G313" s="30"/>
       <c r="H313" s="30"/>
@@ -7205,7 +7202,7 @@
       <c r="D314" s="25"/>
       <c r="E314" s="29"/>
       <c r="F314" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G314" s="30"/>
       <c r="H314" s="30"/>
@@ -7219,7 +7216,7 @@
       <c r="D315" s="25"/>
       <c r="E315" s="29"/>
       <c r="F315" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G315" s="30"/>
       <c r="H315" s="30"/>
@@ -7233,7 +7230,7 @@
       <c r="D316" s="25"/>
       <c r="E316" s="29"/>
       <c r="F316" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G316" s="30"/>
       <c r="H316" s="30"/>
@@ -7247,7 +7244,7 @@
       <c r="D317" s="25"/>
       <c r="E317" s="29"/>
       <c r="F317" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G317" s="30"/>
       <c r="H317" s="30"/>
@@ -7261,7 +7258,7 @@
       <c r="D318" s="25"/>
       <c r="E318" s="29"/>
       <c r="F318" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G318" s="30"/>
       <c r="H318" s="30"/>
@@ -7275,7 +7272,7 @@
       <c r="D319" s="25"/>
       <c r="E319" s="29"/>
       <c r="F319" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G319" s="30"/>
       <c r="H319" s="30"/>
@@ -7289,7 +7286,7 @@
       <c r="D320" s="25"/>
       <c r="E320" s="29"/>
       <c r="F320" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G320" s="30"/>
       <c r="H320" s="30"/>
@@ -7303,7 +7300,7 @@
       <c r="D321" s="25"/>
       <c r="E321" s="29"/>
       <c r="F321" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G321" s="30"/>
       <c r="H321" s="30"/>
@@ -7317,7 +7314,7 @@
       <c r="D322" s="25"/>
       <c r="E322" s="29"/>
       <c r="F322" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G322" s="30"/>
       <c r="H322" s="30"/>
@@ -7331,7 +7328,7 @@
       <c r="D323" s="25"/>
       <c r="E323" s="29"/>
       <c r="F323" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G323" s="30"/>
       <c r="H323" s="30"/>
@@ -7345,7 +7342,7 @@
       <c r="D324" s="25"/>
       <c r="E324" s="29"/>
       <c r="F324" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G324" s="30"/>
       <c r="H324" s="30"/>
@@ -7359,7 +7356,7 @@
       <c r="D325" s="25"/>
       <c r="E325" s="29"/>
       <c r="F325" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G325" s="30"/>
       <c r="H325" s="30"/>
@@ -7373,7 +7370,7 @@
       <c r="D326" s="25"/>
       <c r="E326" s="29"/>
       <c r="F326" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G326" s="30"/>
       <c r="H326" s="30"/>
@@ -7387,7 +7384,7 @@
       <c r="D327" s="25"/>
       <c r="E327" s="29"/>
       <c r="F327" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G327" s="30"/>
       <c r="H327" s="30"/>
@@ -7401,7 +7398,7 @@
       <c r="D328" s="25"/>
       <c r="E328" s="29"/>
       <c r="F328" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G328" s="30"/>
       <c r="H328" s="30"/>
@@ -7415,7 +7412,7 @@
       <c r="D329" s="25"/>
       <c r="E329" s="29"/>
       <c r="F329" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G329" s="30"/>
       <c r="H329" s="30"/>
@@ -7429,7 +7426,7 @@
       <c r="D330" s="25"/>
       <c r="E330" s="29"/>
       <c r="F330" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G330" s="30"/>
       <c r="H330" s="30"/>
@@ -7443,7 +7440,7 @@
       <c r="D331" s="25"/>
       <c r="E331" s="29"/>
       <c r="F331" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G331" s="30"/>
       <c r="H331" s="30"/>
@@ -7457,7 +7454,7 @@
       <c r="D332" s="25"/>
       <c r="E332" s="29"/>
       <c r="F332" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G332" s="30"/>
       <c r="H332" s="30"/>
@@ -7471,7 +7468,7 @@
       <c r="D333" s="25"/>
       <c r="E333" s="29"/>
       <c r="F333" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G333" s="30"/>
       <c r="H333" s="30"/>
@@ -7485,7 +7482,7 @@
       <c r="D334" s="25"/>
       <c r="E334" s="29"/>
       <c r="F334" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G334" s="30"/>
       <c r="H334" s="30"/>
@@ -7499,7 +7496,7 @@
       <c r="D335" s="25"/>
       <c r="E335" s="29"/>
       <c r="F335" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G335" s="30"/>
       <c r="H335" s="30"/>
@@ -7513,7 +7510,7 @@
       <c r="D336" s="25"/>
       <c r="E336" s="29"/>
       <c r="F336" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G336" s="30"/>
       <c r="H336" s="30"/>
@@ -7527,7 +7524,7 @@
       <c r="D337" s="25"/>
       <c r="E337" s="29"/>
       <c r="F337" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G337" s="30"/>
       <c r="H337" s="30"/>
@@ -7541,7 +7538,7 @@
       <c r="D338" s="25"/>
       <c r="E338" s="29"/>
       <c r="F338" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G338" s="30"/>
       <c r="H338" s="30"/>
@@ -7555,7 +7552,7 @@
       <c r="D339" s="25"/>
       <c r="E339" s="29"/>
       <c r="F339" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G339" s="30"/>
       <c r="H339" s="30"/>
@@ -7569,7 +7566,7 @@
       <c r="D340" s="25"/>
       <c r="E340" s="29"/>
       <c r="F340" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G340" s="30"/>
       <c r="H340" s="30"/>
@@ -7583,7 +7580,7 @@
       <c r="D341" s="25"/>
       <c r="E341" s="29"/>
       <c r="F341" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G341" s="30"/>
       <c r="H341" s="30"/>
@@ -7597,7 +7594,7 @@
       <c r="D342" s="25"/>
       <c r="E342" s="29"/>
       <c r="F342" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G342" s="30"/>
       <c r="H342" s="30"/>
@@ -7611,7 +7608,7 @@
       <c r="D343" s="25"/>
       <c r="E343" s="29"/>
       <c r="F343" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G343" s="30"/>
       <c r="H343" s="30"/>
@@ -7625,7 +7622,7 @@
       <c r="D344" s="25"/>
       <c r="E344" s="29"/>
       <c r="F344" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G344" s="30"/>
       <c r="H344" s="30"/>
@@ -7639,7 +7636,7 @@
       <c r="D345" s="25"/>
       <c r="E345" s="29"/>
       <c r="F345" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G345" s="30"/>
       <c r="H345" s="30"/>
@@ -7653,7 +7650,7 @@
       <c r="D346" s="25"/>
       <c r="E346" s="29"/>
       <c r="F346" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G346" s="30"/>
       <c r="H346" s="30"/>
@@ -7667,7 +7664,7 @@
       <c r="D347" s="25"/>
       <c r="E347" s="29"/>
       <c r="F347" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G347" s="30"/>
       <c r="H347" s="30"/>
@@ -7681,7 +7678,7 @@
       <c r="D348" s="25"/>
       <c r="E348" s="29"/>
       <c r="F348" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G348" s="30"/>
       <c r="H348" s="30"/>
@@ -7695,7 +7692,7 @@
       <c r="D349" s="25"/>
       <c r="E349" s="29"/>
       <c r="F349" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G349" s="30"/>
       <c r="H349" s="30"/>
@@ -7709,7 +7706,7 @@
       <c r="D350" s="25"/>
       <c r="E350" s="29"/>
       <c r="F350" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G350" s="30"/>
       <c r="H350" s="30"/>
@@ -7723,7 +7720,7 @@
       <c r="D351" s="25"/>
       <c r="E351" s="29"/>
       <c r="F351" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G351" s="30"/>
       <c r="H351" s="30"/>
@@ -7737,7 +7734,7 @@
       <c r="D352" s="25"/>
       <c r="E352" s="29"/>
       <c r="F352" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G352" s="30"/>
       <c r="H352" s="30"/>
@@ -7751,7 +7748,7 @@
       <c r="D353" s="25"/>
       <c r="E353" s="29"/>
       <c r="F353" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G353" s="30"/>
       <c r="H353" s="30"/>
@@ -7765,7 +7762,7 @@
       <c r="D354" s="25"/>
       <c r="E354" s="29"/>
       <c r="F354" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G354" s="30"/>
       <c r="H354" s="30"/>
@@ -7779,7 +7776,7 @@
       <c r="D355" s="25"/>
       <c r="E355" s="29"/>
       <c r="F355" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G355" s="30"/>
       <c r="H355" s="30"/>
@@ -7793,7 +7790,7 @@
       <c r="D356" s="25"/>
       <c r="E356" s="29"/>
       <c r="F356" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G356" s="30"/>
       <c r="H356" s="30"/>
@@ -7807,7 +7804,7 @@
       <c r="D357" s="25"/>
       <c r="E357" s="29"/>
       <c r="F357" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G357" s="30"/>
       <c r="H357" s="30"/>
@@ -7821,7 +7818,7 @@
       <c r="D358" s="25"/>
       <c r="E358" s="29"/>
       <c r="F358" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G358" s="30"/>
       <c r="H358" s="30"/>
@@ -7835,7 +7832,7 @@
       <c r="D359" s="25"/>
       <c r="E359" s="29"/>
       <c r="F359" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G359" s="30"/>
       <c r="H359" s="30"/>
@@ -7849,7 +7846,7 @@
       <c r="D360" s="25"/>
       <c r="E360" s="29"/>
       <c r="F360" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G360" s="30"/>
       <c r="H360" s="30"/>
@@ -7863,7 +7860,7 @@
       <c r="D361" s="25"/>
       <c r="E361" s="29"/>
       <c r="F361" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G361" s="30"/>
       <c r="H361" s="30"/>
@@ -7877,7 +7874,7 @@
       <c r="D362" s="25"/>
       <c r="E362" s="29"/>
       <c r="F362" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G362" s="30"/>
       <c r="H362" s="30"/>
@@ -7891,7 +7888,7 @@
       <c r="D363" s="25"/>
       <c r="E363" s="29"/>
       <c r="F363" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G363" s="30"/>
       <c r="H363" s="30"/>
@@ -7905,7 +7902,7 @@
       <c r="D364" s="25"/>
       <c r="E364" s="29"/>
       <c r="F364" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G364" s="30"/>
       <c r="H364" s="30"/>
@@ -7919,7 +7916,7 @@
       <c r="D365" s="25"/>
       <c r="E365" s="29"/>
       <c r="F365" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G365" s="30"/>
       <c r="H365" s="30"/>
@@ -7933,7 +7930,7 @@
       <c r="D366" s="25"/>
       <c r="E366" s="29"/>
       <c r="F366" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G366" s="30"/>
       <c r="H366" s="30"/>
@@ -7947,7 +7944,7 @@
       <c r="D367" s="25"/>
       <c r="E367" s="29"/>
       <c r="F367" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G367" s="30"/>
       <c r="H367" s="30"/>
@@ -7961,7 +7958,7 @@
       <c r="D368" s="25"/>
       <c r="E368" s="29"/>
       <c r="F368" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G368" s="30"/>
       <c r="H368" s="30"/>
@@ -7975,7 +7972,7 @@
       <c r="D369" s="25"/>
       <c r="E369" s="29"/>
       <c r="F369" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G369" s="30"/>
       <c r="H369" s="30"/>
@@ -7989,7 +7986,7 @@
       <c r="D370" s="25"/>
       <c r="E370" s="29"/>
       <c r="F370" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G370" s="30"/>
       <c r="H370" s="30"/>
@@ -8003,7 +8000,7 @@
       <c r="D371" s="25"/>
       <c r="E371" s="29"/>
       <c r="F371" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G371" s="30"/>
       <c r="H371" s="30"/>
@@ -8017,7 +8014,7 @@
       <c r="D372" s="25"/>
       <c r="E372" s="29"/>
       <c r="F372" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G372" s="30"/>
       <c r="H372" s="30"/>
@@ -8031,7 +8028,7 @@
       <c r="D373" s="25"/>
       <c r="E373" s="29"/>
       <c r="F373" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G373" s="30"/>
       <c r="H373" s="30"/>
@@ -8045,7 +8042,7 @@
       <c r="D374" s="25"/>
       <c r="E374" s="29"/>
       <c r="F374" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G374" s="30"/>
       <c r="H374" s="30"/>
@@ -8059,7 +8056,7 @@
       <c r="D375" s="25"/>
       <c r="E375" s="29"/>
       <c r="F375" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G375" s="30"/>
       <c r="H375" s="30"/>
@@ -8073,7 +8070,7 @@
       <c r="D376" s="25"/>
       <c r="E376" s="29"/>
       <c r="F376" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G376" s="30"/>
       <c r="H376" s="30"/>
@@ -8087,7 +8084,7 @@
       <c r="D377" s="25"/>
       <c r="E377" s="29"/>
       <c r="F377" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G377" s="30"/>
       <c r="H377" s="30"/>
@@ -8101,7 +8098,7 @@
       <c r="D378" s="25"/>
       <c r="E378" s="29"/>
       <c r="F378" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G378" s="30"/>
       <c r="H378" s="30"/>
@@ -8115,7 +8112,7 @@
       <c r="D379" s="25"/>
       <c r="E379" s="29"/>
       <c r="F379" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G379" s="30"/>
       <c r="H379" s="30"/>
@@ -8129,7 +8126,7 @@
       <c r="D380" s="25"/>
       <c r="E380" s="29"/>
       <c r="F380" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G380" s="30"/>
       <c r="H380" s="30"/>
@@ -8143,7 +8140,7 @@
       <c r="D381" s="25"/>
       <c r="E381" s="29"/>
       <c r="F381" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G381" s="30"/>
       <c r="H381" s="30"/>
@@ -8157,7 +8154,7 @@
       <c r="D382" s="25"/>
       <c r="E382" s="29"/>
       <c r="F382" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G382" s="30"/>
       <c r="H382" s="30"/>
@@ -8171,7 +8168,7 @@
       <c r="D383" s="25"/>
       <c r="E383" s="29"/>
       <c r="F383" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G383" s="30"/>
       <c r="H383" s="30"/>
@@ -8185,7 +8182,7 @@
       <c r="D384" s="25"/>
       <c r="E384" s="29"/>
       <c r="F384" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G384" s="30"/>
       <c r="H384" s="30"/>
@@ -8199,7 +8196,7 @@
       <c r="D385" s="25"/>
       <c r="E385" s="29"/>
       <c r="F385" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G385" s="30"/>
       <c r="H385" s="30"/>
@@ -8213,7 +8210,7 @@
       <c r="D386" s="25"/>
       <c r="E386" s="29"/>
       <c r="F386" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G386" s="30"/>
       <c r="H386" s="30"/>
@@ -8227,7 +8224,7 @@
       <c r="D387" s="25"/>
       <c r="E387" s="29"/>
       <c r="F387" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G387" s="30"/>
       <c r="H387" s="30"/>
@@ -8241,7 +8238,7 @@
       <c r="D388" s="25"/>
       <c r="E388" s="29"/>
       <c r="F388" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G388" s="30"/>
       <c r="H388" s="30"/>
@@ -8255,7 +8252,7 @@
       <c r="D389" s="25"/>
       <c r="E389" s="29"/>
       <c r="F389" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G389" s="30"/>
       <c r="H389" s="30"/>
@@ -8269,7 +8266,7 @@
       <c r="D390" s="25"/>
       <c r="E390" s="29"/>
       <c r="F390" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G390" s="30"/>
       <c r="H390" s="30"/>
@@ -8283,7 +8280,7 @@
       <c r="D391" s="25"/>
       <c r="E391" s="29"/>
       <c r="F391" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G391" s="30"/>
       <c r="H391" s="30"/>
@@ -8297,7 +8294,7 @@
       <c r="D392" s="25"/>
       <c r="E392" s="29"/>
       <c r="F392" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G392" s="30"/>
       <c r="H392" s="30"/>
@@ -8311,7 +8308,7 @@
       <c r="D393" s="25"/>
       <c r="E393" s="29"/>
       <c r="F393" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G393" s="30"/>
       <c r="H393" s="30"/>
@@ -8325,7 +8322,7 @@
       <c r="D394" s="25"/>
       <c r="E394" s="29"/>
       <c r="F394" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G394" s="30"/>
       <c r="H394" s="30"/>
@@ -8339,7 +8336,7 @@
       <c r="D395" s="25"/>
       <c r="E395" s="29"/>
       <c r="F395" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G395" s="30"/>
       <c r="H395" s="30"/>
@@ -8353,7 +8350,7 @@
       <c r="D396" s="25"/>
       <c r="E396" s="29"/>
       <c r="F396" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G396" s="30"/>
       <c r="H396" s="30"/>
@@ -8367,7 +8364,7 @@
       <c r="D397" s="25"/>
       <c r="E397" s="29"/>
       <c r="F397" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G397" s="30"/>
       <c r="H397" s="30"/>
@@ -8381,7 +8378,7 @@
       <c r="D398" s="25"/>
       <c r="E398" s="29"/>
       <c r="F398" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G398" s="30"/>
       <c r="H398" s="30"/>
@@ -8395,7 +8392,7 @@
       <c r="D399" s="25"/>
       <c r="E399" s="29"/>
       <c r="F399" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G399" s="30"/>
       <c r="H399" s="30"/>
@@ -8409,7 +8406,7 @@
       <c r="D400" s="25"/>
       <c r="E400" s="29"/>
       <c r="F400" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G400" s="30"/>
       <c r="H400" s="30"/>
@@ -8423,7 +8420,7 @@
       <c r="D401" s="25"/>
       <c r="E401" s="29"/>
       <c r="F401" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G401" s="30"/>
       <c r="H401" s="30"/>
@@ -8437,7 +8434,7 @@
       <c r="D402" s="25"/>
       <c r="E402" s="29"/>
       <c r="F402" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G402" s="30"/>
       <c r="H402" s="30"/>
@@ -8451,7 +8448,7 @@
       <c r="D403" s="25"/>
       <c r="E403" s="29"/>
       <c r="F403" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G403" s="30"/>
       <c r="H403" s="30"/>
@@ -8465,7 +8462,7 @@
       <c r="D404" s="25"/>
       <c r="E404" s="29"/>
       <c r="F404" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G404" s="30"/>
       <c r="H404" s="30"/>
@@ -8479,7 +8476,7 @@
       <c r="D405" s="25"/>
       <c r="E405" s="29"/>
       <c r="F405" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G405" s="30"/>
       <c r="H405" s="30"/>
@@ -8493,7 +8490,7 @@
       <c r="D406" s="25"/>
       <c r="E406" s="29"/>
       <c r="F406" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G406" s="30"/>
       <c r="H406" s="30"/>
@@ -8507,7 +8504,7 @@
       <c r="D407" s="25"/>
       <c r="E407" s="29"/>
       <c r="F407" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G407" s="30"/>
       <c r="H407" s="30"/>
@@ -8521,7 +8518,7 @@
       <c r="D408" s="25"/>
       <c r="E408" s="29"/>
       <c r="F408" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G408" s="30"/>
       <c r="H408" s="30"/>
@@ -8535,7 +8532,7 @@
       <c r="D409" s="25"/>
       <c r="E409" s="29"/>
       <c r="F409" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G409" s="30"/>
       <c r="H409" s="30"/>
@@ -8549,7 +8546,7 @@
       <c r="D410" s="25"/>
       <c r="E410" s="29"/>
       <c r="F410" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G410" s="30"/>
       <c r="H410" s="30"/>
@@ -8563,7 +8560,7 @@
       <c r="D411" s="25"/>
       <c r="E411" s="29"/>
       <c r="F411" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G411" s="30"/>
       <c r="H411" s="30"/>
@@ -8577,7 +8574,7 @@
       <c r="D412" s="25"/>
       <c r="E412" s="29"/>
       <c r="F412" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G412" s="30"/>
       <c r="H412" s="30"/>
@@ -8591,7 +8588,7 @@
       <c r="D413" s="25"/>
       <c r="E413" s="29"/>
       <c r="F413" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G413" s="30"/>
       <c r="H413" s="30"/>
@@ -8605,7 +8602,7 @@
       <c r="D414" s="25"/>
       <c r="E414" s="29"/>
       <c r="F414" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G414" s="30"/>
       <c r="H414" s="30"/>
@@ -8619,7 +8616,7 @@
       <c r="D415" s="25"/>
       <c r="E415" s="29"/>
       <c r="F415" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G415" s="30"/>
       <c r="H415" s="30"/>
@@ -8633,7 +8630,7 @@
       <c r="D416" s="25"/>
       <c r="E416" s="29"/>
       <c r="F416" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G416" s="30"/>
       <c r="H416" s="30"/>
@@ -8647,7 +8644,7 @@
       <c r="D417" s="25"/>
       <c r="E417" s="29"/>
       <c r="F417" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G417" s="30"/>
       <c r="H417" s="30"/>
@@ -8661,7 +8658,7 @@
       <c r="D418" s="25"/>
       <c r="E418" s="29"/>
       <c r="F418" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G418" s="30"/>
       <c r="H418" s="30"/>
@@ -8675,7 +8672,7 @@
       <c r="D419" s="25"/>
       <c r="E419" s="29"/>
       <c r="F419" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G419" s="30"/>
       <c r="H419" s="30"/>
@@ -8689,7 +8686,7 @@
       <c r="D420" s="25"/>
       <c r="E420" s="29"/>
       <c r="F420" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G420" s="30"/>
       <c r="H420" s="30"/>
@@ -8703,7 +8700,7 @@
       <c r="D421" s="25"/>
       <c r="E421" s="29"/>
       <c r="F421" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G421" s="30"/>
       <c r="H421" s="30"/>
@@ -8717,7 +8714,7 @@
       <c r="D422" s="25"/>
       <c r="E422" s="29"/>
       <c r="F422" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G422" s="30"/>
       <c r="H422" s="30"/>
@@ -8731,7 +8728,7 @@
       <c r="D423" s="25"/>
       <c r="E423" s="29"/>
       <c r="F423" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G423" s="30"/>
       <c r="H423" s="30"/>
@@ -8745,7 +8742,7 @@
       <c r="D424" s="25"/>
       <c r="E424" s="29"/>
       <c r="F424" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G424" s="30"/>
       <c r="H424" s="30"/>
@@ -8759,7 +8756,7 @@
       <c r="D425" s="25"/>
       <c r="E425" s="29"/>
       <c r="F425" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G425" s="30"/>
       <c r="H425" s="30"/>
@@ -8773,7 +8770,7 @@
       <c r="D426" s="25"/>
       <c r="E426" s="29"/>
       <c r="F426" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G426" s="30"/>
       <c r="H426" s="30"/>
@@ -8787,7 +8784,7 @@
       <c r="D427" s="25"/>
       <c r="E427" s="29"/>
       <c r="F427" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G427" s="30"/>
       <c r="H427" s="30"/>
@@ -8801,7 +8798,7 @@
       <c r="D428" s="25"/>
       <c r="E428" s="29"/>
       <c r="F428" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G428" s="30"/>
       <c r="H428" s="30"/>
@@ -8815,7 +8812,7 @@
       <c r="D429" s="25"/>
       <c r="E429" s="29"/>
       <c r="F429" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G429" s="30"/>
       <c r="H429" s="30"/>
@@ -8829,7 +8826,7 @@
       <c r="D430" s="25"/>
       <c r="E430" s="29"/>
       <c r="F430" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G430" s="30"/>
       <c r="H430" s="30"/>
@@ -8843,7 +8840,7 @@
       <c r="D431" s="25"/>
       <c r="E431" s="29"/>
       <c r="F431" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G431" s="30"/>
       <c r="H431" s="30"/>
@@ -8857,7 +8854,7 @@
       <c r="D432" s="25"/>
       <c r="E432" s="29"/>
       <c r="F432" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G432" s="30"/>
       <c r="H432" s="30"/>
@@ -8871,7 +8868,7 @@
       <c r="D433" s="25"/>
       <c r="E433" s="29"/>
       <c r="F433" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G433" s="30"/>
       <c r="H433" s="30"/>
@@ -8885,7 +8882,7 @@
       <c r="D434" s="25"/>
       <c r="E434" s="29"/>
       <c r="F434" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G434" s="30"/>
       <c r="H434" s="30"/>
@@ -8899,7 +8896,7 @@
       <c r="D435" s="25"/>
       <c r="E435" s="29"/>
       <c r="F435" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G435" s="30"/>
       <c r="H435" s="30"/>
@@ -8913,7 +8910,7 @@
       <c r="D436" s="25"/>
       <c r="E436" s="29"/>
       <c r="F436" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G436" s="30"/>
       <c r="H436" s="30"/>
@@ -8927,7 +8924,7 @@
       <c r="D437" s="25"/>
       <c r="E437" s="29"/>
       <c r="F437" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G437" s="30"/>
       <c r="H437" s="30"/>
@@ -8941,7 +8938,7 @@
       <c r="D438" s="25"/>
       <c r="E438" s="29"/>
       <c r="F438" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G438" s="30"/>
       <c r="H438" s="30"/>
@@ -8955,7 +8952,7 @@
       <c r="D439" s="25"/>
       <c r="E439" s="29"/>
       <c r="F439" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G439" s="30"/>
       <c r="H439" s="30"/>
@@ -8969,7 +8966,7 @@
       <c r="D440" s="25"/>
       <c r="E440" s="29"/>
       <c r="F440" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G440" s="30"/>
       <c r="H440" s="30"/>
@@ -8983,7 +8980,7 @@
       <c r="D441" s="25"/>
       <c r="E441" s="29"/>
       <c r="F441" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G441" s="30"/>
       <c r="H441" s="30"/>
@@ -8997,7 +8994,7 @@
       <c r="D442" s="25"/>
       <c r="E442" s="29"/>
       <c r="F442" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G442" s="30"/>
       <c r="H442" s="30"/>
@@ -9011,7 +9008,7 @@
       <c r="D443" s="25"/>
       <c r="E443" s="29"/>
       <c r="F443" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G443" s="30"/>
       <c r="H443" s="30"/>
@@ -9025,7 +9022,7 @@
       <c r="D444" s="25"/>
       <c r="E444" s="29"/>
       <c r="F444" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G444" s="30"/>
       <c r="H444" s="30"/>
@@ -9039,7 +9036,7 @@
       <c r="D445" s="25"/>
       <c r="E445" s="29"/>
       <c r="F445" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G445" s="30"/>
       <c r="H445" s="30"/>
@@ -9053,7 +9050,7 @@
       <c r="D446" s="25"/>
       <c r="E446" s="29"/>
       <c r="F446" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G446" s="30"/>
       <c r="H446" s="30"/>
@@ -9067,7 +9064,7 @@
       <c r="D447" s="25"/>
       <c r="E447" s="29"/>
       <c r="F447" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G447" s="30"/>
       <c r="H447" s="30"/>
@@ -9081,7 +9078,7 @@
       <c r="D448" s="25"/>
       <c r="E448" s="29"/>
       <c r="F448" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G448" s="30"/>
       <c r="H448" s="30"/>
@@ -9095,7 +9092,7 @@
       <c r="D449" s="25"/>
       <c r="E449" s="29"/>
       <c r="F449" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G449" s="30"/>
       <c r="H449" s="30"/>
@@ -9109,7 +9106,7 @@
       <c r="D450" s="25"/>
       <c r="E450" s="29"/>
       <c r="F450" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G450" s="30"/>
       <c r="H450" s="30"/>
@@ -9123,7 +9120,7 @@
       <c r="D451" s="25"/>
       <c r="E451" s="29"/>
       <c r="F451" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G451" s="30"/>
       <c r="H451" s="30"/>
@@ -9137,7 +9134,7 @@
       <c r="D452" s="25"/>
       <c r="E452" s="29"/>
       <c r="F452" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G452" s="30"/>
       <c r="H452" s="30"/>
@@ -9151,7 +9148,7 @@
       <c r="D453" s="25"/>
       <c r="E453" s="29"/>
       <c r="F453" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G453" s="30"/>
       <c r="H453" s="30"/>
@@ -9165,7 +9162,7 @@
       <c r="D454" s="25"/>
       <c r="E454" s="29"/>
       <c r="F454" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G454" s="30"/>
       <c r="H454" s="30"/>
@@ -9179,7 +9176,7 @@
       <c r="D455" s="25"/>
       <c r="E455" s="29"/>
       <c r="F455" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G455" s="30"/>
       <c r="H455" s="30"/>
@@ -9193,7 +9190,7 @@
       <c r="D456" s="25"/>
       <c r="E456" s="29"/>
       <c r="F456" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G456" s="30"/>
       <c r="H456" s="30"/>
@@ -9207,7 +9204,7 @@
       <c r="D457" s="25"/>
       <c r="E457" s="29"/>
       <c r="F457" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G457" s="30"/>
       <c r="H457" s="30"/>
@@ -9221,7 +9218,7 @@
       <c r="D458" s="25"/>
       <c r="E458" s="29"/>
       <c r="F458" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G458" s="30"/>
       <c r="H458" s="30"/>
@@ -9235,7 +9232,7 @@
       <c r="D459" s="25"/>
       <c r="E459" s="29"/>
       <c r="F459" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G459" s="30"/>
       <c r="H459" s="30"/>
@@ -9249,7 +9246,7 @@
       <c r="D460" s="25"/>
       <c r="E460" s="29"/>
       <c r="F460" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G460" s="30"/>
       <c r="H460" s="30"/>
@@ -9263,7 +9260,7 @@
       <c r="D461" s="25"/>
       <c r="E461" s="29"/>
       <c r="F461" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G461" s="30"/>
       <c r="H461" s="30"/>
@@ -9277,7 +9274,7 @@
       <c r="D462" s="25"/>
       <c r="E462" s="29"/>
       <c r="F462" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G462" s="30"/>
       <c r="H462" s="30"/>
@@ -9291,7 +9288,7 @@
       <c r="D463" s="25"/>
       <c r="E463" s="29"/>
       <c r="F463" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G463" s="30"/>
       <c r="H463" s="30"/>
@@ -9305,7 +9302,7 @@
       <c r="D464" s="25"/>
       <c r="E464" s="29"/>
       <c r="F464" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G464" s="30"/>
       <c r="H464" s="30"/>
@@ -9319,7 +9316,7 @@
       <c r="D465" s="25"/>
       <c r="E465" s="29"/>
       <c r="F465" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G465" s="30"/>
       <c r="H465" s="30"/>
@@ -9333,7 +9330,7 @@
       <c r="D466" s="25"/>
       <c r="E466" s="29"/>
       <c r="F466" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G466" s="30"/>
       <c r="H466" s="30"/>
@@ -9347,7 +9344,7 @@
       <c r="D467" s="25"/>
       <c r="E467" s="29"/>
       <c r="F467" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G467" s="30"/>
       <c r="H467" s="30"/>
@@ -9361,7 +9358,7 @@
       <c r="D468" s="25"/>
       <c r="E468" s="29"/>
       <c r="F468" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G468" s="30"/>
       <c r="H468" s="30"/>
@@ -9375,7 +9372,7 @@
       <c r="D469" s="25"/>
       <c r="E469" s="29"/>
       <c r="F469" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G469" s="30"/>
       <c r="H469" s="30"/>
@@ -9389,7 +9386,7 @@
       <c r="D470" s="25"/>
       <c r="E470" s="29"/>
       <c r="F470" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G470" s="30"/>
       <c r="H470" s="30"/>
@@ -9403,7 +9400,7 @@
       <c r="D471" s="25"/>
       <c r="E471" s="29"/>
       <c r="F471" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G471" s="30"/>
       <c r="H471" s="30"/>
@@ -9417,7 +9414,7 @@
       <c r="D472" s="25"/>
       <c r="E472" s="29"/>
       <c r="F472" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G472" s="30"/>
       <c r="H472" s="30"/>
@@ -9431,7 +9428,7 @@
       <c r="D473" s="25"/>
       <c r="E473" s="29"/>
       <c r="F473" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G473" s="30"/>
       <c r="H473" s="30"/>
@@ -9445,7 +9442,7 @@
       <c r="D474" s="25"/>
       <c r="E474" s="29"/>
       <c r="F474" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G474" s="30"/>
       <c r="H474" s="30"/>
@@ -9459,7 +9456,7 @@
       <c r="D475" s="25"/>
       <c r="E475" s="29"/>
       <c r="F475" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G475" s="30"/>
       <c r="H475" s="30"/>
@@ -9473,7 +9470,7 @@
       <c r="D476" s="25"/>
       <c r="E476" s="29"/>
       <c r="F476" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G476" s="30"/>
       <c r="H476" s="30"/>
@@ -9487,7 +9484,7 @@
       <c r="D477" s="25"/>
       <c r="E477" s="29"/>
       <c r="F477" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G477" s="30"/>
       <c r="H477" s="30"/>
@@ -9501,7 +9498,7 @@
       <c r="D478" s="25"/>
       <c r="E478" s="29"/>
       <c r="F478" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G478" s="30"/>
       <c r="H478" s="30"/>
@@ -9515,7 +9512,7 @@
       <c r="D479" s="25"/>
       <c r="E479" s="29"/>
       <c r="F479" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G479" s="30"/>
       <c r="H479" s="30"/>
@@ -9529,7 +9526,7 @@
       <c r="D480" s="25"/>
       <c r="E480" s="29"/>
       <c r="F480" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G480" s="30"/>
       <c r="H480" s="30"/>
@@ -9543,7 +9540,7 @@
       <c r="D481" s="25"/>
       <c r="E481" s="29"/>
       <c r="F481" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G481" s="30"/>
       <c r="H481" s="30"/>
@@ -9557,7 +9554,7 @@
       <c r="D482" s="25"/>
       <c r="E482" s="29"/>
       <c r="F482" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G482" s="30"/>
       <c r="H482" s="30"/>
@@ -9571,7 +9568,7 @@
       <c r="D483" s="25"/>
       <c r="E483" s="29"/>
       <c r="F483" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G483" s="30"/>
       <c r="H483" s="30"/>
@@ -9585,7 +9582,7 @@
       <c r="D484" s="25"/>
       <c r="E484" s="29"/>
       <c r="F484" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G484" s="30"/>
       <c r="H484" s="30"/>
@@ -9599,7 +9596,7 @@
       <c r="D485" s="25"/>
       <c r="E485" s="29"/>
       <c r="F485" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G485" s="30"/>
       <c r="H485" s="30"/>
@@ -9613,7 +9610,7 @@
       <c r="D486" s="25"/>
       <c r="E486" s="29"/>
       <c r="F486" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G486" s="30"/>
       <c r="H486" s="30"/>
@@ -9627,7 +9624,7 @@
       <c r="D487" s="25"/>
       <c r="E487" s="29"/>
       <c r="F487" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G487" s="30"/>
       <c r="H487" s="30"/>
@@ -9641,7 +9638,7 @@
       <c r="D488" s="25"/>
       <c r="E488" s="29"/>
       <c r="F488" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G488" s="30"/>
       <c r="H488" s="30"/>
@@ -9655,7 +9652,7 @@
       <c r="D489" s="25"/>
       <c r="E489" s="29"/>
       <c r="F489" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G489" s="30"/>
       <c r="H489" s="30"/>
@@ -9669,7 +9666,7 @@
       <c r="D490" s="25"/>
       <c r="E490" s="29"/>
       <c r="F490" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G490" s="30"/>
       <c r="H490" s="30"/>
@@ -9683,7 +9680,7 @@
       <c r="D491" s="25"/>
       <c r="E491" s="29"/>
       <c r="F491" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G491" s="30"/>
       <c r="H491" s="30"/>
@@ -9697,7 +9694,7 @@
       <c r="D492" s="25"/>
       <c r="E492" s="29"/>
       <c r="F492" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G492" s="30"/>
       <c r="H492" s="30"/>
@@ -9711,7 +9708,7 @@
       <c r="D493" s="25"/>
       <c r="E493" s="29"/>
       <c r="F493" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G493" s="30"/>
       <c r="H493" s="30"/>
@@ -9725,7 +9722,7 @@
       <c r="D494" s="25"/>
       <c r="E494" s="29"/>
       <c r="F494" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G494" s="30"/>
       <c r="H494" s="30"/>
@@ -9739,7 +9736,7 @@
       <c r="D495" s="25"/>
       <c r="E495" s="29"/>
       <c r="F495" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G495" s="30"/>
       <c r="H495" s="30"/>
@@ -9751,6 +9748,7 @@
       <c r="B496" s="28"/>
       <c r="C496" s="28"/>
       <c r="E496" s="29"/>
+      <c r="F496" s="29"/>
       <c r="G496" s="30"/>
       <c r="H496" s="30"/>
       <c r="I496" s="30"/>
@@ -9761,6 +9759,7 @@
       <c r="B497" s="28"/>
       <c r="C497" s="28"/>
       <c r="E497" s="29"/>
+      <c r="F497" s="29"/>
       <c r="G497" s="30"/>
       <c r="H497" s="30"/>
       <c r="I497" s="30"/>
@@ -9771,6 +9770,7 @@
       <c r="B498" s="28"/>
       <c r="C498" s="28"/>
       <c r="E498" s="29"/>
+      <c r="F498" s="29"/>
       <c r="G498" s="30"/>
       <c r="H498" s="30"/>
       <c r="I498" s="30"/>
@@ -9781,6 +9781,7 @@
       <c r="B499" s="28"/>
       <c r="C499" s="28"/>
       <c r="E499" s="29"/>
+      <c r="F499" s="29"/>
       <c r="G499" s="30"/>
       <c r="H499" s="30"/>
       <c r="I499" s="30"/>
@@ -9791,6 +9792,7 @@
       <c r="B500" s="28"/>
       <c r="C500" s="28"/>
       <c r="E500" s="29"/>
+      <c r="F500" s="29"/>
       <c r="G500" s="30"/>
       <c r="H500" s="30"/>
       <c r="I500" s="30"/>
@@ -9801,6 +9803,7 @@
       <c r="B501" s="28"/>
       <c r="C501" s="28"/>
       <c r="E501" s="29"/>
+      <c r="F501" s="29"/>
       <c r="G501" s="30"/>
       <c r="H501" s="30"/>
       <c r="I501" s="30"/>
@@ -9811,6 +9814,7 @@
       <c r="B502" s="28"/>
       <c r="C502" s="28"/>
       <c r="E502" s="29"/>
+      <c r="F502" s="29"/>
       <c r="G502" s="30"/>
       <c r="H502" s="30"/>
       <c r="I502" s="30"/>
@@ -9821,6 +9825,7 @@
       <c r="B503" s="28"/>
       <c r="C503" s="28"/>
       <c r="E503" s="29"/>
+      <c r="F503" s="29"/>
       <c r="G503" s="30"/>
       <c r="H503" s="30"/>
       <c r="I503" s="30"/>
@@ -9831,6 +9836,7 @@
       <c r="B504" s="28"/>
       <c r="C504" s="28"/>
       <c r="E504" s="29"/>
+      <c r="F504" s="29"/>
       <c r="G504" s="30"/>
       <c r="H504" s="30"/>
       <c r="I504" s="30"/>
@@ -9841,6 +9847,7 @@
       <c r="B505" s="28"/>
       <c r="C505" s="28"/>
       <c r="E505" s="29"/>
+      <c r="F505" s="29"/>
       <c r="G505" s="30"/>
       <c r="H505" s="30"/>
       <c r="I505" s="30"/>
@@ -9851,6 +9858,7 @@
       <c r="B506" s="28"/>
       <c r="C506" s="28"/>
       <c r="E506" s="29"/>
+      <c r="F506" s="29"/>
       <c r="G506" s="30"/>
       <c r="H506" s="30"/>
       <c r="I506" s="30"/>
@@ -9861,6 +9869,7 @@
       <c r="B507" s="28"/>
       <c r="C507" s="28"/>
       <c r="E507" s="29"/>
+      <c r="F507" s="29"/>
       <c r="G507" s="30"/>
       <c r="H507" s="30"/>
       <c r="I507" s="30"/>
@@ -9871,6 +9880,7 @@
       <c r="B508" s="28"/>
       <c r="C508" s="28"/>
       <c r="E508" s="29"/>
+      <c r="F508" s="29"/>
       <c r="G508" s="30"/>
       <c r="H508" s="30"/>
       <c r="I508" s="30"/>
@@ -9881,6 +9891,7 @@
       <c r="B509" s="28"/>
       <c r="C509" s="28"/>
       <c r="E509" s="29"/>
+      <c r="F509" s="29"/>
       <c r="G509" s="30"/>
       <c r="H509" s="30"/>
       <c r="I509" s="30"/>
@@ -9891,6 +9902,7 @@
       <c r="B510" s="28"/>
       <c r="C510" s="28"/>
       <c r="E510" s="29"/>
+      <c r="F510" s="29"/>
       <c r="G510" s="30"/>
       <c r="H510" s="30"/>
       <c r="I510" s="30"/>
@@ -9901,6 +9913,7 @@
       <c r="B511" s="28"/>
       <c r="C511" s="28"/>
       <c r="E511" s="29"/>
+      <c r="F511" s="29"/>
       <c r="G511" s="30"/>
       <c r="H511" s="30"/>
       <c r="I511" s="30"/>
@@ -9911,6 +9924,7 @@
       <c r="B512" s="28"/>
       <c r="C512" s="28"/>
       <c r="E512" s="29"/>
+      <c r="F512" s="29"/>
       <c r="G512" s="30"/>
       <c r="H512" s="30"/>
       <c r="I512" s="30"/>
@@ -9921,6 +9935,7 @@
       <c r="B513" s="28"/>
       <c r="C513" s="28"/>
       <c r="E513" s="29"/>
+      <c r="F513" s="29"/>
       <c r="G513" s="30"/>
       <c r="H513" s="30"/>
       <c r="I513" s="30"/>
@@ -9931,6 +9946,7 @@
       <c r="B514" s="28"/>
       <c r="C514" s="28"/>
       <c r="E514" s="29"/>
+      <c r="F514" s="29"/>
       <c r="G514" s="30"/>
       <c r="H514" s="30"/>
       <c r="I514" s="30"/>
@@ -9941,6 +9957,7 @@
       <c r="B515" s="28"/>
       <c r="C515" s="28"/>
       <c r="E515" s="29"/>
+      <c r="F515" s="29"/>
       <c r="G515" s="30"/>
       <c r="H515" s="30"/>
       <c r="I515" s="30"/>
@@ -9951,6 +9968,7 @@
       <c r="B516" s="28"/>
       <c r="C516" s="28"/>
       <c r="E516" s="29"/>
+      <c r="F516" s="29"/>
       <c r="G516" s="30"/>
       <c r="H516" s="30"/>
       <c r="I516" s="30"/>
@@ -9961,6 +9979,7 @@
       <c r="B517" s="28"/>
       <c r="C517" s="28"/>
       <c r="E517" s="29"/>
+      <c r="F517" s="29"/>
       <c r="G517" s="30"/>
       <c r="H517" s="30"/>
       <c r="I517" s="30"/>
@@ -9971,6 +9990,7 @@
       <c r="B518" s="28"/>
       <c r="C518" s="28"/>
       <c r="E518" s="29"/>
+      <c r="F518" s="29"/>
       <c r="G518" s="30"/>
       <c r="H518" s="30"/>
       <c r="I518" s="30"/>
@@ -9981,6 +10001,7 @@
       <c r="B519" s="28"/>
       <c r="C519" s="28"/>
       <c r="E519" s="29"/>
+      <c r="F519" s="29"/>
       <c r="G519" s="30"/>
       <c r="H519" s="30"/>
       <c r="I519" s="30"/>
@@ -9991,6 +10012,7 @@
       <c r="B520" s="28"/>
       <c r="C520" s="28"/>
       <c r="E520" s="29"/>
+      <c r="F520" s="29"/>
       <c r="G520" s="30"/>
       <c r="H520" s="30"/>
       <c r="I520" s="30"/>
@@ -10001,6 +10023,7 @@
       <c r="B521" s="28"/>
       <c r="C521" s="28"/>
       <c r="E521" s="29"/>
+      <c r="F521" s="29"/>
       <c r="G521" s="30"/>
       <c r="H521" s="30"/>
       <c r="I521" s="30"/>
@@ -10011,6 +10034,7 @@
       <c r="B522" s="28"/>
       <c r="C522" s="28"/>
       <c r="E522" s="29"/>
+      <c r="F522" s="29"/>
       <c r="G522" s="30"/>
       <c r="H522" s="30"/>
       <c r="I522" s="30"/>
@@ -10021,6 +10045,7 @@
       <c r="B523" s="28"/>
       <c r="C523" s="28"/>
       <c r="E523" s="29"/>
+      <c r="F523" s="29"/>
       <c r="G523" s="30"/>
       <c r="H523" s="30"/>
       <c r="I523" s="30"/>
@@ -10031,6 +10056,7 @@
       <c r="B524" s="28"/>
       <c r="C524" s="28"/>
       <c r="E524" s="29"/>
+      <c r="F524" s="29"/>
       <c r="G524" s="30"/>
       <c r="H524" s="30"/>
       <c r="I524" s="30"/>
@@ -10041,6 +10067,7 @@
       <c r="B525" s="28"/>
       <c r="C525" s="28"/>
       <c r="E525" s="29"/>
+      <c r="F525" s="29"/>
       <c r="G525" s="30"/>
       <c r="H525" s="30"/>
       <c r="I525" s="30"/>
@@ -10051,6 +10078,7 @@
       <c r="B526" s="28"/>
       <c r="C526" s="28"/>
       <c r="E526" s="29"/>
+      <c r="F526" s="29"/>
       <c r="G526" s="30"/>
       <c r="H526" s="30"/>
       <c r="I526" s="30"/>
@@ -10061,6 +10089,7 @@
       <c r="B527" s="28"/>
       <c r="C527" s="28"/>
       <c r="E527" s="29"/>
+      <c r="F527" s="29"/>
       <c r="G527" s="30"/>
       <c r="H527" s="30"/>
       <c r="I527" s="30"/>
@@ -10071,6 +10100,7 @@
       <c r="B528" s="28"/>
       <c r="C528" s="28"/>
       <c r="E528" s="29"/>
+      <c r="F528" s="29"/>
       <c r="G528" s="30"/>
       <c r="H528" s="30"/>
       <c r="I528" s="30"/>
@@ -10081,6 +10111,7 @@
       <c r="B529" s="28"/>
       <c r="C529" s="28"/>
       <c r="E529" s="29"/>
+      <c r="F529" s="29"/>
       <c r="G529" s="30"/>
       <c r="H529" s="30"/>
       <c r="I529" s="30"/>
@@ -10091,6 +10122,7 @@
       <c r="B530" s="28"/>
       <c r="C530" s="28"/>
       <c r="E530" s="29"/>
+      <c r="F530" s="29"/>
       <c r="G530" s="30"/>
       <c r="H530" s="30"/>
       <c r="I530" s="30"/>
@@ -10101,6 +10133,7 @@
       <c r="B531" s="28"/>
       <c r="C531" s="28"/>
       <c r="E531" s="29"/>
+      <c r="F531" s="29"/>
       <c r="G531" s="30"/>
       <c r="H531" s="30"/>
       <c r="I531" s="30"/>
@@ -10111,6 +10144,7 @@
       <c r="B532" s="28"/>
       <c r="C532" s="28"/>
       <c r="E532" s="29"/>
+      <c r="F532" s="29"/>
       <c r="G532" s="30"/>
       <c r="H532" s="30"/>
       <c r="I532" s="30"/>
@@ -10121,6 +10155,7 @@
       <c r="B533" s="28"/>
       <c r="C533" s="28"/>
       <c r="E533" s="29"/>
+      <c r="F533" s="29"/>
       <c r="G533" s="30"/>
       <c r="H533" s="30"/>
       <c r="I533" s="30"/>
@@ -10131,6 +10166,7 @@
       <c r="B534" s="28"/>
       <c r="C534" s="28"/>
       <c r="E534" s="29"/>
+      <c r="F534" s="29"/>
       <c r="G534" s="30"/>
       <c r="H534" s="30"/>
       <c r="I534" s="30"/>
@@ -10141,6 +10177,7 @@
       <c r="B535" s="28"/>
       <c r="C535" s="28"/>
       <c r="E535" s="29"/>
+      <c r="F535" s="29"/>
       <c r="G535" s="30"/>
       <c r="H535" s="30"/>
       <c r="I535" s="30"/>
@@ -10151,6 +10188,7 @@
       <c r="B536" s="28"/>
       <c r="C536" s="28"/>
       <c r="E536" s="29"/>
+      <c r="F536" s="29"/>
       <c r="G536" s="30"/>
       <c r="H536" s="30"/>
       <c r="I536" s="30"/>
@@ -10161,6 +10199,7 @@
       <c r="B537" s="28"/>
       <c r="C537" s="28"/>
       <c r="E537" s="29"/>
+      <c r="F537" s="29"/>
       <c r="G537" s="30"/>
       <c r="H537" s="30"/>
       <c r="I537" s="30"/>
@@ -10171,6 +10210,7 @@
       <c r="B538" s="28"/>
       <c r="C538" s="28"/>
       <c r="E538" s="29"/>
+      <c r="F538" s="29"/>
       <c r="G538" s="30"/>
       <c r="H538" s="30"/>
       <c r="I538" s="30"/>
@@ -10181,6 +10221,7 @@
       <c r="B539" s="28"/>
       <c r="C539" s="28"/>
       <c r="E539" s="29"/>
+      <c r="F539" s="29"/>
       <c r="G539" s="30"/>
       <c r="H539" s="30"/>
       <c r="I539" s="30"/>
@@ -10191,6 +10232,7 @@
       <c r="B540" s="28"/>
       <c r="C540" s="28"/>
       <c r="E540" s="29"/>
+      <c r="F540" s="29"/>
       <c r="G540" s="30"/>
       <c r="H540" s="30"/>
       <c r="I540" s="30"/>
@@ -10201,6 +10243,7 @@
       <c r="B541" s="28"/>
       <c r="C541" s="28"/>
       <c r="E541" s="29"/>
+      <c r="F541" s="29"/>
       <c r="G541" s="30"/>
       <c r="H541" s="30"/>
       <c r="I541" s="30"/>
@@ -10211,6 +10254,7 @@
       <c r="B542" s="28"/>
       <c r="C542" s="28"/>
       <c r="E542" s="29"/>
+      <c r="F542" s="29"/>
       <c r="G542" s="30"/>
       <c r="H542" s="30"/>
       <c r="I542" s="30"/>
@@ -10221,6 +10265,7 @@
       <c r="B543" s="28"/>
       <c r="C543" s="28"/>
       <c r="E543" s="29"/>
+      <c r="F543" s="29"/>
       <c r="G543" s="30"/>
       <c r="H543" s="30"/>
       <c r="I543" s="30"/>
@@ -10231,6 +10276,7 @@
       <c r="B544" s="28"/>
       <c r="C544" s="28"/>
       <c r="E544" s="29"/>
+      <c r="F544" s="29"/>
       <c r="G544" s="30"/>
       <c r="H544" s="30"/>
       <c r="I544" s="30"/>
@@ -10241,6 +10287,7 @@
       <c r="B545" s="28"/>
       <c r="C545" s="28"/>
       <c r="E545" s="29"/>
+      <c r="F545" s="29"/>
       <c r="G545" s="30"/>
       <c r="H545" s="30"/>
       <c r="I545" s="30"/>
@@ -10251,6 +10298,7 @@
       <c r="B546" s="28"/>
       <c r="C546" s="28"/>
       <c r="E546" s="29"/>
+      <c r="F546" s="29"/>
       <c r="G546" s="30"/>
       <c r="H546" s="30"/>
       <c r="I546" s="30"/>
@@ -10261,6 +10309,7 @@
       <c r="B547" s="28"/>
       <c r="C547" s="28"/>
       <c r="E547" s="29"/>
+      <c r="F547" s="29"/>
       <c r="G547" s="30"/>
       <c r="H547" s="30"/>
       <c r="I547" s="30"/>
@@ -10271,6 +10320,7 @@
       <c r="B548" s="28"/>
       <c r="C548" s="28"/>
       <c r="E548" s="29"/>
+      <c r="F548" s="29"/>
       <c r="G548" s="30"/>
       <c r="H548" s="30"/>
       <c r="I548" s="30"/>
@@ -10281,6 +10331,7 @@
       <c r="B549" s="28"/>
       <c r="C549" s="28"/>
       <c r="E549" s="29"/>
+      <c r="F549" s="29"/>
       <c r="G549" s="30"/>
       <c r="H549" s="30"/>
       <c r="I549" s="30"/>
@@ -10291,6 +10342,7 @@
       <c r="B550" s="28"/>
       <c r="C550" s="28"/>
       <c r="E550" s="29"/>
+      <c r="F550" s="29"/>
       <c r="G550" s="30"/>
       <c r="H550" s="30"/>
       <c r="I550" s="30"/>
@@ -10301,6 +10353,7 @@
       <c r="B551" s="28"/>
       <c r="C551" s="28"/>
       <c r="E551" s="29"/>
+      <c r="F551" s="29"/>
       <c r="G551" s="30"/>
       <c r="H551" s="30"/>
       <c r="I551" s="30"/>
@@ -10311,6 +10364,7 @@
       <c r="B552" s="28"/>
       <c r="C552" s="28"/>
       <c r="E552" s="29"/>
+      <c r="F552" s="29"/>
       <c r="G552" s="30"/>
       <c r="H552" s="30"/>
       <c r="I552" s="30"/>
@@ -10321,6 +10375,7 @@
       <c r="B553" s="28"/>
       <c r="C553" s="28"/>
       <c r="E553" s="29"/>
+      <c r="F553" s="29"/>
       <c r="G553" s="30"/>
       <c r="H553" s="30"/>
       <c r="I553" s="30"/>
@@ -10331,6 +10386,7 @@
       <c r="B554" s="28"/>
       <c r="C554" s="28"/>
       <c r="E554" s="29"/>
+      <c r="F554" s="29"/>
       <c r="G554" s="30"/>
       <c r="H554" s="30"/>
       <c r="I554" s="30"/>
@@ -10341,6 +10397,7 @@
       <c r="B555" s="28"/>
       <c r="C555" s="28"/>
       <c r="E555" s="29"/>
+      <c r="F555" s="29"/>
       <c r="G555" s="30"/>
       <c r="H555" s="30"/>
       <c r="I555" s="30"/>
@@ -10351,6 +10408,7 @@
       <c r="B556" s="28"/>
       <c r="C556" s="28"/>
       <c r="E556" s="29"/>
+      <c r="F556" s="29"/>
       <c r="G556" s="30"/>
       <c r="H556" s="30"/>
       <c r="I556" s="30"/>
@@ -10361,6 +10419,7 @@
       <c r="B557" s="28"/>
       <c r="C557" s="28"/>
       <c r="E557" s="29"/>
+      <c r="F557" s="29"/>
       <c r="G557" s="30"/>
       <c r="H557" s="30"/>
       <c r="I557" s="30"/>
@@ -10371,6 +10430,7 @@
       <c r="B558" s="28"/>
       <c r="C558" s="28"/>
       <c r="E558" s="29"/>
+      <c r="F558" s="29"/>
       <c r="G558" s="30"/>
       <c r="H558" s="30"/>
       <c r="I558" s="30"/>
@@ -10381,6 +10441,7 @@
       <c r="B559" s="28"/>
       <c r="C559" s="28"/>
       <c r="E559" s="29"/>
+      <c r="F559" s="29"/>
       <c r="G559" s="30"/>
       <c r="H559" s="30"/>
       <c r="I559" s="30"/>
@@ -10391,6 +10452,7 @@
       <c r="B560" s="28"/>
       <c r="C560" s="28"/>
       <c r="E560" s="29"/>
+      <c r="F560" s="29"/>
       <c r="G560" s="30"/>
       <c r="H560" s="30"/>
       <c r="I560" s="30"/>
@@ -10401,6 +10463,7 @@
       <c r="B561" s="28"/>
       <c r="C561" s="28"/>
       <c r="E561" s="29"/>
+      <c r="F561" s="29"/>
       <c r="G561" s="30"/>
       <c r="H561" s="30"/>
       <c r="I561" s="30"/>
@@ -10411,6 +10474,7 @@
       <c r="B562" s="28"/>
       <c r="C562" s="28"/>
       <c r="E562" s="29"/>
+      <c r="F562" s="29"/>
       <c r="G562" s="30"/>
       <c r="H562" s="30"/>
       <c r="I562" s="30"/>
@@ -10421,6 +10485,7 @@
       <c r="B563" s="28"/>
       <c r="C563" s="28"/>
       <c r="E563" s="29"/>
+      <c r="F563" s="29"/>
       <c r="G563" s="30"/>
       <c r="H563" s="30"/>
       <c r="I563" s="30"/>
@@ -10431,6 +10496,7 @@
       <c r="B564" s="28"/>
       <c r="C564" s="28"/>
       <c r="E564" s="29"/>
+      <c r="F564" s="29"/>
       <c r="G564" s="30"/>
       <c r="H564" s="30"/>
       <c r="I564" s="30"/>
@@ -10441,6 +10507,7 @@
       <c r="B565" s="28"/>
       <c r="C565" s="28"/>
       <c r="E565" s="29"/>
+      <c r="F565" s="29"/>
       <c r="G565" s="30"/>
       <c r="H565" s="30"/>
       <c r="I565" s="30"/>
@@ -10451,6 +10518,7 @@
       <c r="B566" s="28"/>
       <c r="C566" s="28"/>
       <c r="E566" s="29"/>
+      <c r="F566" s="29"/>
       <c r="G566" s="30"/>
       <c r="H566" s="30"/>
       <c r="I566" s="30"/>
@@ -10461,6 +10529,7 @@
       <c r="B567" s="28"/>
       <c r="C567" s="28"/>
       <c r="E567" s="29"/>
+      <c r="F567" s="29"/>
       <c r="G567" s="30"/>
       <c r="H567" s="30"/>
       <c r="I567" s="30"/>
@@ -10471,6 +10540,7 @@
       <c r="B568" s="28"/>
       <c r="C568" s="28"/>
       <c r="E568" s="29"/>
+      <c r="F568" s="29"/>
       <c r="G568" s="30"/>
       <c r="H568" s="30"/>
       <c r="I568" s="30"/>
@@ -10481,6 +10551,7 @@
       <c r="B569" s="28"/>
       <c r="C569" s="28"/>
       <c r="E569" s="29"/>
+      <c r="F569" s="29"/>
       <c r="G569" s="30"/>
       <c r="H569" s="30"/>
       <c r="I569" s="30"/>
@@ -10491,6 +10562,7 @@
       <c r="B570" s="28"/>
       <c r="C570" s="28"/>
       <c r="E570" s="29"/>
+      <c r="F570" s="29"/>
       <c r="G570" s="30"/>
       <c r="H570" s="30"/>
       <c r="I570" s="30"/>
@@ -10501,6 +10573,7 @@
       <c r="B571" s="28"/>
       <c r="C571" s="28"/>
       <c r="E571" s="29"/>
+      <c r="F571" s="29"/>
       <c r="G571" s="30"/>
       <c r="H571" s="30"/>
       <c r="I571" s="30"/>
@@ -10511,6 +10584,7 @@
       <c r="B572" s="28"/>
       <c r="C572" s="28"/>
       <c r="E572" s="29"/>
+      <c r="F572" s="29"/>
       <c r="G572" s="30"/>
       <c r="H572" s="30"/>
       <c r="I572" s="30"/>
@@ -10521,6 +10595,7 @@
       <c r="B573" s="28"/>
       <c r="C573" s="28"/>
       <c r="E573" s="29"/>
+      <c r="F573" s="29"/>
       <c r="G573" s="30"/>
       <c r="H573" s="30"/>
       <c r="I573" s="30"/>
@@ -10531,6 +10606,7 @@
       <c r="B574" s="28"/>
       <c r="C574" s="28"/>
       <c r="E574" s="29"/>
+      <c r="F574" s="29"/>
       <c r="G574" s="30"/>
       <c r="H574" s="30"/>
       <c r="I574" s="30"/>
@@ -10541,6 +10617,7 @@
       <c r="B575" s="28"/>
       <c r="C575" s="28"/>
       <c r="E575" s="29"/>
+      <c r="F575" s="29"/>
       <c r="G575" s="30"/>
       <c r="H575" s="30"/>
       <c r="I575" s="30"/>
@@ -10551,6 +10628,7 @@
       <c r="B576" s="28"/>
       <c r="C576" s="28"/>
       <c r="E576" s="29"/>
+      <c r="F576" s="29"/>
       <c r="G576" s="30"/>
       <c r="H576" s="30"/>
       <c r="I576" s="30"/>
@@ -10561,6 +10639,7 @@
       <c r="B577" s="28"/>
       <c r="C577" s="28"/>
       <c r="E577" s="29"/>
+      <c r="F577" s="29"/>
       <c r="G577" s="30"/>
       <c r="H577" s="30"/>
       <c r="I577" s="30"/>
@@ -10571,6 +10650,7 @@
       <c r="B578" s="28"/>
       <c r="C578" s="28"/>
       <c r="E578" s="29"/>
+      <c r="F578" s="29"/>
       <c r="G578" s="30"/>
       <c r="H578" s="30"/>
       <c r="I578" s="30"/>
@@ -10581,6 +10661,7 @@
       <c r="B579" s="28"/>
       <c r="C579" s="28"/>
       <c r="E579" s="29"/>
+      <c r="F579" s="29"/>
       <c r="G579" s="30"/>
       <c r="H579" s="30"/>
       <c r="I579" s="30"/>
@@ -10591,6 +10672,7 @@
       <c r="B580" s="28"/>
       <c r="C580" s="28"/>
       <c r="E580" s="29"/>
+      <c r="F580" s="29"/>
       <c r="G580" s="30"/>
       <c r="H580" s="30"/>
       <c r="I580" s="30"/>
@@ -10601,6 +10683,7 @@
       <c r="B581" s="28"/>
       <c r="C581" s="28"/>
       <c r="E581" s="29"/>
+      <c r="F581" s="29"/>
       <c r="G581" s="30"/>
       <c r="H581" s="30"/>
       <c r="I581" s="30"/>
@@ -10611,6 +10694,7 @@
       <c r="B582" s="28"/>
       <c r="C582" s="28"/>
       <c r="E582" s="29"/>
+      <c r="F582" s="29"/>
       <c r="G582" s="30"/>
       <c r="H582" s="30"/>
       <c r="I582" s="30"/>
@@ -10621,6 +10705,7 @@
       <c r="B583" s="28"/>
       <c r="C583" s="28"/>
       <c r="E583" s="29"/>
+      <c r="F583" s="29"/>
       <c r="G583" s="30"/>
       <c r="H583" s="30"/>
       <c r="I583" s="30"/>
@@ -10631,6 +10716,7 @@
       <c r="B584" s="28"/>
       <c r="C584" s="28"/>
       <c r="E584" s="29"/>
+      <c r="F584" s="29"/>
       <c r="G584" s="30"/>
       <c r="H584" s="30"/>
       <c r="I584" s="30"/>
@@ -10641,6 +10727,7 @@
       <c r="B585" s="28"/>
       <c r="C585" s="28"/>
       <c r="E585" s="29"/>
+      <c r="F585" s="29"/>
       <c r="G585" s="30"/>
       <c r="H585" s="30"/>
       <c r="I585" s="30"/>
@@ -10651,6 +10738,7 @@
       <c r="B586" s="28"/>
       <c r="C586" s="28"/>
       <c r="E586" s="29"/>
+      <c r="F586" s="29"/>
       <c r="G586" s="30"/>
       <c r="H586" s="30"/>
       <c r="I586" s="30"/>
@@ -10661,6 +10749,7 @@
       <c r="B587" s="28"/>
       <c r="C587" s="28"/>
       <c r="E587" s="29"/>
+      <c r="F587" s="29"/>
       <c r="G587" s="30"/>
       <c r="H587" s="30"/>
       <c r="I587" s="30"/>
@@ -10671,6 +10760,7 @@
       <c r="B588" s="28"/>
       <c r="C588" s="28"/>
       <c r="E588" s="29"/>
+      <c r="F588" s="29"/>
       <c r="G588" s="30"/>
       <c r="H588" s="30"/>
       <c r="I588" s="30"/>
@@ -10681,6 +10771,7 @@
       <c r="B589" s="28"/>
       <c r="C589" s="28"/>
       <c r="E589" s="29"/>
+      <c r="F589" s="29"/>
       <c r="G589" s="30"/>
       <c r="H589" s="30"/>
       <c r="I589" s="30"/>
@@ -10691,6 +10782,7 @@
       <c r="B590" s="28"/>
       <c r="C590" s="28"/>
       <c r="E590" s="29"/>
+      <c r="F590" s="29"/>
       <c r="G590" s="30"/>
       <c r="H590" s="30"/>
       <c r="I590" s="30"/>
@@ -10701,6 +10793,7 @@
       <c r="B591" s="28"/>
       <c r="C591" s="28"/>
       <c r="E591" s="29"/>
+      <c r="F591" s="29"/>
       <c r="G591" s="30"/>
       <c r="H591" s="30"/>
       <c r="I591" s="30"/>
@@ -10711,6 +10804,7 @@
       <c r="B592" s="28"/>
       <c r="C592" s="28"/>
       <c r="E592" s="29"/>
+      <c r="F592" s="29"/>
       <c r="G592" s="30"/>
       <c r="H592" s="30"/>
       <c r="I592" s="30"/>
@@ -10721,6 +10815,7 @@
       <c r="B593" s="28"/>
       <c r="C593" s="28"/>
       <c r="E593" s="29"/>
+      <c r="F593" s="29"/>
       <c r="G593" s="30"/>
       <c r="H593" s="30"/>
       <c r="I593" s="30"/>
@@ -10731,6 +10826,7 @@
       <c r="B594" s="28"/>
       <c r="C594" s="28"/>
       <c r="E594" s="29"/>
+      <c r="F594" s="29"/>
       <c r="G594" s="30"/>
       <c r="H594" s="30"/>
       <c r="I594" s="30"/>
@@ -10741,6 +10837,7 @@
       <c r="B595" s="28"/>
       <c r="C595" s="28"/>
       <c r="E595" s="29"/>
+      <c r="F595" s="29"/>
       <c r="G595" s="30"/>
       <c r="H595" s="30"/>
       <c r="I595" s="30"/>
@@ -10751,6 +10848,7 @@
       <c r="B596" s="28"/>
       <c r="C596" s="28"/>
       <c r="E596" s="29"/>
+      <c r="F596" s="29"/>
       <c r="G596" s="30"/>
       <c r="H596" s="30"/>
       <c r="I596" s="30"/>
@@ -10761,6 +10859,7 @@
       <c r="B597" s="28"/>
       <c r="C597" s="28"/>
       <c r="E597" s="29"/>
+      <c r="F597" s="29"/>
       <c r="G597" s="30"/>
       <c r="H597" s="30"/>
       <c r="I597" s="30"/>
@@ -10771,6 +10870,7 @@
       <c r="B598" s="28"/>
       <c r="C598" s="28"/>
       <c r="E598" s="29"/>
+      <c r="F598" s="29"/>
       <c r="G598" s="30"/>
       <c r="H598" s="30"/>
       <c r="I598" s="30"/>
@@ -10781,6 +10881,7 @@
       <c r="B599" s="28"/>
       <c r="C599" s="28"/>
       <c r="E599" s="29"/>
+      <c r="F599" s="29"/>
       <c r="G599" s="30"/>
       <c r="H599" s="30"/>
       <c r="I599" s="30"/>
@@ -10791,6 +10892,7 @@
       <c r="B600" s="28"/>
       <c r="C600" s="28"/>
       <c r="E600" s="29"/>
+      <c r="F600" s="29"/>
       <c r="G600" s="30"/>
       <c r="H600" s="30"/>
       <c r="I600" s="30"/>
@@ -10801,6 +10903,7 @@
       <c r="B601" s="28"/>
       <c r="C601" s="28"/>
       <c r="E601" s="29"/>
+      <c r="F601" s="29"/>
       <c r="G601" s="30"/>
       <c r="H601" s="30"/>
       <c r="I601" s="30"/>
@@ -10811,6 +10914,7 @@
       <c r="B602" s="28"/>
       <c r="C602" s="28"/>
       <c r="E602" s="29"/>
+      <c r="F602" s="29"/>
       <c r="G602" s="30"/>
       <c r="H602" s="30"/>
       <c r="I602" s="30"/>
@@ -10821,6 +10925,7 @@
       <c r="B603" s="28"/>
       <c r="C603" s="28"/>
       <c r="E603" s="29"/>
+      <c r="F603" s="29"/>
       <c r="G603" s="30"/>
       <c r="H603" s="30"/>
       <c r="I603" s="30"/>
@@ -10831,6 +10936,7 @@
       <c r="B604" s="28"/>
       <c r="C604" s="28"/>
       <c r="E604" s="29"/>
+      <c r="F604" s="29"/>
       <c r="G604" s="30"/>
       <c r="H604" s="30"/>
       <c r="I604" s="30"/>
@@ -10841,6 +10947,7 @@
       <c r="B605" s="28"/>
       <c r="C605" s="28"/>
       <c r="E605" s="29"/>
+      <c r="F605" s="29"/>
       <c r="G605" s="30"/>
       <c r="H605" s="30"/>
       <c r="I605" s="30"/>
@@ -10851,6 +10958,7 @@
       <c r="B606" s="28"/>
       <c r="C606" s="28"/>
       <c r="E606" s="29"/>
+      <c r="F606" s="29"/>
       <c r="G606" s="30"/>
       <c r="H606" s="30"/>
       <c r="I606" s="30"/>
@@ -10861,6 +10969,7 @@
       <c r="B607" s="28"/>
       <c r="C607" s="28"/>
       <c r="E607" s="29"/>
+      <c r="F607" s="29"/>
       <c r="G607" s="30"/>
       <c r="H607" s="30"/>
       <c r="I607" s="30"/>
@@ -10871,6 +10980,7 @@
       <c r="B608" s="28"/>
       <c r="C608" s="28"/>
       <c r="E608" s="29"/>
+      <c r="F608" s="29"/>
       <c r="G608" s="30"/>
       <c r="H608" s="30"/>
       <c r="I608" s="30"/>
@@ -10881,6 +10991,7 @@
       <c r="B609" s="28"/>
       <c r="C609" s="28"/>
       <c r="E609" s="29"/>
+      <c r="F609" s="29"/>
       <c r="G609" s="30"/>
       <c r="H609" s="30"/>
       <c r="I609" s="30"/>
@@ -10891,6 +11002,7 @@
       <c r="B610" s="28"/>
       <c r="C610" s="28"/>
       <c r="E610" s="29"/>
+      <c r="F610" s="29"/>
       <c r="G610" s="30"/>
       <c r="H610" s="30"/>
       <c r="I610" s="30"/>
@@ -10901,6 +11013,7 @@
       <c r="B611" s="28"/>
       <c r="C611" s="28"/>
       <c r="E611" s="29"/>
+      <c r="F611" s="29"/>
       <c r="G611" s="30"/>
       <c r="H611" s="30"/>
       <c r="I611" s="30"/>
@@ -10911,6 +11024,7 @@
       <c r="B612" s="28"/>
       <c r="C612" s="28"/>
       <c r="E612" s="29"/>
+      <c r="F612" s="29"/>
       <c r="G612" s="30"/>
       <c r="H612" s="30"/>
       <c r="I612" s="30"/>
@@ -10921,6 +11035,7 @@
       <c r="B613" s="28"/>
       <c r="C613" s="28"/>
       <c r="E613" s="29"/>
+      <c r="F613" s="29"/>
       <c r="G613" s="30"/>
       <c r="H613" s="30"/>
       <c r="I613" s="30"/>
@@ -10931,6 +11046,7 @@
       <c r="B614" s="28"/>
       <c r="C614" s="28"/>
       <c r="E614" s="29"/>
+      <c r="F614" s="29"/>
       <c r="G614" s="30"/>
       <c r="H614" s="30"/>
       <c r="I614" s="30"/>
@@ -10941,6 +11057,7 @@
       <c r="B615" s="28"/>
       <c r="C615" s="28"/>
       <c r="E615" s="29"/>
+      <c r="F615" s="29"/>
       <c r="G615" s="30"/>
       <c r="H615" s="30"/>
       <c r="I615" s="30"/>
@@ -10951,6 +11068,7 @@
       <c r="B616" s="28"/>
       <c r="C616" s="28"/>
       <c r="E616" s="29"/>
+      <c r="F616" s="29"/>
       <c r="G616" s="30"/>
       <c r="H616" s="30"/>
       <c r="I616" s="30"/>
@@ -10961,6 +11079,7 @@
       <c r="B617" s="28"/>
       <c r="C617" s="28"/>
       <c r="E617" s="29"/>
+      <c r="F617" s="29"/>
       <c r="G617" s="30"/>
       <c r="H617" s="30"/>
       <c r="I617" s="30"/>
@@ -10971,6 +11090,7 @@
       <c r="B618" s="28"/>
       <c r="C618" s="28"/>
       <c r="E618" s="29"/>
+      <c r="F618" s="29"/>
       <c r="G618" s="30"/>
       <c r="H618" s="30"/>
       <c r="I618" s="30"/>
@@ -10981,6 +11101,7 @@
       <c r="B619" s="28"/>
       <c r="C619" s="28"/>
       <c r="E619" s="29"/>
+      <c r="F619" s="29"/>
       <c r="G619" s="30"/>
       <c r="H619" s="30"/>
       <c r="I619" s="30"/>
@@ -10991,6 +11112,7 @@
       <c r="B620" s="28"/>
       <c r="C620" s="28"/>
       <c r="E620" s="29"/>
+      <c r="F620" s="29"/>
       <c r="G620" s="30"/>
       <c r="H620" s="30"/>
       <c r="I620" s="30"/>
@@ -11001,6 +11123,7 @@
       <c r="B621" s="28"/>
       <c r="C621" s="28"/>
       <c r="E621" s="29"/>
+      <c r="F621" s="29"/>
       <c r="G621" s="30"/>
       <c r="H621" s="30"/>
       <c r="I621" s="30"/>
@@ -11011,6 +11134,7 @@
       <c r="B622" s="28"/>
       <c r="C622" s="28"/>
       <c r="E622" s="29"/>
+      <c r="F622" s="29"/>
       <c r="G622" s="30"/>
       <c r="H622" s="30"/>
       <c r="I622" s="30"/>
@@ -11021,6 +11145,7 @@
       <c r="B623" s="28"/>
       <c r="C623" s="28"/>
       <c r="E623" s="29"/>
+      <c r="F623" s="29"/>
       <c r="G623" s="30"/>
       <c r="H623" s="30"/>
       <c r="I623" s="30"/>
@@ -11031,6 +11156,7 @@
       <c r="B624" s="28"/>
       <c r="C624" s="28"/>
       <c r="E624" s="29"/>
+      <c r="F624" s="29"/>
       <c r="G624" s="30"/>
       <c r="H624" s="30"/>
       <c r="I624" s="30"/>
@@ -11041,6 +11167,7 @@
       <c r="B625" s="28"/>
       <c r="C625" s="28"/>
       <c r="E625" s="29"/>
+      <c r="F625" s="29"/>
       <c r="G625" s="30"/>
       <c r="H625" s="30"/>
       <c r="I625" s="30"/>
@@ -11051,6 +11178,7 @@
       <c r="B626" s="28"/>
       <c r="C626" s="28"/>
       <c r="E626" s="29"/>
+      <c r="F626" s="29"/>
       <c r="G626" s="30"/>
       <c r="H626" s="30"/>
       <c r="I626" s="30"/>
@@ -11061,6 +11189,7 @@
       <c r="B627" s="28"/>
       <c r="C627" s="28"/>
       <c r="E627" s="29"/>
+      <c r="F627" s="29"/>
       <c r="G627" s="30"/>
       <c r="H627" s="30"/>
       <c r="I627" s="30"/>
@@ -11071,6 +11200,7 @@
       <c r="B628" s="28"/>
       <c r="C628" s="28"/>
       <c r="E628" s="29"/>
+      <c r="F628" s="29"/>
       <c r="G628" s="30"/>
       <c r="H628" s="30"/>
       <c r="I628" s="30"/>
@@ -11081,6 +11211,7 @@
       <c r="B629" s="28"/>
       <c r="C629" s="28"/>
       <c r="E629" s="29"/>
+      <c r="F629" s="29"/>
       <c r="G629" s="30"/>
       <c r="H629" s="30"/>
       <c r="I629" s="30"/>
@@ -11091,6 +11222,7 @@
       <c r="B630" s="28"/>
       <c r="C630" s="28"/>
       <c r="E630" s="29"/>
+      <c r="F630" s="29"/>
       <c r="G630" s="30"/>
       <c r="H630" s="30"/>
       <c r="I630" s="30"/>
@@ -11101,6 +11233,7 @@
       <c r="B631" s="28"/>
       <c r="C631" s="28"/>
       <c r="E631" s="29"/>
+      <c r="F631" s="29"/>
       <c r="G631" s="30"/>
       <c r="H631" s="30"/>
       <c r="I631" s="30"/>
@@ -11111,6 +11244,7 @@
       <c r="B632" s="28"/>
       <c r="C632" s="28"/>
       <c r="E632" s="29"/>
+      <c r="F632" s="29"/>
       <c r="G632" s="30"/>
       <c r="H632" s="30"/>
       <c r="I632" s="30"/>
@@ -11121,6 +11255,7 @@
       <c r="B633" s="28"/>
       <c r="C633" s="28"/>
       <c r="E633" s="29"/>
+      <c r="F633" s="29"/>
       <c r="G633" s="30"/>
       <c r="H633" s="30"/>
       <c r="I633" s="30"/>
@@ -11131,6 +11266,7 @@
       <c r="B634" s="28"/>
       <c r="C634" s="28"/>
       <c r="E634" s="29"/>
+      <c r="F634" s="29"/>
       <c r="G634" s="30"/>
       <c r="H634" s="30"/>
       <c r="I634" s="30"/>
@@ -11141,6 +11277,7 @@
       <c r="B635" s="28"/>
       <c r="C635" s="28"/>
       <c r="E635" s="29"/>
+      <c r="F635" s="29"/>
       <c r="G635" s="30"/>
       <c r="H635" s="30"/>
       <c r="I635" s="30"/>
@@ -11151,6 +11288,7 @@
       <c r="B636" s="28"/>
       <c r="C636" s="28"/>
       <c r="E636" s="29"/>
+      <c r="F636" s="29"/>
       <c r="G636" s="30"/>
       <c r="H636" s="30"/>
       <c r="I636" s="30"/>
@@ -11161,6 +11299,7 @@
       <c r="B637" s="28"/>
       <c r="C637" s="28"/>
       <c r="E637" s="29"/>
+      <c r="F637" s="29"/>
       <c r="G637" s="30"/>
       <c r="H637" s="30"/>
       <c r="I637" s="30"/>
@@ -11171,6 +11310,7 @@
       <c r="B638" s="28"/>
       <c r="C638" s="28"/>
       <c r="E638" s="29"/>
+      <c r="F638" s="29"/>
       <c r="G638" s="30"/>
       <c r="H638" s="30"/>
       <c r="I638" s="30"/>
@@ -11181,6 +11321,7 @@
       <c r="B639" s="28"/>
       <c r="C639" s="28"/>
       <c r="E639" s="29"/>
+      <c r="F639" s="29"/>
       <c r="G639" s="30"/>
       <c r="H639" s="30"/>
       <c r="I639" s="30"/>
@@ -11191,6 +11332,7 @@
       <c r="B640" s="28"/>
       <c r="C640" s="28"/>
       <c r="E640" s="29"/>
+      <c r="F640" s="29"/>
       <c r="G640" s="30"/>
       <c r="H640" s="30"/>
       <c r="I640" s="30"/>
@@ -11201,6 +11343,7 @@
       <c r="B641" s="28"/>
       <c r="C641" s="28"/>
       <c r="E641" s="29"/>
+      <c r="F641" s="29"/>
       <c r="G641" s="30"/>
       <c r="H641" s="30"/>
       <c r="I641" s="30"/>
@@ -11211,6 +11354,7 @@
       <c r="B642" s="28"/>
       <c r="C642" s="28"/>
       <c r="E642" s="29"/>
+      <c r="F642" s="29"/>
       <c r="G642" s="30"/>
       <c r="H642" s="30"/>
       <c r="I642" s="30"/>
@@ -11221,6 +11365,7 @@
       <c r="B643" s="28"/>
       <c r="C643" s="28"/>
       <c r="E643" s="29"/>
+      <c r="F643" s="29"/>
       <c r="G643" s="30"/>
       <c r="H643" s="30"/>
       <c r="I643" s="30"/>
@@ -11231,6 +11376,7 @@
       <c r="B644" s="28"/>
       <c r="C644" s="28"/>
       <c r="E644" s="29"/>
+      <c r="F644" s="29"/>
       <c r="G644" s="30"/>
       <c r="H644" s="30"/>
       <c r="I644" s="30"/>
@@ -11241,6 +11387,7 @@
       <c r="B645" s="28"/>
       <c r="C645" s="28"/>
       <c r="E645" s="29"/>
+      <c r="F645" s="29"/>
       <c r="G645" s="30"/>
       <c r="H645" s="30"/>
       <c r="I645" s="30"/>
@@ -11251,6 +11398,7 @@
       <c r="B646" s="28"/>
       <c r="C646" s="28"/>
       <c r="E646" s="29"/>
+      <c r="F646" s="29"/>
       <c r="G646" s="30"/>
       <c r="H646" s="30"/>
       <c r="I646" s="30"/>
@@ -11261,6 +11409,7 @@
       <c r="B647" s="28"/>
       <c r="C647" s="28"/>
       <c r="E647" s="29"/>
+      <c r="F647" s="29"/>
       <c r="G647" s="30"/>
       <c r="H647" s="30"/>
       <c r="I647" s="30"/>
@@ -11271,6 +11420,7 @@
       <c r="B648" s="28"/>
       <c r="C648" s="28"/>
       <c r="E648" s="29"/>
+      <c r="F648" s="29"/>
       <c r="G648" s="30"/>
       <c r="H648" s="30"/>
       <c r="I648" s="30"/>
@@ -11281,6 +11431,7 @@
       <c r="B649" s="28"/>
       <c r="C649" s="28"/>
       <c r="E649" s="29"/>
+      <c r="F649" s="29"/>
       <c r="G649" s="30"/>
       <c r="H649" s="30"/>
       <c r="I649" s="30"/>
@@ -11291,6 +11442,7 @@
       <c r="B650" s="28"/>
       <c r="C650" s="28"/>
       <c r="E650" s="29"/>
+      <c r="F650" s="29"/>
       <c r="G650" s="30"/>
       <c r="H650" s="30"/>
       <c r="I650" s="30"/>
@@ -11301,6 +11453,7 @@
       <c r="B651" s="28"/>
       <c r="C651" s="28"/>
       <c r="E651" s="29"/>
+      <c r="F651" s="29"/>
       <c r="G651" s="30"/>
       <c r="H651" s="30"/>
       <c r="I651" s="30"/>
@@ -11311,6 +11464,7 @@
       <c r="B652" s="28"/>
       <c r="C652" s="28"/>
       <c r="E652" s="29"/>
+      <c r="F652" s="29"/>
       <c r="G652" s="30"/>
       <c r="H652" s="30"/>
       <c r="I652" s="30"/>
@@ -11321,6 +11475,7 @@
       <c r="B653" s="28"/>
       <c r="C653" s="28"/>
       <c r="E653" s="29"/>
+      <c r="F653" s="29"/>
       <c r="G653" s="30"/>
       <c r="H653" s="30"/>
       <c r="I653" s="30"/>
@@ -11331,6 +11486,7 @@
       <c r="B654" s="28"/>
       <c r="C654" s="28"/>
       <c r="E654" s="29"/>
+      <c r="F654" s="29"/>
       <c r="G654" s="30"/>
       <c r="H654" s="30"/>
       <c r="I654" s="30"/>
@@ -11341,6 +11497,7 @@
       <c r="B655" s="28"/>
       <c r="C655" s="28"/>
       <c r="E655" s="29"/>
+      <c r="F655" s="29"/>
       <c r="G655" s="30"/>
       <c r="H655" s="30"/>
       <c r="I655" s="30"/>
@@ -11351,6 +11508,7 @@
       <c r="B656" s="28"/>
       <c r="C656" s="28"/>
       <c r="E656" s="29"/>
+      <c r="F656" s="29"/>
       <c r="G656" s="30"/>
       <c r="H656" s="30"/>
       <c r="I656" s="30"/>
@@ -11361,6 +11519,7 @@
       <c r="B657" s="28"/>
       <c r="C657" s="28"/>
       <c r="E657" s="29"/>
+      <c r="F657" s="29"/>
       <c r="G657" s="30"/>
       <c r="H657" s="30"/>
       <c r="I657" s="30"/>
@@ -11371,6 +11530,7 @@
       <c r="B658" s="28"/>
       <c r="C658" s="28"/>
       <c r="E658" s="29"/>
+      <c r="F658" s="29"/>
       <c r="G658" s="30"/>
       <c r="H658" s="30"/>
       <c r="I658" s="30"/>
@@ -11381,6 +11541,7 @@
       <c r="B659" s="28"/>
       <c r="C659" s="28"/>
       <c r="E659" s="29"/>
+      <c r="F659" s="29"/>
       <c r="G659" s="30"/>
       <c r="H659" s="30"/>
       <c r="I659" s="30"/>
@@ -11391,6 +11552,7 @@
       <c r="B660" s="28"/>
       <c r="C660" s="28"/>
       <c r="E660" s="29"/>
+      <c r="F660" s="29"/>
       <c r="G660" s="30"/>
       <c r="H660" s="30"/>
       <c r="I660" s="30"/>
@@ -11401,6 +11563,7 @@
       <c r="B661" s="28"/>
       <c r="C661" s="28"/>
       <c r="E661" s="29"/>
+      <c r="F661" s="29"/>
       <c r="G661" s="30"/>
       <c r="H661" s="30"/>
       <c r="I661" s="30"/>
@@ -11411,6 +11574,7 @@
       <c r="B662" s="28"/>
       <c r="C662" s="28"/>
       <c r="E662" s="29"/>
+      <c r="F662" s="29"/>
       <c r="G662" s="30"/>
       <c r="H662" s="30"/>
       <c r="I662" s="30"/>
@@ -11421,6 +11585,7 @@
       <c r="B663" s="28"/>
       <c r="C663" s="28"/>
       <c r="E663" s="29"/>
+      <c r="F663" s="29"/>
       <c r="G663" s="30"/>
       <c r="H663" s="30"/>
       <c r="I663" s="30"/>
@@ -11431,6 +11596,7 @@
       <c r="B664" s="28"/>
       <c r="C664" s="28"/>
       <c r="E664" s="29"/>
+      <c r="F664" s="29"/>
       <c r="G664" s="30"/>
       <c r="H664" s="30"/>
       <c r="I664" s="30"/>
@@ -11441,6 +11607,7 @@
       <c r="B665" s="28"/>
       <c r="C665" s="28"/>
       <c r="E665" s="29"/>
+      <c r="F665" s="29"/>
       <c r="G665" s="30"/>
       <c r="H665" s="30"/>
       <c r="I665" s="30"/>
@@ -11451,6 +11618,7 @@
       <c r="B666" s="28"/>
       <c r="C666" s="28"/>
       <c r="E666" s="29"/>
+      <c r="F666" s="29"/>
       <c r="G666" s="30"/>
       <c r="H666" s="30"/>
       <c r="I666" s="30"/>
@@ -11461,6 +11629,7 @@
       <c r="B667" s="28"/>
       <c r="C667" s="28"/>
       <c r="E667" s="29"/>
+      <c r="F667" s="29"/>
       <c r="G667" s="30"/>
       <c r="H667" s="30"/>
       <c r="I667" s="30"/>
@@ -11471,6 +11640,7 @@
       <c r="B668" s="28"/>
       <c r="C668" s="28"/>
       <c r="E668" s="29"/>
+      <c r="F668" s="29"/>
       <c r="G668" s="30"/>
       <c r="H668" s="30"/>
       <c r="I668" s="30"/>
@@ -11481,6 +11651,7 @@
       <c r="B669" s="28"/>
       <c r="C669" s="28"/>
       <c r="E669" s="29"/>
+      <c r="F669" s="29"/>
       <c r="G669" s="30"/>
       <c r="H669" s="30"/>
       <c r="I669" s="30"/>
@@ -11491,6 +11662,7 @@
       <c r="B670" s="28"/>
       <c r="C670" s="28"/>
       <c r="E670" s="29"/>
+      <c r="F670" s="29"/>
       <c r="G670" s="30"/>
       <c r="H670" s="30"/>
       <c r="I670" s="30"/>
@@ -11501,6 +11673,7 @@
       <c r="B671" s="28"/>
       <c r="C671" s="28"/>
       <c r="E671" s="29"/>
+      <c r="F671" s="29"/>
       <c r="G671" s="30"/>
       <c r="H671" s="30"/>
       <c r="I671" s="30"/>
@@ -11511,6 +11684,7 @@
       <c r="B672" s="28"/>
       <c r="C672" s="28"/>
       <c r="E672" s="29"/>
+      <c r="F672" s="29"/>
       <c r="G672" s="30"/>
       <c r="H672" s="30"/>
       <c r="I672" s="30"/>
@@ -11521,6 +11695,7 @@
       <c r="B673" s="28"/>
       <c r="C673" s="28"/>
       <c r="E673" s="29"/>
+      <c r="F673" s="29"/>
       <c r="G673" s="30"/>
       <c r="H673" s="30"/>
       <c r="I673" s="30"/>
@@ -11531,6 +11706,7 @@
       <c r="B674" s="28"/>
       <c r="C674" s="28"/>
       <c r="E674" s="29"/>
+      <c r="F674" s="29"/>
       <c r="G674" s="30"/>
       <c r="H674" s="30"/>
       <c r="I674" s="30"/>
@@ -11541,6 +11717,7 @@
       <c r="B675" s="28"/>
       <c r="C675" s="28"/>
       <c r="E675" s="29"/>
+      <c r="F675" s="29"/>
       <c r="G675" s="30"/>
       <c r="H675" s="30"/>
       <c r="I675" s="30"/>
@@ -11551,6 +11728,7 @@
       <c r="B676" s="28"/>
       <c r="C676" s="28"/>
       <c r="E676" s="29"/>
+      <c r="F676" s="29"/>
       <c r="G676" s="30"/>
       <c r="H676" s="30"/>
       <c r="I676" s="30"/>
@@ -11561,6 +11739,7 @@
       <c r="B677" s="28"/>
       <c r="C677" s="28"/>
       <c r="E677" s="29"/>
+      <c r="F677" s="29"/>
       <c r="G677" s="30"/>
       <c r="H677" s="30"/>
       <c r="I677" s="30"/>
@@ -11571,6 +11750,7 @@
       <c r="B678" s="28"/>
       <c r="C678" s="28"/>
       <c r="E678" s="29"/>
+      <c r="F678" s="29"/>
       <c r="G678" s="30"/>
       <c r="H678" s="30"/>
       <c r="I678" s="30"/>
@@ -11581,6 +11761,7 @@
       <c r="B679" s="28"/>
       <c r="C679" s="28"/>
       <c r="E679" s="29"/>
+      <c r="F679" s="29"/>
       <c r="G679" s="30"/>
       <c r="H679" s="30"/>
       <c r="I679" s="30"/>
@@ -11591,6 +11772,7 @@
       <c r="B680" s="28"/>
       <c r="C680" s="28"/>
       <c r="E680" s="29"/>
+      <c r="F680" s="29"/>
       <c r="G680" s="30"/>
       <c r="H680" s="30"/>
       <c r="I680" s="30"/>
@@ -11601,6 +11783,7 @@
       <c r="B681" s="28"/>
       <c r="C681" s="28"/>
       <c r="E681" s="29"/>
+      <c r="F681" s="29"/>
       <c r="G681" s="30"/>
       <c r="H681" s="30"/>
       <c r="I681" s="30"/>
@@ -11611,6 +11794,7 @@
       <c r="B682" s="28"/>
       <c r="C682" s="28"/>
       <c r="E682" s="29"/>
+      <c r="F682" s="29"/>
       <c r="G682" s="30"/>
       <c r="H682" s="30"/>
       <c r="I682" s="30"/>
@@ -11621,6 +11805,7 @@
       <c r="B683" s="28"/>
       <c r="C683" s="28"/>
       <c r="E683" s="29"/>
+      <c r="F683" s="29"/>
       <c r="G683" s="30"/>
       <c r="H683" s="30"/>
       <c r="I683" s="30"/>
@@ -11631,6 +11816,7 @@
       <c r="B684" s="28"/>
       <c r="C684" s="28"/>
       <c r="E684" s="29"/>
+      <c r="F684" s="29"/>
       <c r="G684" s="30"/>
       <c r="H684" s="30"/>
       <c r="I684" s="30"/>
@@ -11641,6 +11827,7 @@
       <c r="B685" s="28"/>
       <c r="C685" s="28"/>
       <c r="E685" s="29"/>
+      <c r="F685" s="29"/>
       <c r="G685" s="30"/>
       <c r="H685" s="30"/>
       <c r="I685" s="30"/>
@@ -11651,6 +11838,7 @@
       <c r="B686" s="28"/>
       <c r="C686" s="28"/>
       <c r="E686" s="29"/>
+      <c r="F686" s="29"/>
       <c r="G686" s="30"/>
       <c r="H686" s="30"/>
       <c r="I686" s="30"/>
@@ -11661,6 +11849,7 @@
       <c r="B687" s="28"/>
       <c r="C687" s="28"/>
       <c r="E687" s="29"/>
+      <c r="F687" s="29"/>
       <c r="G687" s="30"/>
       <c r="H687" s="30"/>
       <c r="I687" s="30"/>
@@ -11671,6 +11860,7 @@
       <c r="B688" s="28"/>
       <c r="C688" s="28"/>
       <c r="E688" s="29"/>
+      <c r="F688" s="29"/>
       <c r="G688" s="30"/>
       <c r="H688" s="30"/>
       <c r="I688" s="30"/>
@@ -11681,6 +11871,7 @@
       <c r="B689" s="28"/>
       <c r="C689" s="28"/>
       <c r="E689" s="29"/>
+      <c r="F689" s="29"/>
       <c r="G689" s="30"/>
       <c r="H689" s="30"/>
       <c r="I689" s="30"/>
@@ -11691,6 +11882,7 @@
       <c r="B690" s="28"/>
       <c r="C690" s="28"/>
       <c r="E690" s="29"/>
+      <c r="F690" s="29"/>
       <c r="G690" s="30"/>
       <c r="H690" s="30"/>
       <c r="I690" s="30"/>
@@ -11701,6 +11893,7 @@
       <c r="B691" s="28"/>
       <c r="C691" s="28"/>
       <c r="E691" s="29"/>
+      <c r="F691" s="29"/>
       <c r="G691" s="30"/>
       <c r="H691" s="30"/>
       <c r="I691" s="30"/>
@@ -11711,6 +11904,7 @@
       <c r="B692" s="28"/>
       <c r="C692" s="28"/>
       <c r="E692" s="29"/>
+      <c r="F692" s="29"/>
       <c r="G692" s="30"/>
       <c r="H692" s="30"/>
       <c r="I692" s="30"/>
@@ -11721,6 +11915,7 @@
       <c r="B693" s="28"/>
       <c r="C693" s="28"/>
       <c r="E693" s="29"/>
+      <c r="F693" s="29"/>
       <c r="G693" s="30"/>
       <c r="H693" s="30"/>
       <c r="I693" s="30"/>
@@ -11731,6 +11926,7 @@
       <c r="B694" s="28"/>
       <c r="C694" s="28"/>
       <c r="E694" s="29"/>
+      <c r="F694" s="29"/>
       <c r="G694" s="30"/>
       <c r="H694" s="30"/>
       <c r="I694" s="30"/>
@@ -11741,6 +11937,7 @@
       <c r="B695" s="28"/>
       <c r="C695" s="28"/>
       <c r="E695" s="29"/>
+      <c r="F695" s="29"/>
       <c r="G695" s="30"/>
       <c r="H695" s="30"/>
       <c r="I695" s="30"/>
@@ -11751,6 +11948,7 @@
       <c r="B696" s="28"/>
       <c r="C696" s="28"/>
       <c r="E696" s="29"/>
+      <c r="F696" s="29"/>
       <c r="G696" s="30"/>
       <c r="H696" s="30"/>
       <c r="I696" s="30"/>
@@ -11761,6 +11959,7 @@
       <c r="B697" s="28"/>
       <c r="C697" s="28"/>
       <c r="E697" s="29"/>
+      <c r="F697" s="29"/>
       <c r="G697" s="30"/>
       <c r="H697" s="30"/>
       <c r="I697" s="30"/>
@@ -11771,6 +11970,7 @@
       <c r="B698" s="28"/>
       <c r="C698" s="28"/>
       <c r="E698" s="29"/>
+      <c r="F698" s="29"/>
       <c r="G698" s="30"/>
       <c r="H698" s="30"/>
       <c r="I698" s="30"/>
@@ -11781,6 +11981,7 @@
       <c r="B699" s="28"/>
       <c r="C699" s="28"/>
       <c r="E699" s="29"/>
+      <c r="F699" s="29"/>
       <c r="G699" s="30"/>
       <c r="H699" s="30"/>
       <c r="I699" s="30"/>
@@ -11791,6 +11992,7 @@
       <c r="B700" s="28"/>
       <c r="C700" s="28"/>
       <c r="E700" s="29"/>
+      <c r="F700" s="29"/>
       <c r="G700" s="30"/>
       <c r="H700" s="30"/>
       <c r="I700" s="30"/>
@@ -11801,6 +12003,7 @@
       <c r="B701" s="28"/>
       <c r="C701" s="28"/>
       <c r="E701" s="29"/>
+      <c r="F701" s="29"/>
       <c r="G701" s="30"/>
       <c r="H701" s="30"/>
       <c r="I701" s="30"/>
@@ -11811,6 +12014,7 @@
       <c r="B702" s="28"/>
       <c r="C702" s="28"/>
       <c r="E702" s="29"/>
+      <c r="F702" s="29"/>
       <c r="G702" s="30"/>
       <c r="H702" s="30"/>
       <c r="I702" s="30"/>
@@ -11821,6 +12025,7 @@
       <c r="B703" s="28"/>
       <c r="C703" s="28"/>
       <c r="E703" s="29"/>
+      <c r="F703" s="29"/>
       <c r="G703" s="30"/>
       <c r="H703" s="30"/>
       <c r="I703" s="30"/>
@@ -11831,6 +12036,7 @@
       <c r="B704" s="28"/>
       <c r="C704" s="28"/>
       <c r="E704" s="29"/>
+      <c r="F704" s="29"/>
       <c r="G704" s="30"/>
       <c r="H704" s="30"/>
       <c r="I704" s="30"/>
@@ -11841,6 +12047,7 @@
       <c r="B705" s="28"/>
       <c r="C705" s="28"/>
       <c r="E705" s="29"/>
+      <c r="F705" s="29"/>
       <c r="G705" s="30"/>
       <c r="H705" s="30"/>
       <c r="I705" s="30"/>
@@ -11851,6 +12058,7 @@
       <c r="B706" s="28"/>
       <c r="C706" s="28"/>
       <c r="E706" s="29"/>
+      <c r="F706" s="29"/>
       <c r="G706" s="30"/>
       <c r="H706" s="30"/>
       <c r="I706" s="30"/>
@@ -11861,6 +12069,7 @@
       <c r="B707" s="28"/>
       <c r="C707" s="28"/>
       <c r="E707" s="29"/>
+      <c r="F707" s="29"/>
       <c r="G707" s="30"/>
       <c r="H707" s="30"/>
       <c r="I707" s="30"/>
@@ -11871,6 +12080,7 @@
       <c r="B708" s="28"/>
       <c r="C708" s="28"/>
       <c r="E708" s="29"/>
+      <c r="F708" s="29"/>
       <c r="G708" s="30"/>
       <c r="H708" s="30"/>
       <c r="I708" s="30"/>
@@ -11881,6 +12091,7 @@
       <c r="B709" s="28"/>
       <c r="C709" s="28"/>
       <c r="E709" s="29"/>
+      <c r="F709" s="29"/>
       <c r="G709" s="30"/>
       <c r="H709" s="30"/>
       <c r="I709" s="30"/>
@@ -11891,6 +12102,7 @@
       <c r="B710" s="28"/>
       <c r="C710" s="28"/>
       <c r="E710" s="29"/>
+      <c r="F710" s="29"/>
       <c r="G710" s="30"/>
       <c r="H710" s="30"/>
       <c r="I710" s="30"/>
@@ -11901,6 +12113,7 @@
       <c r="B711" s="28"/>
       <c r="C711" s="28"/>
       <c r="E711" s="29"/>
+      <c r="F711" s="29"/>
       <c r="G711" s="30"/>
       <c r="H711" s="30"/>
       <c r="I711" s="30"/>
@@ -11911,6 +12124,7 @@
       <c r="B712" s="28"/>
       <c r="C712" s="28"/>
       <c r="E712" s="29"/>
+      <c r="F712" s="29"/>
       <c r="G712" s="30"/>
       <c r="H712" s="30"/>
       <c r="I712" s="30"/>
@@ -11921,6 +12135,7 @@
       <c r="B713" s="28"/>
       <c r="C713" s="28"/>
       <c r="E713" s="29"/>
+      <c r="F713" s="29"/>
       <c r="G713" s="30"/>
       <c r="H713" s="30"/>
       <c r="I713" s="30"/>
@@ -11931,6 +12146,7 @@
       <c r="B714" s="28"/>
       <c r="C714" s="28"/>
       <c r="E714" s="29"/>
+      <c r="F714" s="29"/>
       <c r="G714" s="30"/>
       <c r="H714" s="30"/>
       <c r="I714" s="30"/>
@@ -11941,6 +12157,7 @@
       <c r="B715" s="28"/>
       <c r="C715" s="28"/>
       <c r="E715" s="29"/>
+      <c r="F715" s="29"/>
       <c r="G715" s="30"/>
       <c r="H715" s="30"/>
       <c r="I715" s="30"/>
@@ -11951,6 +12168,7 @@
       <c r="B716" s="28"/>
       <c r="C716" s="28"/>
       <c r="E716" s="29"/>
+      <c r="F716" s="29"/>
       <c r="G716" s="30"/>
       <c r="H716" s="30"/>
       <c r="I716" s="30"/>
@@ -11961,6 +12179,7 @@
       <c r="B717" s="28"/>
       <c r="C717" s="28"/>
       <c r="E717" s="29"/>
+      <c r="F717" s="29"/>
       <c r="G717" s="30"/>
       <c r="H717" s="30"/>
       <c r="I717" s="30"/>
@@ -11971,6 +12190,7 @@
       <c r="B718" s="28"/>
       <c r="C718" s="28"/>
       <c r="E718" s="29"/>
+      <c r="F718" s="29"/>
       <c r="G718" s="30"/>
       <c r="H718" s="30"/>
       <c r="I718" s="30"/>
@@ -11981,6 +12201,7 @@
       <c r="B719" s="28"/>
       <c r="C719" s="28"/>
       <c r="E719" s="29"/>
+      <c r="F719" s="29"/>
       <c r="G719" s="30"/>
       <c r="H719" s="30"/>
       <c r="I719" s="30"/>
@@ -11991,6 +12212,7 @@
       <c r="B720" s="28"/>
       <c r="C720" s="28"/>
       <c r="E720" s="29"/>
+      <c r="F720" s="29"/>
       <c r="G720" s="30"/>
       <c r="H720" s="30"/>
       <c r="I720" s="30"/>
@@ -12001,6 +12223,7 @@
       <c r="B721" s="28"/>
       <c r="C721" s="28"/>
       <c r="E721" s="29"/>
+      <c r="F721" s="29"/>
       <c r="G721" s="30"/>
       <c r="H721" s="30"/>
       <c r="I721" s="30"/>
@@ -12011,6 +12234,7 @@
       <c r="B722" s="28"/>
       <c r="C722" s="28"/>
       <c r="E722" s="29"/>
+      <c r="F722" s="29"/>
       <c r="G722" s="30"/>
       <c r="H722" s="30"/>
       <c r="I722" s="30"/>
@@ -12021,6 +12245,7 @@
       <c r="B723" s="28"/>
       <c r="C723" s="28"/>
       <c r="E723" s="29"/>
+      <c r="F723" s="29"/>
       <c r="G723" s="30"/>
       <c r="H723" s="30"/>
       <c r="I723" s="30"/>
@@ -12031,6 +12256,7 @@
       <c r="B724" s="28"/>
       <c r="C724" s="28"/>
       <c r="E724" s="29"/>
+      <c r="F724" s="29"/>
       <c r="G724" s="30"/>
       <c r="H724" s="30"/>
       <c r="I724" s="30"/>
@@ -12041,6 +12267,7 @@
       <c r="B725" s="28"/>
       <c r="C725" s="28"/>
       <c r="E725" s="29"/>
+      <c r="F725" s="29"/>
       <c r="G725" s="30"/>
       <c r="H725" s="30"/>
       <c r="I725" s="30"/>
@@ -12051,6 +12278,7 @@
       <c r="B726" s="28"/>
       <c r="C726" s="28"/>
       <c r="E726" s="29"/>
+      <c r="F726" s="29"/>
       <c r="G726" s="30"/>
       <c r="H726" s="30"/>
       <c r="I726" s="30"/>
@@ -12061,6 +12289,7 @@
       <c r="B727" s="28"/>
       <c r="C727" s="28"/>
       <c r="E727" s="29"/>
+      <c r="F727" s="29"/>
       <c r="G727" s="30"/>
       <c r="H727" s="30"/>
       <c r="I727" s="30"/>
@@ -12071,6 +12300,7 @@
       <c r="B728" s="28"/>
       <c r="C728" s="28"/>
       <c r="E728" s="29"/>
+      <c r="F728" s="29"/>
       <c r="G728" s="30"/>
       <c r="H728" s="30"/>
       <c r="I728" s="30"/>
@@ -12081,6 +12311,7 @@
       <c r="B729" s="28"/>
       <c r="C729" s="28"/>
       <c r="E729" s="29"/>
+      <c r="F729" s="29"/>
       <c r="G729" s="30"/>
       <c r="H729" s="30"/>
       <c r="I729" s="30"/>
@@ -12091,6 +12322,7 @@
       <c r="B730" s="28"/>
       <c r="C730" s="28"/>
       <c r="E730" s="29"/>
+      <c r="F730" s="29"/>
       <c r="G730" s="30"/>
       <c r="H730" s="30"/>
       <c r="I730" s="30"/>
@@ -12101,6 +12333,7 @@
       <c r="B731" s="28"/>
       <c r="C731" s="28"/>
       <c r="E731" s="29"/>
+      <c r="F731" s="29"/>
       <c r="G731" s="30"/>
       <c r="H731" s="30"/>
       <c r="I731" s="30"/>
@@ -12111,6 +12344,7 @@
       <c r="B732" s="28"/>
       <c r="C732" s="28"/>
       <c r="E732" s="29"/>
+      <c r="F732" s="29"/>
       <c r="G732" s="30"/>
       <c r="H732" s="30"/>
       <c r="I732" s="30"/>
@@ -12121,6 +12355,7 @@
       <c r="B733" s="28"/>
       <c r="C733" s="28"/>
       <c r="E733" s="29"/>
+      <c r="F733" s="29"/>
       <c r="G733" s="30"/>
       <c r="H733" s="30"/>
       <c r="I733" s="30"/>
@@ -12131,6 +12366,7 @@
       <c r="B734" s="28"/>
       <c r="C734" s="28"/>
       <c r="E734" s="29"/>
+      <c r="F734" s="29"/>
       <c r="G734" s="30"/>
       <c r="H734" s="30"/>
       <c r="I734" s="30"/>
@@ -12141,6 +12377,7 @@
       <c r="B735" s="28"/>
       <c r="C735" s="28"/>
       <c r="E735" s="29"/>
+      <c r="F735" s="29"/>
       <c r="G735" s="30"/>
       <c r="H735" s="30"/>
       <c r="I735" s="30"/>
@@ -12151,6 +12388,7 @@
       <c r="B736" s="28"/>
       <c r="C736" s="28"/>
       <c r="E736" s="29"/>
+      <c r="F736" s="29"/>
       <c r="G736" s="30"/>
       <c r="H736" s="30"/>
       <c r="I736" s="30"/>
@@ -12161,6 +12399,7 @@
       <c r="B737" s="28"/>
       <c r="C737" s="28"/>
       <c r="E737" s="29"/>
+      <c r="F737" s="29"/>
       <c r="G737" s="30"/>
       <c r="H737" s="30"/>
       <c r="I737" s="30"/>
@@ -12171,6 +12410,7 @@
       <c r="B738" s="28"/>
       <c r="C738" s="28"/>
       <c r="E738" s="29"/>
+      <c r="F738" s="29"/>
       <c r="G738" s="30"/>
       <c r="H738" s="30"/>
       <c r="I738" s="30"/>
@@ -12181,6 +12421,7 @@
       <c r="B739" s="28"/>
       <c r="C739" s="28"/>
       <c r="E739" s="29"/>
+      <c r="F739" s="29"/>
       <c r="G739" s="30"/>
       <c r="H739" s="30"/>
       <c r="I739" s="30"/>
@@ -12191,6 +12432,7 @@
       <c r="B740" s="28"/>
       <c r="C740" s="28"/>
       <c r="E740" s="29"/>
+      <c r="F740" s="29"/>
       <c r="G740" s="30"/>
       <c r="H740" s="30"/>
       <c r="I740" s="30"/>
@@ -12201,6 +12443,7 @@
       <c r="B741" s="28"/>
       <c r="C741" s="28"/>
       <c r="E741" s="29"/>
+      <c r="F741" s="29"/>
       <c r="G741" s="30"/>
       <c r="H741" s="30"/>
       <c r="I741" s="30"/>
@@ -12211,6 +12454,7 @@
       <c r="B742" s="28"/>
       <c r="C742" s="28"/>
       <c r="E742" s="29"/>
+      <c r="F742" s="29"/>
       <c r="G742" s="30"/>
       <c r="H742" s="30"/>
       <c r="I742" s="30"/>
@@ -12221,6 +12465,7 @@
       <c r="B743" s="28"/>
       <c r="C743" s="28"/>
       <c r="E743" s="29"/>
+      <c r="F743" s="29"/>
       <c r="G743" s="30"/>
       <c r="H743" s="30"/>
       <c r="I743" s="30"/>
@@ -12231,6 +12476,7 @@
       <c r="B744" s="28"/>
       <c r="C744" s="28"/>
       <c r="E744" s="29"/>
+      <c r="F744" s="29"/>
       <c r="G744" s="30"/>
       <c r="H744" s="30"/>
       <c r="I744" s="30"/>
@@ -12241,6 +12487,7 @@
       <c r="B745" s="28"/>
       <c r="C745" s="28"/>
       <c r="E745" s="29"/>
+      <c r="F745" s="29"/>
       <c r="G745" s="30"/>
       <c r="H745" s="30"/>
       <c r="I745" s="30"/>
@@ -12251,6 +12498,7 @@
       <c r="B746" s="28"/>
       <c r="C746" s="28"/>
       <c r="E746" s="29"/>
+      <c r="F746" s="29"/>
       <c r="G746" s="30"/>
       <c r="H746" s="30"/>
       <c r="I746" s="30"/>
@@ -12261,6 +12509,7 @@
       <c r="B747" s="28"/>
       <c r="C747" s="28"/>
       <c r="E747" s="29"/>
+      <c r="F747" s="29"/>
       <c r="G747" s="30"/>
       <c r="H747" s="30"/>
       <c r="I747" s="30"/>
@@ -12271,6 +12520,7 @@
       <c r="B748" s="28"/>
       <c r="C748" s="28"/>
       <c r="E748" s="29"/>
+      <c r="F748" s="29"/>
       <c r="G748" s="30"/>
       <c r="H748" s="30"/>
       <c r="I748" s="30"/>
@@ -12281,6 +12531,7 @@
       <c r="B749" s="28"/>
       <c r="C749" s="28"/>
       <c r="E749" s="29"/>
+      <c r="F749" s="29"/>
       <c r="G749" s="30"/>
       <c r="H749" s="30"/>
       <c r="I749" s="30"/>
@@ -12291,6 +12542,7 @@
       <c r="B750" s="28"/>
       <c r="C750" s="28"/>
       <c r="E750" s="29"/>
+      <c r="F750" s="29"/>
       <c r="G750" s="30"/>
       <c r="H750" s="30"/>
       <c r="I750" s="30"/>
@@ -12301,6 +12553,7 @@
       <c r="B751" s="28"/>
       <c r="C751" s="28"/>
       <c r="E751" s="29"/>
+      <c r="F751" s="29"/>
       <c r="G751" s="30"/>
       <c r="H751" s="30"/>
       <c r="I751" s="30"/>
@@ -12311,6 +12564,7 @@
       <c r="B752" s="28"/>
       <c r="C752" s="28"/>
       <c r="E752" s="29"/>
+      <c r="F752" s="29"/>
       <c r="G752" s="30"/>
       <c r="H752" s="30"/>
       <c r="I752" s="30"/>
@@ -12321,6 +12575,7 @@
       <c r="B753" s="28"/>
       <c r="C753" s="28"/>
       <c r="E753" s="29"/>
+      <c r="F753" s="29"/>
       <c r="G753" s="30"/>
       <c r="H753" s="30"/>
       <c r="I753" s="30"/>
@@ -12331,6 +12586,7 @@
       <c r="B754" s="28"/>
       <c r="C754" s="28"/>
       <c r="E754" s="29"/>
+      <c r="F754" s="29"/>
       <c r="G754" s="30"/>
       <c r="H754" s="30"/>
       <c r="I754" s="30"/>
@@ -12341,6 +12597,7 @@
       <c r="B755" s="28"/>
       <c r="C755" s="28"/>
       <c r="E755" s="29"/>
+      <c r="F755" s="29"/>
       <c r="G755" s="30"/>
       <c r="H755" s="30"/>
       <c r="I755" s="30"/>
@@ -12351,6 +12608,7 @@
       <c r="B756" s="28"/>
       <c r="C756" s="28"/>
       <c r="E756" s="29"/>
+      <c r="F756" s="29"/>
       <c r="G756" s="30"/>
       <c r="H756" s="30"/>
       <c r="I756" s="30"/>
@@ -12361,6 +12619,7 @@
       <c r="B757" s="28"/>
       <c r="C757" s="28"/>
       <c r="E757" s="29"/>
+      <c r="F757" s="29"/>
       <c r="G757" s="30"/>
       <c r="H757" s="30"/>
       <c r="I757" s="30"/>
@@ -12371,6 +12630,7 @@
       <c r="B758" s="28"/>
       <c r="C758" s="28"/>
       <c r="E758" s="29"/>
+      <c r="F758" s="29"/>
       <c r="G758" s="30"/>
       <c r="H758" s="30"/>
       <c r="I758" s="30"/>
@@ -12381,6 +12641,7 @@
       <c r="B759" s="28"/>
       <c r="C759" s="28"/>
       <c r="E759" s="29"/>
+      <c r="F759" s="29"/>
       <c r="G759" s="30"/>
       <c r="H759" s="30"/>
       <c r="I759" s="30"/>
@@ -12391,6 +12652,7 @@
       <c r="B760" s="28"/>
       <c r="C760" s="28"/>
       <c r="E760" s="29"/>
+      <c r="F760" s="29"/>
       <c r="G760" s="30"/>
       <c r="H760" s="30"/>
       <c r="I760" s="30"/>
@@ -12401,6 +12663,7 @@
       <c r="B761" s="28"/>
       <c r="C761" s="28"/>
       <c r="E761" s="29"/>
+      <c r="F761" s="29"/>
       <c r="G761" s="30"/>
       <c r="H761" s="30"/>
       <c r="I761" s="30"/>
@@ -12411,6 +12674,7 @@
       <c r="B762" s="28"/>
       <c r="C762" s="28"/>
       <c r="E762" s="29"/>
+      <c r="F762" s="29"/>
       <c r="G762" s="30"/>
       <c r="H762" s="30"/>
       <c r="I762" s="30"/>
@@ -12421,6 +12685,7 @@
       <c r="B763" s="28"/>
       <c r="C763" s="28"/>
       <c r="E763" s="29"/>
+      <c r="F763" s="29"/>
       <c r="G763" s="30"/>
       <c r="H763" s="30"/>
       <c r="I763" s="30"/>
@@ -12431,6 +12696,7 @@
       <c r="B764" s="28"/>
       <c r="C764" s="28"/>
       <c r="E764" s="29"/>
+      <c r="F764" s="29"/>
       <c r="G764" s="30"/>
       <c r="H764" s="30"/>
       <c r="I764" s="30"/>
@@ -12441,6 +12707,7 @@
       <c r="B765" s="28"/>
       <c r="C765" s="28"/>
       <c r="E765" s="29"/>
+      <c r="F765" s="29"/>
       <c r="G765" s="30"/>
       <c r="H765" s="30"/>
       <c r="I765" s="30"/>
@@ -12451,6 +12718,7 @@
       <c r="B766" s="28"/>
       <c r="C766" s="28"/>
       <c r="E766" s="29"/>
+      <c r="F766" s="29"/>
       <c r="G766" s="30"/>
       <c r="H766" s="30"/>
       <c r="I766" s="30"/>
@@ -12461,6 +12729,7 @@
       <c r="B767" s="28"/>
       <c r="C767" s="28"/>
       <c r="E767" s="29"/>
+      <c r="F767" s="29"/>
       <c r="G767" s="30"/>
       <c r="H767" s="30"/>
       <c r="I767" s="30"/>
@@ -12471,6 +12740,7 @@
       <c r="B768" s="28"/>
       <c r="C768" s="28"/>
       <c r="E768" s="29"/>
+      <c r="F768" s="29"/>
       <c r="G768" s="30"/>
       <c r="H768" s="30"/>
       <c r="I768" s="30"/>
@@ -12481,6 +12751,7 @@
       <c r="B769" s="28"/>
       <c r="C769" s="28"/>
       <c r="E769" s="29"/>
+      <c r="F769" s="29"/>
       <c r="G769" s="30"/>
       <c r="H769" s="30"/>
       <c r="I769" s="30"/>
@@ -12491,6 +12762,7 @@
       <c r="B770" s="28"/>
       <c r="C770" s="28"/>
       <c r="E770" s="29"/>
+      <c r="F770" s="29"/>
       <c r="G770" s="30"/>
       <c r="H770" s="30"/>
       <c r="I770" s="30"/>
@@ -12501,6 +12773,7 @@
       <c r="B771" s="28"/>
       <c r="C771" s="28"/>
       <c r="E771" s="29"/>
+      <c r="F771" s="29"/>
       <c r="G771" s="30"/>
       <c r="H771" s="30"/>
       <c r="I771" s="30"/>
@@ -12511,6 +12784,7 @@
       <c r="B772" s="28"/>
       <c r="C772" s="28"/>
       <c r="E772" s="29"/>
+      <c r="F772" s="29"/>
       <c r="G772" s="30"/>
       <c r="H772" s="30"/>
       <c r="I772" s="30"/>
@@ -12521,6 +12795,7 @@
       <c r="B773" s="28"/>
       <c r="C773" s="28"/>
       <c r="E773" s="29"/>
+      <c r="F773" s="29"/>
       <c r="G773" s="30"/>
       <c r="H773" s="30"/>
       <c r="I773" s="30"/>
@@ -12531,6 +12806,7 @@
       <c r="B774" s="28"/>
       <c r="C774" s="28"/>
       <c r="E774" s="29"/>
+      <c r="F774" s="29"/>
       <c r="G774" s="30"/>
       <c r="H774" s="30"/>
       <c r="I774" s="30"/>
@@ -12541,6 +12817,7 @@
       <c r="B775" s="28"/>
       <c r="C775" s="28"/>
       <c r="E775" s="29"/>
+      <c r="F775" s="29"/>
       <c r="G775" s="30"/>
       <c r="H775" s="30"/>
       <c r="I775" s="30"/>
@@ -12551,6 +12828,7 @@
       <c r="B776" s="28"/>
       <c r="C776" s="28"/>
       <c r="E776" s="29"/>
+      <c r="F776" s="29"/>
       <c r="G776" s="30"/>
       <c r="H776" s="30"/>
       <c r="I776" s="30"/>
@@ -12561,6 +12839,7 @@
       <c r="B777" s="28"/>
       <c r="C777" s="28"/>
       <c r="E777" s="29"/>
+      <c r="F777" s="29"/>
       <c r="G777" s="30"/>
       <c r="H777" s="30"/>
       <c r="I777" s="30"/>
@@ -12571,6 +12850,7 @@
       <c r="B778" s="28"/>
       <c r="C778" s="28"/>
       <c r="E778" s="29"/>
+      <c r="F778" s="29"/>
       <c r="G778" s="30"/>
       <c r="H778" s="30"/>
       <c r="I778" s="30"/>
@@ -12581,6 +12861,7 @@
       <c r="B779" s="28"/>
       <c r="C779" s="28"/>
       <c r="E779" s="29"/>
+      <c r="F779" s="29"/>
       <c r="G779" s="30"/>
       <c r="H779" s="30"/>
       <c r="I779" s="30"/>
@@ -12591,6 +12872,7 @@
       <c r="B780" s="28"/>
       <c r="C780" s="28"/>
       <c r="E780" s="29"/>
+      <c r="F780" s="29"/>
       <c r="G780" s="30"/>
       <c r="H780" s="30"/>
       <c r="I780" s="30"/>
@@ -12601,6 +12883,7 @@
       <c r="B781" s="28"/>
       <c r="C781" s="28"/>
       <c r="E781" s="29"/>
+      <c r="F781" s="29"/>
       <c r="G781" s="30"/>
       <c r="H781" s="30"/>
       <c r="I781" s="30"/>
@@ -12611,6 +12894,7 @@
       <c r="B782" s="28"/>
       <c r="C782" s="28"/>
       <c r="E782" s="29"/>
+      <c r="F782" s="29"/>
       <c r="G782" s="30"/>
       <c r="H782" s="30"/>
       <c r="I782" s="30"/>
@@ -12621,6 +12905,7 @@
       <c r="B783" s="28"/>
       <c r="C783" s="28"/>
       <c r="E783" s="29"/>
+      <c r="F783" s="29"/>
       <c r="G783" s="30"/>
       <c r="H783" s="30"/>
       <c r="I783" s="30"/>
@@ -12631,6 +12916,7 @@
       <c r="B784" s="28"/>
       <c r="C784" s="28"/>
       <c r="E784" s="29"/>
+      <c r="F784" s="29"/>
       <c r="G784" s="30"/>
       <c r="H784" s="30"/>
       <c r="I784" s="30"/>
@@ -12641,6 +12927,7 @@
       <c r="B785" s="28"/>
       <c r="C785" s="28"/>
       <c r="E785" s="29"/>
+      <c r="F785" s="29"/>
       <c r="G785" s="30"/>
       <c r="H785" s="30"/>
       <c r="I785" s="30"/>
@@ -12651,6 +12938,7 @@
       <c r="B786" s="28"/>
       <c r="C786" s="28"/>
       <c r="E786" s="29"/>
+      <c r="F786" s="29"/>
       <c r="G786" s="30"/>
       <c r="H786" s="30"/>
       <c r="I786" s="30"/>
@@ -12661,6 +12949,7 @@
       <c r="B787" s="28"/>
       <c r="C787" s="28"/>
       <c r="E787" s="29"/>
+      <c r="F787" s="29"/>
       <c r="G787" s="30"/>
       <c r="H787" s="30"/>
       <c r="I787" s="30"/>
@@ -12671,6 +12960,7 @@
       <c r="B788" s="28"/>
       <c r="C788" s="28"/>
       <c r="E788" s="29"/>
+      <c r="F788" s="29"/>
       <c r="G788" s="30"/>
       <c r="H788" s="30"/>
       <c r="I788" s="30"/>
@@ -12681,6 +12971,7 @@
       <c r="B789" s="28"/>
       <c r="C789" s="28"/>
       <c r="E789" s="29"/>
+      <c r="F789" s="29"/>
       <c r="G789" s="30"/>
       <c r="H789" s="30"/>
       <c r="I789" s="30"/>
@@ -12691,6 +12982,7 @@
       <c r="B790" s="28"/>
       <c r="C790" s="28"/>
       <c r="E790" s="29"/>
+      <c r="F790" s="29"/>
       <c r="G790" s="30"/>
       <c r="H790" s="30"/>
       <c r="I790" s="30"/>
@@ -12701,6 +12993,7 @@
       <c r="B791" s="28"/>
       <c r="C791" s="28"/>
       <c r="E791" s="29"/>
+      <c r="F791" s="29"/>
       <c r="G791" s="30"/>
       <c r="H791" s="30"/>
       <c r="I791" s="30"/>
@@ -12711,6 +13004,7 @@
       <c r="B792" s="28"/>
       <c r="C792" s="28"/>
       <c r="E792" s="29"/>
+      <c r="F792" s="29"/>
       <c r="G792" s="30"/>
       <c r="H792" s="30"/>
       <c r="I792" s="30"/>
@@ -12721,6 +13015,7 @@
       <c r="B793" s="28"/>
       <c r="C793" s="28"/>
       <c r="E793" s="29"/>
+      <c r="F793" s="29"/>
       <c r="G793" s="30"/>
       <c r="H793" s="30"/>
       <c r="I793" s="30"/>
@@ -12731,6 +13026,7 @@
       <c r="B794" s="28"/>
       <c r="C794" s="28"/>
       <c r="E794" s="29"/>
+      <c r="F794" s="29"/>
       <c r="G794" s="30"/>
       <c r="H794" s="30"/>
       <c r="I794" s="30"/>
@@ -12741,6 +13037,7 @@
       <c r="B795" s="28"/>
       <c r="C795" s="28"/>
       <c r="E795" s="29"/>
+      <c r="F795" s="29"/>
       <c r="G795" s="30"/>
       <c r="H795" s="30"/>
       <c r="I795" s="30"/>
@@ -12751,6 +13048,7 @@
       <c r="B796" s="28"/>
       <c r="C796" s="28"/>
       <c r="E796" s="29"/>
+      <c r="F796" s="29"/>
       <c r="G796" s="30"/>
       <c r="H796" s="30"/>
       <c r="I796" s="30"/>
@@ -12761,6 +13059,7 @@
       <c r="B797" s="28"/>
       <c r="C797" s="28"/>
       <c r="E797" s="29"/>
+      <c r="F797" s="29"/>
       <c r="G797" s="30"/>
       <c r="H797" s="30"/>
       <c r="I797" s="30"/>
@@ -12771,6 +13070,7 @@
       <c r="B798" s="28"/>
       <c r="C798" s="28"/>
       <c r="E798" s="29"/>
+      <c r="F798" s="29"/>
       <c r="G798" s="30"/>
       <c r="H798" s="30"/>
       <c r="I798" s="30"/>
@@ -12781,6 +13081,7 @@
       <c r="B799" s="28"/>
       <c r="C799" s="28"/>
       <c r="E799" s="29"/>
+      <c r="F799" s="29"/>
       <c r="G799" s="30"/>
       <c r="H799" s="30"/>
       <c r="I799" s="30"/>
@@ -12791,6 +13092,7 @@
       <c r="B800" s="28"/>
       <c r="C800" s="28"/>
       <c r="E800" s="29"/>
+      <c r="F800" s="29"/>
       <c r="G800" s="30"/>
       <c r="H800" s="30"/>
       <c r="I800" s="30"/>
@@ -12801,6 +13103,7 @@
       <c r="B801" s="28"/>
       <c r="C801" s="28"/>
       <c r="E801" s="29"/>
+      <c r="F801" s="29"/>
       <c r="G801" s="30"/>
       <c r="H801" s="30"/>
       <c r="I801" s="30"/>
@@ -12811,6 +13114,7 @@
       <c r="B802" s="28"/>
       <c r="C802" s="28"/>
       <c r="E802" s="29"/>
+      <c r="F802" s="29"/>
       <c r="G802" s="30"/>
       <c r="H802" s="30"/>
       <c r="I802" s="30"/>
@@ -12821,6 +13125,7 @@
       <c r="B803" s="28"/>
       <c r="C803" s="28"/>
       <c r="E803" s="29"/>
+      <c r="F803" s="29"/>
       <c r="G803" s="30"/>
       <c r="H803" s="30"/>
       <c r="I803" s="30"/>
@@ -12831,6 +13136,7 @@
       <c r="B804" s="28"/>
       <c r="C804" s="28"/>
       <c r="E804" s="29"/>
+      <c r="F804" s="29"/>
       <c r="G804" s="30"/>
       <c r="H804" s="30"/>
       <c r="I804" s="30"/>
@@ -12841,6 +13147,7 @@
       <c r="B805" s="28"/>
       <c r="C805" s="28"/>
       <c r="E805" s="29"/>
+      <c r="F805" s="29"/>
       <c r="G805" s="30"/>
       <c r="H805" s="30"/>
       <c r="I805" s="30"/>
@@ -12851,6 +13158,7 @@
       <c r="B806" s="28"/>
       <c r="C806" s="28"/>
       <c r="E806" s="29"/>
+      <c r="F806" s="29"/>
       <c r="G806" s="30"/>
       <c r="H806" s="30"/>
       <c r="I806" s="30"/>
@@ -12861,6 +13169,7 @@
       <c r="B807" s="28"/>
       <c r="C807" s="28"/>
       <c r="E807" s="29"/>
+      <c r="F807" s="29"/>
       <c r="G807" s="30"/>
       <c r="H807" s="30"/>
       <c r="I807" s="30"/>
@@ -12871,6 +13180,7 @@
       <c r="B808" s="28"/>
       <c r="C808" s="28"/>
       <c r="E808" s="29"/>
+      <c r="F808" s="29"/>
       <c r="G808" s="30"/>
       <c r="H808" s="30"/>
       <c r="I808" s="30"/>
@@ -12881,6 +13191,7 @@
       <c r="B809" s="28"/>
       <c r="C809" s="28"/>
       <c r="E809" s="29"/>
+      <c r="F809" s="29"/>
       <c r="G809" s="30"/>
       <c r="H809" s="30"/>
       <c r="I809" s="30"/>
@@ -12891,6 +13202,7 @@
       <c r="B810" s="28"/>
       <c r="C810" s="28"/>
       <c r="E810" s="29"/>
+      <c r="F810" s="29"/>
       <c r="G810" s="30"/>
       <c r="H810" s="30"/>
       <c r="I810" s="30"/>
@@ -12901,6 +13213,7 @@
       <c r="B811" s="28"/>
       <c r="C811" s="28"/>
       <c r="E811" s="29"/>
+      <c r="F811" s="29"/>
       <c r="G811" s="30"/>
       <c r="H811" s="30"/>
       <c r="I811" s="30"/>
@@ -12911,6 +13224,7 @@
       <c r="B812" s="28"/>
       <c r="C812" s="28"/>
       <c r="E812" s="29"/>
+      <c r="F812" s="29"/>
       <c r="G812" s="30"/>
       <c r="H812" s="30"/>
       <c r="I812" s="30"/>
@@ -12921,6 +13235,7 @@
       <c r="B813" s="28"/>
       <c r="C813" s="28"/>
       <c r="E813" s="29"/>
+      <c r="F813" s="29"/>
       <c r="G813" s="30"/>
       <c r="H813" s="30"/>
       <c r="I813" s="30"/>
@@ -12931,6 +13246,7 @@
       <c r="B814" s="28"/>
       <c r="C814" s="28"/>
       <c r="E814" s="29"/>
+      <c r="F814" s="29"/>
       <c r="G814" s="30"/>
       <c r="H814" s="30"/>
       <c r="I814" s="30"/>
@@ -12941,6 +13257,7 @@
       <c r="B815" s="28"/>
       <c r="C815" s="28"/>
       <c r="E815" s="29"/>
+      <c r="F815" s="29"/>
       <c r="G815" s="30"/>
       <c r="H815" s="30"/>
       <c r="I815" s="30"/>
@@ -12951,6 +13268,7 @@
       <c r="B816" s="28"/>
       <c r="C816" s="28"/>
       <c r="E816" s="29"/>
+      <c r="F816" s="29"/>
       <c r="G816" s="30"/>
       <c r="H816" s="30"/>
       <c r="I816" s="30"/>
@@ -12961,6 +13279,7 @@
       <c r="B817" s="28"/>
       <c r="C817" s="28"/>
       <c r="E817" s="29"/>
+      <c r="F817" s="29"/>
       <c r="G817" s="30"/>
       <c r="H817" s="30"/>
       <c r="I817" s="30"/>
@@ -12971,6 +13290,7 @@
       <c r="B818" s="28"/>
       <c r="C818" s="28"/>
       <c r="E818" s="29"/>
+      <c r="F818" s="29"/>
       <c r="G818" s="30"/>
       <c r="H818" s="30"/>
       <c r="I818" s="30"/>
@@ -12981,6 +13301,7 @@
       <c r="B819" s="28"/>
       <c r="C819" s="28"/>
       <c r="E819" s="29"/>
+      <c r="F819" s="29"/>
       <c r="G819" s="30"/>
       <c r="H819" s="30"/>
       <c r="I819" s="30"/>
@@ -12991,6 +13312,7 @@
       <c r="B820" s="28"/>
       <c r="C820" s="28"/>
       <c r="E820" s="29"/>
+      <c r="F820" s="29"/>
       <c r="G820" s="30"/>
       <c r="H820" s="30"/>
       <c r="I820" s="30"/>
@@ -13001,6 +13323,7 @@
       <c r="B821" s="28"/>
       <c r="C821" s="28"/>
       <c r="E821" s="29"/>
+      <c r="F821" s="29"/>
       <c r="G821" s="30"/>
       <c r="H821" s="30"/>
       <c r="I821" s="30"/>
@@ -13011,6 +13334,7 @@
       <c r="B822" s="28"/>
       <c r="C822" s="28"/>
       <c r="E822" s="29"/>
+      <c r="F822" s="29"/>
       <c r="G822" s="30"/>
       <c r="H822" s="30"/>
       <c r="I822" s="30"/>
@@ -13021,6 +13345,7 @@
       <c r="B823" s="28"/>
       <c r="C823" s="28"/>
       <c r="E823" s="29"/>
+      <c r="F823" s="29"/>
       <c r="G823" s="30"/>
       <c r="H823" s="30"/>
       <c r="I823" s="30"/>
@@ -13031,6 +13356,7 @@
       <c r="B824" s="28"/>
       <c r="C824" s="28"/>
       <c r="E824" s="29"/>
+      <c r="F824" s="29"/>
       <c r="G824" s="30"/>
       <c r="H824" s="30"/>
       <c r="I824" s="30"/>
@@ -13041,6 +13367,7 @@
       <c r="B825" s="28"/>
       <c r="C825" s="28"/>
       <c r="E825" s="29"/>
+      <c r="F825" s="29"/>
       <c r="G825" s="30"/>
       <c r="H825" s="30"/>
       <c r="I825" s="30"/>
@@ -13051,6 +13378,7 @@
       <c r="B826" s="28"/>
       <c r="C826" s="28"/>
       <c r="E826" s="29"/>
+      <c r="F826" s="29"/>
       <c r="G826" s="30"/>
       <c r="H826" s="30"/>
       <c r="I826" s="30"/>
@@ -13061,6 +13389,7 @@
       <c r="B827" s="28"/>
       <c r="C827" s="28"/>
       <c r="E827" s="29"/>
+      <c r="F827" s="29"/>
       <c r="G827" s="30"/>
       <c r="H827" s="30"/>
       <c r="I827" s="30"/>
@@ -13071,6 +13400,7 @@
       <c r="B828" s="28"/>
       <c r="C828" s="28"/>
       <c r="E828" s="29"/>
+      <c r="F828" s="29"/>
       <c r="G828" s="30"/>
       <c r="H828" s="30"/>
       <c r="I828" s="30"/>
@@ -13081,6 +13411,7 @@
       <c r="B829" s="28"/>
       <c r="C829" s="28"/>
       <c r="E829" s="29"/>
+      <c r="F829" s="29"/>
       <c r="G829" s="30"/>
       <c r="H829" s="30"/>
       <c r="I829" s="30"/>
@@ -13091,6 +13422,7 @@
       <c r="B830" s="28"/>
       <c r="C830" s="28"/>
       <c r="E830" s="29"/>
+      <c r="F830" s="29"/>
       <c r="G830" s="30"/>
       <c r="H830" s="30"/>
       <c r="I830" s="30"/>
@@ -13101,6 +13433,7 @@
       <c r="B831" s="28"/>
       <c r="C831" s="28"/>
       <c r="E831" s="29"/>
+      <c r="F831" s="29"/>
       <c r="G831" s="30"/>
       <c r="H831" s="30"/>
       <c r="I831" s="30"/>
@@ -13111,6 +13444,7 @@
       <c r="B832" s="28"/>
       <c r="C832" s="28"/>
       <c r="E832" s="29"/>
+      <c r="F832" s="29"/>
       <c r="G832" s="30"/>
       <c r="H832" s="30"/>
       <c r="I832" s="30"/>
@@ -13121,6 +13455,7 @@
       <c r="B833" s="28"/>
       <c r="C833" s="28"/>
       <c r="E833" s="29"/>
+      <c r="F833" s="29"/>
       <c r="G833" s="30"/>
       <c r="H833" s="30"/>
       <c r="I833" s="30"/>
@@ -13131,6 +13466,7 @@
       <c r="B834" s="28"/>
       <c r="C834" s="28"/>
       <c r="E834" s="29"/>
+      <c r="F834" s="29"/>
       <c r="G834" s="30"/>
       <c r="H834" s="30"/>
       <c r="I834" s="30"/>
@@ -13141,6 +13477,7 @@
       <c r="B835" s="28"/>
       <c r="C835" s="28"/>
       <c r="E835" s="29"/>
+      <c r="F835" s="29"/>
       <c r="G835" s="30"/>
       <c r="H835" s="30"/>
       <c r="I835" s="30"/>
@@ -13151,6 +13488,7 @@
       <c r="B836" s="28"/>
       <c r="C836" s="28"/>
       <c r="E836" s="29"/>
+      <c r="F836" s="29"/>
       <c r="G836" s="30"/>
       <c r="H836" s="30"/>
       <c r="I836" s="30"/>
@@ -13161,6 +13499,7 @@
       <c r="B837" s="28"/>
       <c r="C837" s="28"/>
       <c r="E837" s="29"/>
+      <c r="F837" s="29"/>
       <c r="G837" s="30"/>
       <c r="H837" s="30"/>
       <c r="I837" s="30"/>
@@ -13171,6 +13510,7 @@
       <c r="B838" s="28"/>
       <c r="C838" s="28"/>
       <c r="E838" s="29"/>
+      <c r="F838" s="29"/>
       <c r="G838" s="30"/>
       <c r="H838" s="30"/>
       <c r="I838" s="30"/>
@@ -13181,6 +13521,7 @@
       <c r="B839" s="28"/>
       <c r="C839" s="28"/>
       <c r="E839" s="29"/>
+      <c r="F839" s="29"/>
       <c r="G839" s="30"/>
       <c r="H839" s="30"/>
       <c r="I839" s="30"/>
@@ -13191,6 +13532,7 @@
       <c r="B840" s="28"/>
       <c r="C840" s="28"/>
       <c r="E840" s="29"/>
+      <c r="F840" s="29"/>
       <c r="G840" s="30"/>
       <c r="H840" s="30"/>
       <c r="I840" s="30"/>
@@ -13201,6 +13543,7 @@
       <c r="B841" s="28"/>
       <c r="C841" s="28"/>
       <c r="E841" s="29"/>
+      <c r="F841" s="29"/>
       <c r="G841" s="30"/>
       <c r="H841" s="30"/>
       <c r="I841" s="30"/>
@@ -13211,6 +13554,7 @@
       <c r="B842" s="28"/>
       <c r="C842" s="28"/>
       <c r="E842" s="29"/>
+      <c r="F842" s="29"/>
       <c r="G842" s="30"/>
       <c r="H842" s="30"/>
       <c r="I842" s="30"/>
@@ -13221,6 +13565,7 @@
       <c r="B843" s="28"/>
       <c r="C843" s="28"/>
       <c r="E843" s="29"/>
+      <c r="F843" s="29"/>
       <c r="G843" s="30"/>
       <c r="H843" s="30"/>
       <c r="I843" s="30"/>
@@ -13231,6 +13576,7 @@
       <c r="B844" s="28"/>
       <c r="C844" s="28"/>
       <c r="E844" s="29"/>
+      <c r="F844" s="29"/>
       <c r="G844" s="30"/>
       <c r="H844" s="30"/>
       <c r="I844" s="30"/>
@@ -13241,6 +13587,7 @@
       <c r="B845" s="28"/>
       <c r="C845" s="28"/>
       <c r="E845" s="29"/>
+      <c r="F845" s="29"/>
       <c r="G845" s="30"/>
       <c r="H845" s="30"/>
       <c r="I845" s="30"/>
@@ -13251,6 +13598,7 @@
       <c r="B846" s="28"/>
       <c r="C846" s="28"/>
       <c r="E846" s="29"/>
+      <c r="F846" s="29"/>
       <c r="G846" s="30"/>
       <c r="H846" s="30"/>
       <c r="I846" s="30"/>
@@ -13261,6 +13609,7 @@
       <c r="B847" s="28"/>
       <c r="C847" s="28"/>
       <c r="E847" s="29"/>
+      <c r="F847" s="29"/>
       <c r="G847" s="30"/>
       <c r="H847" s="30"/>
       <c r="I847" s="30"/>
@@ -13271,6 +13620,7 @@
       <c r="B848" s="28"/>
       <c r="C848" s="28"/>
       <c r="E848" s="29"/>
+      <c r="F848" s="29"/>
       <c r="G848" s="30"/>
       <c r="H848" s="30"/>
       <c r="I848" s="30"/>
@@ -13281,6 +13631,7 @@
       <c r="B849" s="28"/>
       <c r="C849" s="28"/>
       <c r="E849" s="29"/>
+      <c r="F849" s="29"/>
       <c r="G849" s="30"/>
       <c r="H849" s="30"/>
       <c r="I849" s="30"/>
@@ -13291,6 +13642,7 @@
       <c r="B850" s="28"/>
       <c r="C850" s="28"/>
       <c r="E850" s="29"/>
+      <c r="F850" s="29"/>
       <c r="G850" s="30"/>
       <c r="H850" s="30"/>
       <c r="I850" s="30"/>
@@ -13301,6 +13653,7 @@
       <c r="B851" s="28"/>
       <c r="C851" s="28"/>
       <c r="E851" s="29"/>
+      <c r="F851" s="29"/>
       <c r="G851" s="30"/>
       <c r="H851" s="30"/>
       <c r="I851" s="30"/>
@@ -13311,6 +13664,7 @@
       <c r="B852" s="28"/>
       <c r="C852" s="28"/>
       <c r="E852" s="29"/>
+      <c r="F852" s="29"/>
       <c r="G852" s="30"/>
       <c r="H852" s="30"/>
       <c r="I852" s="30"/>
@@ -13321,6 +13675,7 @@
       <c r="B853" s="28"/>
       <c r="C853" s="28"/>
       <c r="E853" s="29"/>
+      <c r="F853" s="29"/>
       <c r="G853" s="30"/>
       <c r="H853" s="30"/>
       <c r="I853" s="30"/>
@@ -13331,6 +13686,7 @@
       <c r="B854" s="28"/>
       <c r="C854" s="28"/>
       <c r="E854" s="29"/>
+      <c r="F854" s="29"/>
       <c r="G854" s="30"/>
       <c r="H854" s="30"/>
       <c r="I854" s="30"/>
@@ -13341,6 +13697,7 @@
       <c r="B855" s="28"/>
       <c r="C855" s="28"/>
       <c r="E855" s="29"/>
+      <c r="F855" s="29"/>
       <c r="G855" s="30"/>
       <c r="H855" s="30"/>
       <c r="I855" s="30"/>
@@ -13351,6 +13708,7 @@
       <c r="B856" s="28"/>
       <c r="C856" s="28"/>
       <c r="E856" s="29"/>
+      <c r="F856" s="29"/>
       <c r="G856" s="30"/>
       <c r="H856" s="30"/>
       <c r="I856" s="30"/>
@@ -13361,6 +13719,7 @@
       <c r="B857" s="28"/>
       <c r="C857" s="28"/>
       <c r="E857" s="29"/>
+      <c r="F857" s="29"/>
       <c r="G857" s="30"/>
       <c r="H857" s="30"/>
       <c r="I857" s="30"/>
@@ -13371,6 +13730,7 @@
       <c r="B858" s="28"/>
       <c r="C858" s="28"/>
       <c r="E858" s="29"/>
+      <c r="F858" s="29"/>
       <c r="G858" s="30"/>
       <c r="H858" s="30"/>
       <c r="I858" s="30"/>
@@ -13381,6 +13741,7 @@
       <c r="B859" s="28"/>
       <c r="C859" s="28"/>
       <c r="E859" s="29"/>
+      <c r="F859" s="29"/>
       <c r="G859" s="30"/>
       <c r="H859" s="30"/>
       <c r="I859" s="30"/>
@@ -13391,6 +13752,7 @@
       <c r="B860" s="28"/>
       <c r="C860" s="28"/>
       <c r="E860" s="29"/>
+      <c r="F860" s="29"/>
       <c r="G860" s="30"/>
       <c r="H860" s="30"/>
       <c r="I860" s="30"/>
@@ -13401,6 +13763,7 @@
       <c r="B861" s="28"/>
       <c r="C861" s="28"/>
       <c r="E861" s="29"/>
+      <c r="F861" s="29"/>
       <c r="G861" s="30"/>
       <c r="H861" s="30"/>
       <c r="I861" s="30"/>
@@ -13411,6 +13774,7 @@
       <c r="B862" s="28"/>
       <c r="C862" s="28"/>
       <c r="E862" s="29"/>
+      <c r="F862" s="29"/>
       <c r="G862" s="30"/>
       <c r="H862" s="30"/>
       <c r="I862" s="30"/>
@@ -13421,6 +13785,7 @@
       <c r="B863" s="28"/>
       <c r="C863" s="28"/>
       <c r="E863" s="29"/>
+      <c r="F863" s="29"/>
       <c r="G863" s="30"/>
       <c r="H863" s="30"/>
       <c r="I863" s="30"/>
@@ -13431,6 +13796,7 @@
       <c r="B864" s="28"/>
       <c r="C864" s="28"/>
       <c r="E864" s="29"/>
+      <c r="F864" s="29"/>
       <c r="G864" s="30"/>
       <c r="H864" s="30"/>
       <c r="I864" s="30"/>
@@ -13441,6 +13807,7 @@
       <c r="B865" s="28"/>
       <c r="C865" s="28"/>
       <c r="E865" s="29"/>
+      <c r="F865" s="29"/>
       <c r="G865" s="30"/>
       <c r="H865" s="30"/>
       <c r="I865" s="30"/>
@@ -13451,6 +13818,7 @@
       <c r="B866" s="28"/>
       <c r="C866" s="28"/>
       <c r="E866" s="29"/>
+      <c r="F866" s="29"/>
       <c r="G866" s="30"/>
       <c r="H866" s="30"/>
       <c r="I866" s="30"/>
@@ -13461,6 +13829,7 @@
       <c r="B867" s="28"/>
       <c r="C867" s="28"/>
       <c r="E867" s="29"/>
+      <c r="F867" s="29"/>
       <c r="G867" s="30"/>
       <c r="H867" s="30"/>
       <c r="I867" s="30"/>
@@ -13471,6 +13840,7 @@
       <c r="B868" s="28"/>
       <c r="C868" s="28"/>
       <c r="E868" s="29"/>
+      <c r="F868" s="29"/>
       <c r="G868" s="30"/>
       <c r="H868" s="30"/>
       <c r="I868" s="30"/>
@@ -13481,6 +13851,7 @@
       <c r="B869" s="28"/>
       <c r="C869" s="28"/>
       <c r="E869" s="29"/>
+      <c r="F869" s="29"/>
       <c r="G869" s="30"/>
       <c r="H869" s="30"/>
       <c r="I869" s="30"/>
@@ -13491,6 +13862,7 @@
       <c r="B870" s="28"/>
       <c r="C870" s="28"/>
       <c r="E870" s="29"/>
+      <c r="F870" s="29"/>
       <c r="G870" s="30"/>
       <c r="H870" s="30"/>
       <c r="I870" s="30"/>
@@ -13501,6 +13873,7 @@
       <c r="B871" s="28"/>
       <c r="C871" s="28"/>
       <c r="E871" s="29"/>
+      <c r="F871" s="29"/>
       <c r="G871" s="30"/>
       <c r="H871" s="30"/>
       <c r="I871" s="30"/>
@@ -13511,6 +13884,7 @@
       <c r="B872" s="28"/>
       <c r="C872" s="28"/>
       <c r="E872" s="29"/>
+      <c r="F872" s="29"/>
       <c r="G872" s="30"/>
       <c r="H872" s="30"/>
       <c r="I872" s="30"/>
@@ -13521,6 +13895,7 @@
       <c r="B873" s="28"/>
       <c r="C873" s="28"/>
       <c r="E873" s="29"/>
+      <c r="F873" s="29"/>
       <c r="G873" s="30"/>
       <c r="H873" s="30"/>
       <c r="I873" s="30"/>
@@ -13531,6 +13906,7 @@
       <c r="B874" s="28"/>
       <c r="C874" s="28"/>
       <c r="E874" s="29"/>
+      <c r="F874" s="29"/>
       <c r="G874" s="30"/>
       <c r="H874" s="30"/>
       <c r="I874" s="30"/>
@@ -13541,6 +13917,7 @@
       <c r="B875" s="28"/>
       <c r="C875" s="28"/>
       <c r="E875" s="29"/>
+      <c r="F875" s="29"/>
       <c r="G875" s="30"/>
       <c r="H875" s="30"/>
       <c r="I875" s="30"/>
@@ -13551,6 +13928,7 @@
       <c r="B876" s="28"/>
       <c r="C876" s="28"/>
       <c r="E876" s="29"/>
+      <c r="F876" s="29"/>
       <c r="G876" s="30"/>
       <c r="H876" s="30"/>
       <c r="I876" s="30"/>
@@ -13561,6 +13939,7 @@
       <c r="B877" s="28"/>
       <c r="C877" s="28"/>
       <c r="E877" s="29"/>
+      <c r="F877" s="29"/>
       <c r="G877" s="30"/>
       <c r="H877" s="30"/>
       <c r="I877" s="30"/>
@@ -13571,6 +13950,7 @@
       <c r="B878" s="28"/>
       <c r="C878" s="28"/>
       <c r="E878" s="29"/>
+      <c r="F878" s="29"/>
       <c r="G878" s="30"/>
       <c r="H878" s="30"/>
       <c r="I878" s="30"/>
@@ -13581,6 +13961,7 @@
       <c r="B879" s="28"/>
       <c r="C879" s="28"/>
       <c r="E879" s="29"/>
+      <c r="F879" s="29"/>
       <c r="G879" s="30"/>
       <c r="H879" s="30"/>
       <c r="I879" s="30"/>
@@ -13591,6 +13972,7 @@
       <c r="B880" s="28"/>
       <c r="C880" s="28"/>
       <c r="E880" s="29"/>
+      <c r="F880" s="29"/>
       <c r="G880" s="30"/>
       <c r="H880" s="30"/>
       <c r="I880" s="30"/>
@@ -13601,6 +13983,7 @@
       <c r="B881" s="28"/>
       <c r="C881" s="28"/>
       <c r="E881" s="29"/>
+      <c r="F881" s="29"/>
       <c r="G881" s="30"/>
       <c r="H881" s="30"/>
       <c r="I881" s="30"/>
@@ -13611,6 +13994,7 @@
       <c r="B882" s="28"/>
       <c r="C882" s="28"/>
       <c r="E882" s="29"/>
+      <c r="F882" s="29"/>
       <c r="G882" s="30"/>
       <c r="H882" s="30"/>
       <c r="I882" s="30"/>
@@ -13621,6 +14005,7 @@
       <c r="B883" s="28"/>
       <c r="C883" s="28"/>
       <c r="E883" s="29"/>
+      <c r="F883" s="29"/>
       <c r="G883" s="30"/>
       <c r="H883" s="30"/>
       <c r="I883" s="30"/>
@@ -13631,6 +14016,7 @@
       <c r="B884" s="28"/>
       <c r="C884" s="28"/>
       <c r="E884" s="29"/>
+      <c r="F884" s="29"/>
       <c r="G884" s="30"/>
       <c r="H884" s="30"/>
       <c r="I884" s="30"/>
@@ -13641,6 +14027,7 @@
       <c r="B885" s="28"/>
       <c r="C885" s="28"/>
       <c r="E885" s="29"/>
+      <c r="F885" s="29"/>
       <c r="G885" s="30"/>
       <c r="H885" s="30"/>
       <c r="I885" s="30"/>
@@ -13651,6 +14038,7 @@
       <c r="B886" s="28"/>
       <c r="C886" s="28"/>
       <c r="E886" s="29"/>
+      <c r="F886" s="29"/>
       <c r="G886" s="30"/>
       <c r="H886" s="30"/>
       <c r="I886" s="30"/>
@@ -13661,6 +14049,7 @@
       <c r="B887" s="28"/>
       <c r="C887" s="28"/>
       <c r="E887" s="29"/>
+      <c r="F887" s="29"/>
       <c r="G887" s="30"/>
       <c r="H887" s="30"/>
       <c r="I887" s="30"/>
@@ -13671,6 +14060,7 @@
       <c r="B888" s="28"/>
       <c r="C888" s="28"/>
       <c r="E888" s="29"/>
+      <c r="F888" s="29"/>
       <c r="G888" s="30"/>
       <c r="H888" s="30"/>
       <c r="I888" s="30"/>
@@ -13681,6 +14071,7 @@
       <c r="B889" s="28"/>
       <c r="C889" s="28"/>
       <c r="E889" s="29"/>
+      <c r="F889" s="29"/>
       <c r="G889" s="30"/>
       <c r="H889" s="30"/>
       <c r="I889" s="30"/>
@@ -13691,6 +14082,7 @@
       <c r="B890" s="28"/>
       <c r="C890" s="28"/>
       <c r="E890" s="29"/>
+      <c r="F890" s="29"/>
       <c r="G890" s="30"/>
       <c r="H890" s="30"/>
       <c r="I890" s="30"/>
@@ -13701,6 +14093,7 @@
       <c r="B891" s="28"/>
       <c r="C891" s="28"/>
       <c r="E891" s="29"/>
+      <c r="F891" s="29"/>
       <c r="G891" s="30"/>
       <c r="H891" s="30"/>
       <c r="I891" s="30"/>
@@ -13711,6 +14104,7 @@
       <c r="B892" s="28"/>
       <c r="C892" s="28"/>
       <c r="E892" s="29"/>
+      <c r="F892" s="29"/>
       <c r="G892" s="30"/>
       <c r="H892" s="30"/>
       <c r="I892" s="30"/>
@@ -13721,6 +14115,7 @@
       <c r="B893" s="28"/>
       <c r="C893" s="28"/>
       <c r="E893" s="29"/>
+      <c r="F893" s="29"/>
       <c r="G893" s="30"/>
       <c r="H893" s="30"/>
       <c r="I893" s="30"/>
@@ -13731,6 +14126,7 @@
       <c r="B894" s="28"/>
       <c r="C894" s="28"/>
       <c r="E894" s="29"/>
+      <c r="F894" s="29"/>
       <c r="G894" s="30"/>
       <c r="H894" s="30"/>
       <c r="I894" s="30"/>
@@ -13741,6 +14137,7 @@
       <c r="B895" s="28"/>
       <c r="C895" s="28"/>
       <c r="E895" s="29"/>
+      <c r="F895" s="29"/>
       <c r="G895" s="30"/>
       <c r="H895" s="30"/>
       <c r="I895" s="30"/>
@@ -13751,6 +14148,7 @@
       <c r="B896" s="28"/>
       <c r="C896" s="28"/>
       <c r="E896" s="29"/>
+      <c r="F896" s="29"/>
       <c r="G896" s="30"/>
       <c r="H896" s="30"/>
       <c r="I896" s="30"/>
@@ -13761,6 +14159,7 @@
       <c r="B897" s="28"/>
       <c r="C897" s="28"/>
       <c r="E897" s="29"/>
+      <c r="F897" s="29"/>
       <c r="G897" s="30"/>
       <c r="H897" s="30"/>
       <c r="I897" s="30"/>
@@ -13771,6 +14170,7 @@
       <c r="B898" s="28"/>
       <c r="C898" s="28"/>
       <c r="E898" s="29"/>
+      <c r="F898" s="29"/>
       <c r="G898" s="30"/>
       <c r="H898" s="30"/>
       <c r="I898" s="30"/>
@@ -13781,6 +14181,7 @@
       <c r="B899" s="28"/>
       <c r="C899" s="28"/>
       <c r="E899" s="29"/>
+      <c r="F899" s="29"/>
       <c r="G899" s="30"/>
       <c r="H899" s="30"/>
       <c r="I899" s="30"/>
@@ -13791,6 +14192,7 @@
       <c r="B900" s="28"/>
       <c r="C900" s="28"/>
       <c r="E900" s="29"/>
+      <c r="F900" s="29"/>
       <c r="G900" s="30"/>
       <c r="H900" s="30"/>
       <c r="I900" s="30"/>
@@ -13801,6 +14203,7 @@
       <c r="B901" s="28"/>
       <c r="C901" s="28"/>
       <c r="E901" s="29"/>
+      <c r="F901" s="29"/>
       <c r="G901" s="30"/>
       <c r="H901" s="30"/>
       <c r="I901" s="30"/>
@@ -13811,6 +14214,7 @@
       <c r="B902" s="28"/>
       <c r="C902" s="28"/>
       <c r="E902" s="29"/>
+      <c r="F902" s="29"/>
       <c r="G902" s="30"/>
       <c r="H902" s="30"/>
       <c r="I902" s="30"/>
@@ -13821,6 +14225,7 @@
       <c r="B903" s="28"/>
       <c r="C903" s="28"/>
       <c r="E903" s="29"/>
+      <c r="F903" s="29"/>
       <c r="G903" s="30"/>
       <c r="H903" s="30"/>
       <c r="I903" s="30"/>
@@ -13831,6 +14236,7 @@
       <c r="B904" s="28"/>
       <c r="C904" s="28"/>
       <c r="E904" s="29"/>
+      <c r="F904" s="29"/>
       <c r="G904" s="30"/>
       <c r="H904" s="30"/>
       <c r="I904" s="30"/>
@@ -13841,6 +14247,7 @@
       <c r="B905" s="28"/>
       <c r="C905" s="28"/>
       <c r="E905" s="29"/>
+      <c r="F905" s="29"/>
       <c r="G905" s="30"/>
       <c r="H905" s="30"/>
       <c r="I905" s="30"/>
@@ -13851,6 +14258,7 @@
       <c r="B906" s="28"/>
       <c r="C906" s="28"/>
       <c r="E906" s="29"/>
+      <c r="F906" s="29"/>
       <c r="G906" s="30"/>
       <c r="H906" s="30"/>
       <c r="I906" s="30"/>
@@ -13861,6 +14269,7 @@
       <c r="B907" s="28"/>
       <c r="C907" s="28"/>
       <c r="E907" s="29"/>
+      <c r="F907" s="29"/>
       <c r="G907" s="30"/>
       <c r="H907" s="30"/>
       <c r="I907" s="30"/>
@@ -13871,6 +14280,7 @@
       <c r="B908" s="28"/>
       <c r="C908" s="28"/>
       <c r="E908" s="29"/>
+      <c r="F908" s="29"/>
       <c r="G908" s="30"/>
       <c r="H908" s="30"/>
       <c r="I908" s="30"/>
@@ -13881,6 +14291,7 @@
       <c r="B909" s="28"/>
       <c r="C909" s="28"/>
       <c r="E909" s="29"/>
+      <c r="F909" s="29"/>
       <c r="G909" s="30"/>
       <c r="H909" s="30"/>
       <c r="I909" s="30"/>
@@ -13891,6 +14302,7 @@
       <c r="B910" s="28"/>
       <c r="C910" s="28"/>
       <c r="E910" s="29"/>
+      <c r="F910" s="29"/>
       <c r="G910" s="30"/>
       <c r="H910" s="30"/>
       <c r="I910" s="30"/>
@@ -13901,6 +14313,7 @@
       <c r="B911" s="28"/>
       <c r="C911" s="28"/>
       <c r="E911" s="29"/>
+      <c r="F911" s="29"/>
       <c r="G911" s="30"/>
       <c r="H911" s="30"/>
       <c r="I911" s="30"/>
@@ -13911,6 +14324,7 @@
       <c r="B912" s="28"/>
       <c r="C912" s="28"/>
       <c r="E912" s="29"/>
+      <c r="F912" s="29"/>
       <c r="G912" s="30"/>
       <c r="H912" s="30"/>
       <c r="I912" s="30"/>
@@ -13921,6 +14335,7 @@
       <c r="B913" s="28"/>
       <c r="C913" s="28"/>
       <c r="E913" s="29"/>
+      <c r="F913" s="29"/>
       <c r="G913" s="30"/>
       <c r="H913" s="30"/>
       <c r="I913" s="30"/>
@@ -13931,6 +14346,7 @@
       <c r="B914" s="28"/>
       <c r="C914" s="28"/>
       <c r="E914" s="29"/>
+      <c r="F914" s="29"/>
       <c r="G914" s="30"/>
       <c r="H914" s="30"/>
       <c r="I914" s="30"/>
@@ -13941,6 +14357,7 @@
       <c r="B915" s="28"/>
       <c r="C915" s="28"/>
       <c r="E915" s="29"/>
+      <c r="F915" s="29"/>
       <c r="G915" s="30"/>
       <c r="H915" s="30"/>
       <c r="I915" s="30"/>
@@ -13951,6 +14368,7 @@
       <c r="B916" s="28"/>
       <c r="C916" s="28"/>
       <c r="E916" s="29"/>
+      <c r="F916" s="29"/>
       <c r="G916" s="30"/>
       <c r="H916" s="30"/>
       <c r="I916" s="30"/>
@@ -13961,6 +14379,7 @@
       <c r="B917" s="28"/>
       <c r="C917" s="28"/>
       <c r="E917" s="29"/>
+      <c r="F917" s="29"/>
       <c r="G917" s="30"/>
       <c r="H917" s="30"/>
       <c r="I917" s="30"/>
@@ -13971,6 +14390,7 @@
       <c r="B918" s="28"/>
       <c r="C918" s="28"/>
       <c r="E918" s="29"/>
+      <c r="F918" s="29"/>
       <c r="G918" s="30"/>
       <c r="H918" s="30"/>
       <c r="I918" s="30"/>
@@ -13981,6 +14401,7 @@
       <c r="B919" s="28"/>
       <c r="C919" s="28"/>
       <c r="E919" s="29"/>
+      <c r="F919" s="29"/>
       <c r="G919" s="30"/>
       <c r="H919" s="30"/>
       <c r="I919" s="30"/>
@@ -13991,6 +14412,7 @@
       <c r="B920" s="28"/>
       <c r="C920" s="28"/>
       <c r="E920" s="29"/>
+      <c r="F920" s="29"/>
       <c r="G920" s="30"/>
       <c r="H920" s="30"/>
       <c r="I920" s="30"/>
@@ -14001,6 +14423,7 @@
       <c r="B921" s="28"/>
       <c r="C921" s="28"/>
       <c r="E921" s="29"/>
+      <c r="F921" s="29"/>
       <c r="G921" s="30"/>
       <c r="H921" s="30"/>
       <c r="I921" s="30"/>
@@ -14011,6 +14434,7 @@
       <c r="B922" s="28"/>
       <c r="C922" s="28"/>
       <c r="E922" s="29"/>
+      <c r="F922" s="29"/>
       <c r="G922" s="30"/>
       <c r="H922" s="30"/>
       <c r="I922" s="30"/>
@@ -14021,6 +14445,7 @@
       <c r="B923" s="28"/>
       <c r="C923" s="28"/>
       <c r="E923" s="29"/>
+      <c r="F923" s="29"/>
       <c r="G923" s="30"/>
       <c r="H923" s="30"/>
       <c r="I923" s="30"/>
@@ -14031,6 +14456,7 @@
       <c r="B924" s="28"/>
       <c r="C924" s="28"/>
       <c r="E924" s="29"/>
+      <c r="F924" s="29"/>
       <c r="G924" s="30"/>
       <c r="H924" s="30"/>
       <c r="I924" s="30"/>
@@ -14041,6 +14467,7 @@
       <c r="B925" s="28"/>
       <c r="C925" s="28"/>
       <c r="E925" s="29"/>
+      <c r="F925" s="29"/>
       <c r="G925" s="30"/>
       <c r="H925" s="30"/>
       <c r="I925" s="30"/>
@@ -14051,6 +14478,7 @@
       <c r="B926" s="28"/>
       <c r="C926" s="28"/>
       <c r="E926" s="29"/>
+      <c r="F926" s="29"/>
       <c r="G926" s="30"/>
       <c r="H926" s="30"/>
       <c r="I926" s="30"/>
@@ -14061,6 +14489,7 @@
       <c r="B927" s="28"/>
       <c r="C927" s="28"/>
       <c r="E927" s="29"/>
+      <c r="F927" s="29"/>
       <c r="G927" s="30"/>
       <c r="H927" s="30"/>
       <c r="I927" s="30"/>
@@ -14071,6 +14500,7 @@
       <c r="B928" s="28"/>
       <c r="C928" s="28"/>
       <c r="E928" s="29"/>
+      <c r="F928" s="29"/>
       <c r="G928" s="30"/>
       <c r="H928" s="30"/>
       <c r="I928" s="30"/>
@@ -14081,6 +14511,7 @@
       <c r="B929" s="28"/>
       <c r="C929" s="28"/>
       <c r="E929" s="29"/>
+      <c r="F929" s="29"/>
       <c r="G929" s="30"/>
       <c r="H929" s="30"/>
       <c r="I929" s="30"/>
@@ -14091,6 +14522,7 @@
       <c r="B930" s="28"/>
       <c r="C930" s="28"/>
       <c r="E930" s="29"/>
+      <c r="F930" s="29"/>
       <c r="G930" s="30"/>
       <c r="H930" s="30"/>
       <c r="I930" s="30"/>
@@ -14101,6 +14533,7 @@
       <c r="B931" s="28"/>
       <c r="C931" s="28"/>
       <c r="E931" s="29"/>
+      <c r="F931" s="29"/>
       <c r="G931" s="30"/>
       <c r="H931" s="30"/>
       <c r="I931" s="30"/>
@@ -14111,6 +14544,7 @@
       <c r="B932" s="28"/>
       <c r="C932" s="28"/>
       <c r="E932" s="29"/>
+      <c r="F932" s="29"/>
       <c r="G932" s="30"/>
       <c r="H932" s="30"/>
       <c r="I932" s="30"/>
@@ -14121,6 +14555,7 @@
       <c r="B933" s="28"/>
       <c r="C933" s="28"/>
       <c r="E933" s="29"/>
+      <c r="F933" s="29"/>
       <c r="G933" s="30"/>
       <c r="H933" s="30"/>
       <c r="I933" s="30"/>
@@ -14131,6 +14566,7 @@
       <c r="B934" s="28"/>
       <c r="C934" s="28"/>
       <c r="E934" s="29"/>
+      <c r="F934" s="29"/>
       <c r="G934" s="30"/>
       <c r="H934" s="30"/>
       <c r="I934" s="30"/>
@@ -14141,6 +14577,7 @@
       <c r="B935" s="28"/>
       <c r="C935" s="28"/>
       <c r="E935" s="29"/>
+      <c r="F935" s="29"/>
       <c r="G935" s="30"/>
       <c r="H935" s="30"/>
       <c r="I935" s="30"/>
@@ -14151,6 +14588,7 @@
       <c r="B936" s="28"/>
       <c r="C936" s="28"/>
       <c r="E936" s="29"/>
+      <c r="F936" s="29"/>
       <c r="G936" s="30"/>
       <c r="H936" s="30"/>
       <c r="I936" s="30"/>
@@ -14161,6 +14599,7 @@
       <c r="B937" s="28"/>
       <c r="C937" s="28"/>
       <c r="E937" s="29"/>
+      <c r="F937" s="29"/>
       <c r="G937" s="30"/>
       <c r="H937" s="30"/>
       <c r="I937" s="30"/>
@@ -14171,6 +14610,7 @@
       <c r="B938" s="28"/>
       <c r="C938" s="28"/>
       <c r="E938" s="29"/>
+      <c r="F938" s="29"/>
       <c r="G938" s="30"/>
       <c r="H938" s="30"/>
       <c r="I938" s="30"/>
@@ -14181,6 +14621,7 @@
       <c r="B939" s="28"/>
       <c r="C939" s="28"/>
       <c r="E939" s="29"/>
+      <c r="F939" s="29"/>
       <c r="G939" s="30"/>
       <c r="H939" s="30"/>
       <c r="I939" s="30"/>
@@ -14191,6 +14632,7 @@
       <c r="B940" s="28"/>
       <c r="C940" s="28"/>
       <c r="E940" s="29"/>
+      <c r="F940" s="29"/>
       <c r="G940" s="30"/>
       <c r="H940" s="30"/>
       <c r="I940" s="30"/>
@@ -14201,6 +14643,7 @@
       <c r="B941" s="28"/>
       <c r="C941" s="28"/>
       <c r="E941" s="29"/>
+      <c r="F941" s="29"/>
       <c r="G941" s="30"/>
       <c r="H941" s="30"/>
       <c r="I941" s="30"/>
@@ -14211,6 +14654,7 @@
       <c r="B942" s="28"/>
       <c r="C942" s="28"/>
       <c r="E942" s="29"/>
+      <c r="F942" s="29"/>
       <c r="G942" s="30"/>
       <c r="H942" s="30"/>
       <c r="I942" s="30"/>
@@ -14221,6 +14665,7 @@
       <c r="B943" s="28"/>
       <c r="C943" s="28"/>
       <c r="E943" s="29"/>
+      <c r="F943" s="29"/>
       <c r="G943" s="30"/>
       <c r="H943" s="30"/>
       <c r="I943" s="30"/>
@@ -14231,6 +14676,7 @@
       <c r="B944" s="28"/>
       <c r="C944" s="28"/>
       <c r="E944" s="29"/>
+      <c r="F944" s="29"/>
       <c r="G944" s="30"/>
       <c r="H944" s="30"/>
       <c r="I944" s="30"/>
@@ -14241,6 +14687,7 @@
       <c r="B945" s="28"/>
       <c r="C945" s="28"/>
       <c r="E945" s="29"/>
+      <c r="F945" s="29"/>
       <c r="G945" s="30"/>
       <c r="H945" s="30"/>
       <c r="I945" s="30"/>
@@ -14251,6 +14698,7 @@
       <c r="B946" s="28"/>
       <c r="C946" s="28"/>
       <c r="E946" s="29"/>
+      <c r="F946" s="29"/>
       <c r="G946" s="30"/>
       <c r="H946" s="30"/>
       <c r="I946" s="30"/>
@@ -14261,6 +14709,7 @@
       <c r="B947" s="28"/>
       <c r="C947" s="28"/>
       <c r="E947" s="29"/>
+      <c r="F947" s="29"/>
       <c r="G947" s="30"/>
       <c r="H947" s="30"/>
       <c r="I947" s="30"/>
@@ -14271,6 +14720,7 @@
       <c r="B948" s="28"/>
       <c r="C948" s="28"/>
       <c r="E948" s="29"/>
+      <c r="F948" s="29"/>
       <c r="G948" s="30"/>
       <c r="H948" s="30"/>
       <c r="I948" s="30"/>
@@ -14281,6 +14731,7 @@
       <c r="B949" s="28"/>
       <c r="C949" s="28"/>
       <c r="E949" s="29"/>
+      <c r="F949" s="29"/>
       <c r="G949" s="30"/>
       <c r="H949" s="30"/>
       <c r="I949" s="30"/>
@@ -14291,6 +14742,7 @@
       <c r="B950" s="28"/>
       <c r="C950" s="28"/>
       <c r="E950" s="29"/>
+      <c r="F950" s="29"/>
       <c r="G950" s="30"/>
       <c r="H950" s="30"/>
       <c r="I950" s="30"/>
@@ -14301,6 +14753,7 @@
       <c r="B951" s="28"/>
       <c r="C951" s="28"/>
       <c r="E951" s="29"/>
+      <c r="F951" s="29"/>
       <c r="G951" s="30"/>
       <c r="H951" s="30"/>
       <c r="I951" s="30"/>
@@ -14311,6 +14764,7 @@
       <c r="B952" s="28"/>
       <c r="C952" s="28"/>
       <c r="E952" s="29"/>
+      <c r="F952" s="29"/>
       <c r="G952" s="30"/>
       <c r="H952" s="30"/>
       <c r="I952" s="30"/>
@@ -14321,6 +14775,7 @@
       <c r="B953" s="28"/>
       <c r="C953" s="28"/>
       <c r="E953" s="29"/>
+      <c r="F953" s="29"/>
       <c r="G953" s="30"/>
       <c r="H953" s="30"/>
       <c r="I953" s="30"/>
@@ -14331,6 +14786,7 @@
       <c r="B954" s="28"/>
       <c r="C954" s="28"/>
       <c r="E954" s="29"/>
+      <c r="F954" s="29"/>
       <c r="G954" s="30"/>
       <c r="H954" s="30"/>
       <c r="I954" s="30"/>
@@ -14341,6 +14797,7 @@
       <c r="B955" s="28"/>
       <c r="C955" s="28"/>
       <c r="E955" s="29"/>
+      <c r="F955" s="29"/>
       <c r="G955" s="30"/>
       <c r="H955" s="30"/>
       <c r="I955" s="30"/>
@@ -14351,6 +14808,7 @@
       <c r="B956" s="28"/>
       <c r="C956" s="28"/>
       <c r="E956" s="29"/>
+      <c r="F956" s="29"/>
       <c r="G956" s="30"/>
       <c r="H956" s="30"/>
       <c r="I956" s="30"/>
@@ -14361,6 +14819,7 @@
       <c r="B957" s="28"/>
       <c r="C957" s="28"/>
       <c r="E957" s="29"/>
+      <c r="F957" s="29"/>
       <c r="G957" s="30"/>
       <c r="H957" s="30"/>
       <c r="I957" s="30"/>
@@ -14371,6 +14830,7 @@
       <c r="B958" s="28"/>
       <c r="C958" s="28"/>
       <c r="E958" s="29"/>
+      <c r="F958" s="29"/>
       <c r="G958" s="30"/>
       <c r="H958" s="30"/>
       <c r="I958" s="30"/>
@@ -14381,6 +14841,7 @@
       <c r="B959" s="28"/>
       <c r="C959" s="28"/>
       <c r="E959" s="29"/>
+      <c r="F959" s="29"/>
       <c r="G959" s="30"/>
       <c r="H959" s="30"/>
       <c r="I959" s="30"/>
@@ -14391,6 +14852,7 @@
       <c r="B960" s="28"/>
       <c r="C960" s="28"/>
       <c r="E960" s="29"/>
+      <c r="F960" s="29"/>
       <c r="G960" s="30"/>
       <c r="H960" s="30"/>
       <c r="I960" s="30"/>
@@ -14401,6 +14863,7 @@
       <c r="B961" s="28"/>
       <c r="C961" s="28"/>
       <c r="E961" s="29"/>
+      <c r="F961" s="29"/>
       <c r="G961" s="30"/>
       <c r="H961" s="30"/>
       <c r="I961" s="30"/>
@@ -14411,6 +14874,7 @@
       <c r="B962" s="28"/>
       <c r="C962" s="28"/>
       <c r="E962" s="29"/>
+      <c r="F962" s="29"/>
       <c r="G962" s="30"/>
       <c r="H962" s="30"/>
       <c r="I962" s="30"/>
@@ -14421,6 +14885,7 @@
       <c r="B963" s="28"/>
       <c r="C963" s="28"/>
       <c r="E963" s="29"/>
+      <c r="F963" s="29"/>
       <c r="G963" s="30"/>
       <c r="H963" s="30"/>
       <c r="I963" s="30"/>
@@ -14431,6 +14896,7 @@
       <c r="B964" s="28"/>
       <c r="C964" s="28"/>
       <c r="E964" s="29"/>
+      <c r="F964" s="29"/>
       <c r="G964" s="30"/>
       <c r="H964" s="30"/>
       <c r="I964" s="30"/>
@@ -14441,6 +14907,7 @@
       <c r="B965" s="28"/>
       <c r="C965" s="28"/>
       <c r="E965" s="29"/>
+      <c r="F965" s="29"/>
       <c r="G965" s="30"/>
       <c r="H965" s="30"/>
       <c r="I965" s="30"/>
@@ -14451,6 +14918,7 @@
       <c r="B966" s="28"/>
       <c r="C966" s="28"/>
       <c r="E966" s="29"/>
+      <c r="F966" s="29"/>
       <c r="G966" s="30"/>
       <c r="H966" s="30"/>
       <c r="I966" s="30"/>
@@ -14461,6 +14929,7 @@
       <c r="B967" s="28"/>
       <c r="C967" s="28"/>
       <c r="E967" s="29"/>
+      <c r="F967" s="29"/>
       <c r="G967" s="30"/>
       <c r="H967" s="30"/>
       <c r="I967" s="30"/>
@@ -14471,6 +14940,7 @@
       <c r="B968" s="28"/>
       <c r="C968" s="28"/>
       <c r="E968" s="29"/>
+      <c r="F968" s="29"/>
       <c r="G968" s="30"/>
       <c r="H968" s="30"/>
       <c r="I968" s="30"/>
@@ -14481,6 +14951,7 @@
       <c r="B969" s="28"/>
       <c r="C969" s="28"/>
       <c r="E969" s="29"/>
+      <c r="F969" s="29"/>
       <c r="G969" s="30"/>
       <c r="H969" s="30"/>
       <c r="I969" s="30"/>
@@ -14491,6 +14962,7 @@
       <c r="B970" s="28"/>
       <c r="C970" s="28"/>
       <c r="E970" s="29"/>
+      <c r="F970" s="29"/>
       <c r="G970" s="30"/>
       <c r="H970" s="30"/>
       <c r="I970" s="30"/>
@@ -14501,6 +14973,7 @@
       <c r="B971" s="28"/>
       <c r="C971" s="28"/>
       <c r="E971" s="29"/>
+      <c r="F971" s="29"/>
       <c r="G971" s="30"/>
       <c r="H971" s="30"/>
       <c r="I971" s="30"/>
@@ -14511,6 +14984,7 @@
       <c r="B972" s="28"/>
       <c r="C972" s="28"/>
       <c r="E972" s="29"/>
+      <c r="F972" s="29"/>
       <c r="G972" s="30"/>
       <c r="H972" s="30"/>
       <c r="I972" s="30"/>
@@ -14521,6 +14995,7 @@
       <c r="B973" s="28"/>
       <c r="C973" s="28"/>
       <c r="E973" s="29"/>
+      <c r="F973" s="29"/>
       <c r="G973" s="30"/>
       <c r="H973" s="30"/>
       <c r="I973" s="30"/>
@@ -14531,6 +15006,7 @@
       <c r="B974" s="28"/>
       <c r="C974" s="28"/>
       <c r="E974" s="29"/>
+      <c r="F974" s="29"/>
       <c r="G974" s="30"/>
       <c r="H974" s="30"/>
       <c r="I974" s="30"/>
@@ -14541,6 +15017,7 @@
       <c r="B975" s="28"/>
       <c r="C975" s="28"/>
       <c r="E975" s="29"/>
+      <c r="F975" s="29"/>
       <c r="G975" s="30"/>
       <c r="H975" s="30"/>
       <c r="I975" s="30"/>
@@ -14551,6 +15028,7 @@
       <c r="B976" s="28"/>
       <c r="C976" s="28"/>
       <c r="E976" s="29"/>
+      <c r="F976" s="29"/>
       <c r="G976" s="30"/>
       <c r="H976" s="30"/>
       <c r="I976" s="30"/>
@@ -14561,6 +15039,7 @@
       <c r="B977" s="28"/>
       <c r="C977" s="28"/>
       <c r="E977" s="29"/>
+      <c r="F977" s="29"/>
       <c r="G977" s="30"/>
       <c r="H977" s="30"/>
       <c r="I977" s="30"/>
@@ -14571,6 +15050,7 @@
       <c r="B978" s="28"/>
       <c r="C978" s="28"/>
       <c r="E978" s="29"/>
+      <c r="F978" s="29"/>
       <c r="G978" s="30"/>
       <c r="H978" s="30"/>
       <c r="I978" s="30"/>
@@ -14581,6 +15061,7 @@
       <c r="B979" s="28"/>
       <c r="C979" s="28"/>
       <c r="E979" s="29"/>
+      <c r="F979" s="29"/>
       <c r="G979" s="30"/>
       <c r="H979" s="30"/>
       <c r="I979" s="30"/>
@@ -14591,6 +15072,7 @@
       <c r="B980" s="28"/>
       <c r="C980" s="28"/>
       <c r="E980" s="29"/>
+      <c r="F980" s="29"/>
       <c r="G980" s="30"/>
       <c r="H980" s="30"/>
       <c r="I980" s="30"/>
@@ -14601,6 +15083,7 @@
       <c r="B981" s="28"/>
       <c r="C981" s="28"/>
       <c r="E981" s="29"/>
+      <c r="F981" s="29"/>
       <c r="G981" s="30"/>
       <c r="H981" s="30"/>
       <c r="I981" s="30"/>
@@ -14611,6 +15094,7 @@
       <c r="B982" s="28"/>
       <c r="C982" s="28"/>
       <c r="E982" s="29"/>
+      <c r="F982" s="29"/>
       <c r="G982" s="30"/>
       <c r="H982" s="30"/>
       <c r="I982" s="30"/>
@@ -14621,6 +15105,7 @@
       <c r="B983" s="28"/>
       <c r="C983" s="28"/>
       <c r="E983" s="29"/>
+      <c r="F983" s="29"/>
       <c r="G983" s="30"/>
       <c r="H983" s="30"/>
       <c r="I983" s="30"/>
@@ -14631,6 +15116,7 @@
       <c r="B984" s="28"/>
       <c r="C984" s="28"/>
       <c r="E984" s="29"/>
+      <c r="F984" s="29"/>
       <c r="G984" s="30"/>
       <c r="H984" s="30"/>
       <c r="I984" s="30"/>
@@ -14641,6 +15127,7 @@
       <c r="B985" s="28"/>
       <c r="C985" s="28"/>
       <c r="E985" s="29"/>
+      <c r="F985" s="29"/>
       <c r="G985" s="30"/>
       <c r="H985" s="30"/>
       <c r="I985" s="30"/>
@@ -14651,6 +15138,7 @@
       <c r="B986" s="28"/>
       <c r="C986" s="28"/>
       <c r="E986" s="29"/>
+      <c r="F986" s="29"/>
       <c r="G986" s="30"/>
       <c r="H986" s="30"/>
       <c r="I986" s="30"/>
@@ -14661,6 +15149,7 @@
       <c r="B987" s="28"/>
       <c r="C987" s="28"/>
       <c r="E987" s="29"/>
+      <c r="F987" s="29"/>
       <c r="G987" s="30"/>
       <c r="H987" s="30"/>
       <c r="I987" s="30"/>
@@ -14671,6 +15160,7 @@
       <c r="B988" s="28"/>
       <c r="C988" s="28"/>
       <c r="E988" s="29"/>
+      <c r="F988" s="29"/>
       <c r="G988" s="30"/>
       <c r="H988" s="30"/>
       <c r="I988" s="30"/>
@@ -14681,6 +15171,7 @@
       <c r="B989" s="28"/>
       <c r="C989" s="28"/>
       <c r="E989" s="29"/>
+      <c r="F989" s="29"/>
       <c r="G989" s="30"/>
       <c r="H989" s="30"/>
       <c r="I989" s="30"/>
@@ -14691,6 +15182,7 @@
       <c r="B990" s="28"/>
       <c r="C990" s="28"/>
       <c r="E990" s="29"/>
+      <c r="F990" s="29"/>
       <c r="G990" s="30"/>
       <c r="H990" s="30"/>
       <c r="I990" s="30"/>
@@ -14701,6 +15193,7 @@
       <c r="B991" s="28"/>
       <c r="C991" s="28"/>
       <c r="E991" s="29"/>
+      <c r="F991" s="29"/>
       <c r="G991" s="30"/>
       <c r="H991" s="30"/>
       <c r="I991" s="30"/>
@@ -14711,6 +15204,7 @@
       <c r="B992" s="28"/>
       <c r="C992" s="28"/>
       <c r="E992" s="29"/>
+      <c r="F992" s="29"/>
       <c r="G992" s="30"/>
       <c r="H992" s="30"/>
       <c r="I992" s="30"/>
@@ -14721,6 +15215,7 @@
       <c r="B993" s="28"/>
       <c r="C993" s="28"/>
       <c r="E993" s="29"/>
+      <c r="F993" s="29"/>
       <c r="G993" s="30"/>
       <c r="H993" s="30"/>
       <c r="I993" s="30"/>
@@ -14731,6 +15226,7 @@
       <c r="B994" s="28"/>
       <c r="C994" s="28"/>
       <c r="E994" s="29"/>
+      <c r="F994" s="29"/>
       <c r="G994" s="30"/>
       <c r="H994" s="30"/>
       <c r="I994" s="30"/>
@@ -14741,6 +15237,7 @@
       <c r="B995" s="28"/>
       <c r="C995" s="28"/>
       <c r="E995" s="29"/>
+      <c r="F995" s="29"/>
       <c r="G995" s="30"/>
       <c r="H995" s="30"/>
       <c r="I995" s="30"/>
@@ -14751,6 +15248,7 @@
       <c r="B996" s="28"/>
       <c r="C996" s="28"/>
       <c r="E996" s="29"/>
+      <c r="F996" s="29"/>
       <c r="G996" s="30"/>
       <c r="H996" s="30"/>
       <c r="I996" s="30"/>
@@ -14761,6 +15259,7 @@
       <c r="B997" s="28"/>
       <c r="C997" s="28"/>
       <c r="E997" s="29"/>
+      <c r="F997" s="29"/>
       <c r="G997" s="30"/>
       <c r="H997" s="30"/>
       <c r="I997" s="30"/>
@@ -14771,6 +15270,7 @@
       <c r="B998" s="28"/>
       <c r="C998" s="28"/>
       <c r="E998" s="29"/>
+      <c r="F998" s="29"/>
       <c r="G998" s="30"/>
       <c r="H998" s="30"/>
       <c r="I998" s="30"/>
@@ -14781,6 +15281,7 @@
       <c r="B999" s="28"/>
       <c r="C999" s="28"/>
       <c r="E999" s="29"/>
+      <c r="F999" s="29"/>
       <c r="G999" s="30"/>
       <c r="H999" s="30"/>
       <c r="I999" s="30"/>
@@ -14791,6 +15292,7 @@
       <c r="B1000" s="28"/>
       <c r="C1000" s="28"/>
       <c r="E1000" s="29"/>
+      <c r="F1000" s="29"/>
       <c r="G1000" s="30"/>
       <c r="H1000" s="30"/>
       <c r="I1000" s="30"/>
@@ -14801,6 +15303,7 @@
       <c r="B1001" s="28"/>
       <c r="C1001" s="28"/>
       <c r="E1001" s="29"/>
+      <c r="F1001" s="29"/>
       <c r="G1001" s="30"/>
       <c r="H1001" s="30"/>
       <c r="I1001" s="30"/>
@@ -14811,6 +15314,7 @@
       <c r="B1002" s="28"/>
       <c r="C1002" s="28"/>
       <c r="E1002" s="29"/>
+      <c r="F1002" s="29"/>
       <c r="G1002" s="30"/>
       <c r="H1002" s="30"/>
       <c r="I1002" s="30"/>
@@ -14821,6 +15325,7 @@
       <c r="B1003" s="28"/>
       <c r="C1003" s="28"/>
       <c r="E1003" s="29"/>
+      <c r="F1003" s="29"/>
       <c r="G1003" s="30"/>
       <c r="H1003" s="30"/>
       <c r="I1003" s="30"/>
@@ -14831,6 +15336,7 @@
       <c r="B1004" s="28"/>
       <c r="C1004" s="28"/>
       <c r="E1004" s="29"/>
+      <c r="F1004" s="29"/>
       <c r="G1004" s="30"/>
       <c r="H1004" s="30"/>
       <c r="I1004" s="30"/>
@@ -14841,6 +15347,7 @@
       <c r="B1005" s="28"/>
       <c r="C1005" s="28"/>
       <c r="E1005" s="29"/>
+      <c r="F1005" s="29"/>
       <c r="G1005" s="30"/>
       <c r="H1005" s="30"/>
       <c r="I1005" s="30"/>
@@ -14851,6 +15358,7 @@
       <c r="B1006" s="28"/>
       <c r="C1006" s="28"/>
       <c r="E1006" s="29"/>
+      <c r="F1006" s="29"/>
       <c r="G1006" s="30"/>
       <c r="H1006" s="30"/>
       <c r="I1006" s="30"/>
@@ -14861,6 +15369,7 @@
       <c r="B1007" s="28"/>
       <c r="C1007" s="28"/>
       <c r="E1007" s="29"/>
+      <c r="F1007" s="29"/>
       <c r="G1007" s="30"/>
       <c r="H1007" s="30"/>
       <c r="I1007" s="30"/>
@@ -14871,6 +15380,7 @@
       <c r="B1008" s="28"/>
       <c r="C1008" s="28"/>
       <c r="E1008" s="29"/>
+      <c r="F1008" s="29"/>
       <c r="G1008" s="30"/>
       <c r="H1008" s="30"/>
       <c r="I1008" s="30"/>
@@ -14881,6 +15391,7 @@
       <c r="B1009" s="28"/>
       <c r="C1009" s="28"/>
       <c r="E1009" s="29"/>
+      <c r="F1009" s="29"/>
       <c r="G1009" s="30"/>
       <c r="H1009" s="30"/>
       <c r="I1009" s="30"/>
@@ -14891,6 +15402,7 @@
       <c r="B1010" s="28"/>
       <c r="C1010" s="28"/>
       <c r="E1010" s="29"/>
+      <c r="F1010" s="29"/>
       <c r="G1010" s="30"/>
       <c r="H1010" s="30"/>
       <c r="I1010" s="30"/>
@@ -14901,6 +15413,7 @@
       <c r="B1011" s="28"/>
       <c r="C1011" s="28"/>
       <c r="E1011" s="29"/>
+      <c r="F1011" s="29"/>
       <c r="G1011" s="30"/>
       <c r="H1011" s="30"/>
       <c r="I1011" s="30"/>
@@ -14911,6 +15424,7 @@
       <c r="B1012" s="28"/>
       <c r="C1012" s="28"/>
       <c r="E1012" s="29"/>
+      <c r="F1012" s="29"/>
       <c r="G1012" s="30"/>
       <c r="H1012" s="30"/>
       <c r="I1012" s="30"/>
@@ -14921,6 +15435,7 @@
       <c r="B1013" s="28"/>
       <c r="C1013" s="28"/>
       <c r="E1013" s="29"/>
+      <c r="F1013" s="29"/>
       <c r="G1013" s="30"/>
       <c r="H1013" s="30"/>
       <c r="I1013" s="30"/>
@@ -14931,6 +15446,7 @@
       <c r="B1014" s="28"/>
       <c r="C1014" s="28"/>
       <c r="E1014" s="29"/>
+      <c r="F1014" s="29"/>
       <c r="G1014" s="30"/>
       <c r="H1014" s="30"/>
       <c r="I1014" s="30"/>
@@ -14941,6 +15457,7 @@
       <c r="B1015" s="28"/>
       <c r="C1015" s="28"/>
       <c r="E1015" s="29"/>
+      <c r="F1015" s="29"/>
       <c r="G1015" s="30"/>
       <c r="H1015" s="30"/>
       <c r="I1015" s="30"/>
@@ -14951,6 +15468,7 @@
       <c r="B1016" s="28"/>
       <c r="C1016" s="28"/>
       <c r="E1016" s="29"/>
+      <c r="F1016" s="29"/>
       <c r="G1016" s="30"/>
       <c r="H1016" s="30"/>
       <c r="I1016" s="30"/>
@@ -14961,6 +15479,7 @@
       <c r="B1017" s="28"/>
       <c r="C1017" s="28"/>
       <c r="E1017" s="29"/>
+      <c r="F1017" s="29"/>
       <c r="G1017" s="30"/>
       <c r="H1017" s="30"/>
       <c r="I1017" s="30"/>
@@ -14971,6 +15490,7 @@
       <c r="B1018" s="28"/>
       <c r="C1018" s="28"/>
       <c r="E1018" s="29"/>
+      <c r="F1018" s="29"/>
       <c r="G1018" s="30"/>
       <c r="H1018" s="30"/>
       <c r="I1018" s="30"/>
@@ -14981,6 +15501,7 @@
       <c r="B1019" s="28"/>
       <c r="C1019" s="28"/>
       <c r="E1019" s="29"/>
+      <c r="F1019" s="29"/>
       <c r="G1019" s="30"/>
       <c r="H1019" s="30"/>
       <c r="I1019" s="30"/>
@@ -14991,6 +15512,7 @@
       <c r="B1020" s="28"/>
       <c r="C1020" s="28"/>
       <c r="E1020" s="29"/>
+      <c r="F1020" s="29"/>
       <c r="G1020" s="30"/>
       <c r="H1020" s="30"/>
       <c r="I1020" s="30"/>
@@ -15001,6 +15523,7 @@
       <c r="B1021" s="28"/>
       <c r="C1021" s="28"/>
       <c r="E1021" s="29"/>
+      <c r="F1021" s="29"/>
       <c r="G1021" s="30"/>
       <c r="H1021" s="30"/>
       <c r="I1021" s="30"/>
@@ -15011,6 +15534,7 @@
       <c r="B1022" s="28"/>
       <c r="C1022" s="28"/>
       <c r="E1022" s="29"/>
+      <c r="F1022" s="29"/>
       <c r="G1022" s="30"/>
       <c r="H1022" s="30"/>
       <c r="I1022" s="30"/>
@@ -15021,6 +15545,7 @@
       <c r="B1023" s="28"/>
       <c r="C1023" s="28"/>
       <c r="E1023" s="29"/>
+      <c r="F1023" s="29"/>
       <c r="G1023" s="30"/>
       <c r="H1023" s="30"/>
       <c r="I1023" s="30"/>
@@ -15031,6 +15556,7 @@
       <c r="B1024" s="28"/>
       <c r="C1024" s="28"/>
       <c r="E1024" s="29"/>
+      <c r="F1024" s="29"/>
       <c r="G1024" s="30"/>
       <c r="H1024" s="30"/>
       <c r="I1024" s="30"/>
@@ -15041,6 +15567,7 @@
       <c r="B1025" s="28"/>
       <c r="C1025" s="28"/>
       <c r="E1025" s="29"/>
+      <c r="F1025" s="29"/>
       <c r="G1025" s="30"/>
       <c r="H1025" s="30"/>
       <c r="I1025" s="30"/>
@@ -15051,6 +15578,7 @@
       <c r="B1026" s="28"/>
       <c r="C1026" s="28"/>
       <c r="E1026" s="29"/>
+      <c r="F1026" s="29"/>
       <c r="G1026" s="30"/>
       <c r="H1026" s="30"/>
       <c r="I1026" s="30"/>
@@ -15061,6 +15589,7 @@
       <c r="B1027" s="28"/>
       <c r="C1027" s="28"/>
       <c r="E1027" s="29"/>
+      <c r="F1027" s="29"/>
       <c r="G1027" s="30"/>
       <c r="H1027" s="30"/>
       <c r="I1027" s="30"/>
@@ -15071,6 +15600,7 @@
       <c r="B1028" s="28"/>
       <c r="C1028" s="28"/>
       <c r="E1028" s="29"/>
+      <c r="F1028" s="29"/>
       <c r="G1028" s="30"/>
       <c r="H1028" s="30"/>
       <c r="I1028" s="30"/>
@@ -15081,6 +15611,7 @@
       <c r="B1029" s="28"/>
       <c r="C1029" s="28"/>
       <c r="E1029" s="29"/>
+      <c r="F1029" s="29"/>
       <c r="G1029" s="30"/>
       <c r="H1029" s="30"/>
       <c r="I1029" s="30"/>
@@ -15091,6 +15622,7 @@
       <c r="B1030" s="28"/>
       <c r="C1030" s="28"/>
       <c r="E1030" s="29"/>
+      <c r="F1030" s="29"/>
       <c r="G1030" s="30"/>
       <c r="H1030" s="30"/>
       <c r="I1030" s="30"/>
@@ -15101,6 +15633,7 @@
       <c r="B1031" s="28"/>
       <c r="C1031" s="28"/>
       <c r="E1031" s="29"/>
+      <c r="F1031" s="29"/>
       <c r="G1031" s="30"/>
       <c r="H1031" s="30"/>
       <c r="I1031" s="30"/>
@@ -15111,6 +15644,7 @@
       <c r="B1032" s="28"/>
       <c r="C1032" s="28"/>
       <c r="E1032" s="29"/>
+      <c r="F1032" s="29"/>
       <c r="G1032" s="30"/>
       <c r="H1032" s="30"/>
       <c r="I1032" s="30"/>
@@ -15121,6 +15655,7 @@
       <c r="B1033" s="28"/>
       <c r="C1033" s="28"/>
       <c r="E1033" s="29"/>
+      <c r="F1033" s="29"/>
       <c r="G1033" s="30"/>
       <c r="H1033" s="30"/>
       <c r="I1033" s="30"/>
@@ -15131,6 +15666,7 @@
       <c r="B1034" s="28"/>
       <c r="C1034" s="28"/>
       <c r="E1034" s="29"/>
+      <c r="F1034" s="29"/>
       <c r="G1034" s="30"/>
       <c r="H1034" s="30"/>
       <c r="I1034" s="30"/>
@@ -15141,6 +15677,7 @@
       <c r="B1035" s="28"/>
       <c r="C1035" s="28"/>
       <c r="E1035" s="29"/>
+      <c r="F1035" s="29"/>
       <c r="G1035" s="30"/>
       <c r="H1035" s="30"/>
       <c r="I1035" s="30"/>
@@ -15151,6 +15688,7 @@
       <c r="B1036" s="28"/>
       <c r="C1036" s="28"/>
       <c r="E1036" s="29"/>
+      <c r="F1036" s="29"/>
       <c r="G1036" s="30"/>
       <c r="H1036" s="30"/>
       <c r="I1036" s="30"/>
@@ -15161,6 +15699,7 @@
       <c r="B1037" s="28"/>
       <c r="C1037" s="28"/>
       <c r="E1037" s="29"/>
+      <c r="F1037" s="29"/>
       <c r="G1037" s="30"/>
       <c r="H1037" s="30"/>
       <c r="I1037" s="30"/>
@@ -15171,6 +15710,7 @@
       <c r="B1038" s="28"/>
       <c r="C1038" s="28"/>
       <c r="E1038" s="29"/>
+      <c r="F1038" s="29"/>
       <c r="G1038" s="30"/>
       <c r="H1038" s="30"/>
       <c r="I1038" s="30"/>
@@ -15181,6 +15721,7 @@
       <c r="B1039" s="28"/>
       <c r="C1039" s="28"/>
       <c r="E1039" s="29"/>
+      <c r="F1039" s="29"/>
       <c r="G1039" s="30"/>
       <c r="H1039" s="30"/>
       <c r="I1039" s="30"/>
@@ -15191,6 +15732,7 @@
       <c r="B1040" s="28"/>
       <c r="C1040" s="28"/>
       <c r="E1040" s="29"/>
+      <c r="F1040" s="29"/>
       <c r="G1040" s="30"/>
       <c r="H1040" s="30"/>
       <c r="I1040" s="30"/>
@@ -15201,6 +15743,7 @@
       <c r="B1041" s="28"/>
       <c r="C1041" s="28"/>
       <c r="E1041" s="29"/>
+      <c r="F1041" s="29"/>
       <c r="G1041" s="30"/>
       <c r="H1041" s="30"/>
       <c r="I1041" s="30"/>
@@ -15211,6 +15754,7 @@
       <c r="B1042" s="28"/>
       <c r="C1042" s="28"/>
       <c r="E1042" s="29"/>
+      <c r="F1042" s="29"/>
       <c r="G1042" s="30"/>
       <c r="H1042" s="30"/>
       <c r="I1042" s="30"/>
@@ -15221,6 +15765,7 @@
       <c r="B1043" s="28"/>
       <c r="C1043" s="28"/>
       <c r="E1043" s="29"/>
+      <c r="F1043" s="29"/>
       <c r="G1043" s="30"/>
       <c r="H1043" s="30"/>
       <c r="I1043" s="30"/>
@@ -15231,6 +15776,7 @@
       <c r="B1044" s="28"/>
       <c r="C1044" s="28"/>
       <c r="E1044" s="29"/>
+      <c r="F1044" s="29"/>
       <c r="G1044" s="30"/>
       <c r="H1044" s="30"/>
       <c r="I1044" s="30"/>
@@ -15241,6 +15787,7 @@
       <c r="B1045" s="28"/>
       <c r="C1045" s="28"/>
       <c r="E1045" s="29"/>
+      <c r="F1045" s="29"/>
       <c r="G1045" s="30"/>
       <c r="H1045" s="30"/>
       <c r="I1045" s="30"/>
@@ -15251,6 +15798,7 @@
       <c r="B1046" s="28"/>
       <c r="C1046" s="28"/>
       <c r="E1046" s="29"/>
+      <c r="F1046" s="29"/>
       <c r="G1046" s="30"/>
       <c r="H1046" s="30"/>
       <c r="I1046" s="30"/>
@@ -15261,6 +15809,7 @@
       <c r="B1047" s="28"/>
       <c r="C1047" s="28"/>
       <c r="E1047" s="29"/>
+      <c r="F1047" s="29"/>
       <c r="G1047" s="30"/>
       <c r="H1047" s="30"/>
       <c r="I1047" s="30"/>
@@ -15271,6 +15820,7 @@
       <c r="B1048" s="28"/>
       <c r="C1048" s="28"/>
       <c r="E1048" s="29"/>
+      <c r="F1048" s="29"/>
       <c r="G1048" s="30"/>
       <c r="H1048" s="30"/>
       <c r="I1048" s="30"/>
@@ -15281,6 +15831,7 @@
       <c r="B1049" s="28"/>
       <c r="C1049" s="28"/>
       <c r="E1049" s="29"/>
+      <c r="F1049" s="29"/>
       <c r="G1049" s="30"/>
       <c r="H1049" s="30"/>
       <c r="I1049" s="30"/>
@@ -15291,6 +15842,7 @@
       <c r="B1050" s="28"/>
       <c r="C1050" s="28"/>
       <c r="E1050" s="29"/>
+      <c r="F1050" s="29"/>
       <c r="G1050" s="30"/>
       <c r="H1050" s="30"/>
       <c r="I1050" s="30"/>
@@ -15301,6 +15853,7 @@
       <c r="B1051" s="28"/>
       <c r="C1051" s="28"/>
       <c r="E1051" s="29"/>
+      <c r="F1051" s="29"/>
       <c r="G1051" s="30"/>
       <c r="H1051" s="30"/>
       <c r="I1051" s="30"/>
@@ -15311,6 +15864,7 @@
       <c r="B1052" s="28"/>
       <c r="C1052" s="28"/>
       <c r="E1052" s="29"/>
+      <c r="F1052" s="29"/>
       <c r="G1052" s="30"/>
       <c r="H1052" s="30"/>
       <c r="I1052" s="30"/>
@@ -15359,8 +15913,8 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E1052">
       <formula1>"_,Esperando Revision,En Revision,Reasignado,Validado"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F495">
-      <formula1>"_,Ignacio,Lucia,Luciano,Gabriel,Lucía"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F1052">
+      <formula1>"_,Ignacio,Lucia,Luciano,Gabriel"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="114">
   <si>
     <t>Etapa</t>
   </si>
@@ -166,6 +166,9 @@
     <t>Matriz FODA</t>
   </si>
   <si>
+    <t>Supervision</t>
+  </si>
+  <si>
     <t>Plan de Riesgos y Contingencias</t>
   </si>
   <si>
@@ -242,13 +245,13 @@
     <t>Crear plantilla de formatos de ESRE</t>
   </si>
   <si>
+    <t>Crear Documento Descripcion del Sistema</t>
+  </si>
+  <si>
     <t>RNOF Perfil Director</t>
   </si>
   <si>
     <t>RNOF Perfil Inspector</t>
-  </si>
-  <si>
-    <t>RNOF Perfil Docente</t>
   </si>
   <si>
     <t>RNOF Perfil Estudiante</t>
@@ -350,7 +353,7 @@
     <t>Entrega</t>
   </si>
   <si>
-    <t>Entrega del Proyecto ***</t>
+    <t>Entrega del Proyecto</t>
   </si>
 </sst>
 </file>
@@ -888,7 +891,7 @@
       </c>
       <c r="C2" s="6" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-09-20 16:53</v>
+        <v>Plan de Proyecto: 2026-09-20 18:07</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>14</v>
@@ -1974,22 +1977,22 @@
     </row>
     <row r="27" ht="37.5" customHeight="1">
       <c r="A27" s="10" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G27" s="14">
         <v>46274.0</v>
@@ -2026,14 +2029,14 @@
       <c r="AE27" s="16"/>
     </row>
     <row r="28" ht="37.5" customHeight="1">
-      <c r="A28" s="4" t="s">
-        <v>25</v>
+      <c r="A28" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>14</v>
@@ -2065,7 +2068,7 @@
         <v>26</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>14</v>
@@ -2118,7 +2121,7 @@
         <v>26</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>14</v>
@@ -2149,10 +2152,10 @@
         <v>25</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>14</v>
@@ -2161,7 +2164,7 @@
         <v>15</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G31" s="14">
         <v>46276.0</v>
@@ -2176,7 +2179,7 @@
         <v>20.0</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L31" s="15"/>
       <c r="M31" s="16"/>
@@ -2204,10 +2207,10 @@
         <v>25</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>14</v>
@@ -2231,7 +2234,7 @@
         <v>20.0</v>
       </c>
       <c r="K32" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L32" s="9"/>
     </row>
@@ -2240,10 +2243,10 @@
         <v>25</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>14</v>
@@ -2265,7 +2268,7 @@
       </c>
       <c r="J33" s="15"/>
       <c r="K33" s="15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L33" s="15"/>
       <c r="M33" s="16"/>
@@ -2293,13 +2296,13 @@
         <v>25</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>38</v>
@@ -2316,7 +2319,7 @@
       <c r="I34" s="8"/>
       <c r="J34" s="17"/>
       <c r="K34" s="20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L34" s="9"/>
     </row>
@@ -2325,16 +2328,16 @@
         <v>25</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>16</v>
@@ -2357,16 +2360,16 @@
         <v>25</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>16</v>
@@ -2389,19 +2392,19 @@
         <v>25</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G37" s="14">
         <v>46283.0</v>
@@ -2438,13 +2441,13 @@
         <v>25</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E38" s="7"/>
       <c r="F38" s="7" t="s">
@@ -2466,17 +2469,17 @@
         <v>25</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E39" s="13"/>
       <c r="F39" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G39" s="14">
         <v>46283.0</v>
@@ -2513,13 +2516,13 @@
         <v>25</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E40" s="7"/>
       <c r="F40" s="7" t="s">
@@ -2541,16 +2544,16 @@
         <v>25</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F41" s="13" t="s">
         <v>16</v>
@@ -2590,16 +2593,16 @@
         <v>25</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>16</v>
@@ -2625,7 +2628,7 @@
         <v>20</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D43" s="13" t="s">
         <v>14</v>
@@ -2676,13 +2679,13 @@
         <v>20</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D44" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F44" s="13" t="s">
         <v>16</v>
@@ -2724,27 +2727,29 @@
         <v>25</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G45" s="14">
-        <v>46288.0</v>
+        <v>46284.0</v>
       </c>
       <c r="H45" s="14">
-        <v>46289.0</v>
-      </c>
-      <c r="I45" s="14"/>
+        <v>46285.0</v>
+      </c>
+      <c r="I45" s="14">
+        <v>46285.0</v>
+      </c>
       <c r="J45" s="15"/>
       <c r="K45" s="15"/>
       <c r="L45" s="15"/>
@@ -2769,177 +2774,179 @@
       <c r="AE45" s="16"/>
     </row>
     <row r="46" ht="29.25" customHeight="1">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="10" t="s">
         <v>25</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C46" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F46" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G46" s="14">
+        <v>46288.0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>46289.0</v>
+      </c>
+      <c r="I46" s="14"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="15"/>
+      <c r="L46" s="15"/>
+      <c r="M46" s="16"/>
+      <c r="N46" s="16"/>
+      <c r="O46" s="16"/>
+      <c r="P46" s="16"/>
+      <c r="Q46" s="16"/>
+      <c r="R46" s="16"/>
+      <c r="S46" s="16"/>
+      <c r="T46" s="16"/>
+      <c r="U46" s="16"/>
+      <c r="V46" s="16"/>
+      <c r="W46" s="16"/>
+      <c r="X46" s="16"/>
+      <c r="Y46" s="16"/>
+      <c r="Z46" s="16"/>
+      <c r="AA46" s="16"/>
+      <c r="AB46" s="16"/>
+      <c r="AC46" s="16"/>
+      <c r="AD46" s="16"/>
+      <c r="AE46" s="16"/>
+    </row>
+    <row r="47" ht="29.25" customHeight="1">
+      <c r="A47" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G46" s="8">
+      <c r="G47" s="8">
         <v>46288.0</v>
       </c>
-      <c r="H46" s="8">
+      <c r="H47" s="8">
         <v>46289.0</v>
       </c>
-      <c r="I46" s="8"/>
-      <c r="J46" s="17"/>
-      <c r="K46" s="9"/>
-      <c r="L46" s="9"/>
-    </row>
-    <row r="47" ht="29.25" customHeight="1">
-      <c r="A47" s="10" t="s">
+      <c r="I47" s="8"/>
+      <c r="J47" s="17"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="9"/>
+    </row>
+    <row r="48" ht="29.25" customHeight="1">
+      <c r="A48" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B47" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D47" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G47" s="14">
-        <v>46285.0</v>
-      </c>
-      <c r="H47" s="14">
+      <c r="B48" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G48" s="14">
+        <v>46288.0</v>
+      </c>
+      <c r="H48" s="14">
         <v>46289.0</v>
       </c>
-      <c r="I47" s="14"/>
-      <c r="J47" s="15"/>
-      <c r="K47" s="15"/>
-      <c r="L47" s="15"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="16"/>
-      <c r="O47" s="16"/>
-      <c r="P47" s="16"/>
-      <c r="Q47" s="16"/>
-      <c r="R47" s="16"/>
-      <c r="S47" s="16"/>
-      <c r="T47" s="16"/>
-      <c r="U47" s="16"/>
-      <c r="V47" s="16"/>
-      <c r="W47" s="16"/>
-      <c r="X47" s="16"/>
-      <c r="Y47" s="16"/>
-      <c r="Z47" s="16"/>
-      <c r="AA47" s="16"/>
-      <c r="AB47" s="16"/>
-      <c r="AC47" s="16"/>
-      <c r="AD47" s="16"/>
-      <c r="AE47" s="16"/>
-    </row>
-    <row r="48" ht="29.25" customHeight="1">
-      <c r="A48" s="4" t="s">
+      <c r="I48" s="14"/>
+      <c r="J48" s="15"/>
+      <c r="K48" s="15"/>
+      <c r="L48" s="15"/>
+      <c r="M48" s="16"/>
+      <c r="N48" s="16"/>
+      <c r="O48" s="16"/>
+      <c r="P48" s="16"/>
+      <c r="Q48" s="16"/>
+      <c r="R48" s="16"/>
+      <c r="S48" s="16"/>
+      <c r="T48" s="16"/>
+      <c r="U48" s="16"/>
+      <c r="V48" s="16"/>
+      <c r="W48" s="16"/>
+      <c r="X48" s="16"/>
+      <c r="Y48" s="16"/>
+      <c r="Z48" s="16"/>
+      <c r="AA48" s="16"/>
+      <c r="AB48" s="16"/>
+      <c r="AC48" s="16"/>
+      <c r="AD48" s="16"/>
+      <c r="AE48" s="16"/>
+    </row>
+    <row r="49" ht="29.25" customHeight="1">
+      <c r="A49" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B48" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C48" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7" t="s">
+      <c r="B49" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G48" s="8">
-        <v>46286.0</v>
-      </c>
-      <c r="H48" s="8">
+      <c r="G49" s="8">
         <v>46288.0</v>
       </c>
-      <c r="I48" s="8"/>
-      <c r="J48" s="17"/>
-      <c r="K48" s="9"/>
-      <c r="L48" s="9"/>
-    </row>
-    <row r="49" ht="29.25" customHeight="1">
-      <c r="A49" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B49" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C49" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G49" s="14">
-        <v>46286.0</v>
-      </c>
-      <c r="H49" s="14">
-        <v>46288.0</v>
-      </c>
-      <c r="I49" s="14"/>
-      <c r="J49" s="15"/>
-      <c r="K49" s="15"/>
-      <c r="L49" s="15"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="16"/>
-      <c r="O49" s="16"/>
-      <c r="P49" s="16"/>
-      <c r="Q49" s="16"/>
-      <c r="R49" s="16"/>
-      <c r="S49" s="16"/>
-      <c r="T49" s="16"/>
-      <c r="U49" s="16"/>
-      <c r="V49" s="16"/>
-      <c r="W49" s="16"/>
-      <c r="X49" s="16"/>
-      <c r="Y49" s="16"/>
-      <c r="Z49" s="16"/>
-      <c r="AA49" s="16"/>
-      <c r="AB49" s="16"/>
-      <c r="AC49" s="16"/>
-      <c r="AD49" s="16"/>
-      <c r="AE49" s="16"/>
+      <c r="H49" s="8">
+        <v>46289.0</v>
+      </c>
+      <c r="I49" s="8"/>
+      <c r="J49" s="17"/>
+      <c r="K49" s="9"/>
+      <c r="L49" s="9"/>
     </row>
     <row r="50" ht="29.25" customHeight="1">
       <c r="A50" s="10" t="s">
         <v>25</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>81</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E50" s="13"/>
       <c r="F50" s="13" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G50" s="14">
-        <v>46286.0</v>
+        <v>46288.0</v>
       </c>
       <c r="H50" s="14">
-        <v>46288.0</v>
+        <v>46289.0</v>
       </c>
       <c r="I50" s="14"/>
       <c r="J50" s="15"/>
@@ -2970,23 +2977,23 @@
         <v>25</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>82</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E51" s="13"/>
       <c r="F51" s="13" t="s">
         <v>32</v>
       </c>
       <c r="G51" s="14">
-        <v>46286.0</v>
+        <v>46289.0</v>
       </c>
       <c r="H51" s="14">
-        <v>46288.0</v>
+        <v>46290.0</v>
       </c>
       <c r="I51" s="14"/>
       <c r="J51" s="15"/>
@@ -3017,22 +3024,20 @@
         <v>25</v>
       </c>
       <c r="B52" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C52" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="C52" s="12" t="s">
-        <v>84</v>
-      </c>
       <c r="D52" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="E52" s="13" t="s">
-        <v>67</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="E52" s="13"/>
       <c r="F52" s="13" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="G52" s="14">
-        <v>46287.0</v>
+        <v>46289.0</v>
       </c>
       <c r="H52" s="14">
         <v>46290.0</v>
@@ -3062,200 +3067,221 @@
       <c r="AE52" s="16"/>
     </row>
     <row r="53" ht="29.25" customHeight="1">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="10" t="s">
         <v>25</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C53" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C53" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="D53" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="F53" s="7" t="s">
+      <c r="D53" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E53" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F53" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G53" s="14">
+        <v>46290.0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>46290.0</v>
+      </c>
+      <c r="I53" s="14"/>
+      <c r="J53" s="15"/>
+      <c r="K53" s="15"/>
+      <c r="L53" s="15"/>
+      <c r="M53" s="16"/>
+      <c r="N53" s="16"/>
+      <c r="O53" s="16"/>
+      <c r="P53" s="16"/>
+      <c r="Q53" s="16"/>
+      <c r="R53" s="16"/>
+      <c r="S53" s="16"/>
+      <c r="T53" s="16"/>
+      <c r="U53" s="16"/>
+      <c r="V53" s="16"/>
+      <c r="W53" s="16"/>
+      <c r="X53" s="16"/>
+      <c r="Y53" s="16"/>
+      <c r="Z53" s="16"/>
+      <c r="AA53" s="16"/>
+      <c r="AB53" s="16"/>
+      <c r="AC53" s="16"/>
+      <c r="AD53" s="16"/>
+      <c r="AE53" s="16"/>
+    </row>
+    <row r="54" ht="29.25" customHeight="1">
+      <c r="A54" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F54" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G53" s="8">
+      <c r="G54" s="8">
         <v>46288.0</v>
       </c>
-      <c r="H53" s="8">
-        <v>46290.0</v>
-      </c>
-      <c r="I53" s="8"/>
-      <c r="J53" s="17"/>
-      <c r="K53" s="9"/>
-      <c r="L53" s="9"/>
-    </row>
-    <row r="54" ht="29.25" customHeight="1">
-      <c r="A54" s="10" t="s">
+      <c r="H54" s="8">
+        <v>46291.0</v>
+      </c>
+      <c r="I54" s="8"/>
+      <c r="J54" s="17"/>
+      <c r="K54" s="9"/>
+      <c r="L54" s="9"/>
+    </row>
+    <row r="55" ht="29.25" customHeight="1">
+      <c r="A55" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B54" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="C54" s="12" t="s">
+      <c r="B55" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="D54" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13" t="s">
+      <c r="C55" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G54" s="14">
+      <c r="G55" s="14">
         <v>46291.0</v>
       </c>
-      <c r="H54" s="14">
+      <c r="H55" s="14">
+        <v>46292.0</v>
+      </c>
+      <c r="I55" s="14"/>
+      <c r="J55" s="15"/>
+      <c r="K55" s="15"/>
+      <c r="L55" s="15"/>
+      <c r="M55" s="16"/>
+      <c r="N55" s="16"/>
+      <c r="O55" s="16"/>
+      <c r="P55" s="16"/>
+      <c r="Q55" s="16"/>
+      <c r="R55" s="16"/>
+      <c r="S55" s="16"/>
+      <c r="T55" s="16"/>
+      <c r="U55" s="16"/>
+      <c r="V55" s="16"/>
+      <c r="W55" s="16"/>
+      <c r="X55" s="16"/>
+      <c r="Y55" s="16"/>
+      <c r="Z55" s="16"/>
+      <c r="AA55" s="16"/>
+      <c r="AB55" s="16"/>
+      <c r="AC55" s="16"/>
+      <c r="AD55" s="16"/>
+      <c r="AE55" s="16"/>
+    </row>
+    <row r="56" ht="29.25" customHeight="1">
+      <c r="A56" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G56" s="8">
         <v>46291.0</v>
       </c>
-      <c r="I54" s="14"/>
-      <c r="J54" s="15"/>
-      <c r="K54" s="15"/>
-      <c r="L54" s="15"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="16"/>
-      <c r="O54" s="16"/>
-      <c r="P54" s="16"/>
-      <c r="Q54" s="16"/>
-      <c r="R54" s="16"/>
-      <c r="S54" s="16"/>
-      <c r="T54" s="16"/>
-      <c r="U54" s="16"/>
-      <c r="V54" s="16"/>
-      <c r="W54" s="16"/>
-      <c r="X54" s="16"/>
-      <c r="Y54" s="16"/>
-      <c r="Z54" s="16"/>
-      <c r="AA54" s="16"/>
-      <c r="AB54" s="16"/>
-      <c r="AC54" s="16"/>
-      <c r="AD54" s="16"/>
-      <c r="AE54" s="16"/>
-    </row>
-    <row r="55" ht="29.25" customHeight="1">
-      <c r="A55" s="4" t="s">
+      <c r="H56" s="8">
+        <v>46292.0</v>
+      </c>
+      <c r="I56" s="8"/>
+      <c r="J56" s="9"/>
+      <c r="K56" s="9"/>
+      <c r="L56" s="9"/>
+    </row>
+    <row r="57" ht="29.25" customHeight="1">
+      <c r="A57" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B55" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C55" s="6" t="s">
+      <c r="B57" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="D55" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="F55" s="7" t="s">
+      <c r="C57" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G55" s="8">
+      <c r="G57" s="14">
         <v>46291.0</v>
       </c>
-      <c r="H55" s="8">
-        <v>46291.0</v>
-      </c>
-      <c r="I55" s="8"/>
-      <c r="J55" s="9"/>
-      <c r="K55" s="9"/>
-      <c r="L55" s="9"/>
-    </row>
-    <row r="56" ht="29.25" customHeight="1">
-      <c r="A56" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B56" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C56" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="D56" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G56" s="14">
-        <v>46291.0</v>
-      </c>
-      <c r="H56" s="14">
-        <v>46291.0</v>
-      </c>
-      <c r="I56" s="14"/>
-      <c r="J56" s="15"/>
-      <c r="K56" s="15"/>
-      <c r="L56" s="15"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="16"/>
-      <c r="O56" s="16"/>
-      <c r="P56" s="16"/>
-      <c r="Q56" s="16"/>
-      <c r="R56" s="16"/>
-      <c r="S56" s="16"/>
-      <c r="T56" s="16"/>
-      <c r="U56" s="16"/>
-      <c r="V56" s="16"/>
-      <c r="W56" s="16"/>
-      <c r="X56" s="16"/>
-      <c r="Y56" s="16"/>
-      <c r="Z56" s="16"/>
-      <c r="AA56" s="16"/>
-      <c r="AB56" s="16"/>
-      <c r="AC56" s="16"/>
-      <c r="AD56" s="16"/>
-      <c r="AE56" s="16"/>
-    </row>
-    <row r="57" ht="29.25" customHeight="1">
-      <c r="A57" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G57" s="8">
-        <v>46286.0</v>
-      </c>
-      <c r="H57" s="8">
-        <v>46293.0</v>
-      </c>
-      <c r="I57" s="8"/>
-      <c r="J57" s="9"/>
-      <c r="K57" s="9"/>
-      <c r="L57" s="9"/>
+      <c r="H57" s="14">
+        <v>46292.0</v>
+      </c>
+      <c r="I57" s="14"/>
+      <c r="J57" s="15"/>
+      <c r="K57" s="15"/>
+      <c r="L57" s="15"/>
+      <c r="M57" s="16"/>
+      <c r="N57" s="16"/>
+      <c r="O57" s="16"/>
+      <c r="P57" s="16"/>
+      <c r="Q57" s="16"/>
+      <c r="R57" s="16"/>
+      <c r="S57" s="16"/>
+      <c r="T57" s="16"/>
+      <c r="U57" s="16"/>
+      <c r="V57" s="16"/>
+      <c r="W57" s="16"/>
+      <c r="X57" s="16"/>
+      <c r="Y57" s="16"/>
+      <c r="Z57" s="16"/>
+      <c r="AA57" s="16"/>
+      <c r="AB57" s="16"/>
+      <c r="AC57" s="16"/>
+      <c r="AD57" s="16"/>
+      <c r="AE57" s="16"/>
     </row>
     <row r="58" ht="29.25" customHeight="1">
       <c r="A58" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D58" s="13"/>
+        <v>93</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>73</v>
+      </c>
       <c r="E58" s="13"/>
       <c r="F58" s="13"/>
       <c r="G58" s="14"/>
@@ -3289,12 +3315,14 @@
         <v>25</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="D59" s="13"/>
+        <v>94</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>73</v>
+      </c>
       <c r="E59" s="13"/>
       <c r="F59" s="13"/>
       <c r="G59" s="14"/>
@@ -3328,12 +3356,14 @@
         <v>25</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D60" s="13"/>
+        <v>95</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>73</v>
+      </c>
       <c r="E60" s="13"/>
       <c r="F60" s="13"/>
       <c r="G60" s="14"/>
@@ -3367,12 +3397,14 @@
         <v>25</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D61" s="13"/>
+        <v>96</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>73</v>
+      </c>
       <c r="E61" s="13"/>
       <c r="F61" s="13"/>
       <c r="G61" s="14"/>
@@ -3406,12 +3438,14 @@
         <v>25</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D62" s="13"/>
+        <v>97</v>
+      </c>
+      <c r="D62" s="13" t="s">
+        <v>73</v>
+      </c>
       <c r="E62" s="13"/>
       <c r="F62" s="13"/>
       <c r="G62" s="14"/>
@@ -3441,12 +3475,18 @@
       <c r="AE62" s="16"/>
     </row>
     <row r="63" ht="29.25" customHeight="1">
-      <c r="A63" s="10"/>
-      <c r="B63" s="11"/>
+      <c r="A63" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>92</v>
+      </c>
       <c r="C63" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D63" s="13"/>
+        <v>98</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>73</v>
+      </c>
       <c r="E63" s="13"/>
       <c r="F63" s="13"/>
       <c r="G63" s="14"/>
@@ -3477,19 +3517,19 @@
     </row>
     <row r="64" ht="29.25" customHeight="1">
       <c r="A64" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F64" s="13" t="s">
         <v>32</v>
@@ -3503,7 +3543,7 @@
       <c r="I64" s="14"/>
       <c r="J64" s="15"/>
       <c r="K64" s="15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L64" s="15"/>
       <c r="M64" s="16"/>
@@ -3528,19 +3568,19 @@
     </row>
     <row r="65" ht="29.25" customHeight="1">
       <c r="A65" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F65" s="7" t="s">
         <v>16</v>
@@ -3554,22 +3594,22 @@
       <c r="I65" s="8"/>
       <c r="J65" s="9"/>
       <c r="K65" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L65" s="9"/>
     </row>
     <row r="66" ht="29.25" customHeight="1">
       <c r="A66" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E66" s="7"/>
       <c r="F66" s="7" t="s">
@@ -3588,22 +3628,22 @@
     </row>
     <row r="67" ht="29.25" customHeight="1">
       <c r="A67" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G67" s="14">
         <v>46286.0</v>
@@ -3637,20 +3677,20 @@
     </row>
     <row r="68" ht="29.25" customHeight="1">
       <c r="A68" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E68" s="7"/>
       <c r="F68" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G68" s="8">
         <v>46287.0</v>
@@ -3665,20 +3705,20 @@
     </row>
     <row r="69" ht="29.25" customHeight="1">
       <c r="A69" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E69" s="13"/>
       <c r="F69" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G69" s="14">
         <v>46287.0</v>
@@ -3712,20 +3752,20 @@
     </row>
     <row r="70" ht="29.25" customHeight="1">
       <c r="A70" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E70" s="7"/>
       <c r="F70" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G70" s="8">
         <v>46296.0</v>
@@ -3740,18 +3780,18 @@
     </row>
     <row r="71" ht="29.25" customHeight="1">
       <c r="A71" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D71" s="13"/>
       <c r="E71" s="13"/>
       <c r="F71" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G71" s="14">
         <v>46303.0</v>
@@ -3785,20 +3825,20 @@
     </row>
     <row r="72" ht="29.25" customHeight="1">
       <c r="A72" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E72" s="7"/>
       <c r="F72" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G72" s="8">
         <v>46305.0</v>
@@ -3818,7 +3858,7 @@
       <c r="D73" s="25"/>
       <c r="E73" s="21"/>
       <c r="F73" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G73" s="27"/>
       <c r="H73" s="27"/>
@@ -3834,7 +3874,7 @@
       <c r="D74" s="25"/>
       <c r="E74" s="21"/>
       <c r="F74" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G74" s="27"/>
       <c r="H74" s="27"/>
@@ -3850,7 +3890,7 @@
       <c r="D75" s="25"/>
       <c r="E75" s="21"/>
       <c r="F75" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G75" s="27"/>
       <c r="H75" s="27"/>
@@ -3866,7 +3906,7 @@
       <c r="D76" s="25"/>
       <c r="E76" s="21"/>
       <c r="F76" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G76" s="27"/>
       <c r="H76" s="27"/>
@@ -3882,7 +3922,7 @@
       <c r="D77" s="25"/>
       <c r="E77" s="21"/>
       <c r="F77" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G77" s="27"/>
       <c r="H77" s="27"/>
@@ -3898,7 +3938,7 @@
       <c r="D78" s="25"/>
       <c r="E78" s="29"/>
       <c r="F78" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G78" s="30"/>
       <c r="H78" s="30"/>
@@ -3912,7 +3952,7 @@
       <c r="D79" s="25"/>
       <c r="E79" s="29"/>
       <c r="F79" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G79" s="30"/>
       <c r="H79" s="30"/>
@@ -3926,7 +3966,7 @@
       <c r="D80" s="25"/>
       <c r="E80" s="29"/>
       <c r="F80" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G80" s="30"/>
       <c r="H80" s="30"/>
@@ -3940,7 +3980,7 @@
       <c r="D81" s="25"/>
       <c r="E81" s="29"/>
       <c r="F81" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G81" s="30"/>
       <c r="H81" s="30"/>
@@ -3954,7 +3994,7 @@
       <c r="D82" s="25"/>
       <c r="E82" s="29"/>
       <c r="F82" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G82" s="30"/>
       <c r="H82" s="30"/>
@@ -3968,7 +4008,7 @@
       <c r="D83" s="25"/>
       <c r="E83" s="29"/>
       <c r="F83" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G83" s="30"/>
       <c r="H83" s="30"/>
@@ -3982,7 +4022,7 @@
       <c r="D84" s="25"/>
       <c r="E84" s="29"/>
       <c r="F84" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G84" s="30"/>
       <c r="H84" s="30"/>
@@ -3996,7 +4036,7 @@
       <c r="D85" s="25"/>
       <c r="E85" s="29"/>
       <c r="F85" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G85" s="30"/>
       <c r="H85" s="30"/>
@@ -4010,7 +4050,7 @@
       <c r="D86" s="25"/>
       <c r="E86" s="29"/>
       <c r="F86" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G86" s="30"/>
       <c r="H86" s="30"/>
@@ -4024,7 +4064,7 @@
       <c r="D87" s="25"/>
       <c r="E87" s="29"/>
       <c r="F87" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G87" s="30"/>
       <c r="H87" s="30"/>
@@ -4038,7 +4078,7 @@
       <c r="D88" s="25"/>
       <c r="E88" s="29"/>
       <c r="F88" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G88" s="30"/>
       <c r="H88" s="30"/>
@@ -4052,7 +4092,7 @@
       <c r="D89" s="25"/>
       <c r="E89" s="29"/>
       <c r="F89" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G89" s="30"/>
       <c r="H89" s="30"/>
@@ -4066,7 +4106,7 @@
       <c r="D90" s="25"/>
       <c r="E90" s="29"/>
       <c r="F90" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G90" s="30"/>
       <c r="H90" s="30"/>
@@ -4080,7 +4120,7 @@
       <c r="D91" s="25"/>
       <c r="E91" s="29"/>
       <c r="F91" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G91" s="30"/>
       <c r="H91" s="30"/>
@@ -4094,7 +4134,7 @@
       <c r="D92" s="25"/>
       <c r="E92" s="29"/>
       <c r="F92" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G92" s="30"/>
       <c r="H92" s="30"/>
@@ -4108,7 +4148,7 @@
       <c r="D93" s="25"/>
       <c r="E93" s="29"/>
       <c r="F93" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G93" s="30"/>
       <c r="H93" s="30"/>
@@ -4122,7 +4162,7 @@
       <c r="D94" s="25"/>
       <c r="E94" s="29"/>
       <c r="F94" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G94" s="30"/>
       <c r="H94" s="30"/>
@@ -4136,7 +4176,7 @@
       <c r="D95" s="25"/>
       <c r="E95" s="29"/>
       <c r="F95" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G95" s="30"/>
       <c r="H95" s="30"/>
@@ -4150,7 +4190,7 @@
       <c r="D96" s="25"/>
       <c r="E96" s="29"/>
       <c r="F96" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G96" s="30"/>
       <c r="H96" s="30"/>
@@ -4164,7 +4204,7 @@
       <c r="D97" s="25"/>
       <c r="E97" s="29"/>
       <c r="F97" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G97" s="30"/>
       <c r="H97" s="30"/>
@@ -4178,7 +4218,7 @@
       <c r="D98" s="25"/>
       <c r="E98" s="29"/>
       <c r="F98" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G98" s="30"/>
       <c r="H98" s="30"/>
@@ -4192,7 +4232,7 @@
       <c r="D99" s="25"/>
       <c r="E99" s="29"/>
       <c r="F99" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G99" s="30"/>
       <c r="H99" s="30"/>
@@ -4206,7 +4246,7 @@
       <c r="D100" s="25"/>
       <c r="E100" s="29"/>
       <c r="F100" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G100" s="30"/>
       <c r="H100" s="30"/>
@@ -4220,7 +4260,7 @@
       <c r="D101" s="25"/>
       <c r="E101" s="29"/>
       <c r="F101" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G101" s="30"/>
       <c r="H101" s="30"/>
@@ -4234,7 +4274,7 @@
       <c r="D102" s="25"/>
       <c r="E102" s="29"/>
       <c r="F102" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G102" s="30"/>
       <c r="H102" s="30"/>
@@ -4248,7 +4288,7 @@
       <c r="D103" s="25"/>
       <c r="E103" s="29"/>
       <c r="F103" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G103" s="30"/>
       <c r="H103" s="30"/>
@@ -4262,7 +4302,7 @@
       <c r="D104" s="25"/>
       <c r="E104" s="29"/>
       <c r="F104" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G104" s="30"/>
       <c r="H104" s="30"/>
@@ -4276,7 +4316,7 @@
       <c r="D105" s="25"/>
       <c r="E105" s="29"/>
       <c r="F105" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G105" s="30"/>
       <c r="H105" s="30"/>
@@ -4290,7 +4330,7 @@
       <c r="D106" s="25"/>
       <c r="E106" s="29"/>
       <c r="F106" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G106" s="30"/>
       <c r="H106" s="30"/>
@@ -4304,7 +4344,7 @@
       <c r="D107" s="25"/>
       <c r="E107" s="29"/>
       <c r="F107" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G107" s="30"/>
       <c r="H107" s="30"/>
@@ -4318,7 +4358,7 @@
       <c r="D108" s="25"/>
       <c r="E108" s="29"/>
       <c r="F108" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G108" s="30"/>
       <c r="H108" s="30"/>
@@ -4332,7 +4372,7 @@
       <c r="D109" s="25"/>
       <c r="E109" s="29"/>
       <c r="F109" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G109" s="30"/>
       <c r="H109" s="30"/>
@@ -4346,7 +4386,7 @@
       <c r="D110" s="25"/>
       <c r="E110" s="29"/>
       <c r="F110" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G110" s="30"/>
       <c r="H110" s="30"/>
@@ -4360,7 +4400,7 @@
       <c r="D111" s="25"/>
       <c r="E111" s="29"/>
       <c r="F111" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G111" s="30"/>
       <c r="H111" s="30"/>
@@ -4374,7 +4414,7 @@
       <c r="D112" s="25"/>
       <c r="E112" s="29"/>
       <c r="F112" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G112" s="30"/>
       <c r="H112" s="30"/>
@@ -4388,7 +4428,7 @@
       <c r="D113" s="25"/>
       <c r="E113" s="29"/>
       <c r="F113" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G113" s="30"/>
       <c r="H113" s="30"/>
@@ -4402,7 +4442,7 @@
       <c r="D114" s="25"/>
       <c r="E114" s="29"/>
       <c r="F114" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G114" s="30"/>
       <c r="H114" s="30"/>
@@ -4416,7 +4456,7 @@
       <c r="D115" s="25"/>
       <c r="E115" s="29"/>
       <c r="F115" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G115" s="30"/>
       <c r="H115" s="30"/>
@@ -4430,7 +4470,7 @@
       <c r="D116" s="25"/>
       <c r="E116" s="29"/>
       <c r="F116" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G116" s="30"/>
       <c r="H116" s="30"/>
@@ -4444,7 +4484,7 @@
       <c r="D117" s="25"/>
       <c r="E117" s="29"/>
       <c r="F117" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G117" s="30"/>
       <c r="H117" s="30"/>
@@ -4458,7 +4498,7 @@
       <c r="D118" s="25"/>
       <c r="E118" s="29"/>
       <c r="F118" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G118" s="30"/>
       <c r="H118" s="30"/>
@@ -4472,7 +4512,7 @@
       <c r="D119" s="25"/>
       <c r="E119" s="29"/>
       <c r="F119" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G119" s="30"/>
       <c r="H119" s="30"/>
@@ -4486,7 +4526,7 @@
       <c r="D120" s="25"/>
       <c r="E120" s="29"/>
       <c r="F120" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G120" s="30"/>
       <c r="H120" s="30"/>
@@ -4500,7 +4540,7 @@
       <c r="D121" s="25"/>
       <c r="E121" s="29"/>
       <c r="F121" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G121" s="30"/>
       <c r="H121" s="30"/>
@@ -4514,7 +4554,7 @@
       <c r="D122" s="25"/>
       <c r="E122" s="29"/>
       <c r="F122" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G122" s="30"/>
       <c r="H122" s="30"/>
@@ -4528,7 +4568,7 @@
       <c r="D123" s="25"/>
       <c r="E123" s="29"/>
       <c r="F123" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G123" s="30"/>
       <c r="H123" s="30"/>
@@ -4542,7 +4582,7 @@
       <c r="D124" s="25"/>
       <c r="E124" s="29"/>
       <c r="F124" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G124" s="30"/>
       <c r="H124" s="30"/>
@@ -4556,7 +4596,7 @@
       <c r="D125" s="25"/>
       <c r="E125" s="29"/>
       <c r="F125" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G125" s="30"/>
       <c r="H125" s="30"/>
@@ -4570,7 +4610,7 @@
       <c r="D126" s="25"/>
       <c r="E126" s="29"/>
       <c r="F126" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G126" s="30"/>
       <c r="H126" s="30"/>
@@ -4584,7 +4624,7 @@
       <c r="D127" s="25"/>
       <c r="E127" s="29"/>
       <c r="F127" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G127" s="30"/>
       <c r="H127" s="30"/>
@@ -4598,7 +4638,7 @@
       <c r="D128" s="25"/>
       <c r="E128" s="29"/>
       <c r="F128" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G128" s="30"/>
       <c r="H128" s="30"/>
@@ -4612,7 +4652,7 @@
       <c r="D129" s="25"/>
       <c r="E129" s="29"/>
       <c r="F129" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G129" s="30"/>
       <c r="H129" s="30"/>
@@ -4626,7 +4666,7 @@
       <c r="D130" s="25"/>
       <c r="E130" s="29"/>
       <c r="F130" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G130" s="30"/>
       <c r="H130" s="30"/>
@@ -4640,7 +4680,7 @@
       <c r="D131" s="25"/>
       <c r="E131" s="29"/>
       <c r="F131" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G131" s="30"/>
       <c r="H131" s="30"/>
@@ -4654,7 +4694,7 @@
       <c r="D132" s="25"/>
       <c r="E132" s="29"/>
       <c r="F132" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G132" s="30"/>
       <c r="H132" s="30"/>
@@ -4668,7 +4708,7 @@
       <c r="D133" s="25"/>
       <c r="E133" s="29"/>
       <c r="F133" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G133" s="30"/>
       <c r="H133" s="30"/>
@@ -4682,7 +4722,7 @@
       <c r="D134" s="25"/>
       <c r="E134" s="29"/>
       <c r="F134" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G134" s="30"/>
       <c r="H134" s="30"/>
@@ -4696,7 +4736,7 @@
       <c r="D135" s="25"/>
       <c r="E135" s="29"/>
       <c r="F135" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G135" s="30"/>
       <c r="H135" s="30"/>
@@ -4710,7 +4750,7 @@
       <c r="D136" s="25"/>
       <c r="E136" s="29"/>
       <c r="F136" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G136" s="30"/>
       <c r="H136" s="30"/>
@@ -4724,7 +4764,7 @@
       <c r="D137" s="25"/>
       <c r="E137" s="29"/>
       <c r="F137" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G137" s="30"/>
       <c r="H137" s="30"/>
@@ -4738,7 +4778,7 @@
       <c r="D138" s="25"/>
       <c r="E138" s="29"/>
       <c r="F138" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G138" s="30"/>
       <c r="H138" s="30"/>
@@ -4752,7 +4792,7 @@
       <c r="D139" s="25"/>
       <c r="E139" s="29"/>
       <c r="F139" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G139" s="30"/>
       <c r="H139" s="30"/>
@@ -4766,7 +4806,7 @@
       <c r="D140" s="25"/>
       <c r="E140" s="29"/>
       <c r="F140" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G140" s="30"/>
       <c r="H140" s="30"/>
@@ -4780,7 +4820,7 @@
       <c r="D141" s="25"/>
       <c r="E141" s="29"/>
       <c r="F141" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G141" s="30"/>
       <c r="H141" s="30"/>
@@ -4794,7 +4834,7 @@
       <c r="D142" s="25"/>
       <c r="E142" s="29"/>
       <c r="F142" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G142" s="30"/>
       <c r="H142" s="30"/>
@@ -4808,7 +4848,7 @@
       <c r="D143" s="25"/>
       <c r="E143" s="29"/>
       <c r="F143" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G143" s="30"/>
       <c r="H143" s="30"/>
@@ -4822,7 +4862,7 @@
       <c r="D144" s="25"/>
       <c r="E144" s="29"/>
       <c r="F144" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G144" s="30"/>
       <c r="H144" s="30"/>
@@ -4836,7 +4876,7 @@
       <c r="D145" s="25"/>
       <c r="E145" s="29"/>
       <c r="F145" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G145" s="30"/>
       <c r="H145" s="30"/>
@@ -4850,7 +4890,7 @@
       <c r="D146" s="25"/>
       <c r="E146" s="29"/>
       <c r="F146" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G146" s="30"/>
       <c r="H146" s="30"/>
@@ -4864,7 +4904,7 @@
       <c r="D147" s="25"/>
       <c r="E147" s="29"/>
       <c r="F147" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G147" s="30"/>
       <c r="H147" s="30"/>
@@ -4878,7 +4918,7 @@
       <c r="D148" s="25"/>
       <c r="E148" s="29"/>
       <c r="F148" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G148" s="30"/>
       <c r="H148" s="30"/>
@@ -4892,7 +4932,7 @@
       <c r="D149" s="25"/>
       <c r="E149" s="29"/>
       <c r="F149" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G149" s="30"/>
       <c r="H149" s="30"/>
@@ -4906,7 +4946,7 @@
       <c r="D150" s="25"/>
       <c r="E150" s="29"/>
       <c r="F150" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G150" s="30"/>
       <c r="H150" s="30"/>
@@ -4920,7 +4960,7 @@
       <c r="D151" s="25"/>
       <c r="E151" s="29"/>
       <c r="F151" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G151" s="30"/>
       <c r="H151" s="30"/>
@@ -4934,7 +4974,7 @@
       <c r="D152" s="25"/>
       <c r="E152" s="29"/>
       <c r="F152" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G152" s="30"/>
       <c r="H152" s="30"/>
@@ -4948,7 +4988,7 @@
       <c r="D153" s="25"/>
       <c r="E153" s="29"/>
       <c r="F153" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G153" s="30"/>
       <c r="H153" s="30"/>
@@ -4962,7 +5002,7 @@
       <c r="D154" s="25"/>
       <c r="E154" s="29"/>
       <c r="F154" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G154" s="30"/>
       <c r="H154" s="30"/>
@@ -4976,7 +5016,7 @@
       <c r="D155" s="25"/>
       <c r="E155" s="29"/>
       <c r="F155" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G155" s="30"/>
       <c r="H155" s="30"/>
@@ -4990,7 +5030,7 @@
       <c r="D156" s="25"/>
       <c r="E156" s="29"/>
       <c r="F156" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G156" s="30"/>
       <c r="H156" s="30"/>
@@ -5004,7 +5044,7 @@
       <c r="D157" s="25"/>
       <c r="E157" s="29"/>
       <c r="F157" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G157" s="30"/>
       <c r="H157" s="30"/>
@@ -5018,7 +5058,7 @@
       <c r="D158" s="25"/>
       <c r="E158" s="29"/>
       <c r="F158" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G158" s="30"/>
       <c r="H158" s="30"/>
@@ -5032,7 +5072,7 @@
       <c r="D159" s="25"/>
       <c r="E159" s="29"/>
       <c r="F159" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G159" s="30"/>
       <c r="H159" s="30"/>
@@ -5046,7 +5086,7 @@
       <c r="D160" s="25"/>
       <c r="E160" s="29"/>
       <c r="F160" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G160" s="30"/>
       <c r="H160" s="30"/>
@@ -5060,7 +5100,7 @@
       <c r="D161" s="25"/>
       <c r="E161" s="29"/>
       <c r="F161" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G161" s="30"/>
       <c r="H161" s="30"/>
@@ -5074,7 +5114,7 @@
       <c r="D162" s="25"/>
       <c r="E162" s="29"/>
       <c r="F162" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G162" s="30"/>
       <c r="H162" s="30"/>
@@ -5088,7 +5128,7 @@
       <c r="D163" s="25"/>
       <c r="E163" s="29"/>
       <c r="F163" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G163" s="30"/>
       <c r="H163" s="30"/>
@@ -5102,7 +5142,7 @@
       <c r="D164" s="25"/>
       <c r="E164" s="29"/>
       <c r="F164" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G164" s="30"/>
       <c r="H164" s="30"/>
@@ -5116,7 +5156,7 @@
       <c r="D165" s="25"/>
       <c r="E165" s="29"/>
       <c r="F165" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G165" s="30"/>
       <c r="H165" s="30"/>
@@ -5130,7 +5170,7 @@
       <c r="D166" s="25"/>
       <c r="E166" s="29"/>
       <c r="F166" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G166" s="30"/>
       <c r="H166" s="30"/>
@@ -5144,7 +5184,7 @@
       <c r="D167" s="25"/>
       <c r="E167" s="29"/>
       <c r="F167" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G167" s="30"/>
       <c r="H167" s="30"/>
@@ -5158,7 +5198,7 @@
       <c r="D168" s="25"/>
       <c r="E168" s="29"/>
       <c r="F168" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G168" s="30"/>
       <c r="H168" s="30"/>
@@ -5172,7 +5212,7 @@
       <c r="D169" s="25"/>
       <c r="E169" s="29"/>
       <c r="F169" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G169" s="30"/>
       <c r="H169" s="30"/>
@@ -5186,7 +5226,7 @@
       <c r="D170" s="25"/>
       <c r="E170" s="29"/>
       <c r="F170" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G170" s="30"/>
       <c r="H170" s="30"/>
@@ -5200,7 +5240,7 @@
       <c r="D171" s="25"/>
       <c r="E171" s="29"/>
       <c r="F171" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G171" s="30"/>
       <c r="H171" s="30"/>
@@ -5214,7 +5254,7 @@
       <c r="D172" s="25"/>
       <c r="E172" s="29"/>
       <c r="F172" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G172" s="30"/>
       <c r="H172" s="30"/>
@@ -5228,7 +5268,7 @@
       <c r="D173" s="25"/>
       <c r="E173" s="29"/>
       <c r="F173" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G173" s="30"/>
       <c r="H173" s="30"/>
@@ -5242,7 +5282,7 @@
       <c r="D174" s="25"/>
       <c r="E174" s="29"/>
       <c r="F174" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G174" s="30"/>
       <c r="H174" s="30"/>
@@ -5256,7 +5296,7 @@
       <c r="D175" s="25"/>
       <c r="E175" s="29"/>
       <c r="F175" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G175" s="30"/>
       <c r="H175" s="30"/>
@@ -5270,7 +5310,7 @@
       <c r="D176" s="25"/>
       <c r="E176" s="29"/>
       <c r="F176" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G176" s="30"/>
       <c r="H176" s="30"/>
@@ -5284,7 +5324,7 @@
       <c r="D177" s="25"/>
       <c r="E177" s="29"/>
       <c r="F177" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G177" s="30"/>
       <c r="H177" s="30"/>
@@ -5298,7 +5338,7 @@
       <c r="D178" s="25"/>
       <c r="E178" s="29"/>
       <c r="F178" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G178" s="30"/>
       <c r="H178" s="30"/>
@@ -5312,7 +5352,7 @@
       <c r="D179" s="25"/>
       <c r="E179" s="29"/>
       <c r="F179" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G179" s="30"/>
       <c r="H179" s="30"/>
@@ -5326,7 +5366,7 @@
       <c r="D180" s="25"/>
       <c r="E180" s="29"/>
       <c r="F180" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G180" s="30"/>
       <c r="H180" s="30"/>
@@ -5340,7 +5380,7 @@
       <c r="D181" s="25"/>
       <c r="E181" s="29"/>
       <c r="F181" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G181" s="30"/>
       <c r="H181" s="30"/>
@@ -5354,7 +5394,7 @@
       <c r="D182" s="25"/>
       <c r="E182" s="29"/>
       <c r="F182" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G182" s="30"/>
       <c r="H182" s="30"/>
@@ -5368,7 +5408,7 @@
       <c r="D183" s="25"/>
       <c r="E183" s="29"/>
       <c r="F183" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G183" s="30"/>
       <c r="H183" s="30"/>
@@ -5382,7 +5422,7 @@
       <c r="D184" s="25"/>
       <c r="E184" s="29"/>
       <c r="F184" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G184" s="30"/>
       <c r="H184" s="30"/>
@@ -5396,7 +5436,7 @@
       <c r="D185" s="25"/>
       <c r="E185" s="29"/>
       <c r="F185" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G185" s="30"/>
       <c r="H185" s="30"/>
@@ -5410,7 +5450,7 @@
       <c r="D186" s="25"/>
       <c r="E186" s="29"/>
       <c r="F186" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G186" s="30"/>
       <c r="H186" s="30"/>
@@ -5424,7 +5464,7 @@
       <c r="D187" s="25"/>
       <c r="E187" s="29"/>
       <c r="F187" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G187" s="30"/>
       <c r="H187" s="30"/>
@@ -5438,7 +5478,7 @@
       <c r="D188" s="25"/>
       <c r="E188" s="29"/>
       <c r="F188" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G188" s="30"/>
       <c r="H188" s="30"/>
@@ -5452,7 +5492,7 @@
       <c r="D189" s="25"/>
       <c r="E189" s="29"/>
       <c r="F189" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G189" s="30"/>
       <c r="H189" s="30"/>
@@ -5466,7 +5506,7 @@
       <c r="D190" s="25"/>
       <c r="E190" s="29"/>
       <c r="F190" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G190" s="30"/>
       <c r="H190" s="30"/>
@@ -5480,7 +5520,7 @@
       <c r="D191" s="25"/>
       <c r="E191" s="29"/>
       <c r="F191" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G191" s="30"/>
       <c r="H191" s="30"/>
@@ -5494,7 +5534,7 @@
       <c r="D192" s="25"/>
       <c r="E192" s="29"/>
       <c r="F192" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G192" s="30"/>
       <c r="H192" s="30"/>
@@ -5508,7 +5548,7 @@
       <c r="D193" s="25"/>
       <c r="E193" s="29"/>
       <c r="F193" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G193" s="30"/>
       <c r="H193" s="30"/>
@@ -5522,7 +5562,7 @@
       <c r="D194" s="25"/>
       <c r="E194" s="29"/>
       <c r="F194" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G194" s="30"/>
       <c r="H194" s="30"/>
@@ -5536,7 +5576,7 @@
       <c r="D195" s="25"/>
       <c r="E195" s="29"/>
       <c r="F195" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G195" s="30"/>
       <c r="H195" s="30"/>
@@ -5550,7 +5590,7 @@
       <c r="D196" s="25"/>
       <c r="E196" s="29"/>
       <c r="F196" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G196" s="30"/>
       <c r="H196" s="30"/>
@@ -5564,7 +5604,7 @@
       <c r="D197" s="25"/>
       <c r="E197" s="29"/>
       <c r="F197" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G197" s="30"/>
       <c r="H197" s="30"/>
@@ -5578,7 +5618,7 @@
       <c r="D198" s="25"/>
       <c r="E198" s="29"/>
       <c r="F198" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G198" s="30"/>
       <c r="H198" s="30"/>
@@ -5592,7 +5632,7 @@
       <c r="D199" s="25"/>
       <c r="E199" s="29"/>
       <c r="F199" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G199" s="30"/>
       <c r="H199" s="30"/>
@@ -5606,7 +5646,7 @@
       <c r="D200" s="25"/>
       <c r="E200" s="29"/>
       <c r="F200" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G200" s="30"/>
       <c r="H200" s="30"/>
@@ -5620,7 +5660,7 @@
       <c r="D201" s="25"/>
       <c r="E201" s="29"/>
       <c r="F201" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G201" s="30"/>
       <c r="H201" s="30"/>
@@ -5634,7 +5674,7 @@
       <c r="D202" s="25"/>
       <c r="E202" s="29"/>
       <c r="F202" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G202" s="30"/>
       <c r="H202" s="30"/>
@@ -5648,7 +5688,7 @@
       <c r="D203" s="25"/>
       <c r="E203" s="29"/>
       <c r="F203" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G203" s="30"/>
       <c r="H203" s="30"/>
@@ -5662,7 +5702,7 @@
       <c r="D204" s="25"/>
       <c r="E204" s="29"/>
       <c r="F204" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G204" s="30"/>
       <c r="H204" s="30"/>
@@ -5676,7 +5716,7 @@
       <c r="D205" s="25"/>
       <c r="E205" s="29"/>
       <c r="F205" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G205" s="30"/>
       <c r="H205" s="30"/>
@@ -5690,7 +5730,7 @@
       <c r="D206" s="25"/>
       <c r="E206" s="29"/>
       <c r="F206" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G206" s="30"/>
       <c r="H206" s="30"/>
@@ -5704,7 +5744,7 @@
       <c r="D207" s="25"/>
       <c r="E207" s="29"/>
       <c r="F207" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G207" s="30"/>
       <c r="H207" s="30"/>
@@ -5718,7 +5758,7 @@
       <c r="D208" s="25"/>
       <c r="E208" s="29"/>
       <c r="F208" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G208" s="30"/>
       <c r="H208" s="30"/>
@@ -5732,7 +5772,7 @@
       <c r="D209" s="25"/>
       <c r="E209" s="29"/>
       <c r="F209" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G209" s="30"/>
       <c r="H209" s="30"/>
@@ -5746,7 +5786,7 @@
       <c r="D210" s="25"/>
       <c r="E210" s="29"/>
       <c r="F210" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G210" s="30"/>
       <c r="H210" s="30"/>
@@ -5760,7 +5800,7 @@
       <c r="D211" s="25"/>
       <c r="E211" s="29"/>
       <c r="F211" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G211" s="30"/>
       <c r="H211" s="30"/>
@@ -5774,7 +5814,7 @@
       <c r="D212" s="25"/>
       <c r="E212" s="29"/>
       <c r="F212" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G212" s="30"/>
       <c r="H212" s="30"/>
@@ -5788,7 +5828,7 @@
       <c r="D213" s="25"/>
       <c r="E213" s="29"/>
       <c r="F213" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G213" s="30"/>
       <c r="H213" s="30"/>
@@ -5802,7 +5842,7 @@
       <c r="D214" s="25"/>
       <c r="E214" s="29"/>
       <c r="F214" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G214" s="30"/>
       <c r="H214" s="30"/>
@@ -5816,7 +5856,7 @@
       <c r="D215" s="25"/>
       <c r="E215" s="29"/>
       <c r="F215" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G215" s="30"/>
       <c r="H215" s="30"/>
@@ -5830,7 +5870,7 @@
       <c r="D216" s="25"/>
       <c r="E216" s="29"/>
       <c r="F216" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G216" s="30"/>
       <c r="H216" s="30"/>
@@ -5844,7 +5884,7 @@
       <c r="D217" s="25"/>
       <c r="E217" s="29"/>
       <c r="F217" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G217" s="30"/>
       <c r="H217" s="30"/>
@@ -5858,7 +5898,7 @@
       <c r="D218" s="25"/>
       <c r="E218" s="29"/>
       <c r="F218" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G218" s="30"/>
       <c r="H218" s="30"/>
@@ -5872,7 +5912,7 @@
       <c r="D219" s="25"/>
       <c r="E219" s="29"/>
       <c r="F219" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G219" s="30"/>
       <c r="H219" s="30"/>
@@ -5886,7 +5926,7 @@
       <c r="D220" s="25"/>
       <c r="E220" s="29"/>
       <c r="F220" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G220" s="30"/>
       <c r="H220" s="30"/>
@@ -5900,7 +5940,7 @@
       <c r="D221" s="25"/>
       <c r="E221" s="29"/>
       <c r="F221" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G221" s="30"/>
       <c r="H221" s="30"/>
@@ -5914,7 +5954,7 @@
       <c r="D222" s="25"/>
       <c r="E222" s="29"/>
       <c r="F222" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G222" s="30"/>
       <c r="H222" s="30"/>
@@ -5928,7 +5968,7 @@
       <c r="D223" s="25"/>
       <c r="E223" s="29"/>
       <c r="F223" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G223" s="30"/>
       <c r="H223" s="30"/>
@@ -5942,7 +5982,7 @@
       <c r="D224" s="25"/>
       <c r="E224" s="29"/>
       <c r="F224" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G224" s="30"/>
       <c r="H224" s="30"/>
@@ -5956,7 +5996,7 @@
       <c r="D225" s="25"/>
       <c r="E225" s="29"/>
       <c r="F225" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G225" s="30"/>
       <c r="H225" s="30"/>
@@ -5970,7 +6010,7 @@
       <c r="D226" s="25"/>
       <c r="E226" s="29"/>
       <c r="F226" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G226" s="30"/>
       <c r="H226" s="30"/>
@@ -5984,7 +6024,7 @@
       <c r="D227" s="25"/>
       <c r="E227" s="29"/>
       <c r="F227" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G227" s="30"/>
       <c r="H227" s="30"/>
@@ -5998,7 +6038,7 @@
       <c r="D228" s="25"/>
       <c r="E228" s="29"/>
       <c r="F228" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G228" s="30"/>
       <c r="H228" s="30"/>
@@ -6012,7 +6052,7 @@
       <c r="D229" s="25"/>
       <c r="E229" s="29"/>
       <c r="F229" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G229" s="30"/>
       <c r="H229" s="30"/>
@@ -6026,7 +6066,7 @@
       <c r="D230" s="25"/>
       <c r="E230" s="29"/>
       <c r="F230" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G230" s="30"/>
       <c r="H230" s="30"/>
@@ -6040,7 +6080,7 @@
       <c r="D231" s="25"/>
       <c r="E231" s="29"/>
       <c r="F231" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G231" s="30"/>
       <c r="H231" s="30"/>
@@ -6054,7 +6094,7 @@
       <c r="D232" s="25"/>
       <c r="E232" s="29"/>
       <c r="F232" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G232" s="30"/>
       <c r="H232" s="30"/>
@@ -6068,7 +6108,7 @@
       <c r="D233" s="25"/>
       <c r="E233" s="29"/>
       <c r="F233" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G233" s="30"/>
       <c r="H233" s="30"/>
@@ -6082,7 +6122,7 @@
       <c r="D234" s="25"/>
       <c r="E234" s="29"/>
       <c r="F234" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G234" s="30"/>
       <c r="H234" s="30"/>
@@ -6096,7 +6136,7 @@
       <c r="D235" s="25"/>
       <c r="E235" s="29"/>
       <c r="F235" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G235" s="30"/>
       <c r="H235" s="30"/>
@@ -6110,7 +6150,7 @@
       <c r="D236" s="25"/>
       <c r="E236" s="29"/>
       <c r="F236" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G236" s="30"/>
       <c r="H236" s="30"/>
@@ -6124,7 +6164,7 @@
       <c r="D237" s="25"/>
       <c r="E237" s="29"/>
       <c r="F237" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G237" s="30"/>
       <c r="H237" s="30"/>
@@ -6138,7 +6178,7 @@
       <c r="D238" s="25"/>
       <c r="E238" s="29"/>
       <c r="F238" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G238" s="30"/>
       <c r="H238" s="30"/>
@@ -6152,7 +6192,7 @@
       <c r="D239" s="25"/>
       <c r="E239" s="29"/>
       <c r="F239" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G239" s="30"/>
       <c r="H239" s="30"/>
@@ -6166,7 +6206,7 @@
       <c r="D240" s="25"/>
       <c r="E240" s="29"/>
       <c r="F240" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G240" s="30"/>
       <c r="H240" s="30"/>
@@ -6180,7 +6220,7 @@
       <c r="D241" s="25"/>
       <c r="E241" s="29"/>
       <c r="F241" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G241" s="30"/>
       <c r="H241" s="30"/>
@@ -6194,7 +6234,7 @@
       <c r="D242" s="25"/>
       <c r="E242" s="29"/>
       <c r="F242" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G242" s="30"/>
       <c r="H242" s="30"/>
@@ -6208,7 +6248,7 @@
       <c r="D243" s="25"/>
       <c r="E243" s="29"/>
       <c r="F243" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G243" s="30"/>
       <c r="H243" s="30"/>
@@ -6222,7 +6262,7 @@
       <c r="D244" s="25"/>
       <c r="E244" s="29"/>
       <c r="F244" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G244" s="30"/>
       <c r="H244" s="30"/>
@@ -6236,7 +6276,7 @@
       <c r="D245" s="25"/>
       <c r="E245" s="29"/>
       <c r="F245" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G245" s="30"/>
       <c r="H245" s="30"/>
@@ -6250,7 +6290,7 @@
       <c r="D246" s="25"/>
       <c r="E246" s="29"/>
       <c r="F246" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G246" s="30"/>
       <c r="H246" s="30"/>
@@ -6264,7 +6304,7 @@
       <c r="D247" s="25"/>
       <c r="E247" s="29"/>
       <c r="F247" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G247" s="30"/>
       <c r="H247" s="30"/>
@@ -6278,7 +6318,7 @@
       <c r="D248" s="25"/>
       <c r="E248" s="29"/>
       <c r="F248" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G248" s="30"/>
       <c r="H248" s="30"/>
@@ -6292,7 +6332,7 @@
       <c r="D249" s="25"/>
       <c r="E249" s="29"/>
       <c r="F249" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G249" s="30"/>
       <c r="H249" s="30"/>
@@ -6306,7 +6346,7 @@
       <c r="D250" s="25"/>
       <c r="E250" s="29"/>
       <c r="F250" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G250" s="30"/>
       <c r="H250" s="30"/>
@@ -6320,7 +6360,7 @@
       <c r="D251" s="25"/>
       <c r="E251" s="29"/>
       <c r="F251" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G251" s="30"/>
       <c r="H251" s="30"/>
@@ -6334,7 +6374,7 @@
       <c r="D252" s="25"/>
       <c r="E252" s="29"/>
       <c r="F252" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G252" s="30"/>
       <c r="H252" s="30"/>
@@ -6348,7 +6388,7 @@
       <c r="D253" s="25"/>
       <c r="E253" s="29"/>
       <c r="F253" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G253" s="30"/>
       <c r="H253" s="30"/>
@@ -6362,7 +6402,7 @@
       <c r="D254" s="25"/>
       <c r="E254" s="29"/>
       <c r="F254" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G254" s="30"/>
       <c r="H254" s="30"/>
@@ -6376,7 +6416,7 @@
       <c r="D255" s="25"/>
       <c r="E255" s="29"/>
       <c r="F255" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G255" s="30"/>
       <c r="H255" s="30"/>
@@ -6390,7 +6430,7 @@
       <c r="D256" s="25"/>
       <c r="E256" s="29"/>
       <c r="F256" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G256" s="30"/>
       <c r="H256" s="30"/>
@@ -6404,7 +6444,7 @@
       <c r="D257" s="25"/>
       <c r="E257" s="29"/>
       <c r="F257" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G257" s="30"/>
       <c r="H257" s="30"/>
@@ -6418,7 +6458,7 @@
       <c r="D258" s="25"/>
       <c r="E258" s="29"/>
       <c r="F258" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G258" s="30"/>
       <c r="H258" s="30"/>
@@ -6432,7 +6472,7 @@
       <c r="D259" s="25"/>
       <c r="E259" s="29"/>
       <c r="F259" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G259" s="30"/>
       <c r="H259" s="30"/>
@@ -6446,7 +6486,7 @@
       <c r="D260" s="25"/>
       <c r="E260" s="29"/>
       <c r="F260" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G260" s="30"/>
       <c r="H260" s="30"/>
@@ -6460,7 +6500,7 @@
       <c r="D261" s="25"/>
       <c r="E261" s="29"/>
       <c r="F261" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G261" s="30"/>
       <c r="H261" s="30"/>
@@ -6474,7 +6514,7 @@
       <c r="D262" s="25"/>
       <c r="E262" s="29"/>
       <c r="F262" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G262" s="30"/>
       <c r="H262" s="30"/>
@@ -6488,7 +6528,7 @@
       <c r="D263" s="25"/>
       <c r="E263" s="29"/>
       <c r="F263" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G263" s="30"/>
       <c r="H263" s="30"/>
@@ -6502,7 +6542,7 @@
       <c r="D264" s="25"/>
       <c r="E264" s="29"/>
       <c r="F264" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G264" s="30"/>
       <c r="H264" s="30"/>
@@ -6516,7 +6556,7 @@
       <c r="D265" s="25"/>
       <c r="E265" s="29"/>
       <c r="F265" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G265" s="30"/>
       <c r="H265" s="30"/>
@@ -6530,7 +6570,7 @@
       <c r="D266" s="25"/>
       <c r="E266" s="29"/>
       <c r="F266" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G266" s="30"/>
       <c r="H266" s="30"/>
@@ -6544,7 +6584,7 @@
       <c r="D267" s="25"/>
       <c r="E267" s="29"/>
       <c r="F267" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G267" s="30"/>
       <c r="H267" s="30"/>
@@ -6558,7 +6598,7 @@
       <c r="D268" s="25"/>
       <c r="E268" s="29"/>
       <c r="F268" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G268" s="30"/>
       <c r="H268" s="30"/>
@@ -6572,7 +6612,7 @@
       <c r="D269" s="25"/>
       <c r="E269" s="29"/>
       <c r="F269" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G269" s="30"/>
       <c r="H269" s="30"/>
@@ -6586,7 +6626,7 @@
       <c r="D270" s="25"/>
       <c r="E270" s="29"/>
       <c r="F270" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G270" s="30"/>
       <c r="H270" s="30"/>
@@ -6600,7 +6640,7 @@
       <c r="D271" s="25"/>
       <c r="E271" s="29"/>
       <c r="F271" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G271" s="30"/>
       <c r="H271" s="30"/>
@@ -6614,7 +6654,7 @@
       <c r="D272" s="25"/>
       <c r="E272" s="29"/>
       <c r="F272" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G272" s="30"/>
       <c r="H272" s="30"/>
@@ -6628,7 +6668,7 @@
       <c r="D273" s="25"/>
       <c r="E273" s="29"/>
       <c r="F273" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G273" s="30"/>
       <c r="H273" s="30"/>
@@ -6642,7 +6682,7 @@
       <c r="D274" s="25"/>
       <c r="E274" s="29"/>
       <c r="F274" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G274" s="30"/>
       <c r="H274" s="30"/>
@@ -6656,7 +6696,7 @@
       <c r="D275" s="25"/>
       <c r="E275" s="29"/>
       <c r="F275" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G275" s="30"/>
       <c r="H275" s="30"/>
@@ -6670,7 +6710,7 @@
       <c r="D276" s="25"/>
       <c r="E276" s="29"/>
       <c r="F276" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G276" s="30"/>
       <c r="H276" s="30"/>
@@ -6684,7 +6724,7 @@
       <c r="D277" s="25"/>
       <c r="E277" s="29"/>
       <c r="F277" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G277" s="30"/>
       <c r="H277" s="30"/>
@@ -6698,7 +6738,7 @@
       <c r="D278" s="25"/>
       <c r="E278" s="29"/>
       <c r="F278" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G278" s="30"/>
       <c r="H278" s="30"/>
@@ -6712,7 +6752,7 @@
       <c r="D279" s="25"/>
       <c r="E279" s="29"/>
       <c r="F279" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G279" s="30"/>
       <c r="H279" s="30"/>
@@ -6726,7 +6766,7 @@
       <c r="D280" s="25"/>
       <c r="E280" s="29"/>
       <c r="F280" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G280" s="30"/>
       <c r="H280" s="30"/>
@@ -6740,7 +6780,7 @@
       <c r="D281" s="25"/>
       <c r="E281" s="29"/>
       <c r="F281" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G281" s="30"/>
       <c r="H281" s="30"/>
@@ -6754,7 +6794,7 @@
       <c r="D282" s="25"/>
       <c r="E282" s="29"/>
       <c r="F282" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G282" s="30"/>
       <c r="H282" s="30"/>
@@ -6768,7 +6808,7 @@
       <c r="D283" s="25"/>
       <c r="E283" s="29"/>
       <c r="F283" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G283" s="30"/>
       <c r="H283" s="30"/>
@@ -6782,7 +6822,7 @@
       <c r="D284" s="25"/>
       <c r="E284" s="29"/>
       <c r="F284" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G284" s="30"/>
       <c r="H284" s="30"/>
@@ -6796,7 +6836,7 @@
       <c r="D285" s="25"/>
       <c r="E285" s="29"/>
       <c r="F285" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G285" s="30"/>
       <c r="H285" s="30"/>
@@ -6810,7 +6850,7 @@
       <c r="D286" s="25"/>
       <c r="E286" s="29"/>
       <c r="F286" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G286" s="30"/>
       <c r="H286" s="30"/>
@@ -6824,7 +6864,7 @@
       <c r="D287" s="25"/>
       <c r="E287" s="29"/>
       <c r="F287" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G287" s="30"/>
       <c r="H287" s="30"/>
@@ -6838,7 +6878,7 @@
       <c r="D288" s="25"/>
       <c r="E288" s="29"/>
       <c r="F288" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G288" s="30"/>
       <c r="H288" s="30"/>
@@ -6852,7 +6892,7 @@
       <c r="D289" s="25"/>
       <c r="E289" s="29"/>
       <c r="F289" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G289" s="30"/>
       <c r="H289" s="30"/>
@@ -6866,7 +6906,7 @@
       <c r="D290" s="25"/>
       <c r="E290" s="29"/>
       <c r="F290" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G290" s="30"/>
       <c r="H290" s="30"/>
@@ -6880,7 +6920,7 @@
       <c r="D291" s="25"/>
       <c r="E291" s="29"/>
       <c r="F291" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G291" s="30"/>
       <c r="H291" s="30"/>
@@ -6894,7 +6934,7 @@
       <c r="D292" s="25"/>
       <c r="E292" s="29"/>
       <c r="F292" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G292" s="30"/>
       <c r="H292" s="30"/>
@@ -6908,7 +6948,7 @@
       <c r="D293" s="25"/>
       <c r="E293" s="29"/>
       <c r="F293" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G293" s="30"/>
       <c r="H293" s="30"/>
@@ -6922,7 +6962,7 @@
       <c r="D294" s="25"/>
       <c r="E294" s="29"/>
       <c r="F294" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G294" s="30"/>
       <c r="H294" s="30"/>
@@ -6936,7 +6976,7 @@
       <c r="D295" s="25"/>
       <c r="E295" s="29"/>
       <c r="F295" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G295" s="30"/>
       <c r="H295" s="30"/>
@@ -6950,7 +6990,7 @@
       <c r="D296" s="25"/>
       <c r="E296" s="29"/>
       <c r="F296" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G296" s="30"/>
       <c r="H296" s="30"/>
@@ -6964,7 +7004,7 @@
       <c r="D297" s="25"/>
       <c r="E297" s="29"/>
       <c r="F297" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G297" s="30"/>
       <c r="H297" s="30"/>
@@ -6978,7 +7018,7 @@
       <c r="D298" s="25"/>
       <c r="E298" s="29"/>
       <c r="F298" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G298" s="30"/>
       <c r="H298" s="30"/>
@@ -6992,7 +7032,7 @@
       <c r="D299" s="25"/>
       <c r="E299" s="29"/>
       <c r="F299" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G299" s="30"/>
       <c r="H299" s="30"/>
@@ -7006,7 +7046,7 @@
       <c r="D300" s="25"/>
       <c r="E300" s="29"/>
       <c r="F300" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G300" s="30"/>
       <c r="H300" s="30"/>
@@ -7020,7 +7060,7 @@
       <c r="D301" s="25"/>
       <c r="E301" s="29"/>
       <c r="F301" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G301" s="30"/>
       <c r="H301" s="30"/>
@@ -7034,7 +7074,7 @@
       <c r="D302" s="25"/>
       <c r="E302" s="29"/>
       <c r="F302" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G302" s="30"/>
       <c r="H302" s="30"/>
@@ -7048,7 +7088,7 @@
       <c r="D303" s="25"/>
       <c r="E303" s="29"/>
       <c r="F303" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G303" s="30"/>
       <c r="H303" s="30"/>
@@ -7062,7 +7102,7 @@
       <c r="D304" s="25"/>
       <c r="E304" s="29"/>
       <c r="F304" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G304" s="30"/>
       <c r="H304" s="30"/>
@@ -7076,7 +7116,7 @@
       <c r="D305" s="25"/>
       <c r="E305" s="29"/>
       <c r="F305" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G305" s="30"/>
       <c r="H305" s="30"/>
@@ -7090,7 +7130,7 @@
       <c r="D306" s="25"/>
       <c r="E306" s="29"/>
       <c r="F306" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G306" s="30"/>
       <c r="H306" s="30"/>
@@ -7104,7 +7144,7 @@
       <c r="D307" s="25"/>
       <c r="E307" s="29"/>
       <c r="F307" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G307" s="30"/>
       <c r="H307" s="30"/>
@@ -7118,7 +7158,7 @@
       <c r="D308" s="25"/>
       <c r="E308" s="29"/>
       <c r="F308" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G308" s="30"/>
       <c r="H308" s="30"/>
@@ -7132,7 +7172,7 @@
       <c r="D309" s="25"/>
       <c r="E309" s="29"/>
       <c r="F309" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G309" s="30"/>
       <c r="H309" s="30"/>
@@ -7146,7 +7186,7 @@
       <c r="D310" s="25"/>
       <c r="E310" s="29"/>
       <c r="F310" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G310" s="30"/>
       <c r="H310" s="30"/>
@@ -7160,7 +7200,7 @@
       <c r="D311" s="25"/>
       <c r="E311" s="29"/>
       <c r="F311" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G311" s="30"/>
       <c r="H311" s="30"/>
@@ -7174,7 +7214,7 @@
       <c r="D312" s="25"/>
       <c r="E312" s="29"/>
       <c r="F312" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G312" s="30"/>
       <c r="H312" s="30"/>
@@ -7188,7 +7228,7 @@
       <c r="D313" s="25"/>
       <c r="E313" s="29"/>
       <c r="F313" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G313" s="30"/>
       <c r="H313" s="30"/>
@@ -7202,7 +7242,7 @@
       <c r="D314" s="25"/>
       <c r="E314" s="29"/>
       <c r="F314" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G314" s="30"/>
       <c r="H314" s="30"/>
@@ -7216,7 +7256,7 @@
       <c r="D315" s="25"/>
       <c r="E315" s="29"/>
       <c r="F315" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G315" s="30"/>
       <c r="H315" s="30"/>
@@ -7230,7 +7270,7 @@
       <c r="D316" s="25"/>
       <c r="E316" s="29"/>
       <c r="F316" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G316" s="30"/>
       <c r="H316" s="30"/>
@@ -7244,7 +7284,7 @@
       <c r="D317" s="25"/>
       <c r="E317" s="29"/>
       <c r="F317" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G317" s="30"/>
       <c r="H317" s="30"/>
@@ -7258,7 +7298,7 @@
       <c r="D318" s="25"/>
       <c r="E318" s="29"/>
       <c r="F318" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G318" s="30"/>
       <c r="H318" s="30"/>
@@ -7272,7 +7312,7 @@
       <c r="D319" s="25"/>
       <c r="E319" s="29"/>
       <c r="F319" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G319" s="30"/>
       <c r="H319" s="30"/>
@@ -7286,7 +7326,7 @@
       <c r="D320" s="25"/>
       <c r="E320" s="29"/>
       <c r="F320" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G320" s="30"/>
       <c r="H320" s="30"/>
@@ -7300,7 +7340,7 @@
       <c r="D321" s="25"/>
       <c r="E321" s="29"/>
       <c r="F321" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G321" s="30"/>
       <c r="H321" s="30"/>
@@ -7314,7 +7354,7 @@
       <c r="D322" s="25"/>
       <c r="E322" s="29"/>
       <c r="F322" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G322" s="30"/>
       <c r="H322" s="30"/>
@@ -7328,7 +7368,7 @@
       <c r="D323" s="25"/>
       <c r="E323" s="29"/>
       <c r="F323" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G323" s="30"/>
       <c r="H323" s="30"/>
@@ -7342,7 +7382,7 @@
       <c r="D324" s="25"/>
       <c r="E324" s="29"/>
       <c r="F324" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G324" s="30"/>
       <c r="H324" s="30"/>
@@ -7356,7 +7396,7 @@
       <c r="D325" s="25"/>
       <c r="E325" s="29"/>
       <c r="F325" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G325" s="30"/>
       <c r="H325" s="30"/>
@@ -7370,7 +7410,7 @@
       <c r="D326" s="25"/>
       <c r="E326" s="29"/>
       <c r="F326" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G326" s="30"/>
       <c r="H326" s="30"/>
@@ -7384,7 +7424,7 @@
       <c r="D327" s="25"/>
       <c r="E327" s="29"/>
       <c r="F327" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G327" s="30"/>
       <c r="H327" s="30"/>
@@ -7398,7 +7438,7 @@
       <c r="D328" s="25"/>
       <c r="E328" s="29"/>
       <c r="F328" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G328" s="30"/>
       <c r="H328" s="30"/>
@@ -7412,7 +7452,7 @@
       <c r="D329" s="25"/>
       <c r="E329" s="29"/>
       <c r="F329" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G329" s="30"/>
       <c r="H329" s="30"/>
@@ -7426,7 +7466,7 @@
       <c r="D330" s="25"/>
       <c r="E330" s="29"/>
       <c r="F330" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G330" s="30"/>
       <c r="H330" s="30"/>
@@ -7440,7 +7480,7 @@
       <c r="D331" s="25"/>
       <c r="E331" s="29"/>
       <c r="F331" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G331" s="30"/>
       <c r="H331" s="30"/>
@@ -7454,7 +7494,7 @@
       <c r="D332" s="25"/>
       <c r="E332" s="29"/>
       <c r="F332" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G332" s="30"/>
       <c r="H332" s="30"/>
@@ -7468,7 +7508,7 @@
       <c r="D333" s="25"/>
       <c r="E333" s="29"/>
       <c r="F333" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G333" s="30"/>
       <c r="H333" s="30"/>
@@ -7482,7 +7522,7 @@
       <c r="D334" s="25"/>
       <c r="E334" s="29"/>
       <c r="F334" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G334" s="30"/>
       <c r="H334" s="30"/>
@@ -7496,7 +7536,7 @@
       <c r="D335" s="25"/>
       <c r="E335" s="29"/>
       <c r="F335" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G335" s="30"/>
       <c r="H335" s="30"/>
@@ -7510,7 +7550,7 @@
       <c r="D336" s="25"/>
       <c r="E336" s="29"/>
       <c r="F336" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G336" s="30"/>
       <c r="H336" s="30"/>
@@ -7524,7 +7564,7 @@
       <c r="D337" s="25"/>
       <c r="E337" s="29"/>
       <c r="F337" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G337" s="30"/>
       <c r="H337" s="30"/>
@@ -7538,7 +7578,7 @@
       <c r="D338" s="25"/>
       <c r="E338" s="29"/>
       <c r="F338" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G338" s="30"/>
       <c r="H338" s="30"/>
@@ -7552,7 +7592,7 @@
       <c r="D339" s="25"/>
       <c r="E339" s="29"/>
       <c r="F339" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G339" s="30"/>
       <c r="H339" s="30"/>
@@ -7566,7 +7606,7 @@
       <c r="D340" s="25"/>
       <c r="E340" s="29"/>
       <c r="F340" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G340" s="30"/>
       <c r="H340" s="30"/>
@@ -7580,7 +7620,7 @@
       <c r="D341" s="25"/>
       <c r="E341" s="29"/>
       <c r="F341" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G341" s="30"/>
       <c r="H341" s="30"/>
@@ -7594,7 +7634,7 @@
       <c r="D342" s="25"/>
       <c r="E342" s="29"/>
       <c r="F342" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G342" s="30"/>
       <c r="H342" s="30"/>
@@ -7608,7 +7648,7 @@
       <c r="D343" s="25"/>
       <c r="E343" s="29"/>
       <c r="F343" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G343" s="30"/>
       <c r="H343" s="30"/>
@@ -7622,7 +7662,7 @@
       <c r="D344" s="25"/>
       <c r="E344" s="29"/>
       <c r="F344" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G344" s="30"/>
       <c r="H344" s="30"/>
@@ -7636,7 +7676,7 @@
       <c r="D345" s="25"/>
       <c r="E345" s="29"/>
       <c r="F345" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G345" s="30"/>
       <c r="H345" s="30"/>
@@ -7650,7 +7690,7 @@
       <c r="D346" s="25"/>
       <c r="E346" s="29"/>
       <c r="F346" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G346" s="30"/>
       <c r="H346" s="30"/>
@@ -7664,7 +7704,7 @@
       <c r="D347" s="25"/>
       <c r="E347" s="29"/>
       <c r="F347" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G347" s="30"/>
       <c r="H347" s="30"/>
@@ -7678,7 +7718,7 @@
       <c r="D348" s="25"/>
       <c r="E348" s="29"/>
       <c r="F348" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G348" s="30"/>
       <c r="H348" s="30"/>
@@ -7692,7 +7732,7 @@
       <c r="D349" s="25"/>
       <c r="E349" s="29"/>
       <c r="F349" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G349" s="30"/>
       <c r="H349" s="30"/>
@@ -7706,7 +7746,7 @@
       <c r="D350" s="25"/>
       <c r="E350" s="29"/>
       <c r="F350" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G350" s="30"/>
       <c r="H350" s="30"/>
@@ -7720,7 +7760,7 @@
       <c r="D351" s="25"/>
       <c r="E351" s="29"/>
       <c r="F351" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G351" s="30"/>
       <c r="H351" s="30"/>
@@ -7734,7 +7774,7 @@
       <c r="D352" s="25"/>
       <c r="E352" s="29"/>
       <c r="F352" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G352" s="30"/>
       <c r="H352" s="30"/>
@@ -7748,7 +7788,7 @@
       <c r="D353" s="25"/>
       <c r="E353" s="29"/>
       <c r="F353" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G353" s="30"/>
       <c r="H353" s="30"/>
@@ -7762,7 +7802,7 @@
       <c r="D354" s="25"/>
       <c r="E354" s="29"/>
       <c r="F354" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G354" s="30"/>
       <c r="H354" s="30"/>
@@ -7776,7 +7816,7 @@
       <c r="D355" s="25"/>
       <c r="E355" s="29"/>
       <c r="F355" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G355" s="30"/>
       <c r="H355" s="30"/>
@@ -7790,7 +7830,7 @@
       <c r="D356" s="25"/>
       <c r="E356" s="29"/>
       <c r="F356" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G356" s="30"/>
       <c r="H356" s="30"/>
@@ -7804,7 +7844,7 @@
       <c r="D357" s="25"/>
       <c r="E357" s="29"/>
       <c r="F357" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G357" s="30"/>
       <c r="H357" s="30"/>
@@ -7818,7 +7858,7 @@
       <c r="D358" s="25"/>
       <c r="E358" s="29"/>
       <c r="F358" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G358" s="30"/>
       <c r="H358" s="30"/>
@@ -7832,7 +7872,7 @@
       <c r="D359" s="25"/>
       <c r="E359" s="29"/>
       <c r="F359" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G359" s="30"/>
       <c r="H359" s="30"/>
@@ -7846,7 +7886,7 @@
       <c r="D360" s="25"/>
       <c r="E360" s="29"/>
       <c r="F360" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G360" s="30"/>
       <c r="H360" s="30"/>
@@ -7860,7 +7900,7 @@
       <c r="D361" s="25"/>
       <c r="E361" s="29"/>
       <c r="F361" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G361" s="30"/>
       <c r="H361" s="30"/>
@@ -7874,7 +7914,7 @@
       <c r="D362" s="25"/>
       <c r="E362" s="29"/>
       <c r="F362" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G362" s="30"/>
       <c r="H362" s="30"/>
@@ -7888,7 +7928,7 @@
       <c r="D363" s="25"/>
       <c r="E363" s="29"/>
       <c r="F363" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G363" s="30"/>
       <c r="H363" s="30"/>
@@ -7902,7 +7942,7 @@
       <c r="D364" s="25"/>
       <c r="E364" s="29"/>
       <c r="F364" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G364" s="30"/>
       <c r="H364" s="30"/>
@@ -7916,7 +7956,7 @@
       <c r="D365" s="25"/>
       <c r="E365" s="29"/>
       <c r="F365" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G365" s="30"/>
       <c r="H365" s="30"/>
@@ -7930,7 +7970,7 @@
       <c r="D366" s="25"/>
       <c r="E366" s="29"/>
       <c r="F366" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G366" s="30"/>
       <c r="H366" s="30"/>
@@ -7944,7 +7984,7 @@
       <c r="D367" s="25"/>
       <c r="E367" s="29"/>
       <c r="F367" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G367" s="30"/>
       <c r="H367" s="30"/>
@@ -7958,7 +7998,7 @@
       <c r="D368" s="25"/>
       <c r="E368" s="29"/>
       <c r="F368" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G368" s="30"/>
       <c r="H368" s="30"/>
@@ -7972,7 +8012,7 @@
       <c r="D369" s="25"/>
       <c r="E369" s="29"/>
       <c r="F369" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G369" s="30"/>
       <c r="H369" s="30"/>
@@ -7986,7 +8026,7 @@
       <c r="D370" s="25"/>
       <c r="E370" s="29"/>
       <c r="F370" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G370" s="30"/>
       <c r="H370" s="30"/>
@@ -8000,7 +8040,7 @@
       <c r="D371" s="25"/>
       <c r="E371" s="29"/>
       <c r="F371" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G371" s="30"/>
       <c r="H371" s="30"/>
@@ -8014,7 +8054,7 @@
       <c r="D372" s="25"/>
       <c r="E372" s="29"/>
       <c r="F372" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G372" s="30"/>
       <c r="H372" s="30"/>
@@ -8028,7 +8068,7 @@
       <c r="D373" s="25"/>
       <c r="E373" s="29"/>
       <c r="F373" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G373" s="30"/>
       <c r="H373" s="30"/>
@@ -8042,7 +8082,7 @@
       <c r="D374" s="25"/>
       <c r="E374" s="29"/>
       <c r="F374" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G374" s="30"/>
       <c r="H374" s="30"/>
@@ -8056,7 +8096,7 @@
       <c r="D375" s="25"/>
       <c r="E375" s="29"/>
       <c r="F375" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G375" s="30"/>
       <c r="H375" s="30"/>
@@ -8070,7 +8110,7 @@
       <c r="D376" s="25"/>
       <c r="E376" s="29"/>
       <c r="F376" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G376" s="30"/>
       <c r="H376" s="30"/>
@@ -8084,7 +8124,7 @@
       <c r="D377" s="25"/>
       <c r="E377" s="29"/>
       <c r="F377" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G377" s="30"/>
       <c r="H377" s="30"/>
@@ -8098,7 +8138,7 @@
       <c r="D378" s="25"/>
       <c r="E378" s="29"/>
       <c r="F378" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G378" s="30"/>
       <c r="H378" s="30"/>
@@ -8112,7 +8152,7 @@
       <c r="D379" s="25"/>
       <c r="E379" s="29"/>
       <c r="F379" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G379" s="30"/>
       <c r="H379" s="30"/>
@@ -8126,7 +8166,7 @@
       <c r="D380" s="25"/>
       <c r="E380" s="29"/>
       <c r="F380" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G380" s="30"/>
       <c r="H380" s="30"/>
@@ -8140,7 +8180,7 @@
       <c r="D381" s="25"/>
       <c r="E381" s="29"/>
       <c r="F381" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G381" s="30"/>
       <c r="H381" s="30"/>
@@ -8154,7 +8194,7 @@
       <c r="D382" s="25"/>
       <c r="E382" s="29"/>
       <c r="F382" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G382" s="30"/>
       <c r="H382" s="30"/>
@@ -8168,7 +8208,7 @@
       <c r="D383" s="25"/>
       <c r="E383" s="29"/>
       <c r="F383" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G383" s="30"/>
       <c r="H383" s="30"/>
@@ -8182,7 +8222,7 @@
       <c r="D384" s="25"/>
       <c r="E384" s="29"/>
       <c r="F384" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G384" s="30"/>
       <c r="H384" s="30"/>
@@ -8196,7 +8236,7 @@
       <c r="D385" s="25"/>
       <c r="E385" s="29"/>
       <c r="F385" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G385" s="30"/>
       <c r="H385" s="30"/>
@@ -8210,7 +8250,7 @@
       <c r="D386" s="25"/>
       <c r="E386" s="29"/>
       <c r="F386" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G386" s="30"/>
       <c r="H386" s="30"/>
@@ -8224,7 +8264,7 @@
       <c r="D387" s="25"/>
       <c r="E387" s="29"/>
       <c r="F387" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G387" s="30"/>
       <c r="H387" s="30"/>
@@ -8238,7 +8278,7 @@
       <c r="D388" s="25"/>
       <c r="E388" s="29"/>
       <c r="F388" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G388" s="30"/>
       <c r="H388" s="30"/>
@@ -8252,7 +8292,7 @@
       <c r="D389" s="25"/>
       <c r="E389" s="29"/>
       <c r="F389" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G389" s="30"/>
       <c r="H389" s="30"/>
@@ -8266,7 +8306,7 @@
       <c r="D390" s="25"/>
       <c r="E390" s="29"/>
       <c r="F390" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G390" s="30"/>
       <c r="H390" s="30"/>
@@ -8280,7 +8320,7 @@
       <c r="D391" s="25"/>
       <c r="E391" s="29"/>
       <c r="F391" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G391" s="30"/>
       <c r="H391" s="30"/>
@@ -8294,7 +8334,7 @@
       <c r="D392" s="25"/>
       <c r="E392" s="29"/>
       <c r="F392" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G392" s="30"/>
       <c r="H392" s="30"/>
@@ -8308,7 +8348,7 @@
       <c r="D393" s="25"/>
       <c r="E393" s="29"/>
       <c r="F393" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G393" s="30"/>
       <c r="H393" s="30"/>
@@ -8322,7 +8362,7 @@
       <c r="D394" s="25"/>
       <c r="E394" s="29"/>
       <c r="F394" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G394" s="30"/>
       <c r="H394" s="30"/>
@@ -8336,7 +8376,7 @@
       <c r="D395" s="25"/>
       <c r="E395" s="29"/>
       <c r="F395" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G395" s="30"/>
       <c r="H395" s="30"/>
@@ -8350,7 +8390,7 @@
       <c r="D396" s="25"/>
       <c r="E396" s="29"/>
       <c r="F396" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G396" s="30"/>
       <c r="H396" s="30"/>
@@ -8364,7 +8404,7 @@
       <c r="D397" s="25"/>
       <c r="E397" s="29"/>
       <c r="F397" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G397" s="30"/>
       <c r="H397" s="30"/>
@@ -8378,7 +8418,7 @@
       <c r="D398" s="25"/>
       <c r="E398" s="29"/>
       <c r="F398" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G398" s="30"/>
       <c r="H398" s="30"/>
@@ -8392,7 +8432,7 @@
       <c r="D399" s="25"/>
       <c r="E399" s="29"/>
       <c r="F399" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G399" s="30"/>
       <c r="H399" s="30"/>
@@ -8406,7 +8446,7 @@
       <c r="D400" s="25"/>
       <c r="E400" s="29"/>
       <c r="F400" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G400" s="30"/>
       <c r="H400" s="30"/>
@@ -8420,7 +8460,7 @@
       <c r="D401" s="25"/>
       <c r="E401" s="29"/>
       <c r="F401" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G401" s="30"/>
       <c r="H401" s="30"/>
@@ -8434,7 +8474,7 @@
       <c r="D402" s="25"/>
       <c r="E402" s="29"/>
       <c r="F402" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G402" s="30"/>
       <c r="H402" s="30"/>
@@ -8448,7 +8488,7 @@
       <c r="D403" s="25"/>
       <c r="E403" s="29"/>
       <c r="F403" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G403" s="30"/>
       <c r="H403" s="30"/>
@@ -8462,7 +8502,7 @@
       <c r="D404" s="25"/>
       <c r="E404" s="29"/>
       <c r="F404" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G404" s="30"/>
       <c r="H404" s="30"/>
@@ -8476,7 +8516,7 @@
       <c r="D405" s="25"/>
       <c r="E405" s="29"/>
       <c r="F405" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G405" s="30"/>
       <c r="H405" s="30"/>
@@ -8490,7 +8530,7 @@
       <c r="D406" s="25"/>
       <c r="E406" s="29"/>
       <c r="F406" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G406" s="30"/>
       <c r="H406" s="30"/>
@@ -8504,7 +8544,7 @@
       <c r="D407" s="25"/>
       <c r="E407" s="29"/>
       <c r="F407" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G407" s="30"/>
       <c r="H407" s="30"/>
@@ -8518,7 +8558,7 @@
       <c r="D408" s="25"/>
       <c r="E408" s="29"/>
       <c r="F408" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G408" s="30"/>
       <c r="H408" s="30"/>
@@ -8532,7 +8572,7 @@
       <c r="D409" s="25"/>
       <c r="E409" s="29"/>
       <c r="F409" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G409" s="30"/>
       <c r="H409" s="30"/>
@@ -8546,7 +8586,7 @@
       <c r="D410" s="25"/>
       <c r="E410" s="29"/>
       <c r="F410" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G410" s="30"/>
       <c r="H410" s="30"/>
@@ -8560,7 +8600,7 @@
       <c r="D411" s="25"/>
       <c r="E411" s="29"/>
       <c r="F411" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G411" s="30"/>
       <c r="H411" s="30"/>
@@ -8574,7 +8614,7 @@
       <c r="D412" s="25"/>
       <c r="E412" s="29"/>
       <c r="F412" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G412" s="30"/>
       <c r="H412" s="30"/>
@@ -8588,7 +8628,7 @@
       <c r="D413" s="25"/>
       <c r="E413" s="29"/>
       <c r="F413" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G413" s="30"/>
       <c r="H413" s="30"/>
@@ -8602,7 +8642,7 @@
       <c r="D414" s="25"/>
       <c r="E414" s="29"/>
       <c r="F414" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G414" s="30"/>
       <c r="H414" s="30"/>
@@ -8616,7 +8656,7 @@
       <c r="D415" s="25"/>
       <c r="E415" s="29"/>
       <c r="F415" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G415" s="30"/>
       <c r="H415" s="30"/>
@@ -8630,7 +8670,7 @@
       <c r="D416" s="25"/>
       <c r="E416" s="29"/>
       <c r="F416" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G416" s="30"/>
       <c r="H416" s="30"/>
@@ -8644,7 +8684,7 @@
       <c r="D417" s="25"/>
       <c r="E417" s="29"/>
       <c r="F417" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G417" s="30"/>
       <c r="H417" s="30"/>
@@ -8658,7 +8698,7 @@
       <c r="D418" s="25"/>
       <c r="E418" s="29"/>
       <c r="F418" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G418" s="30"/>
       <c r="H418" s="30"/>
@@ -8672,7 +8712,7 @@
       <c r="D419" s="25"/>
       <c r="E419" s="29"/>
       <c r="F419" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G419" s="30"/>
       <c r="H419" s="30"/>
@@ -8686,7 +8726,7 @@
       <c r="D420" s="25"/>
       <c r="E420" s="29"/>
       <c r="F420" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G420" s="30"/>
       <c r="H420" s="30"/>
@@ -8700,7 +8740,7 @@
       <c r="D421" s="25"/>
       <c r="E421" s="29"/>
       <c r="F421" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G421" s="30"/>
       <c r="H421" s="30"/>
@@ -8714,7 +8754,7 @@
       <c r="D422" s="25"/>
       <c r="E422" s="29"/>
       <c r="F422" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G422" s="30"/>
       <c r="H422" s="30"/>
@@ -8728,7 +8768,7 @@
       <c r="D423" s="25"/>
       <c r="E423" s="29"/>
       <c r="F423" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G423" s="30"/>
       <c r="H423" s="30"/>
@@ -8742,7 +8782,7 @@
       <c r="D424" s="25"/>
       <c r="E424" s="29"/>
       <c r="F424" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G424" s="30"/>
       <c r="H424" s="30"/>
@@ -8756,7 +8796,7 @@
       <c r="D425" s="25"/>
       <c r="E425" s="29"/>
       <c r="F425" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G425" s="30"/>
       <c r="H425" s="30"/>
@@ -8770,7 +8810,7 @@
       <c r="D426" s="25"/>
       <c r="E426" s="29"/>
       <c r="F426" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G426" s="30"/>
       <c r="H426" s="30"/>
@@ -8784,7 +8824,7 @@
       <c r="D427" s="25"/>
       <c r="E427" s="29"/>
       <c r="F427" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G427" s="30"/>
       <c r="H427" s="30"/>
@@ -8798,7 +8838,7 @@
       <c r="D428" s="25"/>
       <c r="E428" s="29"/>
       <c r="F428" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G428" s="30"/>
       <c r="H428" s="30"/>
@@ -8812,7 +8852,7 @@
       <c r="D429" s="25"/>
       <c r="E429" s="29"/>
       <c r="F429" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G429" s="30"/>
       <c r="H429" s="30"/>
@@ -8826,7 +8866,7 @@
       <c r="D430" s="25"/>
       <c r="E430" s="29"/>
       <c r="F430" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G430" s="30"/>
       <c r="H430" s="30"/>
@@ -8840,7 +8880,7 @@
       <c r="D431" s="25"/>
       <c r="E431" s="29"/>
       <c r="F431" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G431" s="30"/>
       <c r="H431" s="30"/>
@@ -8854,7 +8894,7 @@
       <c r="D432" s="25"/>
       <c r="E432" s="29"/>
       <c r="F432" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G432" s="30"/>
       <c r="H432" s="30"/>
@@ -8868,7 +8908,7 @@
       <c r="D433" s="25"/>
       <c r="E433" s="29"/>
       <c r="F433" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G433" s="30"/>
       <c r="H433" s="30"/>
@@ -8882,7 +8922,7 @@
       <c r="D434" s="25"/>
       <c r="E434" s="29"/>
       <c r="F434" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G434" s="30"/>
       <c r="H434" s="30"/>
@@ -8896,7 +8936,7 @@
       <c r="D435" s="25"/>
       <c r="E435" s="29"/>
       <c r="F435" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G435" s="30"/>
       <c r="H435" s="30"/>
@@ -8910,7 +8950,7 @@
       <c r="D436" s="25"/>
       <c r="E436" s="29"/>
       <c r="F436" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G436" s="30"/>
       <c r="H436" s="30"/>
@@ -8924,7 +8964,7 @@
       <c r="D437" s="25"/>
       <c r="E437" s="29"/>
       <c r="F437" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G437" s="30"/>
       <c r="H437" s="30"/>
@@ -8938,7 +8978,7 @@
       <c r="D438" s="25"/>
       <c r="E438" s="29"/>
       <c r="F438" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G438" s="30"/>
       <c r="H438" s="30"/>
@@ -8952,7 +8992,7 @@
       <c r="D439" s="25"/>
       <c r="E439" s="29"/>
       <c r="F439" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G439" s="30"/>
       <c r="H439" s="30"/>
@@ -8966,7 +9006,7 @@
       <c r="D440" s="25"/>
       <c r="E440" s="29"/>
       <c r="F440" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G440" s="30"/>
       <c r="H440" s="30"/>
@@ -8980,7 +9020,7 @@
       <c r="D441" s="25"/>
       <c r="E441" s="29"/>
       <c r="F441" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G441" s="30"/>
       <c r="H441" s="30"/>
@@ -8994,7 +9034,7 @@
       <c r="D442" s="25"/>
       <c r="E442" s="29"/>
       <c r="F442" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G442" s="30"/>
       <c r="H442" s="30"/>
@@ -9008,7 +9048,7 @@
       <c r="D443" s="25"/>
       <c r="E443" s="29"/>
       <c r="F443" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G443" s="30"/>
       <c r="H443" s="30"/>
@@ -9022,7 +9062,7 @@
       <c r="D444" s="25"/>
       <c r="E444" s="29"/>
       <c r="F444" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G444" s="30"/>
       <c r="H444" s="30"/>
@@ -9036,7 +9076,7 @@
       <c r="D445" s="25"/>
       <c r="E445" s="29"/>
       <c r="F445" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G445" s="30"/>
       <c r="H445" s="30"/>
@@ -9050,7 +9090,7 @@
       <c r="D446" s="25"/>
       <c r="E446" s="29"/>
       <c r="F446" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G446" s="30"/>
       <c r="H446" s="30"/>
@@ -9064,7 +9104,7 @@
       <c r="D447" s="25"/>
       <c r="E447" s="29"/>
       <c r="F447" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G447" s="30"/>
       <c r="H447" s="30"/>
@@ -9078,7 +9118,7 @@
       <c r="D448" s="25"/>
       <c r="E448" s="29"/>
       <c r="F448" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G448" s="30"/>
       <c r="H448" s="30"/>
@@ -9092,7 +9132,7 @@
       <c r="D449" s="25"/>
       <c r="E449" s="29"/>
       <c r="F449" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G449" s="30"/>
       <c r="H449" s="30"/>
@@ -9106,7 +9146,7 @@
       <c r="D450" s="25"/>
       <c r="E450" s="29"/>
       <c r="F450" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G450" s="30"/>
       <c r="H450" s="30"/>
@@ -9120,7 +9160,7 @@
       <c r="D451" s="25"/>
       <c r="E451" s="29"/>
       <c r="F451" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G451" s="30"/>
       <c r="H451" s="30"/>
@@ -9134,7 +9174,7 @@
       <c r="D452" s="25"/>
       <c r="E452" s="29"/>
       <c r="F452" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G452" s="30"/>
       <c r="H452" s="30"/>
@@ -9148,7 +9188,7 @@
       <c r="D453" s="25"/>
       <c r="E453" s="29"/>
       <c r="F453" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G453" s="30"/>
       <c r="H453" s="30"/>
@@ -9162,7 +9202,7 @@
       <c r="D454" s="25"/>
       <c r="E454" s="29"/>
       <c r="F454" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G454" s="30"/>
       <c r="H454" s="30"/>
@@ -9176,7 +9216,7 @@
       <c r="D455" s="25"/>
       <c r="E455" s="29"/>
       <c r="F455" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G455" s="30"/>
       <c r="H455" s="30"/>
@@ -9190,7 +9230,7 @@
       <c r="D456" s="25"/>
       <c r="E456" s="29"/>
       <c r="F456" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G456" s="30"/>
       <c r="H456" s="30"/>
@@ -9204,7 +9244,7 @@
       <c r="D457" s="25"/>
       <c r="E457" s="29"/>
       <c r="F457" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G457" s="30"/>
       <c r="H457" s="30"/>
@@ -9218,7 +9258,7 @@
       <c r="D458" s="25"/>
       <c r="E458" s="29"/>
       <c r="F458" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G458" s="30"/>
       <c r="H458" s="30"/>
@@ -9232,7 +9272,7 @@
       <c r="D459" s="25"/>
       <c r="E459" s="29"/>
       <c r="F459" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G459" s="30"/>
       <c r="H459" s="30"/>
@@ -9246,7 +9286,7 @@
       <c r="D460" s="25"/>
       <c r="E460" s="29"/>
       <c r="F460" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G460" s="30"/>
       <c r="H460" s="30"/>
@@ -9260,7 +9300,7 @@
       <c r="D461" s="25"/>
       <c r="E461" s="29"/>
       <c r="F461" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G461" s="30"/>
       <c r="H461" s="30"/>
@@ -9274,7 +9314,7 @@
       <c r="D462" s="25"/>
       <c r="E462" s="29"/>
       <c r="F462" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G462" s="30"/>
       <c r="H462" s="30"/>
@@ -9288,7 +9328,7 @@
       <c r="D463" s="25"/>
       <c r="E463" s="29"/>
       <c r="F463" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G463" s="30"/>
       <c r="H463" s="30"/>
@@ -9302,7 +9342,7 @@
       <c r="D464" s="25"/>
       <c r="E464" s="29"/>
       <c r="F464" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G464" s="30"/>
       <c r="H464" s="30"/>
@@ -9316,7 +9356,7 @@
       <c r="D465" s="25"/>
       <c r="E465" s="29"/>
       <c r="F465" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G465" s="30"/>
       <c r="H465" s="30"/>
@@ -9330,7 +9370,7 @@
       <c r="D466" s="25"/>
       <c r="E466" s="29"/>
       <c r="F466" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G466" s="30"/>
       <c r="H466" s="30"/>
@@ -9344,7 +9384,7 @@
       <c r="D467" s="25"/>
       <c r="E467" s="29"/>
       <c r="F467" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G467" s="30"/>
       <c r="H467" s="30"/>
@@ -9358,7 +9398,7 @@
       <c r="D468" s="25"/>
       <c r="E468" s="29"/>
       <c r="F468" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G468" s="30"/>
       <c r="H468" s="30"/>
@@ -9372,7 +9412,7 @@
       <c r="D469" s="25"/>
       <c r="E469" s="29"/>
       <c r="F469" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G469" s="30"/>
       <c r="H469" s="30"/>
@@ -9386,7 +9426,7 @@
       <c r="D470" s="25"/>
       <c r="E470" s="29"/>
       <c r="F470" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G470" s="30"/>
       <c r="H470" s="30"/>
@@ -9400,7 +9440,7 @@
       <c r="D471" s="25"/>
       <c r="E471" s="29"/>
       <c r="F471" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G471" s="30"/>
       <c r="H471" s="30"/>
@@ -9414,7 +9454,7 @@
       <c r="D472" s="25"/>
       <c r="E472" s="29"/>
       <c r="F472" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G472" s="30"/>
       <c r="H472" s="30"/>
@@ -9428,7 +9468,7 @@
       <c r="D473" s="25"/>
       <c r="E473" s="29"/>
       <c r="F473" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G473" s="30"/>
       <c r="H473" s="30"/>
@@ -9442,7 +9482,7 @@
       <c r="D474" s="25"/>
       <c r="E474" s="29"/>
       <c r="F474" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G474" s="30"/>
       <c r="H474" s="30"/>
@@ -9456,7 +9496,7 @@
       <c r="D475" s="25"/>
       <c r="E475" s="29"/>
       <c r="F475" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G475" s="30"/>
       <c r="H475" s="30"/>
@@ -9470,7 +9510,7 @@
       <c r="D476" s="25"/>
       <c r="E476" s="29"/>
       <c r="F476" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G476" s="30"/>
       <c r="H476" s="30"/>
@@ -9484,7 +9524,7 @@
       <c r="D477" s="25"/>
       <c r="E477" s="29"/>
       <c r="F477" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G477" s="30"/>
       <c r="H477" s="30"/>
@@ -9498,7 +9538,7 @@
       <c r="D478" s="25"/>
       <c r="E478" s="29"/>
       <c r="F478" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G478" s="30"/>
       <c r="H478" s="30"/>
@@ -9512,7 +9552,7 @@
       <c r="D479" s="25"/>
       <c r="E479" s="29"/>
       <c r="F479" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G479" s="30"/>
       <c r="H479" s="30"/>
@@ -9526,7 +9566,7 @@
       <c r="D480" s="25"/>
       <c r="E480" s="29"/>
       <c r="F480" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G480" s="30"/>
       <c r="H480" s="30"/>
@@ -9540,7 +9580,7 @@
       <c r="D481" s="25"/>
       <c r="E481" s="29"/>
       <c r="F481" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G481" s="30"/>
       <c r="H481" s="30"/>
@@ -9554,7 +9594,7 @@
       <c r="D482" s="25"/>
       <c r="E482" s="29"/>
       <c r="F482" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G482" s="30"/>
       <c r="H482" s="30"/>
@@ -9568,7 +9608,7 @@
       <c r="D483" s="25"/>
       <c r="E483" s="29"/>
       <c r="F483" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G483" s="30"/>
       <c r="H483" s="30"/>
@@ -9582,7 +9622,7 @@
       <c r="D484" s="25"/>
       <c r="E484" s="29"/>
       <c r="F484" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G484" s="30"/>
       <c r="H484" s="30"/>
@@ -9596,7 +9636,7 @@
       <c r="D485" s="25"/>
       <c r="E485" s="29"/>
       <c r="F485" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G485" s="30"/>
       <c r="H485" s="30"/>
@@ -9610,7 +9650,7 @@
       <c r="D486" s="25"/>
       <c r="E486" s="29"/>
       <c r="F486" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G486" s="30"/>
       <c r="H486" s="30"/>
@@ -9624,7 +9664,7 @@
       <c r="D487" s="25"/>
       <c r="E487" s="29"/>
       <c r="F487" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G487" s="30"/>
       <c r="H487" s="30"/>
@@ -9638,7 +9678,7 @@
       <c r="D488" s="25"/>
       <c r="E488" s="29"/>
       <c r="F488" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G488" s="30"/>
       <c r="H488" s="30"/>
@@ -9652,7 +9692,7 @@
       <c r="D489" s="25"/>
       <c r="E489" s="29"/>
       <c r="F489" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G489" s="30"/>
       <c r="H489" s="30"/>
@@ -9666,7 +9706,7 @@
       <c r="D490" s="25"/>
       <c r="E490" s="29"/>
       <c r="F490" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G490" s="30"/>
       <c r="H490" s="30"/>
@@ -9680,7 +9720,7 @@
       <c r="D491" s="25"/>
       <c r="E491" s="29"/>
       <c r="F491" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G491" s="30"/>
       <c r="H491" s="30"/>
@@ -9694,7 +9734,7 @@
       <c r="D492" s="25"/>
       <c r="E492" s="29"/>
       <c r="F492" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G492" s="30"/>
       <c r="H492" s="30"/>
@@ -9708,7 +9748,7 @@
       <c r="D493" s="25"/>
       <c r="E493" s="29"/>
       <c r="F493" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G493" s="30"/>
       <c r="H493" s="30"/>
@@ -9722,7 +9762,7 @@
       <c r="D494" s="25"/>
       <c r="E494" s="29"/>
       <c r="F494" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G494" s="30"/>
       <c r="H494" s="30"/>
@@ -9736,7 +9776,7 @@
       <c r="D495" s="25"/>
       <c r="E495" s="29"/>
       <c r="F495" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G495" s="30"/>
       <c r="H495" s="30"/>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="118">
   <si>
     <t>Etapa</t>
   </si>
@@ -166,7 +166,7 @@
     <t>Matriz FODA</t>
   </si>
   <si>
-    <t>Supervision</t>
+    <t>Plan de Riesgos</t>
   </si>
   <si>
     <t>Plan de Riesgos y Contingencias</t>
@@ -176,6 +176,9 @@
   </si>
   <si>
     <t>Ignacio</t>
+  </si>
+  <si>
+    <t>Supervision</t>
   </si>
   <si>
     <t>Modificacion Plan Riesgos y Contingencias</t>
@@ -909,7 +912,7 @@
       </c>
       <c r="C2" s="6" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-09-20 23:03</v>
+        <v>Plan de Proyecto: 2026-09-20 23:24</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>14</v>
@@ -1994,8 +1997,8 @@
       <c r="L26" s="9"/>
     </row>
     <row r="27" ht="37.5" customHeight="1">
-      <c r="A27" s="10" t="s">
-        <v>12</v>
+      <c r="A27" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>51</v>
@@ -2047,14 +2050,14 @@
       <c r="AE27" s="16"/>
     </row>
     <row r="28" ht="37.5" customHeight="1">
-      <c r="A28" s="10" t="s">
-        <v>12</v>
+      <c r="A28" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>14</v>
@@ -2086,7 +2089,7 @@
         <v>26</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>14</v>
@@ -2139,7 +2142,7 @@
         <v>26</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>14</v>
@@ -2170,10 +2173,10 @@
         <v>25</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>14</v>
@@ -2197,7 +2200,7 @@
         <v>20.0</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L31" s="15"/>
       <c r="M31" s="16"/>
@@ -2225,10 +2228,10 @@
         <v>25</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>14</v>
@@ -2252,7 +2255,7 @@
         <v>20.0</v>
       </c>
       <c r="K32" s="19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L32" s="9"/>
     </row>
@@ -2261,10 +2264,10 @@
         <v>25</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>14</v>
@@ -2286,7 +2289,7 @@
       </c>
       <c r="J33" s="15"/>
       <c r="K33" s="15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L33" s="15"/>
       <c r="M33" s="16"/>
@@ -2314,10 +2317,10 @@
         <v>25</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>14</v>
@@ -2337,7 +2340,7 @@
       <c r="I34" s="8"/>
       <c r="J34" s="17"/>
       <c r="K34" s="20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L34" s="9"/>
     </row>
@@ -2346,10 +2349,10 @@
         <v>25</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>14</v>
@@ -2378,16 +2381,16 @@
         <v>25</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>16</v>
@@ -2410,16 +2413,16 @@
         <v>25</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F37" s="13" t="s">
         <v>54</v>
@@ -2459,13 +2462,13 @@
         <v>25</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E38" s="7"/>
       <c r="F38" s="7" t="s">
@@ -2487,13 +2490,13 @@
         <v>25</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E39" s="13"/>
       <c r="F39" s="13" t="s">
@@ -2534,13 +2537,13 @@
         <v>25</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E40" s="7"/>
       <c r="F40" s="7" t="s">
@@ -2562,16 +2565,16 @@
         <v>25</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F41" s="13" t="s">
         <v>16</v>
@@ -2611,16 +2614,16 @@
         <v>25</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>16</v>
@@ -2646,7 +2649,7 @@
         <v>20</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D43" s="13" t="s">
         <v>14</v>
@@ -2697,13 +2700,13 @@
         <v>20</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D44" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F44" s="13" t="s">
         <v>16</v>
@@ -2745,16 +2748,16 @@
         <v>25</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D45" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F45" s="13" t="s">
         <v>32</v>
@@ -2796,13 +2799,13 @@
         <v>25</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E46" s="13"/>
       <c r="F46" s="13" t="s">
@@ -2841,16 +2844,16 @@
     <row r="47" ht="29.25" customHeight="1">
       <c r="A47" s="22"/>
       <c r="B47" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D47" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F47" s="13" t="s">
         <v>32</v>
@@ -2888,16 +2891,16 @@
     <row r="48" ht="29.25" customHeight="1">
       <c r="A48" s="22"/>
       <c r="B48" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F48" s="13" t="s">
         <v>16</v>
@@ -2937,16 +2940,16 @@
         <v>25</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F49" s="13" t="s">
         <v>54</v>
@@ -2986,13 +2989,13 @@
         <v>25</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C50" s="23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E50" s="7"/>
       <c r="F50" s="7" t="s">
@@ -3014,13 +3017,13 @@
         <v>25</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>37</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E51" s="13"/>
       <c r="F51" s="13" t="s">
@@ -3061,13 +3064,13 @@
         <v>25</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E52" s="7"/>
       <c r="F52" s="7" t="s">
@@ -3089,13 +3092,13 @@
         <v>25</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E53" s="13"/>
       <c r="F53" s="13" t="s">
@@ -3136,13 +3139,13 @@
         <v>25</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E54" s="13"/>
       <c r="F54" s="13" t="s">
@@ -3183,13 +3186,13 @@
         <v>25</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E55" s="13"/>
       <c r="F55" s="13" t="s">
@@ -3230,19 +3233,19 @@
         <v>25</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G56" s="14">
         <v>46290.0</v>
@@ -3279,16 +3282,16 @@
         <v>25</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F57" s="7" t="s">
         <v>32</v>
@@ -3309,13 +3312,13 @@
         <v>25</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E58" s="13"/>
       <c r="F58" s="13" t="s">
@@ -3356,16 +3359,16 @@
         <v>25</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F59" s="7" t="s">
         <v>16</v>
@@ -3386,13 +3389,13 @@
         <v>25</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E60" s="13"/>
       <c r="F60" s="13" t="s">
@@ -3433,13 +3436,13 @@
         <v>25</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E61" s="13"/>
       <c r="F61" s="13"/>
@@ -3474,13 +3477,13 @@
         <v>25</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E62" s="13"/>
       <c r="F62" s="13"/>
@@ -3515,13 +3518,13 @@
         <v>25</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E63" s="13"/>
       <c r="F63" s="13"/>
@@ -3556,13 +3559,13 @@
         <v>25</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E64" s="13"/>
       <c r="F64" s="13"/>
@@ -3597,13 +3600,13 @@
         <v>25</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E65" s="13"/>
       <c r="F65" s="13"/>
@@ -3638,13 +3641,13 @@
         <v>25</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E66" s="13"/>
       <c r="F66" s="13"/>
@@ -3676,19 +3679,19 @@
     </row>
     <row r="67" ht="29.25" customHeight="1">
       <c r="A67" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F67" s="13" t="s">
         <v>32</v>
@@ -3702,7 +3705,7 @@
       <c r="I67" s="14"/>
       <c r="J67" s="15"/>
       <c r="K67" s="15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L67" s="15"/>
       <c r="M67" s="16"/>
@@ -3727,19 +3730,19 @@
     </row>
     <row r="68" ht="29.25" customHeight="1">
       <c r="A68" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F68" s="7" t="s">
         <v>16</v>
@@ -3753,22 +3756,22 @@
       <c r="I68" s="8"/>
       <c r="J68" s="9"/>
       <c r="K68" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L68" s="9"/>
     </row>
     <row r="69" ht="29.25" customHeight="1">
       <c r="A69" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E69" s="7"/>
       <c r="F69" s="7" t="s">
@@ -3787,22 +3790,22 @@
     </row>
     <row r="70" ht="29.25" customHeight="1">
       <c r="A70" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G70" s="14">
         <v>46286.0</v>
@@ -3836,20 +3839,20 @@
     </row>
     <row r="71" ht="29.25" customHeight="1">
       <c r="A71" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E71" s="7"/>
       <c r="F71" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G71" s="8">
         <v>46287.0</v>
@@ -3864,20 +3867,20 @@
     </row>
     <row r="72" ht="29.25" customHeight="1">
       <c r="A72" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E72" s="13"/>
       <c r="F72" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G72" s="14">
         <v>46287.0</v>
@@ -3911,20 +3914,20 @@
     </row>
     <row r="73" ht="29.25" customHeight="1">
       <c r="A73" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E73" s="7"/>
       <c r="F73" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G73" s="8">
         <v>46296.0</v>
@@ -3939,18 +3942,18 @@
     </row>
     <row r="74" ht="29.25" customHeight="1">
       <c r="A74" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D74" s="13"/>
       <c r="E74" s="13"/>
       <c r="F74" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G74" s="14">
         <v>46303.0</v>
@@ -3984,20 +3987,20 @@
     </row>
     <row r="75" ht="29.25" customHeight="1">
       <c r="A75" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E75" s="7"/>
       <c r="F75" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G75" s="8">
         <v>46305.0</v>
@@ -4017,7 +4020,7 @@
       <c r="D76" s="26"/>
       <c r="E76" s="21"/>
       <c r="F76" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G76" s="28"/>
       <c r="H76" s="28"/>
@@ -4033,7 +4036,7 @@
       <c r="D77" s="26"/>
       <c r="E77" s="21"/>
       <c r="F77" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G77" s="28"/>
       <c r="H77" s="28"/>
@@ -4049,7 +4052,7 @@
       <c r="D78" s="26"/>
       <c r="E78" s="21"/>
       <c r="F78" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G78" s="28"/>
       <c r="H78" s="28"/>
@@ -4065,7 +4068,7 @@
       <c r="D79" s="26"/>
       <c r="E79" s="21"/>
       <c r="F79" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G79" s="28"/>
       <c r="H79" s="28"/>
@@ -4081,7 +4084,7 @@
       <c r="D80" s="26"/>
       <c r="E80" s="21"/>
       <c r="F80" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G80" s="28"/>
       <c r="H80" s="28"/>
@@ -4097,7 +4100,7 @@
       <c r="D81" s="26"/>
       <c r="E81" s="30"/>
       <c r="F81" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G81" s="31"/>
       <c r="H81" s="31"/>
@@ -4111,7 +4114,7 @@
       <c r="D82" s="26"/>
       <c r="E82" s="30"/>
       <c r="F82" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G82" s="31"/>
       <c r="H82" s="31"/>
@@ -4125,7 +4128,7 @@
       <c r="D83" s="26"/>
       <c r="E83" s="30"/>
       <c r="F83" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G83" s="31"/>
       <c r="H83" s="31"/>
@@ -4139,7 +4142,7 @@
       <c r="D84" s="26"/>
       <c r="E84" s="30"/>
       <c r="F84" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G84" s="31"/>
       <c r="H84" s="31"/>
@@ -4153,7 +4156,7 @@
       <c r="D85" s="26"/>
       <c r="E85" s="30"/>
       <c r="F85" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G85" s="31"/>
       <c r="H85" s="31"/>
@@ -4167,7 +4170,7 @@
       <c r="D86" s="26"/>
       <c r="E86" s="30"/>
       <c r="F86" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G86" s="31"/>
       <c r="H86" s="31"/>
@@ -4181,7 +4184,7 @@
       <c r="D87" s="26"/>
       <c r="E87" s="30"/>
       <c r="F87" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G87" s="31"/>
       <c r="H87" s="31"/>
@@ -4195,7 +4198,7 @@
       <c r="D88" s="26"/>
       <c r="E88" s="30"/>
       <c r="F88" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G88" s="31"/>
       <c r="H88" s="31"/>
@@ -4209,7 +4212,7 @@
       <c r="D89" s="26"/>
       <c r="E89" s="30"/>
       <c r="F89" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G89" s="31"/>
       <c r="H89" s="31"/>
@@ -4223,7 +4226,7 @@
       <c r="D90" s="26"/>
       <c r="E90" s="30"/>
       <c r="F90" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G90" s="31"/>
       <c r="H90" s="31"/>
@@ -4237,7 +4240,7 @@
       <c r="D91" s="26"/>
       <c r="E91" s="30"/>
       <c r="F91" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G91" s="31"/>
       <c r="H91" s="31"/>
@@ -4251,7 +4254,7 @@
       <c r="D92" s="26"/>
       <c r="E92" s="30"/>
       <c r="F92" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G92" s="31"/>
       <c r="H92" s="31"/>
@@ -4265,7 +4268,7 @@
       <c r="D93" s="26"/>
       <c r="E93" s="30"/>
       <c r="F93" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G93" s="31"/>
       <c r="H93" s="31"/>
@@ -4279,7 +4282,7 @@
       <c r="D94" s="26"/>
       <c r="E94" s="30"/>
       <c r="F94" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G94" s="31"/>
       <c r="H94" s="31"/>
@@ -4293,7 +4296,7 @@
       <c r="D95" s="26"/>
       <c r="E95" s="30"/>
       <c r="F95" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G95" s="31"/>
       <c r="H95" s="31"/>
@@ -4307,7 +4310,7 @@
       <c r="D96" s="26"/>
       <c r="E96" s="30"/>
       <c r="F96" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G96" s="31"/>
       <c r="H96" s="31"/>
@@ -4321,7 +4324,7 @@
       <c r="D97" s="26"/>
       <c r="E97" s="30"/>
       <c r="F97" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G97" s="31"/>
       <c r="H97" s="31"/>
@@ -4335,7 +4338,7 @@
       <c r="D98" s="26"/>
       <c r="E98" s="30"/>
       <c r="F98" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G98" s="31"/>
       <c r="H98" s="31"/>
@@ -4349,7 +4352,7 @@
       <c r="D99" s="26"/>
       <c r="E99" s="30"/>
       <c r="F99" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G99" s="31"/>
       <c r="H99" s="31"/>
@@ -4363,7 +4366,7 @@
       <c r="D100" s="26"/>
       <c r="E100" s="30"/>
       <c r="F100" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G100" s="31"/>
       <c r="H100" s="31"/>
@@ -4377,7 +4380,7 @@
       <c r="D101" s="26"/>
       <c r="E101" s="30"/>
       <c r="F101" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G101" s="31"/>
       <c r="H101" s="31"/>
@@ -4391,7 +4394,7 @@
       <c r="D102" s="26"/>
       <c r="E102" s="30"/>
       <c r="F102" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G102" s="31"/>
       <c r="H102" s="31"/>
@@ -4405,7 +4408,7 @@
       <c r="D103" s="26"/>
       <c r="E103" s="30"/>
       <c r="F103" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G103" s="31"/>
       <c r="H103" s="31"/>
@@ -4419,7 +4422,7 @@
       <c r="D104" s="26"/>
       <c r="E104" s="30"/>
       <c r="F104" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G104" s="31"/>
       <c r="H104" s="31"/>
@@ -4433,7 +4436,7 @@
       <c r="D105" s="26"/>
       <c r="E105" s="30"/>
       <c r="F105" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G105" s="31"/>
       <c r="H105" s="31"/>
@@ -4447,7 +4450,7 @@
       <c r="D106" s="26"/>
       <c r="E106" s="30"/>
       <c r="F106" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G106" s="31"/>
       <c r="H106" s="31"/>
@@ -4461,7 +4464,7 @@
       <c r="D107" s="26"/>
       <c r="E107" s="30"/>
       <c r="F107" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G107" s="31"/>
       <c r="H107" s="31"/>
@@ -4475,7 +4478,7 @@
       <c r="D108" s="26"/>
       <c r="E108" s="30"/>
       <c r="F108" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G108" s="31"/>
       <c r="H108" s="31"/>
@@ -4489,7 +4492,7 @@
       <c r="D109" s="26"/>
       <c r="E109" s="30"/>
       <c r="F109" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G109" s="31"/>
       <c r="H109" s="31"/>
@@ -4503,7 +4506,7 @@
       <c r="D110" s="26"/>
       <c r="E110" s="30"/>
       <c r="F110" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G110" s="31"/>
       <c r="H110" s="31"/>
@@ -4517,7 +4520,7 @@
       <c r="D111" s="26"/>
       <c r="E111" s="30"/>
       <c r="F111" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G111" s="31"/>
       <c r="H111" s="31"/>
@@ -4531,7 +4534,7 @@
       <c r="D112" s="26"/>
       <c r="E112" s="30"/>
       <c r="F112" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G112" s="31"/>
       <c r="H112" s="31"/>
@@ -4545,7 +4548,7 @@
       <c r="D113" s="26"/>
       <c r="E113" s="30"/>
       <c r="F113" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G113" s="31"/>
       <c r="H113" s="31"/>
@@ -4559,7 +4562,7 @@
       <c r="D114" s="26"/>
       <c r="E114" s="30"/>
       <c r="F114" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G114" s="31"/>
       <c r="H114" s="31"/>
@@ -4573,7 +4576,7 @@
       <c r="D115" s="26"/>
       <c r="E115" s="30"/>
       <c r="F115" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G115" s="31"/>
       <c r="H115" s="31"/>
@@ -4587,7 +4590,7 @@
       <c r="D116" s="26"/>
       <c r="E116" s="30"/>
       <c r="F116" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G116" s="31"/>
       <c r="H116" s="31"/>
@@ -4601,7 +4604,7 @@
       <c r="D117" s="26"/>
       <c r="E117" s="30"/>
       <c r="F117" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G117" s="31"/>
       <c r="H117" s="31"/>
@@ -4615,7 +4618,7 @@
       <c r="D118" s="26"/>
       <c r="E118" s="30"/>
       <c r="F118" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G118" s="31"/>
       <c r="H118" s="31"/>
@@ -4629,7 +4632,7 @@
       <c r="D119" s="26"/>
       <c r="E119" s="30"/>
       <c r="F119" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G119" s="31"/>
       <c r="H119" s="31"/>
@@ -4643,7 +4646,7 @@
       <c r="D120" s="26"/>
       <c r="E120" s="30"/>
       <c r="F120" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G120" s="31"/>
       <c r="H120" s="31"/>
@@ -4657,7 +4660,7 @@
       <c r="D121" s="26"/>
       <c r="E121" s="30"/>
       <c r="F121" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G121" s="31"/>
       <c r="H121" s="31"/>
@@ -4671,7 +4674,7 @@
       <c r="D122" s="26"/>
       <c r="E122" s="30"/>
       <c r="F122" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G122" s="31"/>
       <c r="H122" s="31"/>
@@ -4685,7 +4688,7 @@
       <c r="D123" s="26"/>
       <c r="E123" s="30"/>
       <c r="F123" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G123" s="31"/>
       <c r="H123" s="31"/>
@@ -4699,7 +4702,7 @@
       <c r="D124" s="26"/>
       <c r="E124" s="30"/>
       <c r="F124" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G124" s="31"/>
       <c r="H124" s="31"/>
@@ -4713,7 +4716,7 @@
       <c r="D125" s="26"/>
       <c r="E125" s="30"/>
       <c r="F125" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G125" s="31"/>
       <c r="H125" s="31"/>
@@ -4727,7 +4730,7 @@
       <c r="D126" s="26"/>
       <c r="E126" s="30"/>
       <c r="F126" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G126" s="31"/>
       <c r="H126" s="31"/>
@@ -4741,7 +4744,7 @@
       <c r="D127" s="26"/>
       <c r="E127" s="30"/>
       <c r="F127" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G127" s="31"/>
       <c r="H127" s="31"/>
@@ -4755,7 +4758,7 @@
       <c r="D128" s="26"/>
       <c r="E128" s="30"/>
       <c r="F128" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G128" s="31"/>
       <c r="H128" s="31"/>
@@ -4769,7 +4772,7 @@
       <c r="D129" s="26"/>
       <c r="E129" s="30"/>
       <c r="F129" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G129" s="31"/>
       <c r="H129" s="31"/>
@@ -4783,7 +4786,7 @@
       <c r="D130" s="26"/>
       <c r="E130" s="30"/>
       <c r="F130" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G130" s="31"/>
       <c r="H130" s="31"/>
@@ -4797,7 +4800,7 @@
       <c r="D131" s="26"/>
       <c r="E131" s="30"/>
       <c r="F131" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G131" s="31"/>
       <c r="H131" s="31"/>
@@ -4811,7 +4814,7 @@
       <c r="D132" s="26"/>
       <c r="E132" s="30"/>
       <c r="F132" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G132" s="31"/>
       <c r="H132" s="31"/>
@@ -4825,7 +4828,7 @@
       <c r="D133" s="26"/>
       <c r="E133" s="30"/>
       <c r="F133" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G133" s="31"/>
       <c r="H133" s="31"/>
@@ -4839,7 +4842,7 @@
       <c r="D134" s="26"/>
       <c r="E134" s="30"/>
       <c r="F134" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G134" s="31"/>
       <c r="H134" s="31"/>
@@ -4853,7 +4856,7 @@
       <c r="D135" s="26"/>
       <c r="E135" s="30"/>
       <c r="F135" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G135" s="31"/>
       <c r="H135" s="31"/>
@@ -4867,7 +4870,7 @@
       <c r="D136" s="26"/>
       <c r="E136" s="30"/>
       <c r="F136" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G136" s="31"/>
       <c r="H136" s="31"/>
@@ -4881,7 +4884,7 @@
       <c r="D137" s="26"/>
       <c r="E137" s="30"/>
       <c r="F137" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G137" s="31"/>
       <c r="H137" s="31"/>
@@ -4895,7 +4898,7 @@
       <c r="D138" s="26"/>
       <c r="E138" s="30"/>
       <c r="F138" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G138" s="31"/>
       <c r="H138" s="31"/>
@@ -4909,7 +4912,7 @@
       <c r="D139" s="26"/>
       <c r="E139" s="30"/>
       <c r="F139" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G139" s="31"/>
       <c r="H139" s="31"/>
@@ -4923,7 +4926,7 @@
       <c r="D140" s="26"/>
       <c r="E140" s="30"/>
       <c r="F140" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G140" s="31"/>
       <c r="H140" s="31"/>
@@ -4937,7 +4940,7 @@
       <c r="D141" s="26"/>
       <c r="E141" s="30"/>
       <c r="F141" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G141" s="31"/>
       <c r="H141" s="31"/>
@@ -4951,7 +4954,7 @@
       <c r="D142" s="26"/>
       <c r="E142" s="30"/>
       <c r="F142" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G142" s="31"/>
       <c r="H142" s="31"/>
@@ -4965,7 +4968,7 @@
       <c r="D143" s="26"/>
       <c r="E143" s="30"/>
       <c r="F143" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G143" s="31"/>
       <c r="H143" s="31"/>
@@ -4979,7 +4982,7 @@
       <c r="D144" s="26"/>
       <c r="E144" s="30"/>
       <c r="F144" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G144" s="31"/>
       <c r="H144" s="31"/>
@@ -4993,7 +4996,7 @@
       <c r="D145" s="26"/>
       <c r="E145" s="30"/>
       <c r="F145" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G145" s="31"/>
       <c r="H145" s="31"/>
@@ -5007,7 +5010,7 @@
       <c r="D146" s="26"/>
       <c r="E146" s="30"/>
       <c r="F146" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G146" s="31"/>
       <c r="H146" s="31"/>
@@ -5021,7 +5024,7 @@
       <c r="D147" s="26"/>
       <c r="E147" s="30"/>
       <c r="F147" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G147" s="31"/>
       <c r="H147" s="31"/>
@@ -5035,7 +5038,7 @@
       <c r="D148" s="26"/>
       <c r="E148" s="30"/>
       <c r="F148" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G148" s="31"/>
       <c r="H148" s="31"/>
@@ -5049,7 +5052,7 @@
       <c r="D149" s="26"/>
       <c r="E149" s="30"/>
       <c r="F149" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G149" s="31"/>
       <c r="H149" s="31"/>
@@ -5063,7 +5066,7 @@
       <c r="D150" s="26"/>
       <c r="E150" s="30"/>
       <c r="F150" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G150" s="31"/>
       <c r="H150" s="31"/>
@@ -5077,7 +5080,7 @@
       <c r="D151" s="26"/>
       <c r="E151" s="30"/>
       <c r="F151" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G151" s="31"/>
       <c r="H151" s="31"/>
@@ -5091,7 +5094,7 @@
       <c r="D152" s="26"/>
       <c r="E152" s="30"/>
       <c r="F152" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G152" s="31"/>
       <c r="H152" s="31"/>
@@ -5105,7 +5108,7 @@
       <c r="D153" s="26"/>
       <c r="E153" s="30"/>
       <c r="F153" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G153" s="31"/>
       <c r="H153" s="31"/>
@@ -5119,7 +5122,7 @@
       <c r="D154" s="26"/>
       <c r="E154" s="30"/>
       <c r="F154" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G154" s="31"/>
       <c r="H154" s="31"/>
@@ -5133,7 +5136,7 @@
       <c r="D155" s="26"/>
       <c r="E155" s="30"/>
       <c r="F155" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G155" s="31"/>
       <c r="H155" s="31"/>
@@ -5147,7 +5150,7 @@
       <c r="D156" s="26"/>
       <c r="E156" s="30"/>
       <c r="F156" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G156" s="31"/>
       <c r="H156" s="31"/>
@@ -5161,7 +5164,7 @@
       <c r="D157" s="26"/>
       <c r="E157" s="30"/>
       <c r="F157" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G157" s="31"/>
       <c r="H157" s="31"/>
@@ -5175,7 +5178,7 @@
       <c r="D158" s="26"/>
       <c r="E158" s="30"/>
       <c r="F158" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G158" s="31"/>
       <c r="H158" s="31"/>
@@ -5189,7 +5192,7 @@
       <c r="D159" s="26"/>
       <c r="E159" s="30"/>
       <c r="F159" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G159" s="31"/>
       <c r="H159" s="31"/>
@@ -5203,7 +5206,7 @@
       <c r="D160" s="26"/>
       <c r="E160" s="30"/>
       <c r="F160" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G160" s="31"/>
       <c r="H160" s="31"/>
@@ -5217,7 +5220,7 @@
       <c r="D161" s="26"/>
       <c r="E161" s="30"/>
       <c r="F161" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G161" s="31"/>
       <c r="H161" s="31"/>
@@ -5231,7 +5234,7 @@
       <c r="D162" s="26"/>
       <c r="E162" s="30"/>
       <c r="F162" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G162" s="31"/>
       <c r="H162" s="31"/>
@@ -5245,7 +5248,7 @@
       <c r="D163" s="26"/>
       <c r="E163" s="30"/>
       <c r="F163" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G163" s="31"/>
       <c r="H163" s="31"/>
@@ -5259,7 +5262,7 @@
       <c r="D164" s="26"/>
       <c r="E164" s="30"/>
       <c r="F164" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G164" s="31"/>
       <c r="H164" s="31"/>
@@ -5273,7 +5276,7 @@
       <c r="D165" s="26"/>
       <c r="E165" s="30"/>
       <c r="F165" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G165" s="31"/>
       <c r="H165" s="31"/>
@@ -5287,7 +5290,7 @@
       <c r="D166" s="26"/>
       <c r="E166" s="30"/>
       <c r="F166" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G166" s="31"/>
       <c r="H166" s="31"/>
@@ -5301,7 +5304,7 @@
       <c r="D167" s="26"/>
       <c r="E167" s="30"/>
       <c r="F167" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G167" s="31"/>
       <c r="H167" s="31"/>
@@ -5315,7 +5318,7 @@
       <c r="D168" s="26"/>
       <c r="E168" s="30"/>
       <c r="F168" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G168" s="31"/>
       <c r="H168" s="31"/>
@@ -5329,7 +5332,7 @@
       <c r="D169" s="26"/>
       <c r="E169" s="30"/>
       <c r="F169" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G169" s="31"/>
       <c r="H169" s="31"/>
@@ -5343,7 +5346,7 @@
       <c r="D170" s="26"/>
       <c r="E170" s="30"/>
       <c r="F170" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G170" s="31"/>
       <c r="H170" s="31"/>
@@ -5357,7 +5360,7 @@
       <c r="D171" s="26"/>
       <c r="E171" s="30"/>
       <c r="F171" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G171" s="31"/>
       <c r="H171" s="31"/>
@@ -5371,7 +5374,7 @@
       <c r="D172" s="26"/>
       <c r="E172" s="30"/>
       <c r="F172" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G172" s="31"/>
       <c r="H172" s="31"/>
@@ -5385,7 +5388,7 @@
       <c r="D173" s="26"/>
       <c r="E173" s="30"/>
       <c r="F173" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G173" s="31"/>
       <c r="H173" s="31"/>
@@ -5399,7 +5402,7 @@
       <c r="D174" s="26"/>
       <c r="E174" s="30"/>
       <c r="F174" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G174" s="31"/>
       <c r="H174" s="31"/>
@@ -5413,7 +5416,7 @@
       <c r="D175" s="26"/>
       <c r="E175" s="30"/>
       <c r="F175" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G175" s="31"/>
       <c r="H175" s="31"/>
@@ -5427,7 +5430,7 @@
       <c r="D176" s="26"/>
       <c r="E176" s="30"/>
       <c r="F176" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G176" s="31"/>
       <c r="H176" s="31"/>
@@ -5441,7 +5444,7 @@
       <c r="D177" s="26"/>
       <c r="E177" s="30"/>
       <c r="F177" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G177" s="31"/>
       <c r="H177" s="31"/>
@@ -5455,7 +5458,7 @@
       <c r="D178" s="26"/>
       <c r="E178" s="30"/>
       <c r="F178" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G178" s="31"/>
       <c r="H178" s="31"/>
@@ -5469,7 +5472,7 @@
       <c r="D179" s="26"/>
       <c r="E179" s="30"/>
       <c r="F179" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G179" s="31"/>
       <c r="H179" s="31"/>
@@ -5483,7 +5486,7 @@
       <c r="D180" s="26"/>
       <c r="E180" s="30"/>
       <c r="F180" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G180" s="31"/>
       <c r="H180" s="31"/>
@@ -5497,7 +5500,7 @@
       <c r="D181" s="26"/>
       <c r="E181" s="30"/>
       <c r="F181" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G181" s="31"/>
       <c r="H181" s="31"/>
@@ -5511,7 +5514,7 @@
       <c r="D182" s="26"/>
       <c r="E182" s="30"/>
       <c r="F182" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G182" s="31"/>
       <c r="H182" s="31"/>
@@ -5525,7 +5528,7 @@
       <c r="D183" s="26"/>
       <c r="E183" s="30"/>
       <c r="F183" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G183" s="31"/>
       <c r="H183" s="31"/>
@@ -5539,7 +5542,7 @@
       <c r="D184" s="26"/>
       <c r="E184" s="30"/>
       <c r="F184" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G184" s="31"/>
       <c r="H184" s="31"/>
@@ -5553,7 +5556,7 @@
       <c r="D185" s="26"/>
       <c r="E185" s="30"/>
       <c r="F185" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G185" s="31"/>
       <c r="H185" s="31"/>
@@ -5567,7 +5570,7 @@
       <c r="D186" s="26"/>
       <c r="E186" s="30"/>
       <c r="F186" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G186" s="31"/>
       <c r="H186" s="31"/>
@@ -5581,7 +5584,7 @@
       <c r="D187" s="26"/>
       <c r="E187" s="30"/>
       <c r="F187" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G187" s="31"/>
       <c r="H187" s="31"/>
@@ -5595,7 +5598,7 @@
       <c r="D188" s="26"/>
       <c r="E188" s="30"/>
       <c r="F188" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G188" s="31"/>
       <c r="H188" s="31"/>
@@ -5609,7 +5612,7 @@
       <c r="D189" s="26"/>
       <c r="E189" s="30"/>
       <c r="F189" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G189" s="31"/>
       <c r="H189" s="31"/>
@@ -5623,7 +5626,7 @@
       <c r="D190" s="26"/>
       <c r="E190" s="30"/>
       <c r="F190" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G190" s="31"/>
       <c r="H190" s="31"/>
@@ -5637,7 +5640,7 @@
       <c r="D191" s="26"/>
       <c r="E191" s="30"/>
       <c r="F191" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G191" s="31"/>
       <c r="H191" s="31"/>
@@ -5651,7 +5654,7 @@
       <c r="D192" s="26"/>
       <c r="E192" s="30"/>
       <c r="F192" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G192" s="31"/>
       <c r="H192" s="31"/>
@@ -5665,7 +5668,7 @@
       <c r="D193" s="26"/>
       <c r="E193" s="30"/>
       <c r="F193" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G193" s="31"/>
       <c r="H193" s="31"/>
@@ -5679,7 +5682,7 @@
       <c r="D194" s="26"/>
       <c r="E194" s="30"/>
       <c r="F194" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G194" s="31"/>
       <c r="H194" s="31"/>
@@ -5693,7 +5696,7 @@
       <c r="D195" s="26"/>
       <c r="E195" s="30"/>
       <c r="F195" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G195" s="31"/>
       <c r="H195" s="31"/>
@@ -5707,7 +5710,7 @@
       <c r="D196" s="26"/>
       <c r="E196" s="30"/>
       <c r="F196" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G196" s="31"/>
       <c r="H196" s="31"/>
@@ -5721,7 +5724,7 @@
       <c r="D197" s="26"/>
       <c r="E197" s="30"/>
       <c r="F197" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G197" s="31"/>
       <c r="H197" s="31"/>
@@ -5735,7 +5738,7 @@
       <c r="D198" s="26"/>
       <c r="E198" s="30"/>
       <c r="F198" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G198" s="31"/>
       <c r="H198" s="31"/>
@@ -5749,7 +5752,7 @@
       <c r="D199" s="26"/>
       <c r="E199" s="30"/>
       <c r="F199" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G199" s="31"/>
       <c r="H199" s="31"/>
@@ -5763,7 +5766,7 @@
       <c r="D200" s="26"/>
       <c r="E200" s="30"/>
       <c r="F200" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G200" s="31"/>
       <c r="H200" s="31"/>
@@ -5777,7 +5780,7 @@
       <c r="D201" s="26"/>
       <c r="E201" s="30"/>
       <c r="F201" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G201" s="31"/>
       <c r="H201" s="31"/>
@@ -5791,7 +5794,7 @@
       <c r="D202" s="26"/>
       <c r="E202" s="30"/>
       <c r="F202" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G202" s="31"/>
       <c r="H202" s="31"/>
@@ -5805,7 +5808,7 @@
       <c r="D203" s="26"/>
       <c r="E203" s="30"/>
       <c r="F203" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G203" s="31"/>
       <c r="H203" s="31"/>
@@ -5819,7 +5822,7 @@
       <c r="D204" s="26"/>
       <c r="E204" s="30"/>
       <c r="F204" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G204" s="31"/>
       <c r="H204" s="31"/>
@@ -5833,7 +5836,7 @@
       <c r="D205" s="26"/>
       <c r="E205" s="30"/>
       <c r="F205" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G205" s="31"/>
       <c r="H205" s="31"/>
@@ -5847,7 +5850,7 @@
       <c r="D206" s="26"/>
       <c r="E206" s="30"/>
       <c r="F206" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G206" s="31"/>
       <c r="H206" s="31"/>
@@ -5861,7 +5864,7 @@
       <c r="D207" s="26"/>
       <c r="E207" s="30"/>
       <c r="F207" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G207" s="31"/>
       <c r="H207" s="31"/>
@@ -5875,7 +5878,7 @@
       <c r="D208" s="26"/>
       <c r="E208" s="30"/>
       <c r="F208" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G208" s="31"/>
       <c r="H208" s="31"/>
@@ -5889,7 +5892,7 @@
       <c r="D209" s="26"/>
       <c r="E209" s="30"/>
       <c r="F209" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G209" s="31"/>
       <c r="H209" s="31"/>
@@ -5903,7 +5906,7 @@
       <c r="D210" s="26"/>
       <c r="E210" s="30"/>
       <c r="F210" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G210" s="31"/>
       <c r="H210" s="31"/>
@@ -5917,7 +5920,7 @@
       <c r="D211" s="26"/>
       <c r="E211" s="30"/>
       <c r="F211" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G211" s="31"/>
       <c r="H211" s="31"/>
@@ -5931,7 +5934,7 @@
       <c r="D212" s="26"/>
       <c r="E212" s="30"/>
       <c r="F212" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G212" s="31"/>
       <c r="H212" s="31"/>
@@ -5945,7 +5948,7 @@
       <c r="D213" s="26"/>
       <c r="E213" s="30"/>
       <c r="F213" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G213" s="31"/>
       <c r="H213" s="31"/>
@@ -5959,7 +5962,7 @@
       <c r="D214" s="26"/>
       <c r="E214" s="30"/>
       <c r="F214" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G214" s="31"/>
       <c r="H214" s="31"/>
@@ -5973,7 +5976,7 @@
       <c r="D215" s="26"/>
       <c r="E215" s="30"/>
       <c r="F215" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G215" s="31"/>
       <c r="H215" s="31"/>
@@ -5987,7 +5990,7 @@
       <c r="D216" s="26"/>
       <c r="E216" s="30"/>
       <c r="F216" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G216" s="31"/>
       <c r="H216" s="31"/>
@@ -6001,7 +6004,7 @@
       <c r="D217" s="26"/>
       <c r="E217" s="30"/>
       <c r="F217" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G217" s="31"/>
       <c r="H217" s="31"/>
@@ -6015,7 +6018,7 @@
       <c r="D218" s="26"/>
       <c r="E218" s="30"/>
       <c r="F218" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G218" s="31"/>
       <c r="H218" s="31"/>
@@ -6029,7 +6032,7 @@
       <c r="D219" s="26"/>
       <c r="E219" s="30"/>
       <c r="F219" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G219" s="31"/>
       <c r="H219" s="31"/>
@@ -6043,7 +6046,7 @@
       <c r="D220" s="26"/>
       <c r="E220" s="30"/>
       <c r="F220" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G220" s="31"/>
       <c r="H220" s="31"/>
@@ -6057,7 +6060,7 @@
       <c r="D221" s="26"/>
       <c r="E221" s="30"/>
       <c r="F221" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G221" s="31"/>
       <c r="H221" s="31"/>
@@ -6071,7 +6074,7 @@
       <c r="D222" s="26"/>
       <c r="E222" s="30"/>
       <c r="F222" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G222" s="31"/>
       <c r="H222" s="31"/>
@@ -6085,7 +6088,7 @@
       <c r="D223" s="26"/>
       <c r="E223" s="30"/>
       <c r="F223" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G223" s="31"/>
       <c r="H223" s="31"/>
@@ -6099,7 +6102,7 @@
       <c r="D224" s="26"/>
       <c r="E224" s="30"/>
       <c r="F224" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G224" s="31"/>
       <c r="H224" s="31"/>
@@ -6113,7 +6116,7 @@
       <c r="D225" s="26"/>
       <c r="E225" s="30"/>
       <c r="F225" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G225" s="31"/>
       <c r="H225" s="31"/>
@@ -6127,7 +6130,7 @@
       <c r="D226" s="26"/>
       <c r="E226" s="30"/>
       <c r="F226" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G226" s="31"/>
       <c r="H226" s="31"/>
@@ -6141,7 +6144,7 @@
       <c r="D227" s="26"/>
       <c r="E227" s="30"/>
       <c r="F227" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G227" s="31"/>
       <c r="H227" s="31"/>
@@ -6155,7 +6158,7 @@
       <c r="D228" s="26"/>
       <c r="E228" s="30"/>
       <c r="F228" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G228" s="31"/>
       <c r="H228" s="31"/>
@@ -6169,7 +6172,7 @@
       <c r="D229" s="26"/>
       <c r="E229" s="30"/>
       <c r="F229" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G229" s="31"/>
       <c r="H229" s="31"/>
@@ -6183,7 +6186,7 @@
       <c r="D230" s="26"/>
       <c r="E230" s="30"/>
       <c r="F230" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G230" s="31"/>
       <c r="H230" s="31"/>
@@ -6197,7 +6200,7 @@
       <c r="D231" s="26"/>
       <c r="E231" s="30"/>
       <c r="F231" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G231" s="31"/>
       <c r="H231" s="31"/>
@@ -6211,7 +6214,7 @@
       <c r="D232" s="26"/>
       <c r="E232" s="30"/>
       <c r="F232" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G232" s="31"/>
       <c r="H232" s="31"/>
@@ -6225,7 +6228,7 @@
       <c r="D233" s="26"/>
       <c r="E233" s="30"/>
       <c r="F233" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G233" s="31"/>
       <c r="H233" s="31"/>
@@ -6239,7 +6242,7 @@
       <c r="D234" s="26"/>
       <c r="E234" s="30"/>
       <c r="F234" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G234" s="31"/>
       <c r="H234" s="31"/>
@@ -6253,7 +6256,7 @@
       <c r="D235" s="26"/>
       <c r="E235" s="30"/>
       <c r="F235" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G235" s="31"/>
       <c r="H235" s="31"/>
@@ -6267,7 +6270,7 @@
       <c r="D236" s="26"/>
       <c r="E236" s="30"/>
       <c r="F236" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G236" s="31"/>
       <c r="H236" s="31"/>
@@ -6281,7 +6284,7 @@
       <c r="D237" s="26"/>
       <c r="E237" s="30"/>
       <c r="F237" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G237" s="31"/>
       <c r="H237" s="31"/>
@@ -6295,7 +6298,7 @@
       <c r="D238" s="26"/>
       <c r="E238" s="30"/>
       <c r="F238" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G238" s="31"/>
       <c r="H238" s="31"/>
@@ -6309,7 +6312,7 @@
       <c r="D239" s="26"/>
       <c r="E239" s="30"/>
       <c r="F239" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G239" s="31"/>
       <c r="H239" s="31"/>
@@ -6323,7 +6326,7 @@
       <c r="D240" s="26"/>
       <c r="E240" s="30"/>
       <c r="F240" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G240" s="31"/>
       <c r="H240" s="31"/>
@@ -6337,7 +6340,7 @@
       <c r="D241" s="26"/>
       <c r="E241" s="30"/>
       <c r="F241" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G241" s="31"/>
       <c r="H241" s="31"/>
@@ -6351,7 +6354,7 @@
       <c r="D242" s="26"/>
       <c r="E242" s="30"/>
       <c r="F242" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G242" s="31"/>
       <c r="H242" s="31"/>
@@ -6365,7 +6368,7 @@
       <c r="D243" s="26"/>
       <c r="E243" s="30"/>
       <c r="F243" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G243" s="31"/>
       <c r="H243" s="31"/>
@@ -6379,7 +6382,7 @@
       <c r="D244" s="26"/>
       <c r="E244" s="30"/>
       <c r="F244" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G244" s="31"/>
       <c r="H244" s="31"/>
@@ -6393,7 +6396,7 @@
       <c r="D245" s="26"/>
       <c r="E245" s="30"/>
       <c r="F245" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G245" s="31"/>
       <c r="H245" s="31"/>
@@ -6407,7 +6410,7 @@
       <c r="D246" s="26"/>
       <c r="E246" s="30"/>
       <c r="F246" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G246" s="31"/>
       <c r="H246" s="31"/>
@@ -6421,7 +6424,7 @@
       <c r="D247" s="26"/>
       <c r="E247" s="30"/>
       <c r="F247" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G247" s="31"/>
       <c r="H247" s="31"/>
@@ -6435,7 +6438,7 @@
       <c r="D248" s="26"/>
       <c r="E248" s="30"/>
       <c r="F248" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G248" s="31"/>
       <c r="H248" s="31"/>
@@ -6449,7 +6452,7 @@
       <c r="D249" s="26"/>
       <c r="E249" s="30"/>
       <c r="F249" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G249" s="31"/>
       <c r="H249" s="31"/>
@@ -6463,7 +6466,7 @@
       <c r="D250" s="26"/>
       <c r="E250" s="30"/>
       <c r="F250" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G250" s="31"/>
       <c r="H250" s="31"/>
@@ -6477,7 +6480,7 @@
       <c r="D251" s="26"/>
       <c r="E251" s="30"/>
       <c r="F251" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G251" s="31"/>
       <c r="H251" s="31"/>
@@ -6491,7 +6494,7 @@
       <c r="D252" s="26"/>
       <c r="E252" s="30"/>
       <c r="F252" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G252" s="31"/>
       <c r="H252" s="31"/>
@@ -6505,7 +6508,7 @@
       <c r="D253" s="26"/>
       <c r="E253" s="30"/>
       <c r="F253" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G253" s="31"/>
       <c r="H253" s="31"/>
@@ -6519,7 +6522,7 @@
       <c r="D254" s="26"/>
       <c r="E254" s="30"/>
       <c r="F254" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G254" s="31"/>
       <c r="H254" s="31"/>
@@ -6533,7 +6536,7 @@
       <c r="D255" s="26"/>
       <c r="E255" s="30"/>
       <c r="F255" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G255" s="31"/>
       <c r="H255" s="31"/>
@@ -6547,7 +6550,7 @@
       <c r="D256" s="26"/>
       <c r="E256" s="30"/>
       <c r="F256" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G256" s="31"/>
       <c r="H256" s="31"/>
@@ -6561,7 +6564,7 @@
       <c r="D257" s="26"/>
       <c r="E257" s="30"/>
       <c r="F257" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G257" s="31"/>
       <c r="H257" s="31"/>
@@ -6575,7 +6578,7 @@
       <c r="D258" s="26"/>
       <c r="E258" s="30"/>
       <c r="F258" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G258" s="31"/>
       <c r="H258" s="31"/>
@@ -6589,7 +6592,7 @@
       <c r="D259" s="26"/>
       <c r="E259" s="30"/>
       <c r="F259" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G259" s="31"/>
       <c r="H259" s="31"/>
@@ -6603,7 +6606,7 @@
       <c r="D260" s="26"/>
       <c r="E260" s="30"/>
       <c r="F260" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G260" s="31"/>
       <c r="H260" s="31"/>
@@ -6617,7 +6620,7 @@
       <c r="D261" s="26"/>
       <c r="E261" s="30"/>
       <c r="F261" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G261" s="31"/>
       <c r="H261" s="31"/>
@@ -6631,7 +6634,7 @@
       <c r="D262" s="26"/>
       <c r="E262" s="30"/>
       <c r="F262" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G262" s="31"/>
       <c r="H262" s="31"/>
@@ -6645,7 +6648,7 @@
       <c r="D263" s="26"/>
       <c r="E263" s="30"/>
       <c r="F263" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G263" s="31"/>
       <c r="H263" s="31"/>
@@ -6659,7 +6662,7 @@
       <c r="D264" s="26"/>
       <c r="E264" s="30"/>
       <c r="F264" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G264" s="31"/>
       <c r="H264" s="31"/>
@@ -6673,7 +6676,7 @@
       <c r="D265" s="26"/>
       <c r="E265" s="30"/>
       <c r="F265" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G265" s="31"/>
       <c r="H265" s="31"/>
@@ -6687,7 +6690,7 @@
       <c r="D266" s="26"/>
       <c r="E266" s="30"/>
       <c r="F266" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G266" s="31"/>
       <c r="H266" s="31"/>
@@ -6701,7 +6704,7 @@
       <c r="D267" s="26"/>
       <c r="E267" s="30"/>
       <c r="F267" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G267" s="31"/>
       <c r="H267" s="31"/>
@@ -6715,7 +6718,7 @@
       <c r="D268" s="26"/>
       <c r="E268" s="30"/>
       <c r="F268" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G268" s="31"/>
       <c r="H268" s="31"/>
@@ -6729,7 +6732,7 @@
       <c r="D269" s="26"/>
       <c r="E269" s="30"/>
       <c r="F269" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G269" s="31"/>
       <c r="H269" s="31"/>
@@ -6743,7 +6746,7 @@
       <c r="D270" s="26"/>
       <c r="E270" s="30"/>
       <c r="F270" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G270" s="31"/>
       <c r="H270" s="31"/>
@@ -6757,7 +6760,7 @@
       <c r="D271" s="26"/>
       <c r="E271" s="30"/>
       <c r="F271" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G271" s="31"/>
       <c r="H271" s="31"/>
@@ -6771,7 +6774,7 @@
       <c r="D272" s="26"/>
       <c r="E272" s="30"/>
       <c r="F272" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G272" s="31"/>
       <c r="H272" s="31"/>
@@ -6785,7 +6788,7 @@
       <c r="D273" s="26"/>
       <c r="E273" s="30"/>
       <c r="F273" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G273" s="31"/>
       <c r="H273" s="31"/>
@@ -6799,7 +6802,7 @@
       <c r="D274" s="26"/>
       <c r="E274" s="30"/>
       <c r="F274" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G274" s="31"/>
       <c r="H274" s="31"/>
@@ -6813,7 +6816,7 @@
       <c r="D275" s="26"/>
       <c r="E275" s="30"/>
       <c r="F275" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G275" s="31"/>
       <c r="H275" s="31"/>
@@ -6827,7 +6830,7 @@
       <c r="D276" s="26"/>
       <c r="E276" s="30"/>
       <c r="F276" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G276" s="31"/>
       <c r="H276" s="31"/>
@@ -6841,7 +6844,7 @@
       <c r="D277" s="26"/>
       <c r="E277" s="30"/>
       <c r="F277" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G277" s="31"/>
       <c r="H277" s="31"/>
@@ -6855,7 +6858,7 @@
       <c r="D278" s="26"/>
       <c r="E278" s="30"/>
       <c r="F278" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G278" s="31"/>
       <c r="H278" s="31"/>
@@ -6869,7 +6872,7 @@
       <c r="D279" s="26"/>
       <c r="E279" s="30"/>
       <c r="F279" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G279" s="31"/>
       <c r="H279" s="31"/>
@@ -6883,7 +6886,7 @@
       <c r="D280" s="26"/>
       <c r="E280" s="30"/>
       <c r="F280" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G280" s="31"/>
       <c r="H280" s="31"/>
@@ -6897,7 +6900,7 @@
       <c r="D281" s="26"/>
       <c r="E281" s="30"/>
       <c r="F281" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G281" s="31"/>
       <c r="H281" s="31"/>
@@ -6911,7 +6914,7 @@
       <c r="D282" s="26"/>
       <c r="E282" s="30"/>
       <c r="F282" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G282" s="31"/>
       <c r="H282" s="31"/>
@@ -6925,7 +6928,7 @@
       <c r="D283" s="26"/>
       <c r="E283" s="30"/>
       <c r="F283" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G283" s="31"/>
       <c r="H283" s="31"/>
@@ -6939,7 +6942,7 @@
       <c r="D284" s="26"/>
       <c r="E284" s="30"/>
       <c r="F284" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G284" s="31"/>
       <c r="H284" s="31"/>
@@ -6953,7 +6956,7 @@
       <c r="D285" s="26"/>
       <c r="E285" s="30"/>
       <c r="F285" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G285" s="31"/>
       <c r="H285" s="31"/>
@@ -6967,7 +6970,7 @@
       <c r="D286" s="26"/>
       <c r="E286" s="30"/>
       <c r="F286" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G286" s="31"/>
       <c r="H286" s="31"/>
@@ -6981,7 +6984,7 @@
       <c r="D287" s="26"/>
       <c r="E287" s="30"/>
       <c r="F287" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G287" s="31"/>
       <c r="H287" s="31"/>
@@ -6995,7 +6998,7 @@
       <c r="D288" s="26"/>
       <c r="E288" s="30"/>
       <c r="F288" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G288" s="31"/>
       <c r="H288" s="31"/>
@@ -7009,7 +7012,7 @@
       <c r="D289" s="26"/>
       <c r="E289" s="30"/>
       <c r="F289" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G289" s="31"/>
       <c r="H289" s="31"/>
@@ -7023,7 +7026,7 @@
       <c r="D290" s="26"/>
       <c r="E290" s="30"/>
       <c r="F290" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G290" s="31"/>
       <c r="H290" s="31"/>
@@ -7037,7 +7040,7 @@
       <c r="D291" s="26"/>
       <c r="E291" s="30"/>
       <c r="F291" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G291" s="31"/>
       <c r="H291" s="31"/>
@@ -7051,7 +7054,7 @@
       <c r="D292" s="26"/>
       <c r="E292" s="30"/>
       <c r="F292" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G292" s="31"/>
       <c r="H292" s="31"/>
@@ -7065,7 +7068,7 @@
       <c r="D293" s="26"/>
       <c r="E293" s="30"/>
       <c r="F293" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G293" s="31"/>
       <c r="H293" s="31"/>
@@ -7079,7 +7082,7 @@
       <c r="D294" s="26"/>
       <c r="E294" s="30"/>
       <c r="F294" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G294" s="31"/>
       <c r="H294" s="31"/>
@@ -7093,7 +7096,7 @@
       <c r="D295" s="26"/>
       <c r="E295" s="30"/>
       <c r="F295" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G295" s="31"/>
       <c r="H295" s="31"/>
@@ -7107,7 +7110,7 @@
       <c r="D296" s="26"/>
       <c r="E296" s="30"/>
       <c r="F296" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G296" s="31"/>
       <c r="H296" s="31"/>
@@ -7121,7 +7124,7 @@
       <c r="D297" s="26"/>
       <c r="E297" s="30"/>
       <c r="F297" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G297" s="31"/>
       <c r="H297" s="31"/>
@@ -7135,7 +7138,7 @@
       <c r="D298" s="26"/>
       <c r="E298" s="30"/>
       <c r="F298" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G298" s="31"/>
       <c r="H298" s="31"/>
@@ -7149,7 +7152,7 @@
       <c r="D299" s="26"/>
       <c r="E299" s="30"/>
       <c r="F299" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G299" s="31"/>
       <c r="H299" s="31"/>
@@ -7163,7 +7166,7 @@
       <c r="D300" s="26"/>
       <c r="E300" s="30"/>
       <c r="F300" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G300" s="31"/>
       <c r="H300" s="31"/>
@@ -7177,7 +7180,7 @@
       <c r="D301" s="26"/>
       <c r="E301" s="30"/>
       <c r="F301" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G301" s="31"/>
       <c r="H301" s="31"/>
@@ -7191,7 +7194,7 @@
       <c r="D302" s="26"/>
       <c r="E302" s="30"/>
       <c r="F302" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G302" s="31"/>
       <c r="H302" s="31"/>
@@ -7205,7 +7208,7 @@
       <c r="D303" s="26"/>
       <c r="E303" s="30"/>
       <c r="F303" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G303" s="31"/>
       <c r="H303" s="31"/>
@@ -7219,7 +7222,7 @@
       <c r="D304" s="26"/>
       <c r="E304" s="30"/>
       <c r="F304" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G304" s="31"/>
       <c r="H304" s="31"/>
@@ -7233,7 +7236,7 @@
       <c r="D305" s="26"/>
       <c r="E305" s="30"/>
       <c r="F305" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G305" s="31"/>
       <c r="H305" s="31"/>
@@ -7247,7 +7250,7 @@
       <c r="D306" s="26"/>
       <c r="E306" s="30"/>
       <c r="F306" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G306" s="31"/>
       <c r="H306" s="31"/>
@@ -7261,7 +7264,7 @@
       <c r="D307" s="26"/>
       <c r="E307" s="30"/>
       <c r="F307" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G307" s="31"/>
       <c r="H307" s="31"/>
@@ -7275,7 +7278,7 @@
       <c r="D308" s="26"/>
       <c r="E308" s="30"/>
       <c r="F308" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G308" s="31"/>
       <c r="H308" s="31"/>
@@ -7289,7 +7292,7 @@
       <c r="D309" s="26"/>
       <c r="E309" s="30"/>
       <c r="F309" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G309" s="31"/>
       <c r="H309" s="31"/>
@@ -7303,7 +7306,7 @@
       <c r="D310" s="26"/>
       <c r="E310" s="30"/>
       <c r="F310" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G310" s="31"/>
       <c r="H310" s="31"/>
@@ -7317,7 +7320,7 @@
       <c r="D311" s="26"/>
       <c r="E311" s="30"/>
       <c r="F311" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G311" s="31"/>
       <c r="H311" s="31"/>
@@ -7331,7 +7334,7 @@
       <c r="D312" s="26"/>
       <c r="E312" s="30"/>
       <c r="F312" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G312" s="31"/>
       <c r="H312" s="31"/>
@@ -7345,7 +7348,7 @@
       <c r="D313" s="26"/>
       <c r="E313" s="30"/>
       <c r="F313" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G313" s="31"/>
       <c r="H313" s="31"/>
@@ -7359,7 +7362,7 @@
       <c r="D314" s="26"/>
       <c r="E314" s="30"/>
       <c r="F314" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G314" s="31"/>
       <c r="H314" s="31"/>
@@ -7373,7 +7376,7 @@
       <c r="D315" s="26"/>
       <c r="E315" s="30"/>
       <c r="F315" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G315" s="31"/>
       <c r="H315" s="31"/>
@@ -7387,7 +7390,7 @@
       <c r="D316" s="26"/>
       <c r="E316" s="30"/>
       <c r="F316" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G316" s="31"/>
       <c r="H316" s="31"/>
@@ -7401,7 +7404,7 @@
       <c r="D317" s="26"/>
       <c r="E317" s="30"/>
       <c r="F317" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G317" s="31"/>
       <c r="H317" s="31"/>
@@ -7415,7 +7418,7 @@
       <c r="D318" s="26"/>
       <c r="E318" s="30"/>
       <c r="F318" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G318" s="31"/>
       <c r="H318" s="31"/>
@@ -7429,7 +7432,7 @@
       <c r="D319" s="26"/>
       <c r="E319" s="30"/>
       <c r="F319" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G319" s="31"/>
       <c r="H319" s="31"/>
@@ -7443,7 +7446,7 @@
       <c r="D320" s="26"/>
       <c r="E320" s="30"/>
       <c r="F320" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G320" s="31"/>
       <c r="H320" s="31"/>
@@ -7457,7 +7460,7 @@
       <c r="D321" s="26"/>
       <c r="E321" s="30"/>
       <c r="F321" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G321" s="31"/>
       <c r="H321" s="31"/>
@@ -7471,7 +7474,7 @@
       <c r="D322" s="26"/>
       <c r="E322" s="30"/>
       <c r="F322" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G322" s="31"/>
       <c r="H322" s="31"/>
@@ -7485,7 +7488,7 @@
       <c r="D323" s="26"/>
       <c r="E323" s="30"/>
       <c r="F323" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G323" s="31"/>
       <c r="H323" s="31"/>
@@ -7499,7 +7502,7 @@
       <c r="D324" s="26"/>
       <c r="E324" s="30"/>
       <c r="F324" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G324" s="31"/>
       <c r="H324" s="31"/>
@@ -7513,7 +7516,7 @@
       <c r="D325" s="26"/>
       <c r="E325" s="30"/>
       <c r="F325" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G325" s="31"/>
       <c r="H325" s="31"/>
@@ -7527,7 +7530,7 @@
       <c r="D326" s="26"/>
       <c r="E326" s="30"/>
       <c r="F326" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G326" s="31"/>
       <c r="H326" s="31"/>
@@ -7541,7 +7544,7 @@
       <c r="D327" s="26"/>
       <c r="E327" s="30"/>
       <c r="F327" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G327" s="31"/>
       <c r="H327" s="31"/>
@@ -7555,7 +7558,7 @@
       <c r="D328" s="26"/>
       <c r="E328" s="30"/>
       <c r="F328" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G328" s="31"/>
       <c r="H328" s="31"/>
@@ -7569,7 +7572,7 @@
       <c r="D329" s="26"/>
       <c r="E329" s="30"/>
       <c r="F329" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G329" s="31"/>
       <c r="H329" s="31"/>
@@ -7583,7 +7586,7 @@
       <c r="D330" s="26"/>
       <c r="E330" s="30"/>
       <c r="F330" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G330" s="31"/>
       <c r="H330" s="31"/>
@@ -7597,7 +7600,7 @@
       <c r="D331" s="26"/>
       <c r="E331" s="30"/>
       <c r="F331" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G331" s="31"/>
       <c r="H331" s="31"/>
@@ -7611,7 +7614,7 @@
       <c r="D332" s="26"/>
       <c r="E332" s="30"/>
       <c r="F332" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G332" s="31"/>
       <c r="H332" s="31"/>
@@ -7625,7 +7628,7 @@
       <c r="D333" s="26"/>
       <c r="E333" s="30"/>
       <c r="F333" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G333" s="31"/>
       <c r="H333" s="31"/>
@@ -7639,7 +7642,7 @@
       <c r="D334" s="26"/>
       <c r="E334" s="30"/>
       <c r="F334" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G334" s="31"/>
       <c r="H334" s="31"/>
@@ -7653,7 +7656,7 @@
       <c r="D335" s="26"/>
       <c r="E335" s="30"/>
       <c r="F335" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G335" s="31"/>
       <c r="H335" s="31"/>
@@ -7667,7 +7670,7 @@
       <c r="D336" s="26"/>
       <c r="E336" s="30"/>
       <c r="F336" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G336" s="31"/>
       <c r="H336" s="31"/>
@@ -7681,7 +7684,7 @@
       <c r="D337" s="26"/>
       <c r="E337" s="30"/>
       <c r="F337" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G337" s="31"/>
       <c r="H337" s="31"/>
@@ -7695,7 +7698,7 @@
       <c r="D338" s="26"/>
       <c r="E338" s="30"/>
       <c r="F338" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G338" s="31"/>
       <c r="H338" s="31"/>
@@ -7709,7 +7712,7 @@
       <c r="D339" s="26"/>
       <c r="E339" s="30"/>
       <c r="F339" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G339" s="31"/>
       <c r="H339" s="31"/>
@@ -7723,7 +7726,7 @@
       <c r="D340" s="26"/>
       <c r="E340" s="30"/>
       <c r="F340" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G340" s="31"/>
       <c r="H340" s="31"/>
@@ -7737,7 +7740,7 @@
       <c r="D341" s="26"/>
       <c r="E341" s="30"/>
       <c r="F341" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G341" s="31"/>
       <c r="H341" s="31"/>
@@ -7751,7 +7754,7 @@
       <c r="D342" s="26"/>
       <c r="E342" s="30"/>
       <c r="F342" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G342" s="31"/>
       <c r="H342" s="31"/>
@@ -7765,7 +7768,7 @@
       <c r="D343" s="26"/>
       <c r="E343" s="30"/>
       <c r="F343" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G343" s="31"/>
       <c r="H343" s="31"/>
@@ -7779,7 +7782,7 @@
       <c r="D344" s="26"/>
       <c r="E344" s="30"/>
       <c r="F344" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G344" s="31"/>
       <c r="H344" s="31"/>
@@ -7793,7 +7796,7 @@
       <c r="D345" s="26"/>
       <c r="E345" s="30"/>
       <c r="F345" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G345" s="31"/>
       <c r="H345" s="31"/>
@@ -7807,7 +7810,7 @@
       <c r="D346" s="26"/>
       <c r="E346" s="30"/>
       <c r="F346" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G346" s="31"/>
       <c r="H346" s="31"/>
@@ -7821,7 +7824,7 @@
       <c r="D347" s="26"/>
       <c r="E347" s="30"/>
       <c r="F347" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G347" s="31"/>
       <c r="H347" s="31"/>
@@ -7835,7 +7838,7 @@
       <c r="D348" s="26"/>
       <c r="E348" s="30"/>
       <c r="F348" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G348" s="31"/>
       <c r="H348" s="31"/>
@@ -7849,7 +7852,7 @@
       <c r="D349" s="26"/>
       <c r="E349" s="30"/>
       <c r="F349" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G349" s="31"/>
       <c r="H349" s="31"/>
@@ -7863,7 +7866,7 @@
       <c r="D350" s="26"/>
       <c r="E350" s="30"/>
       <c r="F350" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G350" s="31"/>
       <c r="H350" s="31"/>
@@ -7877,7 +7880,7 @@
       <c r="D351" s="26"/>
       <c r="E351" s="30"/>
       <c r="F351" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G351" s="31"/>
       <c r="H351" s="31"/>
@@ -7891,7 +7894,7 @@
       <c r="D352" s="26"/>
       <c r="E352" s="30"/>
       <c r="F352" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G352" s="31"/>
       <c r="H352" s="31"/>
@@ -7905,7 +7908,7 @@
       <c r="D353" s="26"/>
       <c r="E353" s="30"/>
       <c r="F353" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G353" s="31"/>
       <c r="H353" s="31"/>
@@ -7919,7 +7922,7 @@
       <c r="D354" s="26"/>
       <c r="E354" s="30"/>
       <c r="F354" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G354" s="31"/>
       <c r="H354" s="31"/>
@@ -7933,7 +7936,7 @@
       <c r="D355" s="26"/>
       <c r="E355" s="30"/>
       <c r="F355" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G355" s="31"/>
       <c r="H355" s="31"/>
@@ -7947,7 +7950,7 @@
       <c r="D356" s="26"/>
       <c r="E356" s="30"/>
       <c r="F356" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G356" s="31"/>
       <c r="H356" s="31"/>
@@ -7961,7 +7964,7 @@
       <c r="D357" s="26"/>
       <c r="E357" s="30"/>
       <c r="F357" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G357" s="31"/>
       <c r="H357" s="31"/>
@@ -7975,7 +7978,7 @@
       <c r="D358" s="26"/>
       <c r="E358" s="30"/>
       <c r="F358" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G358" s="31"/>
       <c r="H358" s="31"/>
@@ -7989,7 +7992,7 @@
       <c r="D359" s="26"/>
       <c r="E359" s="30"/>
       <c r="F359" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G359" s="31"/>
       <c r="H359" s="31"/>
@@ -8003,7 +8006,7 @@
       <c r="D360" s="26"/>
       <c r="E360" s="30"/>
       <c r="F360" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G360" s="31"/>
       <c r="H360" s="31"/>
@@ -8017,7 +8020,7 @@
       <c r="D361" s="26"/>
       <c r="E361" s="30"/>
       <c r="F361" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G361" s="31"/>
       <c r="H361" s="31"/>
@@ -8031,7 +8034,7 @@
       <c r="D362" s="26"/>
       <c r="E362" s="30"/>
       <c r="F362" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G362" s="31"/>
       <c r="H362" s="31"/>
@@ -8045,7 +8048,7 @@
       <c r="D363" s="26"/>
       <c r="E363" s="30"/>
       <c r="F363" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G363" s="31"/>
       <c r="H363" s="31"/>
@@ -8059,7 +8062,7 @@
       <c r="D364" s="26"/>
       <c r="E364" s="30"/>
       <c r="F364" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G364" s="31"/>
       <c r="H364" s="31"/>
@@ -8073,7 +8076,7 @@
       <c r="D365" s="26"/>
       <c r="E365" s="30"/>
       <c r="F365" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G365" s="31"/>
       <c r="H365" s="31"/>
@@ -8087,7 +8090,7 @@
       <c r="D366" s="26"/>
       <c r="E366" s="30"/>
       <c r="F366" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G366" s="31"/>
       <c r="H366" s="31"/>
@@ -8101,7 +8104,7 @@
       <c r="D367" s="26"/>
       <c r="E367" s="30"/>
       <c r="F367" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G367" s="31"/>
       <c r="H367" s="31"/>
@@ -8115,7 +8118,7 @@
       <c r="D368" s="26"/>
       <c r="E368" s="30"/>
       <c r="F368" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G368" s="31"/>
       <c r="H368" s="31"/>
@@ -8129,7 +8132,7 @@
       <c r="D369" s="26"/>
       <c r="E369" s="30"/>
       <c r="F369" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G369" s="31"/>
       <c r="H369" s="31"/>
@@ -8143,7 +8146,7 @@
       <c r="D370" s="26"/>
       <c r="E370" s="30"/>
       <c r="F370" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G370" s="31"/>
       <c r="H370" s="31"/>
@@ -8157,7 +8160,7 @@
       <c r="D371" s="26"/>
       <c r="E371" s="30"/>
       <c r="F371" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G371" s="31"/>
       <c r="H371" s="31"/>
@@ -8171,7 +8174,7 @@
       <c r="D372" s="26"/>
       <c r="E372" s="30"/>
       <c r="F372" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G372" s="31"/>
       <c r="H372" s="31"/>
@@ -8185,7 +8188,7 @@
       <c r="D373" s="26"/>
       <c r="E373" s="30"/>
       <c r="F373" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G373" s="31"/>
       <c r="H373" s="31"/>
@@ -8199,7 +8202,7 @@
       <c r="D374" s="26"/>
       <c r="E374" s="30"/>
       <c r="F374" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G374" s="31"/>
       <c r="H374" s="31"/>
@@ -8213,7 +8216,7 @@
       <c r="D375" s="26"/>
       <c r="E375" s="30"/>
       <c r="F375" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G375" s="31"/>
       <c r="H375" s="31"/>
@@ -8227,7 +8230,7 @@
       <c r="D376" s="26"/>
       <c r="E376" s="30"/>
       <c r="F376" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G376" s="31"/>
       <c r="H376" s="31"/>
@@ -8241,7 +8244,7 @@
       <c r="D377" s="26"/>
       <c r="E377" s="30"/>
       <c r="F377" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G377" s="31"/>
       <c r="H377" s="31"/>
@@ -8255,7 +8258,7 @@
       <c r="D378" s="26"/>
       <c r="E378" s="30"/>
       <c r="F378" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G378" s="31"/>
       <c r="H378" s="31"/>
@@ -8269,7 +8272,7 @@
       <c r="D379" s="26"/>
       <c r="E379" s="30"/>
       <c r="F379" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G379" s="31"/>
       <c r="H379" s="31"/>
@@ -8283,7 +8286,7 @@
       <c r="D380" s="26"/>
       <c r="E380" s="30"/>
       <c r="F380" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G380" s="31"/>
       <c r="H380" s="31"/>
@@ -8297,7 +8300,7 @@
       <c r="D381" s="26"/>
       <c r="E381" s="30"/>
       <c r="F381" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G381" s="31"/>
       <c r="H381" s="31"/>
@@ -8311,7 +8314,7 @@
       <c r="D382" s="26"/>
       <c r="E382" s="30"/>
       <c r="F382" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G382" s="31"/>
       <c r="H382" s="31"/>
@@ -8325,7 +8328,7 @@
       <c r="D383" s="26"/>
       <c r="E383" s="30"/>
       <c r="F383" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G383" s="31"/>
       <c r="H383" s="31"/>
@@ -8339,7 +8342,7 @@
       <c r="D384" s="26"/>
       <c r="E384" s="30"/>
       <c r="F384" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G384" s="31"/>
       <c r="H384" s="31"/>
@@ -8353,7 +8356,7 @@
       <c r="D385" s="26"/>
       <c r="E385" s="30"/>
       <c r="F385" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G385" s="31"/>
       <c r="H385" s="31"/>
@@ -8367,7 +8370,7 @@
       <c r="D386" s="26"/>
       <c r="E386" s="30"/>
       <c r="F386" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G386" s="31"/>
       <c r="H386" s="31"/>
@@ -8381,7 +8384,7 @@
       <c r="D387" s="26"/>
       <c r="E387" s="30"/>
       <c r="F387" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G387" s="31"/>
       <c r="H387" s="31"/>
@@ -8395,7 +8398,7 @@
       <c r="D388" s="26"/>
       <c r="E388" s="30"/>
       <c r="F388" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G388" s="31"/>
       <c r="H388" s="31"/>
@@ -8409,7 +8412,7 @@
       <c r="D389" s="26"/>
       <c r="E389" s="30"/>
       <c r="F389" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G389" s="31"/>
       <c r="H389" s="31"/>
@@ -8423,7 +8426,7 @@
       <c r="D390" s="26"/>
       <c r="E390" s="30"/>
       <c r="F390" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G390" s="31"/>
       <c r="H390" s="31"/>
@@ -8437,7 +8440,7 @@
       <c r="D391" s="26"/>
       <c r="E391" s="30"/>
       <c r="F391" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G391" s="31"/>
       <c r="H391" s="31"/>
@@ -8451,7 +8454,7 @@
       <c r="D392" s="26"/>
       <c r="E392" s="30"/>
       <c r="F392" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G392" s="31"/>
       <c r="H392" s="31"/>
@@ -8465,7 +8468,7 @@
       <c r="D393" s="26"/>
       <c r="E393" s="30"/>
       <c r="F393" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G393" s="31"/>
       <c r="H393" s="31"/>
@@ -8479,7 +8482,7 @@
       <c r="D394" s="26"/>
       <c r="E394" s="30"/>
       <c r="F394" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G394" s="31"/>
       <c r="H394" s="31"/>
@@ -8493,7 +8496,7 @@
       <c r="D395" s="26"/>
       <c r="E395" s="30"/>
       <c r="F395" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G395" s="31"/>
       <c r="H395" s="31"/>
@@ -8507,7 +8510,7 @@
       <c r="D396" s="26"/>
       <c r="E396" s="30"/>
       <c r="F396" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G396" s="31"/>
       <c r="H396" s="31"/>
@@ -8521,7 +8524,7 @@
       <c r="D397" s="26"/>
       <c r="E397" s="30"/>
       <c r="F397" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G397" s="31"/>
       <c r="H397" s="31"/>
@@ -8535,7 +8538,7 @@
       <c r="D398" s="26"/>
       <c r="E398" s="30"/>
       <c r="F398" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G398" s="31"/>
       <c r="H398" s="31"/>
@@ -8549,7 +8552,7 @@
       <c r="D399" s="26"/>
       <c r="E399" s="30"/>
       <c r="F399" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G399" s="31"/>
       <c r="H399" s="31"/>
@@ -8563,7 +8566,7 @@
       <c r="D400" s="26"/>
       <c r="E400" s="30"/>
       <c r="F400" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G400" s="31"/>
       <c r="H400" s="31"/>
@@ -8577,7 +8580,7 @@
       <c r="D401" s="26"/>
       <c r="E401" s="30"/>
       <c r="F401" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G401" s="31"/>
       <c r="H401" s="31"/>
@@ -8591,7 +8594,7 @@
       <c r="D402" s="26"/>
       <c r="E402" s="30"/>
       <c r="F402" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G402" s="31"/>
       <c r="H402" s="31"/>
@@ -8605,7 +8608,7 @@
       <c r="D403" s="26"/>
       <c r="E403" s="30"/>
       <c r="F403" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G403" s="31"/>
       <c r="H403" s="31"/>
@@ -8619,7 +8622,7 @@
       <c r="D404" s="26"/>
       <c r="E404" s="30"/>
       <c r="F404" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G404" s="31"/>
       <c r="H404" s="31"/>
@@ -8633,7 +8636,7 @@
       <c r="D405" s="26"/>
       <c r="E405" s="30"/>
       <c r="F405" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G405" s="31"/>
       <c r="H405" s="31"/>
@@ -8647,7 +8650,7 @@
       <c r="D406" s="26"/>
       <c r="E406" s="30"/>
       <c r="F406" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G406" s="31"/>
       <c r="H406" s="31"/>
@@ -8661,7 +8664,7 @@
       <c r="D407" s="26"/>
       <c r="E407" s="30"/>
       <c r="F407" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G407" s="31"/>
       <c r="H407" s="31"/>
@@ -8675,7 +8678,7 @@
       <c r="D408" s="26"/>
       <c r="E408" s="30"/>
       <c r="F408" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G408" s="31"/>
       <c r="H408" s="31"/>
@@ -8689,7 +8692,7 @@
       <c r="D409" s="26"/>
       <c r="E409" s="30"/>
       <c r="F409" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G409" s="31"/>
       <c r="H409" s="31"/>
@@ -8703,7 +8706,7 @@
       <c r="D410" s="26"/>
       <c r="E410" s="30"/>
       <c r="F410" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G410" s="31"/>
       <c r="H410" s="31"/>
@@ -8717,7 +8720,7 @@
       <c r="D411" s="26"/>
       <c r="E411" s="30"/>
       <c r="F411" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G411" s="31"/>
       <c r="H411" s="31"/>
@@ -8731,7 +8734,7 @@
       <c r="D412" s="26"/>
       <c r="E412" s="30"/>
       <c r="F412" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G412" s="31"/>
       <c r="H412" s="31"/>
@@ -8745,7 +8748,7 @@
       <c r="D413" s="26"/>
       <c r="E413" s="30"/>
       <c r="F413" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G413" s="31"/>
       <c r="H413" s="31"/>
@@ -8759,7 +8762,7 @@
       <c r="D414" s="26"/>
       <c r="E414" s="30"/>
       <c r="F414" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G414" s="31"/>
       <c r="H414" s="31"/>
@@ -8773,7 +8776,7 @@
       <c r="D415" s="26"/>
       <c r="E415" s="30"/>
       <c r="F415" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G415" s="31"/>
       <c r="H415" s="31"/>
@@ -8787,7 +8790,7 @@
       <c r="D416" s="26"/>
       <c r="E416" s="30"/>
       <c r="F416" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G416" s="31"/>
       <c r="H416" s="31"/>
@@ -8801,7 +8804,7 @@
       <c r="D417" s="26"/>
       <c r="E417" s="30"/>
       <c r="F417" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G417" s="31"/>
       <c r="H417" s="31"/>
@@ -8815,7 +8818,7 @@
       <c r="D418" s="26"/>
       <c r="E418" s="30"/>
       <c r="F418" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G418" s="31"/>
       <c r="H418" s="31"/>
@@ -8829,7 +8832,7 @@
       <c r="D419" s="26"/>
       <c r="E419" s="30"/>
       <c r="F419" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G419" s="31"/>
       <c r="H419" s="31"/>
@@ -8843,7 +8846,7 @@
       <c r="D420" s="26"/>
       <c r="E420" s="30"/>
       <c r="F420" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G420" s="31"/>
       <c r="H420" s="31"/>
@@ -8857,7 +8860,7 @@
       <c r="D421" s="26"/>
       <c r="E421" s="30"/>
       <c r="F421" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G421" s="31"/>
       <c r="H421" s="31"/>
@@ -8871,7 +8874,7 @@
       <c r="D422" s="26"/>
       <c r="E422" s="30"/>
       <c r="F422" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G422" s="31"/>
       <c r="H422" s="31"/>
@@ -8885,7 +8888,7 @@
       <c r="D423" s="26"/>
       <c r="E423" s="30"/>
       <c r="F423" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G423" s="31"/>
       <c r="H423" s="31"/>
@@ -8899,7 +8902,7 @@
       <c r="D424" s="26"/>
       <c r="E424" s="30"/>
       <c r="F424" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G424" s="31"/>
       <c r="H424" s="31"/>
@@ -8913,7 +8916,7 @@
       <c r="D425" s="26"/>
       <c r="E425" s="30"/>
       <c r="F425" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G425" s="31"/>
       <c r="H425" s="31"/>
@@ -8927,7 +8930,7 @@
       <c r="D426" s="26"/>
       <c r="E426" s="30"/>
       <c r="F426" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G426" s="31"/>
       <c r="H426" s="31"/>
@@ -8941,7 +8944,7 @@
       <c r="D427" s="26"/>
       <c r="E427" s="30"/>
       <c r="F427" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G427" s="31"/>
       <c r="H427" s="31"/>
@@ -8955,7 +8958,7 @@
       <c r="D428" s="26"/>
       <c r="E428" s="30"/>
       <c r="F428" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G428" s="31"/>
       <c r="H428" s="31"/>
@@ -8969,7 +8972,7 @@
       <c r="D429" s="26"/>
       <c r="E429" s="30"/>
       <c r="F429" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G429" s="31"/>
       <c r="H429" s="31"/>
@@ -8983,7 +8986,7 @@
       <c r="D430" s="26"/>
       <c r="E430" s="30"/>
       <c r="F430" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G430" s="31"/>
       <c r="H430" s="31"/>
@@ -8997,7 +9000,7 @@
       <c r="D431" s="26"/>
       <c r="E431" s="30"/>
       <c r="F431" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G431" s="31"/>
       <c r="H431" s="31"/>
@@ -9011,7 +9014,7 @@
       <c r="D432" s="26"/>
       <c r="E432" s="30"/>
       <c r="F432" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G432" s="31"/>
       <c r="H432" s="31"/>
@@ -9025,7 +9028,7 @@
       <c r="D433" s="26"/>
       <c r="E433" s="30"/>
       <c r="F433" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G433" s="31"/>
       <c r="H433" s="31"/>
@@ -9039,7 +9042,7 @@
       <c r="D434" s="26"/>
       <c r="E434" s="30"/>
       <c r="F434" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G434" s="31"/>
       <c r="H434" s="31"/>
@@ -9053,7 +9056,7 @@
       <c r="D435" s="26"/>
       <c r="E435" s="30"/>
       <c r="F435" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G435" s="31"/>
       <c r="H435" s="31"/>
@@ -9067,7 +9070,7 @@
       <c r="D436" s="26"/>
       <c r="E436" s="30"/>
       <c r="F436" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G436" s="31"/>
       <c r="H436" s="31"/>
@@ -9081,7 +9084,7 @@
       <c r="D437" s="26"/>
       <c r="E437" s="30"/>
       <c r="F437" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G437" s="31"/>
       <c r="H437" s="31"/>
@@ -9095,7 +9098,7 @@
       <c r="D438" s="26"/>
       <c r="E438" s="30"/>
       <c r="F438" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G438" s="31"/>
       <c r="H438" s="31"/>
@@ -9109,7 +9112,7 @@
       <c r="D439" s="26"/>
       <c r="E439" s="30"/>
       <c r="F439" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G439" s="31"/>
       <c r="H439" s="31"/>
@@ -9123,7 +9126,7 @@
       <c r="D440" s="26"/>
       <c r="E440" s="30"/>
       <c r="F440" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G440" s="31"/>
       <c r="H440" s="31"/>
@@ -9137,7 +9140,7 @@
       <c r="D441" s="26"/>
       <c r="E441" s="30"/>
       <c r="F441" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G441" s="31"/>
       <c r="H441" s="31"/>
@@ -9151,7 +9154,7 @@
       <c r="D442" s="26"/>
       <c r="E442" s="30"/>
       <c r="F442" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G442" s="31"/>
       <c r="H442" s="31"/>
@@ -9165,7 +9168,7 @@
       <c r="D443" s="26"/>
       <c r="E443" s="30"/>
       <c r="F443" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G443" s="31"/>
       <c r="H443" s="31"/>
@@ -9179,7 +9182,7 @@
       <c r="D444" s="26"/>
       <c r="E444" s="30"/>
       <c r="F444" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G444" s="31"/>
       <c r="H444" s="31"/>
@@ -9193,7 +9196,7 @@
       <c r="D445" s="26"/>
       <c r="E445" s="30"/>
       <c r="F445" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G445" s="31"/>
       <c r="H445" s="31"/>
@@ -9207,7 +9210,7 @@
       <c r="D446" s="26"/>
       <c r="E446" s="30"/>
       <c r="F446" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G446" s="31"/>
       <c r="H446" s="31"/>
@@ -9221,7 +9224,7 @@
       <c r="D447" s="26"/>
       <c r="E447" s="30"/>
       <c r="F447" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G447" s="31"/>
       <c r="H447" s="31"/>
@@ -9235,7 +9238,7 @@
       <c r="D448" s="26"/>
       <c r="E448" s="30"/>
       <c r="F448" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G448" s="31"/>
       <c r="H448" s="31"/>
@@ -9249,7 +9252,7 @@
       <c r="D449" s="26"/>
       <c r="E449" s="30"/>
       <c r="F449" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G449" s="31"/>
       <c r="H449" s="31"/>
@@ -9263,7 +9266,7 @@
       <c r="D450" s="26"/>
       <c r="E450" s="30"/>
       <c r="F450" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G450" s="31"/>
       <c r="H450" s="31"/>
@@ -9277,7 +9280,7 @@
       <c r="D451" s="26"/>
       <c r="E451" s="30"/>
       <c r="F451" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G451" s="31"/>
       <c r="H451" s="31"/>
@@ -9291,7 +9294,7 @@
       <c r="D452" s="26"/>
       <c r="E452" s="30"/>
       <c r="F452" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G452" s="31"/>
       <c r="H452" s="31"/>
@@ -9305,7 +9308,7 @@
       <c r="D453" s="26"/>
       <c r="E453" s="30"/>
       <c r="F453" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G453" s="31"/>
       <c r="H453" s="31"/>
@@ -9319,7 +9322,7 @@
       <c r="D454" s="26"/>
       <c r="E454" s="30"/>
       <c r="F454" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G454" s="31"/>
       <c r="H454" s="31"/>
@@ -9333,7 +9336,7 @@
       <c r="D455" s="26"/>
       <c r="E455" s="30"/>
       <c r="F455" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G455" s="31"/>
       <c r="H455" s="31"/>
@@ -9347,7 +9350,7 @@
       <c r="D456" s="26"/>
       <c r="E456" s="30"/>
       <c r="F456" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G456" s="31"/>
       <c r="H456" s="31"/>
@@ -9361,7 +9364,7 @@
       <c r="D457" s="26"/>
       <c r="E457" s="30"/>
       <c r="F457" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G457" s="31"/>
       <c r="H457" s="31"/>
@@ -9375,7 +9378,7 @@
       <c r="D458" s="26"/>
       <c r="E458" s="30"/>
       <c r="F458" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G458" s="31"/>
       <c r="H458" s="31"/>
@@ -9389,7 +9392,7 @@
       <c r="D459" s="26"/>
       <c r="E459" s="30"/>
       <c r="F459" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G459" s="31"/>
       <c r="H459" s="31"/>
@@ -9403,7 +9406,7 @@
       <c r="D460" s="26"/>
       <c r="E460" s="30"/>
       <c r="F460" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G460" s="31"/>
       <c r="H460" s="31"/>
@@ -9417,7 +9420,7 @@
       <c r="D461" s="26"/>
       <c r="E461" s="30"/>
       <c r="F461" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G461" s="31"/>
       <c r="H461" s="31"/>
@@ -9431,7 +9434,7 @@
       <c r="D462" s="26"/>
       <c r="E462" s="30"/>
       <c r="F462" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G462" s="31"/>
       <c r="H462" s="31"/>
@@ -9445,7 +9448,7 @@
       <c r="D463" s="26"/>
       <c r="E463" s="30"/>
       <c r="F463" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G463" s="31"/>
       <c r="H463" s="31"/>
@@ -9459,7 +9462,7 @@
       <c r="D464" s="26"/>
       <c r="E464" s="30"/>
       <c r="F464" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G464" s="31"/>
       <c r="H464" s="31"/>
@@ -9473,7 +9476,7 @@
       <c r="D465" s="26"/>
       <c r="E465" s="30"/>
       <c r="F465" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G465" s="31"/>
       <c r="H465" s="31"/>
@@ -9487,7 +9490,7 @@
       <c r="D466" s="26"/>
       <c r="E466" s="30"/>
       <c r="F466" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G466" s="31"/>
       <c r="H466" s="31"/>
@@ -9501,7 +9504,7 @@
       <c r="D467" s="26"/>
       <c r="E467" s="30"/>
       <c r="F467" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G467" s="31"/>
       <c r="H467" s="31"/>
@@ -9515,7 +9518,7 @@
       <c r="D468" s="26"/>
       <c r="E468" s="30"/>
       <c r="F468" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G468" s="31"/>
       <c r="H468" s="31"/>
@@ -9529,7 +9532,7 @@
       <c r="D469" s="26"/>
       <c r="E469" s="30"/>
       <c r="F469" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G469" s="31"/>
       <c r="H469" s="31"/>
@@ -9543,7 +9546,7 @@
       <c r="D470" s="26"/>
       <c r="E470" s="30"/>
       <c r="F470" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G470" s="31"/>
       <c r="H470" s="31"/>
@@ -9557,7 +9560,7 @@
       <c r="D471" s="26"/>
       <c r="E471" s="30"/>
       <c r="F471" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G471" s="31"/>
       <c r="H471" s="31"/>
@@ -9571,7 +9574,7 @@
       <c r="D472" s="26"/>
       <c r="E472" s="30"/>
       <c r="F472" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G472" s="31"/>
       <c r="H472" s="31"/>
@@ -9585,7 +9588,7 @@
       <c r="D473" s="26"/>
       <c r="E473" s="30"/>
       <c r="F473" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G473" s="31"/>
       <c r="H473" s="31"/>
@@ -9599,7 +9602,7 @@
       <c r="D474" s="26"/>
       <c r="E474" s="30"/>
       <c r="F474" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G474" s="31"/>
       <c r="H474" s="31"/>
@@ -9613,7 +9616,7 @@
       <c r="D475" s="26"/>
       <c r="E475" s="30"/>
       <c r="F475" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G475" s="31"/>
       <c r="H475" s="31"/>
@@ -9627,7 +9630,7 @@
       <c r="D476" s="26"/>
       <c r="E476" s="30"/>
       <c r="F476" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G476" s="31"/>
       <c r="H476" s="31"/>
@@ -9641,7 +9644,7 @@
       <c r="D477" s="26"/>
       <c r="E477" s="30"/>
       <c r="F477" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G477" s="31"/>
       <c r="H477" s="31"/>
@@ -9655,7 +9658,7 @@
       <c r="D478" s="26"/>
       <c r="E478" s="30"/>
       <c r="F478" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G478" s="31"/>
       <c r="H478" s="31"/>
@@ -9669,7 +9672,7 @@
       <c r="D479" s="26"/>
       <c r="E479" s="30"/>
       <c r="F479" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G479" s="31"/>
       <c r="H479" s="31"/>
@@ -9683,7 +9686,7 @@
       <c r="D480" s="26"/>
       <c r="E480" s="30"/>
       <c r="F480" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G480" s="31"/>
       <c r="H480" s="31"/>
@@ -9697,7 +9700,7 @@
       <c r="D481" s="26"/>
       <c r="E481" s="30"/>
       <c r="F481" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G481" s="31"/>
       <c r="H481" s="31"/>
@@ -9711,7 +9714,7 @@
       <c r="D482" s="26"/>
       <c r="E482" s="30"/>
       <c r="F482" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G482" s="31"/>
       <c r="H482" s="31"/>
@@ -9725,7 +9728,7 @@
       <c r="D483" s="26"/>
       <c r="E483" s="30"/>
       <c r="F483" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G483" s="31"/>
       <c r="H483" s="31"/>
@@ -9739,7 +9742,7 @@
       <c r="D484" s="26"/>
       <c r="E484" s="30"/>
       <c r="F484" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G484" s="31"/>
       <c r="H484" s="31"/>
@@ -9753,7 +9756,7 @@
       <c r="D485" s="26"/>
       <c r="E485" s="30"/>
       <c r="F485" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G485" s="31"/>
       <c r="H485" s="31"/>
@@ -9767,7 +9770,7 @@
       <c r="D486" s="26"/>
       <c r="E486" s="30"/>
       <c r="F486" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G486" s="31"/>
       <c r="H486" s="31"/>
@@ -9781,7 +9784,7 @@
       <c r="D487" s="26"/>
       <c r="E487" s="30"/>
       <c r="F487" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G487" s="31"/>
       <c r="H487" s="31"/>
@@ -9795,7 +9798,7 @@
       <c r="D488" s="26"/>
       <c r="E488" s="30"/>
       <c r="F488" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G488" s="31"/>
       <c r="H488" s="31"/>
@@ -9809,7 +9812,7 @@
       <c r="D489" s="26"/>
       <c r="E489" s="30"/>
       <c r="F489" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G489" s="31"/>
       <c r="H489" s="31"/>
@@ -9823,7 +9826,7 @@
       <c r="D490" s="26"/>
       <c r="E490" s="30"/>
       <c r="F490" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G490" s="31"/>
       <c r="H490" s="31"/>
@@ -9837,7 +9840,7 @@
       <c r="D491" s="26"/>
       <c r="E491" s="30"/>
       <c r="F491" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G491" s="31"/>
       <c r="H491" s="31"/>
@@ -9851,7 +9854,7 @@
       <c r="D492" s="26"/>
       <c r="E492" s="30"/>
       <c r="F492" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G492" s="31"/>
       <c r="H492" s="31"/>
@@ -9865,7 +9868,7 @@
       <c r="D493" s="26"/>
       <c r="E493" s="30"/>
       <c r="F493" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G493" s="31"/>
       <c r="H493" s="31"/>
@@ -9879,7 +9882,7 @@
       <c r="D494" s="26"/>
       <c r="E494" s="30"/>
       <c r="F494" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G494" s="31"/>
       <c r="H494" s="31"/>
@@ -9893,7 +9896,7 @@
       <c r="D495" s="26"/>
       <c r="E495" s="30"/>
       <c r="F495" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G495" s="31"/>
       <c r="H495" s="31"/>
@@ -9907,7 +9910,7 @@
       <c r="D496" s="26"/>
       <c r="E496" s="30"/>
       <c r="F496" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G496" s="31"/>
       <c r="H496" s="31"/>
@@ -9921,7 +9924,7 @@
       <c r="D497" s="26"/>
       <c r="E497" s="30"/>
       <c r="F497" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G497" s="31"/>
       <c r="H497" s="31"/>
@@ -9935,7 +9938,7 @@
       <c r="D498" s="26"/>
       <c r="E498" s="30"/>
       <c r="F498" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G498" s="31"/>
       <c r="H498" s="31"/>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -899,7 +899,7 @@
       </c>
       <c r="C2" s="6" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-09-21 00:52</v>
+        <v>Plan de Proyecto: 2026-09-21 00:59</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>14</v>
@@ -3835,8 +3835,12 @@
       </c>
       <c r="E59" s="7"/>
       <c r="F59" s="7"/>
-      <c r="G59" s="8"/>
-      <c r="H59" s="8"/>
+      <c r="G59" s="8">
+        <v>46291.0</v>
+      </c>
+      <c r="H59" s="8">
+        <v>46294.0</v>
+      </c>
       <c r="I59" s="8"/>
       <c r="J59" s="9"/>
       <c r="K59" s="9"/>
@@ -3876,8 +3880,12 @@
       </c>
       <c r="E60" s="7"/>
       <c r="F60" s="7"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="8"/>
+      <c r="G60" s="8">
+        <v>46291.0</v>
+      </c>
+      <c r="H60" s="8">
+        <v>46294.0</v>
+      </c>
       <c r="I60" s="8"/>
       <c r="J60" s="9"/>
       <c r="K60" s="9"/>
@@ -3917,8 +3925,12 @@
       </c>
       <c r="E61" s="7"/>
       <c r="F61" s="7"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="8"/>
+      <c r="G61" s="8">
+        <v>46291.0</v>
+      </c>
+      <c r="H61" s="8">
+        <v>46294.0</v>
+      </c>
       <c r="I61" s="8"/>
       <c r="J61" s="9"/>
       <c r="K61" s="9"/>
@@ -3958,8 +3970,12 @@
       </c>
       <c r="E62" s="7"/>
       <c r="F62" s="7"/>
-      <c r="G62" s="8"/>
-      <c r="H62" s="8"/>
+      <c r="G62" s="8">
+        <v>46291.0</v>
+      </c>
+      <c r="H62" s="8">
+        <v>46294.0</v>
+      </c>
       <c r="I62" s="8"/>
       <c r="J62" s="9"/>
       <c r="K62" s="9"/>
@@ -3999,8 +4015,12 @@
       </c>
       <c r="E63" s="7"/>
       <c r="F63" s="7"/>
-      <c r="G63" s="8"/>
-      <c r="H63" s="8"/>
+      <c r="G63" s="8">
+        <v>46291.0</v>
+      </c>
+      <c r="H63" s="8">
+        <v>46294.0</v>
+      </c>
       <c r="I63" s="8"/>
       <c r="J63" s="9"/>
       <c r="K63" s="9"/>
@@ -4040,8 +4060,12 @@
       </c>
       <c r="E64" s="7"/>
       <c r="F64" s="7"/>
-      <c r="G64" s="8"/>
-      <c r="H64" s="8"/>
+      <c r="G64" s="8">
+        <v>46291.0</v>
+      </c>
+      <c r="H64" s="8">
+        <v>46294.0</v>
+      </c>
       <c r="I64" s="8"/>
       <c r="J64" s="9"/>
       <c r="K64" s="9"/>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="117">
   <si>
     <t>Etapa</t>
   </si>
@@ -243,6 +243,12 @@
   </si>
   <si>
     <t>Revisar Doc Descripcion del Sistema</t>
+  </si>
+  <si>
+    <t>Reorganizar Doc Descripcion del Sistema</t>
+  </si>
+  <si>
+    <t>Rearmar y completar Funcionalidades del Sistema</t>
   </si>
   <si>
     <t>RNOF Perfil Cliente</t>
@@ -910,7 +916,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-09-21 01:27</v>
+        <v>Plan de Proyecto: 2026-09-21 15:31</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>
@@ -2727,7 +2733,7 @@
         <v>65</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E36" s="8" t="s">
         <v>66</v>
@@ -2837,7 +2843,7 @@
         <v>46283.0</v>
       </c>
       <c r="H38" s="9">
-        <v>46285.0</v>
+        <v>46286.0</v>
       </c>
       <c r="I38" s="9"/>
       <c r="J38" s="12"/>
@@ -2884,7 +2890,7 @@
         <v>46283.0</v>
       </c>
       <c r="H39" s="9">
-        <v>46285.0</v>
+        <v>46286.0</v>
       </c>
       <c r="I39" s="9"/>
       <c r="J39" s="10"/>
@@ -2931,7 +2937,7 @@
         <v>46283.0</v>
       </c>
       <c r="H40" s="9">
-        <v>46285.0</v>
+        <v>46286.0</v>
       </c>
       <c r="I40" s="9"/>
       <c r="J40" s="12"/>
@@ -3170,7 +3176,7 @@
         <v>76</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E45" s="8" t="s">
         <v>66</v>
@@ -3216,20 +3222,22 @@
         <v>58</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E46" s="8"/>
+        <v>14</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>66</v>
+      </c>
       <c r="F46" s="8" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="G46" s="9">
-        <v>46288.0</v>
+        <v>46286.0</v>
       </c>
       <c r="H46" s="9">
-        <v>46289.0</v>
+        <v>46287.0</v>
       </c>
       <c r="I46" s="9"/>
       <c r="J46" s="10"/>
@@ -3263,29 +3271,25 @@
         <v>58</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>66</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="E47" s="8"/>
       <c r="F47" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G47" s="9">
-        <v>46284.0</v>
+        <v>46286.0</v>
       </c>
       <c r="H47" s="9">
-        <v>46289.0</v>
-      </c>
-      <c r="I47" s="9">
-        <v>46285.0</v>
-      </c>
-      <c r="J47" s="12"/>
-      <c r="K47" s="15"/>
-      <c r="L47" s="15"/>
+        <v>46288.0</v>
+      </c>
+      <c r="I47" s="9"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10"/>
       <c r="M47" s="11"/>
       <c r="N47" s="11"/>
       <c r="O47" s="11"/>
@@ -3314,16 +3318,14 @@
         <v>58</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="D48" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E48" s="8" t="s">
-        <v>39</v>
-      </c>
+      <c r="E48" s="8"/>
       <c r="F48" s="8" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="G48" s="9">
         <v>46288.0</v>
@@ -3362,26 +3364,30 @@
       <c r="B49" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C49" s="7" t="s">
         <v>79</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E49" s="8"/>
+        <v>14</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>66</v>
+      </c>
       <c r="F49" s="8" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G49" s="9">
-        <v>46288.0</v>
+        <v>46284.0</v>
       </c>
       <c r="H49" s="9">
         <v>46289.0</v>
       </c>
-      <c r="I49" s="9"/>
+      <c r="I49" s="9">
+        <v>46285.0</v>
+      </c>
       <c r="J49" s="12"/>
-      <c r="K49" s="10"/>
-      <c r="L49" s="10"/>
+      <c r="K49" s="15"/>
+      <c r="L49" s="15"/>
       <c r="M49" s="11"/>
       <c r="N49" s="11"/>
       <c r="O49" s="11"/>
@@ -3407,23 +3413,25 @@
         <v>25</v>
       </c>
       <c r="B50" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C50" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>81</v>
       </c>
       <c r="D50" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E50" s="8"/>
+      <c r="E50" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="F50" s="8" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="G50" s="9">
-        <v>46291.0</v>
+        <v>46288.0</v>
       </c>
       <c r="H50" s="9">
-        <v>46294.0</v>
+        <v>46289.0</v>
       </c>
       <c r="I50" s="9"/>
       <c r="J50" s="10"/>
@@ -3457,7 +3465,7 @@
         <v>58</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>72</v>
@@ -3501,7 +3509,7 @@
         <v>25</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>83</v>
@@ -3511,13 +3519,13 @@
       </c>
       <c r="E52" s="8"/>
       <c r="F52" s="8" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G52" s="9">
-        <v>46288.0</v>
+        <v>46291.0</v>
       </c>
       <c r="H52" s="9">
-        <v>46289.0</v>
+        <v>46294.0</v>
       </c>
       <c r="I52" s="9"/>
       <c r="J52" s="10"/>
@@ -3550,7 +3558,7 @@
       <c r="B53" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="16" t="s">
         <v>84</v>
       </c>
       <c r="D53" s="8" t="s">
@@ -3558,16 +3566,16 @@
       </c>
       <c r="E53" s="8"/>
       <c r="F53" s="8" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G53" s="9">
+        <v>46288.0</v>
+      </c>
+      <c r="H53" s="9">
         <v>46289.0</v>
       </c>
-      <c r="H53" s="9">
-        <v>46290.0</v>
-      </c>
       <c r="I53" s="9"/>
-      <c r="J53" s="10"/>
+      <c r="J53" s="12"/>
       <c r="K53" s="10"/>
       <c r="L53" s="10"/>
       <c r="M53" s="11"/>
@@ -3605,13 +3613,13 @@
       </c>
       <c r="E54" s="8"/>
       <c r="F54" s="8" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G54" s="9">
+        <v>46288.0</v>
+      </c>
+      <c r="H54" s="9">
         <v>46289.0</v>
-      </c>
-      <c r="H54" s="9">
-        <v>46290.0</v>
       </c>
       <c r="I54" s="9"/>
       <c r="J54" s="10"/>
@@ -3642,22 +3650,20 @@
         <v>25</v>
       </c>
       <c r="B55" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C55" s="7" t="s">
         <v>86</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>87</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E55" s="8" t="s">
-        <v>39</v>
-      </c>
+      <c r="E55" s="8"/>
       <c r="F55" s="8" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G55" s="9">
-        <v>46290.0</v>
+        <v>46289.0</v>
       </c>
       <c r="H55" s="9">
         <v>46290.0</v>
@@ -3691,28 +3697,26 @@
         <v>25</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D56" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E56" s="8" t="s">
-        <v>39</v>
-      </c>
+      <c r="E56" s="8"/>
       <c r="F56" s="8" t="s">
         <v>32</v>
       </c>
       <c r="G56" s="9">
-        <v>46288.0</v>
+        <v>46289.0</v>
       </c>
       <c r="H56" s="9">
-        <v>46291.0</v>
+        <v>46290.0</v>
       </c>
       <c r="I56" s="9"/>
-      <c r="J56" s="12"/>
+      <c r="J56" s="10"/>
       <c r="K56" s="10"/>
       <c r="L56" s="10"/>
       <c r="M56" s="11"/>
@@ -3740,23 +3744,25 @@
         <v>25</v>
       </c>
       <c r="B57" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C57" s="7" t="s">
         <v>89</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>90</v>
       </c>
       <c r="D57" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E57" s="8"/>
+      <c r="E57" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="F57" s="8" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G57" s="9">
-        <v>46291.0</v>
+        <v>46290.0</v>
       </c>
       <c r="H57" s="9">
-        <v>46292.0</v>
+        <v>46290.0</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="10"/>
@@ -3787,10 +3793,10 @@
         <v>25</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>72</v>
@@ -3799,16 +3805,16 @@
         <v>39</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G58" s="9">
+        <v>46288.0</v>
+      </c>
+      <c r="H58" s="9">
         <v>46291.0</v>
       </c>
-      <c r="H58" s="9">
-        <v>46292.0</v>
-      </c>
       <c r="I58" s="9"/>
-      <c r="J58" s="10"/>
+      <c r="J58" s="12"/>
       <c r="K58" s="10"/>
       <c r="L58" s="10"/>
       <c r="M58" s="11"/>
@@ -3839,7 +3845,7 @@
         <v>91</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>72</v>
@@ -3883,7 +3889,7 @@
         <v>25</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>94</v>
@@ -3891,7 +3897,9 @@
       <c r="D60" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E60" s="8"/>
+      <c r="E60" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="F60" s="8" t="s">
         <v>16</v>
       </c>
@@ -3899,7 +3907,7 @@
         <v>46291.0</v>
       </c>
       <c r="H60" s="9">
-        <v>46294.0</v>
+        <v>46292.0</v>
       </c>
       <c r="I60" s="9"/>
       <c r="J60" s="10"/>
@@ -3930,7 +3938,7 @@
         <v>25</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>95</v>
@@ -3940,13 +3948,13 @@
       </c>
       <c r="E61" s="8"/>
       <c r="F61" s="8" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="G61" s="9">
         <v>46291.0</v>
       </c>
       <c r="H61" s="9">
-        <v>46294.0</v>
+        <v>46292.0</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="10"/>
@@ -3977,7 +3985,7 @@
         <v>25</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>96</v>
@@ -3987,7 +3995,7 @@
       </c>
       <c r="E62" s="8"/>
       <c r="F62" s="8" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G62" s="9">
         <v>46291.0</v>
@@ -4024,7 +4032,7 @@
         <v>25</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>97</v>
@@ -4071,7 +4079,7 @@
         <v>25</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C64" s="7" t="s">
         <v>98</v>
@@ -4118,7 +4126,7 @@
         <v>25</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>99</v>
@@ -4128,7 +4136,7 @@
       </c>
       <c r="E65" s="8"/>
       <c r="F65" s="8" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="G65" s="9">
         <v>46291.0</v>
@@ -4162,34 +4170,30 @@
     </row>
     <row r="66" ht="29.25" customHeight="1">
       <c r="A66" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C66" s="7" t="s">
         <v>100</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>102</v>
       </c>
       <c r="D66" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E66" s="8" t="s">
-        <v>39</v>
-      </c>
+      <c r="E66" s="8"/>
       <c r="F66" s="8" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G66" s="9">
-        <v>46289.0</v>
+        <v>46291.0</v>
       </c>
       <c r="H66" s="9">
-        <v>46289.0</v>
+        <v>46294.0</v>
       </c>
       <c r="I66" s="9"/>
       <c r="J66" s="10"/>
-      <c r="K66" s="10" t="s">
-        <v>103</v>
-      </c>
+      <c r="K66" s="10"/>
       <c r="L66" s="10"/>
       <c r="M66" s="11"/>
       <c r="N66" s="11"/>
@@ -4213,34 +4217,30 @@
     </row>
     <row r="67" ht="29.25" customHeight="1">
       <c r="A67" s="5" t="s">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="B67" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C67" s="7" t="s">
         <v>101</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>102</v>
       </c>
       <c r="D67" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E67" s="8" t="s">
-        <v>39</v>
-      </c>
+      <c r="E67" s="8"/>
       <c r="F67" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G67" s="9">
-        <v>46289.0</v>
+        <v>46291.0</v>
       </c>
       <c r="H67" s="9">
-        <v>46289.0</v>
+        <v>46294.0</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="10"/>
-      <c r="K67" s="10" t="s">
-        <v>103</v>
-      </c>
+      <c r="K67" s="10"/>
       <c r="L67" s="10"/>
       <c r="M67" s="11"/>
       <c r="N67" s="11"/>
@@ -4264,18 +4264,20 @@
     </row>
     <row r="68" ht="29.25" customHeight="1">
       <c r="A68" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B68" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C68" s="7" t="s">
         <v>104</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>105</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E68" s="8"/>
+      <c r="E68" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="F68" s="8" t="s">
         <v>32</v>
       </c>
@@ -4287,7 +4289,9 @@
       </c>
       <c r="I68" s="9"/>
       <c r="J68" s="10"/>
-      <c r="K68" s="10"/>
+      <c r="K68" s="10" t="s">
+        <v>105</v>
+      </c>
       <c r="L68" s="10"/>
       <c r="M68" s="11"/>
       <c r="N68" s="11"/>
@@ -4311,13 +4315,13 @@
     </row>
     <row r="69" ht="29.25" customHeight="1">
       <c r="A69" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>72</v>
@@ -4326,17 +4330,19 @@
         <v>39</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="G69" s="9">
-        <v>46286.0</v>
+        <v>46289.0</v>
       </c>
       <c r="H69" s="9">
-        <v>46293.0</v>
+        <v>46289.0</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="10"/>
-      <c r="K69" s="10"/>
+      <c r="K69" s="10" t="s">
+        <v>105</v>
+      </c>
       <c r="L69" s="10"/>
       <c r="M69" s="11"/>
       <c r="N69" s="11"/>
@@ -4360,10 +4366,10 @@
     </row>
     <row r="70" ht="29.25" customHeight="1">
       <c r="A70" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C70" s="7" t="s">
         <v>107</v>
@@ -4373,13 +4379,13 @@
       </c>
       <c r="E70" s="8"/>
       <c r="F70" s="8" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G70" s="9">
-        <v>46287.0</v>
+        <v>46289.0</v>
       </c>
       <c r="H70" s="9">
-        <v>46295.0</v>
+        <v>46289.0</v>
       </c>
       <c r="I70" s="9"/>
       <c r="J70" s="10"/>
@@ -4407,7 +4413,7 @@
     </row>
     <row r="71" ht="29.25" customHeight="1">
       <c r="A71" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>108</v>
@@ -4418,12 +4424,14 @@
       <c r="D71" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E71" s="8"/>
+      <c r="E71" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="F71" s="8" t="s">
         <v>39</v>
       </c>
       <c r="G71" s="9">
-        <v>46287.0</v>
+        <v>46286.0</v>
       </c>
       <c r="H71" s="9">
         <v>46293.0</v>
@@ -4454,13 +4462,13 @@
     </row>
     <row r="72" ht="29.25" customHeight="1">
       <c r="A72" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>109</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D72" s="8" t="s">
         <v>72</v>
@@ -4470,10 +4478,10 @@
         <v>39</v>
       </c>
       <c r="G72" s="9">
-        <v>46296.0</v>
+        <v>46287.0</v>
       </c>
       <c r="H72" s="9">
-        <v>46303.0</v>
+        <v>46295.0</v>
       </c>
       <c r="I72" s="9"/>
       <c r="J72" s="10"/>
@@ -4501,24 +4509,26 @@
     </row>
     <row r="73" ht="29.25" customHeight="1">
       <c r="A73" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="D73" s="8"/>
+        <v>110</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>72</v>
+      </c>
       <c r="E73" s="8"/>
       <c r="F73" s="8" t="s">
         <v>39</v>
       </c>
       <c r="G73" s="9">
-        <v>46303.0</v>
+        <v>46287.0</v>
       </c>
       <c r="H73" s="9">
-        <v>46303.0</v>
+        <v>46293.0</v>
       </c>
       <c r="I73" s="9"/>
       <c r="J73" s="10"/>
@@ -4546,13 +4556,13 @@
     </row>
     <row r="74" ht="29.25" customHeight="1">
       <c r="A74" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D74" s="8" t="s">
         <v>72</v>
@@ -4562,10 +4572,10 @@
         <v>39</v>
       </c>
       <c r="G74" s="9">
-        <v>46305.0</v>
+        <v>46296.0</v>
       </c>
       <c r="H74" s="9">
-        <v>46305.0</v>
+        <v>46303.0</v>
       </c>
       <c r="I74" s="9"/>
       <c r="J74" s="10"/>
@@ -4592,20 +4602,30 @@
       <c r="AE74" s="11"/>
     </row>
     <row r="75" ht="29.25" customHeight="1">
-      <c r="A75" s="17"/>
-      <c r="B75" s="7"/>
-      <c r="C75" s="18"/>
-      <c r="D75" s="19"/>
-      <c r="E75" s="15"/>
-      <c r="F75" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="G75" s="21"/>
-      <c r="H75" s="21"/>
-      <c r="I75" s="21"/>
-      <c r="J75" s="12"/>
-      <c r="K75" s="15"/>
-      <c r="L75" s="15"/>
+      <c r="A75" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D75" s="8"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G75" s="9">
+        <v>46303.0</v>
+      </c>
+      <c r="H75" s="9">
+        <v>46303.0</v>
+      </c>
+      <c r="I75" s="9"/>
+      <c r="J75" s="10"/>
+      <c r="K75" s="10"/>
+      <c r="L75" s="10"/>
       <c r="M75" s="11"/>
       <c r="N75" s="11"/>
       <c r="O75" s="11"/>
@@ -4627,20 +4647,32 @@
       <c r="AE75" s="11"/>
     </row>
     <row r="76" ht="29.25" customHeight="1">
-      <c r="A76" s="17"/>
-      <c r="B76" s="7"/>
-      <c r="C76" s="18"/>
-      <c r="D76" s="19"/>
-      <c r="E76" s="15"/>
-      <c r="F76" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="G76" s="21"/>
-      <c r="H76" s="21"/>
-      <c r="I76" s="21"/>
-      <c r="J76" s="12"/>
-      <c r="K76" s="15"/>
-      <c r="L76" s="15"/>
+      <c r="A76" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G76" s="9">
+        <v>46305.0</v>
+      </c>
+      <c r="H76" s="9">
+        <v>46305.0</v>
+      </c>
+      <c r="I76" s="9"/>
+      <c r="J76" s="10"/>
+      <c r="K76" s="10"/>
+      <c r="L76" s="10"/>
       <c r="M76" s="11"/>
       <c r="N76" s="11"/>
       <c r="O76" s="11"/>
@@ -4769,18 +4801,18 @@
     <row r="80" ht="29.25" customHeight="1">
       <c r="A80" s="17"/>
       <c r="B80" s="7"/>
-      <c r="C80" s="22"/>
+      <c r="C80" s="18"/>
       <c r="D80" s="19"/>
-      <c r="E80" s="11"/>
+      <c r="E80" s="15"/>
       <c r="F80" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G80" s="23"/>
-      <c r="H80" s="23"/>
-      <c r="I80" s="23"/>
+      <c r="G80" s="21"/>
+      <c r="H80" s="21"/>
+      <c r="I80" s="21"/>
       <c r="J80" s="12"/>
-      <c r="K80" s="11"/>
-      <c r="L80" s="11"/>
+      <c r="K80" s="15"/>
+      <c r="L80" s="15"/>
       <c r="M80" s="11"/>
       <c r="N80" s="11"/>
       <c r="O80" s="11"/>
@@ -4802,20 +4834,20 @@
       <c r="AE80" s="11"/>
     </row>
     <row r="81" ht="29.25" customHeight="1">
-      <c r="A81" s="24"/>
-      <c r="B81" s="22"/>
-      <c r="C81" s="22"/>
+      <c r="A81" s="17"/>
+      <c r="B81" s="7"/>
+      <c r="C81" s="18"/>
       <c r="D81" s="19"/>
-      <c r="E81" s="11"/>
+      <c r="E81" s="15"/>
       <c r="F81" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G81" s="23"/>
-      <c r="H81" s="23"/>
-      <c r="I81" s="23"/>
+      <c r="G81" s="21"/>
+      <c r="H81" s="21"/>
+      <c r="I81" s="21"/>
       <c r="J81" s="12"/>
-      <c r="K81" s="11"/>
-      <c r="L81" s="11"/>
+      <c r="K81" s="15"/>
+      <c r="L81" s="15"/>
       <c r="M81" s="11"/>
       <c r="N81" s="11"/>
       <c r="O81" s="11"/>
@@ -4837,8 +4869,8 @@
       <c r="AE81" s="11"/>
     </row>
     <row r="82" ht="29.25" customHeight="1">
-      <c r="A82" s="24"/>
-      <c r="B82" s="22"/>
+      <c r="A82" s="17"/>
+      <c r="B82" s="7"/>
       <c r="C82" s="22"/>
       <c r="D82" s="19"/>
       <c r="E82" s="11"/>
@@ -5129,6 +5161,27 @@
       <c r="H90" s="23"/>
       <c r="I90" s="23"/>
       <c r="J90" s="12"/>
+      <c r="K90" s="11"/>
+      <c r="L90" s="11"/>
+      <c r="M90" s="11"/>
+      <c r="N90" s="11"/>
+      <c r="O90" s="11"/>
+      <c r="P90" s="11"/>
+      <c r="Q90" s="11"/>
+      <c r="R90" s="11"/>
+      <c r="S90" s="11"/>
+      <c r="T90" s="11"/>
+      <c r="U90" s="11"/>
+      <c r="V90" s="11"/>
+      <c r="W90" s="11"/>
+      <c r="X90" s="11"/>
+      <c r="Y90" s="11"/>
+      <c r="Z90" s="11"/>
+      <c r="AA90" s="11"/>
+      <c r="AB90" s="11"/>
+      <c r="AC90" s="11"/>
+      <c r="AD90" s="11"/>
+      <c r="AE90" s="11"/>
     </row>
     <row r="91" ht="29.25" customHeight="1">
       <c r="A91" s="24"/>
@@ -5143,6 +5196,27 @@
       <c r="H91" s="23"/>
       <c r="I91" s="23"/>
       <c r="J91" s="12"/>
+      <c r="K91" s="11"/>
+      <c r="L91" s="11"/>
+      <c r="M91" s="11"/>
+      <c r="N91" s="11"/>
+      <c r="O91" s="11"/>
+      <c r="P91" s="11"/>
+      <c r="Q91" s="11"/>
+      <c r="R91" s="11"/>
+      <c r="S91" s="11"/>
+      <c r="T91" s="11"/>
+      <c r="U91" s="11"/>
+      <c r="V91" s="11"/>
+      <c r="W91" s="11"/>
+      <c r="X91" s="11"/>
+      <c r="Y91" s="11"/>
+      <c r="Z91" s="11"/>
+      <c r="AA91" s="11"/>
+      <c r="AB91" s="11"/>
+      <c r="AC91" s="11"/>
+      <c r="AD91" s="11"/>
+      <c r="AE91" s="11"/>
     </row>
     <row r="92" ht="29.25" customHeight="1">
       <c r="A92" s="24"/>
@@ -5968,7 +6042,7 @@
       <c r="G150" s="23"/>
       <c r="H150" s="23"/>
       <c r="I150" s="23"/>
-      <c r="J150" s="25"/>
+      <c r="J150" s="12"/>
     </row>
     <row r="151" ht="29.25" customHeight="1">
       <c r="A151" s="24"/>
@@ -5982,7 +6056,7 @@
       <c r="G151" s="23"/>
       <c r="H151" s="23"/>
       <c r="I151" s="23"/>
-      <c r="J151" s="25"/>
+      <c r="J151" s="12"/>
     </row>
     <row r="152" ht="29.25" customHeight="1">
       <c r="A152" s="24"/>
@@ -10832,8 +10906,11 @@
       <c r="A498" s="24"/>
       <c r="B498" s="22"/>
       <c r="C498" s="22"/>
+      <c r="D498" s="19"/>
       <c r="E498" s="11"/>
-      <c r="F498" s="11"/>
+      <c r="F498" s="20" t="s">
+        <v>39</v>
+      </c>
       <c r="G498" s="23"/>
       <c r="H498" s="23"/>
       <c r="I498" s="23"/>
@@ -10843,8 +10920,11 @@
       <c r="A499" s="24"/>
       <c r="B499" s="22"/>
       <c r="C499" s="22"/>
+      <c r="D499" s="19"/>
       <c r="E499" s="11"/>
-      <c r="F499" s="11"/>
+      <c r="F499" s="20" t="s">
+        <v>39</v>
+      </c>
       <c r="G499" s="23"/>
       <c r="H499" s="23"/>
       <c r="I499" s="23"/>
@@ -16955,75 +17035,97 @@
       <c r="I1054" s="23"/>
       <c r="J1054" s="25"/>
     </row>
+    <row r="1055" ht="29.25" customHeight="1">
+      <c r="A1055" s="24"/>
+      <c r="B1055" s="22"/>
+      <c r="C1055" s="22"/>
+      <c r="E1055" s="11"/>
+      <c r="F1055" s="11"/>
+      <c r="G1055" s="23"/>
+      <c r="H1055" s="23"/>
+      <c r="I1055" s="23"/>
+      <c r="J1055" s="25"/>
+    </row>
+    <row r="1056" ht="29.25" customHeight="1">
+      <c r="A1056" s="24"/>
+      <c r="B1056" s="22"/>
+      <c r="C1056" s="22"/>
+      <c r="E1056" s="11"/>
+      <c r="F1056" s="11"/>
+      <c r="G1056" s="23"/>
+      <c r="H1056" s="23"/>
+      <c r="I1056" s="23"/>
+      <c r="J1056" s="25"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D74">
+  <conditionalFormatting sqref="D2:D76">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Finalizada">
       <formula>NOT(ISERROR(SEARCH(("Finalizada"),(D2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D74">
+  <conditionalFormatting sqref="D2:D76">
     <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="En Proceso">
       <formula>NOT(ISERROR(SEARCH(("En Proceso"),(D2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D74">
+  <conditionalFormatting sqref="D2:D76">
     <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Pendiente de Revision">
       <formula>NOT(ISERROR(SEARCH(("Pendiente de Revision"),(D2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J1054">
+  <conditionalFormatting sqref="J2:J1056">
     <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="SI">
       <formula>NOT(ISERROR(SEARCH(("SI"),(J2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E1054">
+  <conditionalFormatting sqref="E2:E1056">
     <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Validado">
       <formula>NOT(ISERROR(SEARCH(("Validado"),(E2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E1054">
+  <conditionalFormatting sqref="E2:E1056">
     <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="Revision">
       <formula>NOT(ISERROR(SEARCH(("Revision"),(E2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E99">
+  <conditionalFormatting sqref="E2:E101">
     <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="Reasignado">
       <formula>NOT(ISERROR(SEARCH(("Reasignado"),(E2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1054">
+  <conditionalFormatting sqref="F1:F1056">
     <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="Gabriel">
       <formula>NOT(ISERROR(SEARCH(("Gabriel"),(F1))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1054">
+  <conditionalFormatting sqref="F1:F1056">
     <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
       <formula>"Lucia"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1054">
+  <conditionalFormatting sqref="F1:F1056">
     <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
       <formula>"Luciano"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1054">
+  <conditionalFormatting sqref="F1:F1056">
     <cfRule type="cellIs" dxfId="4" priority="11" operator="equal">
       <formula>"Ignacio"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:AE89">
+  <conditionalFormatting sqref="A2:AE91">
     <cfRule type="expression" dxfId="9" priority="12">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D497">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D499">
       <formula1>"Sin Comenzar,En Proceso,Finalizada"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E1054">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E1056">
       <formula1>"_,Esperando Revision,En Revision,Reasignado,Validado"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F1054">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F1056">
       <formula1>"_,Ignacio,Lucia,Luciano,Gabriel"</formula1>
     </dataValidation>
   </dataValidations>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="122">
   <si>
     <t>Etapa</t>
   </si>
@@ -169,13 +169,13 @@
     <t>Riesgos y Contingencias</t>
   </si>
   <si>
-    <t>Plan de Riesgos y Contingencias</t>
+    <t>ID: TR01 : Plan de Riesgos y Contingencias</t>
   </si>
   <si>
     <t>Ignacio</t>
   </si>
   <si>
-    <t>Modificacion Plan Riesgos y Contingencias</t>
+    <t>ID: TR01 : Modificacion Plan Riesgos y Contingencias</t>
   </si>
   <si>
     <t>Eleccion del Ciclo de Vida</t>
@@ -197,13 +197,10 @@
 2. Evaluación competencial opcional: Asegurarse de que en los Requerimientos Funcionales la vinculación de tareas a competencias sea opcional y no obligatoria, permitiendo también actividades tradicionales, foros y listas de cotejo. </t>
   </si>
   <si>
-    <t>Completar Sintesis Entrevistas</t>
+    <t>ID: TR02 : Completar Sintesis Entrevistas</t>
   </si>
   <si>
     <t>Conciliar Sintesis con Cuestionarios</t>
-  </si>
-  <si>
-    <t>Completar y Finalizar Sintesis Entrevistas</t>
   </si>
   <si>
     <t>RF Perfil Cliente</t>
@@ -221,13 +218,16 @@
     <t>RF Perfil Docente</t>
   </si>
   <si>
+    <t>Entrega Incompleta</t>
+  </si>
+  <si>
     <t>RF Perfil Estudiante</t>
   </si>
   <si>
     <t>RF Perfil Tecnicos</t>
   </si>
   <si>
-    <t>Sin Comenzar</t>
+    <t>Asignada</t>
   </si>
   <si>
     <t>_</t>
@@ -257,7 +257,16 @@
     <t>Formatear Documento de RF al formato estandar acordado</t>
   </si>
   <si>
+    <t>Desistida</t>
+  </si>
+  <si>
     <t>RNOF Perfil Cliente</t>
+  </si>
+  <si>
+    <t>Revision - RF Perfil Director</t>
+  </si>
+  <si>
+    <t>Revision - RF Perfil Docente</t>
   </si>
   <si>
     <t>RNOF Perfil Director</t>
@@ -556,7 +565,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="12">
     <dxf>
       <font/>
       <fill>
@@ -655,8 +664,8 @@
       <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF3F3F3"/>
-          <bgColor rgb="FFF3F3F3"/>
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
       <border/>
@@ -665,8 +674,18 @@
       <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF46C27"/>
-          <bgColor rgb="FFF46C27"/>
+          <fgColor rgb="FF8E7CC3"/>
+          <bgColor rgb="FF8E7CC3"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3F3F3"/>
+          <bgColor rgb="FFF3F3F3"/>
         </patternFill>
       </fill>
       <border/>
@@ -944,7 +963,7 @@
       </c>
       <c r="C2" s="6" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-09-22 00:31</v>
+        <v>Plan de Proyecto: 2026-09-22 11:04</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>14</v>
@@ -1870,7 +1889,9 @@
       <c r="H19" s="8">
         <v>46276.0</v>
       </c>
-      <c r="I19" s="8"/>
+      <c r="I19" s="8">
+        <v>46276.0</v>
+      </c>
       <c r="J19" s="9"/>
       <c r="K19" s="11" t="s">
         <v>41</v>
@@ -2284,7 +2305,7 @@
         <v>52</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>39</v>
@@ -2758,7 +2779,7 @@
         <v>56</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>14</v>
@@ -2769,9 +2790,15 @@
       <c r="F36" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
+      <c r="G36" s="8">
+        <v>46286.0</v>
+      </c>
+      <c r="H36" s="8">
+        <v>46286.0</v>
+      </c>
+      <c r="I36" s="8">
+        <v>46286.0</v>
+      </c>
       <c r="J36" s="12"/>
       <c r="K36" s="9"/>
       <c r="L36" s="9"/>
@@ -2803,13 +2830,13 @@
         <v>56</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>16</v>
@@ -2854,13 +2881,13 @@
         <v>56</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>53</v>
@@ -2905,13 +2932,13 @@
         <v>56</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>40</v>
@@ -2956,13 +2983,13 @@
         <v>56</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>53</v>
@@ -3013,7 +3040,7 @@
         <v>14</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>40</v>
@@ -3067,13 +3094,13 @@
         <v>72</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="G42" s="8">
-        <v>46286.0</v>
+        <v>46287.0</v>
       </c>
       <c r="H42" s="8">
-        <v>46289.0</v>
+        <v>46288.0</v>
       </c>
       <c r="I42" s="8"/>
       <c r="J42" s="9"/>
@@ -3122,10 +3149,10 @@
         <v>46285.0</v>
       </c>
       <c r="H43" s="8">
-        <v>46285.0</v>
+        <v>46288.0</v>
       </c>
       <c r="I43" s="8">
-        <v>46285.0</v>
+        <v>46287.0</v>
       </c>
       <c r="J43" s="9"/>
       <c r="K43" s="9"/>
@@ -3363,7 +3390,7 @@
         <v>79</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E48" s="7"/>
       <c r="F48" s="7" t="s">
@@ -3410,14 +3437,14 @@
         <v>80</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E49" s="7"/>
       <c r="F49" s="7" t="s">
         <v>53</v>
       </c>
       <c r="G49" s="8">
-        <v>46286.0</v>
+        <v>46287.0</v>
       </c>
       <c r="H49" s="8">
         <v>46287.0</v>
@@ -3501,13 +3528,13 @@
         <v>56</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F51" s="7" t="s">
         <v>16</v>
@@ -3516,7 +3543,7 @@
         <v>46284.0</v>
       </c>
       <c r="H51" s="8">
-        <v>46289.0</v>
+        <v>46286.0</v>
       </c>
       <c r="I51" s="8">
         <v>46285.0</v>
@@ -3552,16 +3579,14 @@
         <v>56</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>72</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="E52" s="7"/>
       <c r="F52" s="7" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="G52" s="8">
         <v>46286.0</v>
@@ -3570,9 +3595,9 @@
         <v>46287.0</v>
       </c>
       <c r="I52" s="8"/>
-      <c r="J52" s="9"/>
-      <c r="K52" s="9"/>
-      <c r="L52" s="9"/>
+      <c r="J52" s="12"/>
+      <c r="K52" s="15"/>
+      <c r="L52" s="15"/>
       <c r="M52" s="10"/>
       <c r="N52" s="10"/>
       <c r="O52" s="10"/>
@@ -3600,26 +3625,26 @@
       <c r="B53" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C53" s="18" t="s">
+      <c r="C53" s="6" t="s">
         <v>83</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E53" s="7"/>
       <c r="F53" s="7" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G53" s="8">
-        <v>46286.0</v>
+        <v>46287.0</v>
       </c>
       <c r="H53" s="8">
-        <v>46289.0</v>
+        <v>46287.0</v>
       </c>
       <c r="I53" s="8"/>
       <c r="J53" s="12"/>
-      <c r="K53" s="9"/>
-      <c r="L53" s="9"/>
+      <c r="K53" s="15"/>
+      <c r="L53" s="15"/>
       <c r="M53" s="10"/>
       <c r="N53" s="10"/>
       <c r="O53" s="10"/>
@@ -3645,28 +3670,26 @@
         <v>25</v>
       </c>
       <c r="B54" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C54" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C54" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>71</v>
-      </c>
+      <c r="D54" s="7"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G54" s="8">
-        <v>46286.0</v>
+        <v>46287.0</v>
       </c>
       <c r="H54" s="8">
         <v>46287.0</v>
       </c>
       <c r="I54" s="8"/>
-      <c r="J54" s="9"/>
-      <c r="K54" s="9"/>
-      <c r="L54" s="9"/>
+      <c r="J54" s="12"/>
+      <c r="K54" s="15"/>
+      <c r="L54" s="15"/>
       <c r="M54" s="10"/>
       <c r="N54" s="10"/>
       <c r="O54" s="10"/>
@@ -3694,24 +3717,24 @@
       <c r="B55" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C55" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E55" s="7"/>
+      <c r="C55" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7" t="s">
+        <v>72</v>
+      </c>
       <c r="F55" s="7" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="G55" s="8">
+        <v>46286.0</v>
+      </c>
+      <c r="H55" s="8">
         <v>46287.0</v>
       </c>
-      <c r="H55" s="8">
-        <v>46288.0</v>
-      </c>
       <c r="I55" s="8"/>
-      <c r="J55" s="12"/>
+      <c r="J55" s="9"/>
       <c r="K55" s="9"/>
       <c r="L55" s="9"/>
       <c r="M55" s="10"/>
@@ -3741,24 +3764,22 @@
       <c r="B56" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C56" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>71</v>
-      </c>
+      <c r="C56" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D56" s="7"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="G56" s="8">
-        <v>46287.0</v>
+        <v>46286.0</v>
       </c>
       <c r="H56" s="8">
-        <v>46288.0</v>
+        <v>46289.0</v>
       </c>
       <c r="I56" s="8"/>
-      <c r="J56" s="9"/>
+      <c r="J56" s="12"/>
       <c r="K56" s="9"/>
       <c r="L56" s="9"/>
       <c r="M56" s="10"/>
@@ -3786,23 +3807,21 @@
         <v>25</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="D57" s="7" t="s">
-        <v>71</v>
-      </c>
+      <c r="D57" s="7"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G57" s="8">
-        <v>46289.0</v>
+        <v>46286.0</v>
       </c>
       <c r="H57" s="8">
-        <v>46290.0</v>
+        <v>46287.0</v>
       </c>
       <c r="I57" s="8"/>
       <c r="J57" s="9"/>
@@ -3835,24 +3854,22 @@
       <c r="B58" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="C58" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="D58" s="7" t="s">
-        <v>71</v>
-      </c>
+      <c r="D58" s="7"/>
       <c r="E58" s="7"/>
       <c r="F58" s="7" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G58" s="8">
-        <v>46289.0</v>
+        <v>46287.0</v>
       </c>
       <c r="H58" s="8">
-        <v>46290.0</v>
+        <v>46288.0</v>
       </c>
       <c r="I58" s="8"/>
-      <c r="J58" s="9"/>
+      <c r="J58" s="12"/>
       <c r="K58" s="9"/>
       <c r="L58" s="9"/>
       <c r="M58" s="10"/>
@@ -3880,25 +3897,21 @@
         <v>25</v>
       </c>
       <c r="B59" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C59" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C59" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>72</v>
-      </c>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
       <c r="F59" s="7" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G59" s="8">
-        <v>46290.0</v>
+        <v>46287.0</v>
       </c>
       <c r="H59" s="8">
-        <v>46290.0</v>
+        <v>46288.0</v>
       </c>
       <c r="I59" s="8"/>
       <c r="J59" s="9"/>
@@ -3929,28 +3942,24 @@
         <v>25</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>72</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
       <c r="F60" s="7" t="s">
         <v>32</v>
       </c>
       <c r="G60" s="8">
+        <v>46289.0</v>
+      </c>
+      <c r="H60" s="8">
         <v>46290.0</v>
       </c>
-      <c r="H60" s="8">
-        <v>46291.0</v>
-      </c>
       <c r="I60" s="8"/>
-      <c r="J60" s="12"/>
+      <c r="J60" s="9"/>
       <c r="K60" s="9"/>
       <c r="L60" s="9"/>
       <c r="M60" s="10"/>
@@ -3978,23 +3987,21 @@
         <v>25</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>71</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="D61" s="7"/>
       <c r="E61" s="7"/>
       <c r="F61" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G61" s="8">
-        <v>46291.0</v>
+        <v>46289.0</v>
       </c>
       <c r="H61" s="8">
-        <v>46292.0</v>
+        <v>46290.0</v>
       </c>
       <c r="I61" s="8"/>
       <c r="J61" s="9"/>
@@ -4025,25 +4032,23 @@
         <v>25</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>71</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="D62" s="7"/>
       <c r="E62" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G62" s="8">
-        <v>46291.0</v>
+        <v>46290.0</v>
       </c>
       <c r="H62" s="8">
-        <v>46292.0</v>
+        <v>46290.0</v>
       </c>
       <c r="I62" s="8"/>
       <c r="J62" s="9"/>
@@ -4074,26 +4079,26 @@
         <v>25</v>
       </c>
       <c r="B63" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C63" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C63" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7" t="s">
+        <v>72</v>
+      </c>
       <c r="F63" s="7" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G63" s="8">
+        <v>46290.0</v>
+      </c>
+      <c r="H63" s="8">
         <v>46291.0</v>
       </c>
-      <c r="H63" s="8">
-        <v>46292.0</v>
-      </c>
       <c r="I63" s="8"/>
-      <c r="J63" s="9"/>
+      <c r="J63" s="12"/>
       <c r="K63" s="9"/>
       <c r="L63" s="9"/>
       <c r="M63" s="10"/>
@@ -4121,14 +4126,12 @@
         <v>25</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>71</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="D64" s="7"/>
       <c r="E64" s="7"/>
       <c r="F64" s="7" t="s">
         <v>16</v>
@@ -4137,7 +4140,7 @@
         <v>46291.0</v>
       </c>
       <c r="H64" s="8">
-        <v>46294.0</v>
+        <v>46292.0</v>
       </c>
       <c r="I64" s="8"/>
       <c r="J64" s="9"/>
@@ -4168,23 +4171,23 @@
         <v>25</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="D65" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E65" s="7"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7" t="s">
+        <v>72</v>
+      </c>
       <c r="F65" s="7" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G65" s="8">
-        <v>46289.0</v>
+        <v>46291.0</v>
       </c>
       <c r="H65" s="8">
-        <v>46291.0</v>
+        <v>46292.0</v>
       </c>
       <c r="I65" s="8"/>
       <c r="J65" s="9"/>
@@ -4215,23 +4218,21 @@
         <v>25</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="D66" s="7" t="s">
-        <v>71</v>
-      </c>
+      <c r="D66" s="7"/>
       <c r="E66" s="7"/>
       <c r="F66" s="7" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G66" s="8">
         <v>46291.0</v>
       </c>
       <c r="H66" s="8">
-        <v>46294.0</v>
+        <v>46292.0</v>
       </c>
       <c r="I66" s="8"/>
       <c r="J66" s="9"/>
@@ -4262,23 +4263,21 @@
         <v>25</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D67" s="7" t="s">
-        <v>71</v>
-      </c>
+      <c r="D67" s="7"/>
       <c r="E67" s="7"/>
       <c r="F67" s="7" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G67" s="8">
-        <v>46289.0</v>
+        <v>46291.0</v>
       </c>
       <c r="H67" s="8">
-        <v>46291.0</v>
+        <v>46294.0</v>
       </c>
       <c r="I67" s="8"/>
       <c r="J67" s="9"/>
@@ -4309,23 +4308,21 @@
         <v>25</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="D68" s="7" t="s">
-        <v>71</v>
-      </c>
+      <c r="D68" s="7"/>
       <c r="E68" s="7"/>
       <c r="F68" s="7" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="G68" s="8">
+        <v>46289.0</v>
+      </c>
+      <c r="H68" s="8">
         <v>46291.0</v>
-      </c>
-      <c r="H68" s="8">
-        <v>46294.0</v>
       </c>
       <c r="I68" s="8"/>
       <c r="J68" s="9"/>
@@ -4356,17 +4353,15 @@
         <v>25</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D69" s="7" t="s">
-        <v>71</v>
-      </c>
+      <c r="D69" s="7"/>
       <c r="E69" s="7"/>
       <c r="F69" s="7" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G69" s="8">
         <v>46291.0</v>
@@ -4400,34 +4395,28 @@
     </row>
     <row r="70" ht="29.25" customHeight="1">
       <c r="A70" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C70" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="B70" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E70" s="7" t="s">
-        <v>72</v>
-      </c>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
       <c r="F70" s="7" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G70" s="8">
         <v>46289.0</v>
       </c>
       <c r="H70" s="8">
-        <v>46289.0</v>
+        <v>46291.0</v>
       </c>
       <c r="I70" s="8"/>
       <c r="J70" s="9"/>
-      <c r="K70" s="9" t="s">
-        <v>107</v>
-      </c>
+      <c r="K70" s="9"/>
       <c r="L70" s="9"/>
       <c r="M70" s="10"/>
       <c r="N70" s="10"/>
@@ -4451,34 +4440,28 @@
     </row>
     <row r="71" ht="29.25" customHeight="1">
       <c r="A71" s="4" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="B71" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C71" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="C71" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E71" s="7" t="s">
-        <v>72</v>
-      </c>
+      <c r="D71" s="7"/>
+      <c r="E71" s="7"/>
       <c r="F71" s="7" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G71" s="8">
-        <v>46289.0</v>
+        <v>46291.0</v>
       </c>
       <c r="H71" s="8">
-        <v>46289.0</v>
+        <v>46294.0</v>
       </c>
       <c r="I71" s="8"/>
       <c r="J71" s="9"/>
-      <c r="K71" s="9" t="s">
-        <v>107</v>
-      </c>
+      <c r="K71" s="9"/>
       <c r="L71" s="9"/>
       <c r="M71" s="10"/>
       <c r="N71" s="10"/>
@@ -4502,26 +4485,24 @@
     </row>
     <row r="72" ht="29.25" customHeight="1">
       <c r="A72" s="4" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D72" s="7" t="s">
-        <v>71</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="D72" s="7"/>
       <c r="E72" s="7"/>
       <c r="F72" s="7" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G72" s="8">
-        <v>46289.0</v>
+        <v>46291.0</v>
       </c>
       <c r="H72" s="8">
-        <v>46289.0</v>
+        <v>46294.0</v>
       </c>
       <c r="I72" s="8"/>
       <c r="J72" s="9"/>
@@ -4549,32 +4530,32 @@
     </row>
     <row r="73" ht="29.25" customHeight="1">
       <c r="A73" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>71</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D73" s="7"/>
       <c r="E73" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="G73" s="8">
-        <v>46286.0</v>
+        <v>46289.0</v>
       </c>
       <c r="H73" s="8">
-        <v>46293.0</v>
+        <v>46289.0</v>
       </c>
       <c r="I73" s="8"/>
       <c r="J73" s="9"/>
-      <c r="K73" s="9"/>
+      <c r="K73" s="9" t="s">
+        <v>110</v>
+      </c>
       <c r="L73" s="9"/>
       <c r="M73" s="10"/>
       <c r="N73" s="10"/>
@@ -4598,30 +4579,32 @@
     </row>
     <row r="74" ht="29.25" customHeight="1">
       <c r="A74" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E74" s="7"/>
+        <v>109</v>
+      </c>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7" t="s">
+        <v>72</v>
+      </c>
       <c r="F74" s="7" t="s">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="G74" s="8">
-        <v>46287.0</v>
+        <v>46289.0</v>
       </c>
       <c r="H74" s="8">
-        <v>46295.0</v>
+        <v>46289.0</v>
       </c>
       <c r="I74" s="8"/>
       <c r="J74" s="9"/>
-      <c r="K74" s="9"/>
+      <c r="K74" s="9" t="s">
+        <v>110</v>
+      </c>
       <c r="L74" s="9"/>
       <c r="M74" s="10"/>
       <c r="N74" s="10"/>
@@ -4645,26 +4628,24 @@
     </row>
     <row r="75" ht="29.25" customHeight="1">
       <c r="A75" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="D75" s="7" t="s">
-        <v>71</v>
-      </c>
+      <c r="D75" s="7"/>
       <c r="E75" s="7"/>
       <c r="F75" s="7" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="G75" s="8">
-        <v>46287.0</v>
+        <v>46289.0</v>
       </c>
       <c r="H75" s="8">
-        <v>46293.0</v>
+        <v>46289.0</v>
       </c>
       <c r="I75" s="8"/>
       <c r="J75" s="9"/>
@@ -4692,26 +4673,26 @@
     </row>
     <row r="76" ht="29.25" customHeight="1">
       <c r="A76" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>113</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E76" s="7"/>
+        <v>113</v>
+      </c>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7" t="s">
+        <v>72</v>
+      </c>
       <c r="F76" s="7" t="s">
         <v>72</v>
       </c>
       <c r="G76" s="8">
-        <v>46296.0</v>
+        <v>46286.0</v>
       </c>
       <c r="H76" s="8">
-        <v>46303.0</v>
+        <v>46293.0</v>
       </c>
       <c r="I76" s="8"/>
       <c r="J76" s="9"/>
@@ -4739,13 +4720,13 @@
     </row>
     <row r="77" ht="29.25" customHeight="1">
       <c r="A77" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D77" s="7"/>
       <c r="E77" s="7"/>
@@ -4753,10 +4734,10 @@
         <v>72</v>
       </c>
       <c r="G77" s="8">
-        <v>46303.0</v>
+        <v>46287.0</v>
       </c>
       <c r="H77" s="8">
-        <v>46303.0</v>
+        <v>46295.0</v>
       </c>
       <c r="I77" s="8"/>
       <c r="J77" s="9"/>
@@ -4784,26 +4765,24 @@
     </row>
     <row r="78" ht="29.25" customHeight="1">
       <c r="A78" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>71</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="D78" s="7"/>
       <c r="E78" s="7"/>
       <c r="F78" s="7" t="s">
         <v>72</v>
       </c>
       <c r="G78" s="8">
-        <v>46305.0</v>
+        <v>46287.0</v>
       </c>
       <c r="H78" s="8">
-        <v>46305.0</v>
+        <v>46293.0</v>
       </c>
       <c r="I78" s="8"/>
       <c r="J78" s="9"/>
@@ -4830,20 +4809,30 @@
       <c r="AE78" s="10"/>
     </row>
     <row r="79" ht="29.25" customHeight="1">
-      <c r="A79" s="19"/>
-      <c r="B79" s="6"/>
-      <c r="C79" s="20"/>
-      <c r="D79" s="21"/>
-      <c r="E79" s="15"/>
-      <c r="F79" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="G79" s="23"/>
-      <c r="H79" s="23"/>
-      <c r="I79" s="23"/>
-      <c r="J79" s="12"/>
-      <c r="K79" s="15"/>
-      <c r="L79" s="15"/>
+      <c r="A79" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D79" s="7"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G79" s="8">
+        <v>46296.0</v>
+      </c>
+      <c r="H79" s="8">
+        <v>46303.0</v>
+      </c>
+      <c r="I79" s="8"/>
+      <c r="J79" s="9"/>
+      <c r="K79" s="9"/>
+      <c r="L79" s="9"/>
       <c r="M79" s="10"/>
       <c r="N79" s="10"/>
       <c r="O79" s="10"/>
@@ -4865,20 +4854,30 @@
       <c r="AE79" s="10"/>
     </row>
     <row r="80" ht="29.25" customHeight="1">
-      <c r="A80" s="19"/>
-      <c r="B80" s="6"/>
-      <c r="C80" s="20"/>
-      <c r="D80" s="21"/>
-      <c r="E80" s="15"/>
-      <c r="F80" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="G80" s="23"/>
-      <c r="H80" s="23"/>
-      <c r="I80" s="23"/>
-      <c r="J80" s="12"/>
-      <c r="K80" s="15"/>
-      <c r="L80" s="15"/>
+      <c r="A80" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D80" s="7"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G80" s="8">
+        <v>46303.0</v>
+      </c>
+      <c r="H80" s="8">
+        <v>46303.0</v>
+      </c>
+      <c r="I80" s="8"/>
+      <c r="J80" s="9"/>
+      <c r="K80" s="9"/>
+      <c r="L80" s="9"/>
       <c r="M80" s="10"/>
       <c r="N80" s="10"/>
       <c r="O80" s="10"/>
@@ -4900,20 +4899,30 @@
       <c r="AE80" s="10"/>
     </row>
     <row r="81" ht="29.25" customHeight="1">
-      <c r="A81" s="19"/>
-      <c r="B81" s="6"/>
-      <c r="C81" s="20"/>
-      <c r="D81" s="21"/>
-      <c r="E81" s="15"/>
-      <c r="F81" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="G81" s="23"/>
-      <c r="H81" s="23"/>
-      <c r="I81" s="23"/>
-      <c r="J81" s="12"/>
-      <c r="K81" s="15"/>
-      <c r="L81" s="15"/>
+      <c r="A81" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G81" s="8">
+        <v>46305.0</v>
+      </c>
+      <c r="H81" s="8">
+        <v>46305.0</v>
+      </c>
+      <c r="I81" s="8"/>
+      <c r="J81" s="9"/>
+      <c r="K81" s="9"/>
+      <c r="L81" s="9"/>
       <c r="M81" s="10"/>
       <c r="N81" s="10"/>
       <c r="O81" s="10"/>
@@ -5007,18 +5016,18 @@
     <row r="84" ht="29.25" customHeight="1">
       <c r="A84" s="19"/>
       <c r="B84" s="6"/>
-      <c r="C84" s="24"/>
+      <c r="C84" s="20"/>
       <c r="D84" s="21"/>
-      <c r="E84" s="10"/>
+      <c r="E84" s="15"/>
       <c r="F84" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="G84" s="25"/>
-      <c r="H84" s="25"/>
-      <c r="I84" s="25"/>
+      <c r="G84" s="23"/>
+      <c r="H84" s="23"/>
+      <c r="I84" s="23"/>
       <c r="J84" s="12"/>
-      <c r="K84" s="10"/>
-      <c r="L84" s="10"/>
+      <c r="K84" s="15"/>
+      <c r="L84" s="15"/>
       <c r="M84" s="10"/>
       <c r="N84" s="10"/>
       <c r="O84" s="10"/>
@@ -5040,20 +5049,20 @@
       <c r="AE84" s="10"/>
     </row>
     <row r="85" ht="29.25" customHeight="1">
-      <c r="A85" s="26"/>
-      <c r="B85" s="24"/>
-      <c r="C85" s="24"/>
+      <c r="A85" s="19"/>
+      <c r="B85" s="6"/>
+      <c r="C85" s="20"/>
       <c r="D85" s="21"/>
-      <c r="E85" s="10"/>
+      <c r="E85" s="15"/>
       <c r="F85" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="G85" s="25"/>
-      <c r="H85" s="25"/>
-      <c r="I85" s="25"/>
+      <c r="G85" s="23"/>
+      <c r="H85" s="23"/>
+      <c r="I85" s="23"/>
       <c r="J85" s="12"/>
-      <c r="K85" s="10"/>
-      <c r="L85" s="10"/>
+      <c r="K85" s="15"/>
+      <c r="L85" s="15"/>
       <c r="M85" s="10"/>
       <c r="N85" s="10"/>
       <c r="O85" s="10"/>
@@ -5075,20 +5084,20 @@
       <c r="AE85" s="10"/>
     </row>
     <row r="86" ht="29.25" customHeight="1">
-      <c r="A86" s="26"/>
-      <c r="B86" s="24"/>
-      <c r="C86" s="24"/>
+      <c r="A86" s="19"/>
+      <c r="B86" s="6"/>
+      <c r="C86" s="20"/>
       <c r="D86" s="21"/>
-      <c r="E86" s="10"/>
+      <c r="E86" s="15"/>
       <c r="F86" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="G86" s="25"/>
-      <c r="H86" s="25"/>
-      <c r="I86" s="25"/>
+      <c r="G86" s="23"/>
+      <c r="H86" s="23"/>
+      <c r="I86" s="23"/>
       <c r="J86" s="12"/>
-      <c r="K86" s="10"/>
-      <c r="L86" s="10"/>
+      <c r="K86" s="15"/>
+      <c r="L86" s="15"/>
       <c r="M86" s="10"/>
       <c r="N86" s="10"/>
       <c r="O86" s="10"/>
@@ -5110,8 +5119,8 @@
       <c r="AE86" s="10"/>
     </row>
     <row r="87" ht="29.25" customHeight="1">
-      <c r="A87" s="26"/>
-      <c r="B87" s="24"/>
+      <c r="A87" s="19"/>
+      <c r="B87" s="6"/>
       <c r="C87" s="24"/>
       <c r="D87" s="21"/>
       <c r="E87" s="10"/>
@@ -5367,6 +5376,27 @@
       <c r="H94" s="25"/>
       <c r="I94" s="25"/>
       <c r="J94" s="12"/>
+      <c r="K94" s="10"/>
+      <c r="L94" s="10"/>
+      <c r="M94" s="10"/>
+      <c r="N94" s="10"/>
+      <c r="O94" s="10"/>
+      <c r="P94" s="10"/>
+      <c r="Q94" s="10"/>
+      <c r="R94" s="10"/>
+      <c r="S94" s="10"/>
+      <c r="T94" s="10"/>
+      <c r="U94" s="10"/>
+      <c r="V94" s="10"/>
+      <c r="W94" s="10"/>
+      <c r="X94" s="10"/>
+      <c r="Y94" s="10"/>
+      <c r="Z94" s="10"/>
+      <c r="AA94" s="10"/>
+      <c r="AB94" s="10"/>
+      <c r="AC94" s="10"/>
+      <c r="AD94" s="10"/>
+      <c r="AE94" s="10"/>
     </row>
     <row r="95" ht="29.25" customHeight="1">
       <c r="A95" s="26"/>
@@ -5381,6 +5411,27 @@
       <c r="H95" s="25"/>
       <c r="I95" s="25"/>
       <c r="J95" s="12"/>
+      <c r="K95" s="10"/>
+      <c r="L95" s="10"/>
+      <c r="M95" s="10"/>
+      <c r="N95" s="10"/>
+      <c r="O95" s="10"/>
+      <c r="P95" s="10"/>
+      <c r="Q95" s="10"/>
+      <c r="R95" s="10"/>
+      <c r="S95" s="10"/>
+      <c r="T95" s="10"/>
+      <c r="U95" s="10"/>
+      <c r="V95" s="10"/>
+      <c r="W95" s="10"/>
+      <c r="X95" s="10"/>
+      <c r="Y95" s="10"/>
+      <c r="Z95" s="10"/>
+      <c r="AA95" s="10"/>
+      <c r="AB95" s="10"/>
+      <c r="AC95" s="10"/>
+      <c r="AD95" s="10"/>
+      <c r="AE95" s="10"/>
     </row>
     <row r="96" ht="29.25" customHeight="1">
       <c r="A96" s="26"/>
@@ -5395,6 +5446,27 @@
       <c r="H96" s="25"/>
       <c r="I96" s="25"/>
       <c r="J96" s="12"/>
+      <c r="K96" s="10"/>
+      <c r="L96" s="10"/>
+      <c r="M96" s="10"/>
+      <c r="N96" s="10"/>
+      <c r="O96" s="10"/>
+      <c r="P96" s="10"/>
+      <c r="Q96" s="10"/>
+      <c r="R96" s="10"/>
+      <c r="S96" s="10"/>
+      <c r="T96" s="10"/>
+      <c r="U96" s="10"/>
+      <c r="V96" s="10"/>
+      <c r="W96" s="10"/>
+      <c r="X96" s="10"/>
+      <c r="Y96" s="10"/>
+      <c r="Z96" s="10"/>
+      <c r="AA96" s="10"/>
+      <c r="AB96" s="10"/>
+      <c r="AC96" s="10"/>
+      <c r="AD96" s="10"/>
+      <c r="AE96" s="10"/>
     </row>
     <row r="97" ht="29.25" customHeight="1">
       <c r="A97" s="26"/>
@@ -6206,7 +6278,7 @@
       <c r="G154" s="25"/>
       <c r="H154" s="25"/>
       <c r="I154" s="25"/>
-      <c r="J154" s="27"/>
+      <c r="J154" s="12"/>
     </row>
     <row r="155" ht="29.25" customHeight="1">
       <c r="A155" s="26"/>
@@ -6220,7 +6292,7 @@
       <c r="G155" s="25"/>
       <c r="H155" s="25"/>
       <c r="I155" s="25"/>
-      <c r="J155" s="27"/>
+      <c r="J155" s="12"/>
     </row>
     <row r="156" ht="29.25" customHeight="1">
       <c r="A156" s="26"/>
@@ -6234,7 +6306,7 @@
       <c r="G156" s="25"/>
       <c r="H156" s="25"/>
       <c r="I156" s="25"/>
-      <c r="J156" s="27"/>
+      <c r="J156" s="12"/>
     </row>
     <row r="157" ht="29.25" customHeight="1">
       <c r="A157" s="26"/>
@@ -11070,9 +11142,11 @@
       <c r="A502" s="26"/>
       <c r="B502" s="24"/>
       <c r="C502" s="24"/>
-      <c r="D502" s="10"/>
+      <c r="D502" s="21"/>
       <c r="E502" s="10"/>
-      <c r="F502" s="10"/>
+      <c r="F502" s="22" t="s">
+        <v>72</v>
+      </c>
       <c r="G502" s="25"/>
       <c r="H502" s="25"/>
       <c r="I502" s="25"/>
@@ -11082,9 +11156,11 @@
       <c r="A503" s="26"/>
       <c r="B503" s="24"/>
       <c r="C503" s="24"/>
-      <c r="D503" s="10"/>
+      <c r="D503" s="21"/>
       <c r="E503" s="10"/>
-      <c r="F503" s="10"/>
+      <c r="F503" s="22" t="s">
+        <v>72</v>
+      </c>
       <c r="G503" s="25"/>
       <c r="H503" s="25"/>
       <c r="I503" s="25"/>
@@ -11094,9 +11170,11 @@
       <c r="A504" s="26"/>
       <c r="B504" s="24"/>
       <c r="C504" s="24"/>
-      <c r="D504" s="10"/>
+      <c r="D504" s="21"/>
       <c r="E504" s="10"/>
-      <c r="F504" s="10"/>
+      <c r="F504" s="22" t="s">
+        <v>72</v>
+      </c>
       <c r="G504" s="25"/>
       <c r="H504" s="25"/>
       <c r="I504" s="25"/>
@@ -17750,81 +17828,122 @@
       <c r="I1058" s="25"/>
       <c r="J1058" s="27"/>
     </row>
+    <row r="1059" ht="29.25" customHeight="1">
+      <c r="A1059" s="26"/>
+      <c r="B1059" s="24"/>
+      <c r="C1059" s="24"/>
+      <c r="D1059" s="10"/>
+      <c r="E1059" s="10"/>
+      <c r="F1059" s="10"/>
+      <c r="G1059" s="25"/>
+      <c r="H1059" s="25"/>
+      <c r="I1059" s="25"/>
+      <c r="J1059" s="27"/>
+    </row>
+    <row r="1060" ht="29.25" customHeight="1">
+      <c r="A1060" s="26"/>
+      <c r="B1060" s="24"/>
+      <c r="C1060" s="24"/>
+      <c r="D1060" s="10"/>
+      <c r="E1060" s="10"/>
+      <c r="F1060" s="10"/>
+      <c r="G1060" s="25"/>
+      <c r="H1060" s="25"/>
+      <c r="I1060" s="25"/>
+      <c r="J1060" s="27"/>
+    </row>
+    <row r="1061" ht="29.25" customHeight="1">
+      <c r="A1061" s="26"/>
+      <c r="B1061" s="24"/>
+      <c r="C1061" s="24"/>
+      <c r="D1061" s="10"/>
+      <c r="E1061" s="10"/>
+      <c r="F1061" s="10"/>
+      <c r="G1061" s="25"/>
+      <c r="H1061" s="25"/>
+      <c r="I1061" s="25"/>
+      <c r="J1061" s="27"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D78">
+  <conditionalFormatting sqref="D2:D81">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Finalizada">
       <formula>NOT(ISERROR(SEARCH(("Finalizada"),(D2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D78">
+  <conditionalFormatting sqref="D2:D81">
     <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="En Proceso">
       <formula>NOT(ISERROR(SEARCH(("En Proceso"),(D2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D78">
+  <conditionalFormatting sqref="D2:D81">
     <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Pendiente de Revision">
       <formula>NOT(ISERROR(SEARCH(("Pendiente de Revision"),(D2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J1058">
+  <conditionalFormatting sqref="J2:J1061">
     <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="SI">
       <formula>NOT(ISERROR(SEARCH(("SI"),(J2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E1058">
+  <conditionalFormatting sqref="E2:E1061">
     <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Validado">
       <formula>NOT(ISERROR(SEARCH(("Validado"),(E2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E1058">
+  <conditionalFormatting sqref="E2:E1061">
     <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="Revision">
       <formula>NOT(ISERROR(SEARCH(("Revision"),(E2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E103">
+  <conditionalFormatting sqref="E2:E106">
     <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="Reasignado">
       <formula>NOT(ISERROR(SEARCH(("Reasignado"),(E2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1058">
+  <conditionalFormatting sqref="F1:F1061">
     <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="Gabriel">
       <formula>NOT(ISERROR(SEARCH(("Gabriel"),(F1))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1058">
+  <conditionalFormatting sqref="F1:F1061">
     <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
       <formula>"Lucia"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1058">
+  <conditionalFormatting sqref="F1:F1061">
     <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
       <formula>"Luciano"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1058">
+  <conditionalFormatting sqref="F1:F1061">
     <cfRule type="cellIs" dxfId="4" priority="11" operator="equal">
       <formula>"Ignacio"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:AE93">
-    <cfRule type="expression" dxfId="9" priority="12">
+  <conditionalFormatting sqref="D2:D1061">
+    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
+      <formula>"Desistida"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D1061">
+    <cfRule type="cellIs" dxfId="10" priority="13" operator="equal">
+      <formula>"Asignada"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:AE96">
+    <cfRule type="expression" dxfId="11" priority="14">
       <formula>MOD(ROW(), 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D1058">
-    <cfRule type="cellIs" dxfId="10" priority="13" operator="equal">
-      <formula>"Reasignada"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E1058">
-      <formula1>"_,Esperando Revision,En Revision,Reasignado,Validado,Situacion"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D1061">
+      <formula1>"Sin Comenzar,En Proceso,Finalizada,Asignada,Reasignada,Desistida"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F1058">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E1061">
+      <formula1>"_,Esperando Revision,En Revision,Reasignado,Validado,Entrega Incompleta,Situacion"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F1061">
       <formula1>"_,Ignacio,Lucia,Luciano,Gabriel"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D1058">
-      <formula1>"Sin Comenzar,En Proceso,Finalizada,Estado,Reasignada"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -5,13 +5,15 @@
   <sheets>
     <sheet state="visible" name="Hoja 1" sheetId="1" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Hoja 1'!$A$1:$AE$80</definedName>
+  </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="124">
   <si>
     <t>Etapa</t>
   </si>
@@ -125,9 +127,6 @@
   </si>
   <si>
     <t>Sintesis Entrevistas</t>
-  </si>
-  <si>
-    <t>Reasignada</t>
   </si>
   <si>
     <t>Reasignado</t>
@@ -215,61 +214,64 @@
     <t>RF Perfil Director</t>
   </si>
   <si>
+    <t>En Revision</t>
+  </si>
+  <si>
+    <t>RF Perfil Inspector</t>
+  </si>
+  <si>
+    <t>RF Perfil Docente</t>
+  </si>
+  <si>
+    <t>RF Perfil Estudiante</t>
+  </si>
+  <si>
+    <t>RF Perfil Tecnicos</t>
+  </si>
+  <si>
+    <t>Automatizacion de Reportes al Cliente</t>
+  </si>
+  <si>
+    <t>Crear plantilla de formatos de ESRE</t>
+  </si>
+  <si>
+    <t>Crear Documento Descripcion del Sistema</t>
+  </si>
+  <si>
+    <t>Revisar Doc Descripcion del Sistema</t>
+  </si>
+  <si>
+    <t>Redactar Sintesis a los Interesados Documento Definitivo</t>
+  </si>
+  <si>
+    <t>Completar Redaccion de Funcionalidades del Sistema</t>
+  </si>
+  <si>
+    <t>Sin Comenzar</t>
+  </si>
+  <si>
+    <t>Pendiente</t>
+  </si>
+  <si>
+    <t>_</t>
+  </si>
+  <si>
+    <t>Formatear Documento de RF al formato estandar acordado</t>
+  </si>
+  <si>
+    <t>Desistida</t>
+  </si>
+  <si>
+    <t>RNOF Perfil Cliente</t>
+  </si>
+  <si>
+    <t>Revision - RF Perfil Director</t>
+  </si>
+  <si>
+    <t>Asignada</t>
+  </si>
+  <si>
     <t>Esperando Revision</t>
-  </si>
-  <si>
-    <t>RF Perfil Inspector</t>
-  </si>
-  <si>
-    <t>RF Perfil Docente</t>
-  </si>
-  <si>
-    <t>RF Perfil Estudiante</t>
-  </si>
-  <si>
-    <t>RF Perfil Tecnicos</t>
-  </si>
-  <si>
-    <t>Pendiente</t>
-  </si>
-  <si>
-    <t>Automatizacion de Reportes al Cliente</t>
-  </si>
-  <si>
-    <t>Crear plantilla de formatos de ESRE</t>
-  </si>
-  <si>
-    <t>Crear Documento Descripcion del Sistema</t>
-  </si>
-  <si>
-    <t>Revisar Doc Descripcion del Sistema</t>
-  </si>
-  <si>
-    <t>Redactar Sintesis a los Interesados Documento Definitivo</t>
-  </si>
-  <si>
-    <t>Completar Redaccion de Funcionalidades del Sistema</t>
-  </si>
-  <si>
-    <t>Sin Comenzar</t>
-  </si>
-  <si>
-    <t>_</t>
-  </si>
-  <si>
-    <t>Formatear Documento de RF al formato estandar acordado</t>
-  </si>
-  <si>
-    <t>Desistida</t>
-  </si>
-  <si>
-    <t>Asignada</t>
-  </si>
-  <si>
-    <t>RNOF Perfil Cliente</t>
-  </si>
-  <si>
-    <t>Revision - RF Perfil Director</t>
   </si>
   <si>
     <t>Revision - RF Perfil Docente</t>
@@ -973,7 +975,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="29.25" customHeight="1">
+    <row r="2" ht="29.25" hidden="1" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>12</v>
       </c>
@@ -982,7 +984,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-09-23 23:40</v>
+        <v>Plan de Proyecto: 2026-09-24 23:57</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>
@@ -1031,7 +1033,7 @@
       <c r="AD2" s="11"/>
       <c r="AE2" s="11"/>
     </row>
-    <row r="3" ht="29.25" customHeight="1">
+    <row r="3" ht="29.25" hidden="1" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>12</v>
       </c>
@@ -1088,7 +1090,7 @@
       <c r="AD3" s="11"/>
       <c r="AE3" s="11"/>
     </row>
-    <row r="4" ht="29.25" customHeight="1">
+    <row r="4" ht="29.25" hidden="1" customHeight="1">
       <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
@@ -1141,7 +1143,7 @@
       <c r="AD4" s="11"/>
       <c r="AE4" s="11"/>
     </row>
-    <row r="5" ht="29.25" customHeight="1">
+    <row r="5" ht="29.25" hidden="1" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>12</v>
       </c>
@@ -1194,7 +1196,7 @@
       <c r="AD5" s="11"/>
       <c r="AE5" s="11"/>
     </row>
-    <row r="6" ht="29.25" customHeight="1">
+    <row r="6" ht="29.25" hidden="1" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
@@ -1247,7 +1249,7 @@
       <c r="AD6" s="11"/>
       <c r="AE6" s="11"/>
     </row>
-    <row r="7" ht="29.25" customHeight="1">
+    <row r="7" ht="29.25" hidden="1" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>12</v>
       </c>
@@ -1300,7 +1302,7 @@
       <c r="AD7" s="11"/>
       <c r="AE7" s="11"/>
     </row>
-    <row r="8" ht="29.25" customHeight="1">
+    <row r="8" ht="29.25" hidden="1" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>25</v>
       </c>
@@ -1353,7 +1355,7 @@
       <c r="AD8" s="11"/>
       <c r="AE8" s="11"/>
     </row>
-    <row r="9" ht="29.25" customHeight="1">
+    <row r="9" ht="29.25" hidden="1" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>25</v>
       </c>
@@ -1406,7 +1408,7 @@
       <c r="AD9" s="11"/>
       <c r="AE9" s="11"/>
     </row>
-    <row r="10" ht="29.25" customHeight="1">
+    <row r="10" ht="29.25" hidden="1" customHeight="1">
       <c r="A10" s="5" t="s">
         <v>25</v>
       </c>
@@ -1459,7 +1461,7 @@
       <c r="AD10" s="11"/>
       <c r="AE10" s="11"/>
     </row>
-    <row r="11" ht="29.25" customHeight="1">
+    <row r="11" ht="29.25" hidden="1" customHeight="1">
       <c r="A11" s="5" t="s">
         <v>25</v>
       </c>
@@ -1512,7 +1514,7 @@
       <c r="AD11" s="11"/>
       <c r="AE11" s="11"/>
     </row>
-    <row r="12" ht="29.25" customHeight="1">
+    <row r="12" ht="29.25" hidden="1" customHeight="1">
       <c r="A12" s="5" t="s">
         <v>25</v>
       </c>
@@ -1671,7 +1673,7 @@
       <c r="AD14" s="11"/>
       <c r="AE14" s="11"/>
     </row>
-    <row r="15" ht="29.25" customHeight="1">
+    <row r="15" ht="29.25" hidden="1" customHeight="1">
       <c r="A15" s="5" t="s">
         <v>25</v>
       </c>
@@ -1724,7 +1726,7 @@
       <c r="AD15" s="11"/>
       <c r="AE15" s="11"/>
     </row>
-    <row r="16" ht="29.25" customHeight="1">
+    <row r="16" ht="29.25" hidden="1" customHeight="1">
       <c r="A16" s="5" t="s">
         <v>25</v>
       </c>
@@ -1777,7 +1779,7 @@
       <c r="AD16" s="11"/>
       <c r="AE16" s="11"/>
     </row>
-    <row r="17" ht="29.25" customHeight="1">
+    <row r="17" ht="29.25" hidden="1" customHeight="1">
       <c r="A17" s="5" t="s">
         <v>25</v>
       </c>
@@ -1883,7 +1885,7 @@
       <c r="AD18" s="11"/>
       <c r="AE18" s="11"/>
     </row>
-    <row r="19" ht="29.25" customHeight="1">
+    <row r="19" ht="29.25" hidden="1" customHeight="1">
       <c r="A19" s="5" t="s">
         <v>25</v>
       </c>
@@ -1894,13 +1896,13 @@
         <v>37</v>
       </c>
       <c r="D19" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="F19" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>40</v>
       </c>
       <c r="G19" s="9">
         <v>46274.0</v>
@@ -1915,10 +1917,10 @@
         <v>70.0</v>
       </c>
       <c r="K19" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="L19" s="10" t="s">
         <v>41</v>
-      </c>
-      <c r="L19" s="10" t="s">
-        <v>42</v>
       </c>
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
@@ -1942,7 +1944,7 @@
     </row>
     <row r="20" ht="29.25" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>26</v>
@@ -1972,10 +1974,10 @@
         <v>100.0</v>
       </c>
       <c r="K20" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="L20" s="20" t="s">
         <v>41</v>
-      </c>
-      <c r="L20" s="20" t="s">
-        <v>42</v>
       </c>
       <c r="M20" s="21"/>
       <c r="N20" s="21"/>
@@ -2002,10 +2004,10 @@
         <v>25</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>45</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>14</v>
@@ -2030,7 +2032,7 @@
       </c>
       <c r="K21" s="10"/>
       <c r="L21" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M21" s="11"/>
       <c r="N21" s="11"/>
@@ -2052,15 +2054,15 @@
       <c r="AD21" s="11"/>
       <c r="AE21" s="11"/>
     </row>
-    <row r="22" ht="29.25" customHeight="1">
+    <row r="22" ht="29.25" hidden="1" customHeight="1">
       <c r="A22" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>14</v>
@@ -2110,10 +2112,10 @@
         <v>25</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>14</v>
@@ -2163,10 +2165,10 @@
         <v>25</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>14</v>
@@ -2211,15 +2213,15 @@
       <c r="AD24" s="11"/>
       <c r="AE24" s="11"/>
     </row>
-    <row r="25" ht="29.25" customHeight="1">
+    <row r="25" ht="29.25" hidden="1" customHeight="1">
       <c r="A25" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>49</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>50</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>14</v>
@@ -2228,7 +2230,7 @@
         <v>15</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G25" s="9">
         <v>46271.0</v>
@@ -2269,10 +2271,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>14</v>
@@ -2317,24 +2319,24 @@
       <c r="AD26" s="11"/>
       <c r="AE26" s="11"/>
     </row>
-    <row r="27" ht="37.5" customHeight="1">
+    <row r="27" ht="37.5" hidden="1" customHeight="1">
       <c r="A27" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>52</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>53</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G27" s="9">
         <v>46274.0</v>
@@ -2370,15 +2372,15 @@
       <c r="AD27" s="11"/>
       <c r="AE27" s="11"/>
     </row>
-    <row r="28" ht="37.5" customHeight="1">
+    <row r="28" ht="37.5" hidden="1" customHeight="1">
       <c r="A28" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>14</v>
@@ -2431,7 +2433,7 @@
         <v>12</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>14</v>
@@ -2476,7 +2478,7 @@
       <c r="AD29" s="11"/>
       <c r="AE29" s="11"/>
     </row>
-    <row r="30" ht="37.5" customHeight="1">
+    <row r="30" ht="37.5" hidden="1" customHeight="1">
       <c r="A30" s="5" t="s">
         <v>12</v>
       </c>
@@ -2484,7 +2486,7 @@
         <v>12</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>14</v>
@@ -2529,15 +2531,15 @@
       <c r="AD30" s="11"/>
       <c r="AE30" s="11"/>
     </row>
-    <row r="31" ht="29.25" customHeight="1">
+    <row r="31" ht="29.25" hidden="1" customHeight="1">
       <c r="A31" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B31" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>57</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>14</v>
@@ -2546,7 +2548,7 @@
         <v>15</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G31" s="9">
         <v>46276.0</v>
@@ -2561,7 +2563,7 @@
         <v>20.0</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L31" s="10"/>
       <c r="M31" s="11"/>
@@ -2584,24 +2586,24 @@
       <c r="AD31" s="11"/>
       <c r="AE31" s="11"/>
     </row>
-    <row r="32" ht="29.25" customHeight="1">
+    <row r="32" ht="29.25" hidden="1" customHeight="1">
       <c r="A32" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B32" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>57</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G32" s="9">
         <v>46276.0</v>
@@ -2616,7 +2618,7 @@
         <v>20.0</v>
       </c>
       <c r="K32" s="22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L32" s="10"/>
       <c r="M32" s="11"/>
@@ -2639,15 +2641,15 @@
       <c r="AD32" s="11"/>
       <c r="AE32" s="11"/>
     </row>
-    <row r="33" ht="29.25" customHeight="1">
+    <row r="33" ht="29.25" hidden="1" customHeight="1">
       <c r="A33" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>14</v>
@@ -2671,7 +2673,7 @@
         <v>100.0</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L33" s="10"/>
       <c r="M33" s="11"/>
@@ -2699,10 +2701,10 @@
         <v>25</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>14</v>
@@ -2726,7 +2728,7 @@
         <v>90.0</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L34" s="10"/>
       <c r="M34" s="11"/>
@@ -2749,15 +2751,15 @@
       <c r="AD34" s="11"/>
       <c r="AE34" s="11"/>
     </row>
-    <row r="35" ht="29.25" customHeight="1">
+    <row r="35" ht="29.25" hidden="1" customHeight="1">
       <c r="A35" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>14</v>
@@ -2802,15 +2804,15 @@
       <c r="AD35" s="11"/>
       <c r="AE35" s="11"/>
     </row>
-    <row r="36" ht="29.25" customHeight="1">
+    <row r="36" ht="29.25" hidden="1" customHeight="1">
       <c r="A36" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>14</v>
@@ -2855,15 +2857,15 @@
       <c r="AD36" s="11"/>
       <c r="AE36" s="11"/>
     </row>
-    <row r="37" ht="29.25" customHeight="1">
+    <row r="37" ht="29.25" hidden="1" customHeight="1">
       <c r="A37" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>14</v>
@@ -2908,24 +2910,24 @@
       <c r="AD37" s="11"/>
       <c r="AE37" s="11"/>
     </row>
-    <row r="38" ht="29.25" customHeight="1">
+    <row r="38" ht="29.25" hidden="1" customHeight="1">
       <c r="A38" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G38" s="9">
         <v>46283.0</v>
@@ -2959,24 +2961,24 @@
       <c r="AD38" s="11"/>
       <c r="AE38" s="11"/>
     </row>
-    <row r="39" ht="29.25" customHeight="1">
+    <row r="39" ht="29.25" hidden="1" customHeight="1">
       <c r="A39" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G39" s="9">
         <v>46283.0</v>
@@ -3010,24 +3012,24 @@
       <c r="AD39" s="11"/>
       <c r="AE39" s="11"/>
     </row>
-    <row r="40" ht="29.25" customHeight="1">
+    <row r="40" ht="29.25" hidden="1" customHeight="1">
       <c r="A40" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G40" s="9">
         <v>46283.0</v>
@@ -3063,24 +3065,24 @@
       <c r="AD40" s="11"/>
       <c r="AE40" s="11"/>
     </row>
-    <row r="41" ht="29.25" customHeight="1">
+    <row r="41" ht="29.25" hidden="1" customHeight="1">
       <c r="A41" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G41" s="9">
         <v>46283.0</v>
@@ -3114,24 +3116,24 @@
       <c r="AD41" s="11"/>
       <c r="AE41" s="11"/>
     </row>
-    <row r="42" ht="29.25" customHeight="1">
+    <row r="42" ht="29.25" hidden="1" customHeight="1">
       <c r="A42" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G42" s="9">
         <v>46287.0</v>
@@ -3163,7 +3165,7 @@
       <c r="AD42" s="11"/>
       <c r="AE42" s="11"/>
     </row>
-    <row r="43" ht="29.25" customHeight="1">
+    <row r="43" ht="29.25" hidden="1" customHeight="1">
       <c r="A43" s="5" t="s">
         <v>12</v>
       </c>
@@ -3171,7 +3173,7 @@
         <v>20</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>14</v>
@@ -3216,7 +3218,7 @@
       <c r="AD43" s="11"/>
       <c r="AE43" s="11"/>
     </row>
-    <row r="44" ht="29.25" customHeight="1">
+    <row r="44" ht="29.25" hidden="1" customHeight="1">
       <c r="A44" s="5" t="s">
         <v>12</v>
       </c>
@@ -3224,7 +3226,7 @@
         <v>20</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>14</v>
@@ -3274,10 +3276,10 @@
         <v>25</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>14</v>
@@ -3320,15 +3322,15 @@
       <c r="AD45" s="11"/>
       <c r="AE45" s="11"/>
     </row>
-    <row r="46" ht="29.25" customHeight="1">
+    <row r="46" ht="29.25" hidden="1" customHeight="1">
       <c r="A46" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D46" s="8" t="s">
         <v>14</v>
@@ -3373,15 +3375,15 @@
       <c r="AD46" s="11"/>
       <c r="AE46" s="11"/>
     </row>
-    <row r="47" ht="29.25" customHeight="1">
+    <row r="47" ht="29.25" hidden="1" customHeight="1">
       <c r="A47" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>14</v>
@@ -3426,24 +3428,24 @@
       <c r="AD47" s="11"/>
       <c r="AE47" s="11"/>
     </row>
-    <row r="48" ht="29.25" customHeight="1">
+    <row r="48" ht="29.25" hidden="1" customHeight="1">
       <c r="A48" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C48" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E48" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="F48" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>80</v>
       </c>
       <c r="G48" s="9">
         <v>46286.0</v>
@@ -3475,24 +3477,24 @@
       <c r="AD48" s="11"/>
       <c r="AE48" s="11"/>
     </row>
-    <row r="49" ht="29.25" customHeight="1">
+    <row r="49" ht="29.25" hidden="1" customHeight="1">
       <c r="A49" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C49" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D49" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D49" s="8" t="s">
-        <v>82</v>
-      </c>
       <c r="E49" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G49" s="9">
         <v>46287.0</v>
@@ -3526,24 +3528,24 @@
       <c r="AD49" s="11"/>
       <c r="AE49" s="11"/>
     </row>
-    <row r="50" ht="29.25" customHeight="1">
+    <row r="50" ht="29.25" hidden="1" customHeight="1">
       <c r="A50" s="25" t="s">
         <v>25</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G50" s="9">
         <v>46286.0</v>
@@ -3551,7 +3553,9 @@
       <c r="H50" s="9">
         <v>46287.0</v>
       </c>
-      <c r="I50" s="9"/>
+      <c r="I50" s="9">
+        <v>46287.0</v>
+      </c>
       <c r="J50" s="23"/>
       <c r="K50" s="24"/>
       <c r="L50" s="24"/>
@@ -3575,15 +3579,15 @@
       <c r="AD50" s="11"/>
       <c r="AE50" s="11"/>
     </row>
-    <row r="51" ht="29.25" customHeight="1">
+    <row r="51" ht="29.25" hidden="1" customHeight="1">
       <c r="A51" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>14</v>
@@ -3633,16 +3637,16 @@
         <v>25</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C52" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E52" s="8" t="s">
         <v>85</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>67</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>32</v>
@@ -3677,20 +3681,24 @@
       <c r="AD52" s="11"/>
       <c r="AE52" s="11"/>
     </row>
-    <row r="53" ht="29.25" customHeight="1">
+    <row r="53" ht="29.25" hidden="1" customHeight="1">
       <c r="A53" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
+      <c r="D53" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>78</v>
+      </c>
       <c r="F53" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G53" s="9">
         <v>46287.0</v>
@@ -3722,22 +3730,22 @@
       <c r="AD53" s="11"/>
       <c r="AE53" s="11"/>
     </row>
-    <row r="54" ht="29.25" customHeight="1">
+    <row r="54" ht="29.25" hidden="1" customHeight="1">
       <c r="A54" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>87</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E54" s="8"/>
       <c r="F54" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G54" s="9">
         <v>46286.0</v>
@@ -3769,12 +3777,12 @@
       <c r="AD54" s="11"/>
       <c r="AE54" s="11"/>
     </row>
-    <row r="55" ht="29.25" customHeight="1">
+    <row r="55" ht="29.25" hidden="1" customHeight="1">
       <c r="A55" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C55" s="27" t="s">
         <v>88</v>
@@ -3782,7 +3790,7 @@
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
       <c r="F55" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G55" s="9">
         <v>46286.0</v>
@@ -3814,7 +3822,7 @@
       <c r="AD55" s="11"/>
       <c r="AE55" s="11"/>
     </row>
-    <row r="56" ht="29.25" customHeight="1">
+    <row r="56" ht="29.25" hidden="1" customHeight="1">
       <c r="A56" s="5" t="s">
         <v>25</v>
       </c>
@@ -3827,7 +3835,7 @@
       <c r="D56" s="8"/>
       <c r="E56" s="8"/>
       <c r="F56" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G56" s="9">
         <v>46286.0</v>
@@ -3859,12 +3867,12 @@
       <c r="AD56" s="11"/>
       <c r="AE56" s="11"/>
     </row>
-    <row r="57" ht="29.25" customHeight="1">
+    <row r="57" ht="29.25" hidden="1" customHeight="1">
       <c r="A57" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C57" s="27" t="s">
         <v>91</v>
@@ -3872,7 +3880,7 @@
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
       <c r="F57" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G57" s="9">
         <v>46287.0</v>
@@ -3904,12 +3912,12 @@
       <c r="AD57" s="11"/>
       <c r="AE57" s="11"/>
     </row>
-    <row r="58" ht="29.25" customHeight="1">
+    <row r="58" ht="29.25" hidden="1" customHeight="1">
       <c r="A58" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>92</v>
@@ -3917,7 +3925,7 @@
       <c r="D58" s="8"/>
       <c r="E58" s="8"/>
       <c r="F58" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G58" s="9">
         <v>46287.0</v>
@@ -3954,7 +3962,7 @@
         <v>25</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>93</v>
@@ -3994,12 +4002,12 @@
       <c r="AD59" s="11"/>
       <c r="AE59" s="11"/>
     </row>
-    <row r="60" ht="29.25" customHeight="1">
+    <row r="60" ht="29.25" hidden="1" customHeight="1">
       <c r="A60" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>94</v>
@@ -4051,7 +4059,7 @@
       </c>
       <c r="D61" s="8"/>
       <c r="E61" s="8" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>32</v>
@@ -4131,7 +4139,7 @@
       <c r="AD62" s="11"/>
       <c r="AE62" s="11"/>
     </row>
-    <row r="63" ht="29.25" customHeight="1">
+    <row r="63" ht="29.25" hidden="1" customHeight="1">
       <c r="A63" s="5" t="s">
         <v>25</v>
       </c>
@@ -4176,7 +4184,7 @@
       <c r="AD63" s="11"/>
       <c r="AE63" s="11"/>
     </row>
-    <row r="64" ht="29.25" customHeight="1">
+    <row r="64" ht="29.25" hidden="1" customHeight="1">
       <c r="A64" s="5" t="s">
         <v>25</v>
       </c>
@@ -4221,7 +4229,7 @@
       <c r="AD64" s="11"/>
       <c r="AE64" s="11"/>
     </row>
-    <row r="65" ht="29.25" customHeight="1">
+    <row r="65" ht="29.25" hidden="1" customHeight="1">
       <c r="A65" s="5" t="s">
         <v>25</v>
       </c>
@@ -4266,7 +4274,7 @@
       <c r="AD65" s="11"/>
       <c r="AE65" s="11"/>
     </row>
-    <row r="66" ht="29.25" customHeight="1">
+    <row r="66" ht="29.25" hidden="1" customHeight="1">
       <c r="A66" s="5" t="s">
         <v>25</v>
       </c>
@@ -4311,7 +4319,7 @@
       <c r="AD66" s="11"/>
       <c r="AE66" s="11"/>
     </row>
-    <row r="67" ht="29.25" customHeight="1">
+    <row r="67" ht="29.25" hidden="1" customHeight="1">
       <c r="A67" s="5" t="s">
         <v>25</v>
       </c>
@@ -4324,7 +4332,7 @@
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
       <c r="F67" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G67" s="9">
         <v>46289.0</v>
@@ -4356,7 +4364,7 @@
       <c r="AD67" s="11"/>
       <c r="AE67" s="11"/>
     </row>
-    <row r="68" ht="29.25" customHeight="1">
+    <row r="68" ht="29.25" hidden="1" customHeight="1">
       <c r="A68" s="5" t="s">
         <v>25</v>
       </c>
@@ -4369,7 +4377,7 @@
       <c r="D68" s="8"/>
       <c r="E68" s="8"/>
       <c r="F68" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G68" s="9">
         <v>46291.0</v>
@@ -4401,7 +4409,7 @@
       <c r="AD68" s="11"/>
       <c r="AE68" s="11"/>
     </row>
-    <row r="69" ht="29.25" customHeight="1">
+    <row r="69" ht="29.25" hidden="1" customHeight="1">
       <c r="A69" s="5" t="s">
         <v>25</v>
       </c>
@@ -4414,7 +4422,7 @@
       <c r="D69" s="8"/>
       <c r="E69" s="8"/>
       <c r="F69" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G69" s="9">
         <v>46289.0</v>
@@ -4446,7 +4454,7 @@
       <c r="AD69" s="11"/>
       <c r="AE69" s="11"/>
     </row>
-    <row r="70" ht="29.25" customHeight="1">
+    <row r="70" ht="29.25" hidden="1" customHeight="1">
       <c r="A70" s="5" t="s">
         <v>25</v>
       </c>
@@ -4459,7 +4467,7 @@
       <c r="D70" s="8"/>
       <c r="E70" s="8"/>
       <c r="F70" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G70" s="9">
         <v>46291.0</v>
@@ -4491,7 +4499,7 @@
       <c r="AD70" s="11"/>
       <c r="AE70" s="11"/>
     </row>
-    <row r="71" ht="29.25" customHeight="1">
+    <row r="71" ht="29.25" hidden="1" customHeight="1">
       <c r="A71" s="5" t="s">
         <v>25</v>
       </c>
@@ -4583,7 +4591,7 @@
       <c r="AD72" s="11"/>
       <c r="AE72" s="11"/>
     </row>
-    <row r="73" ht="29.25" customHeight="1">
+    <row r="73" ht="29.25" hidden="1" customHeight="1">
       <c r="A73" s="5" t="s">
         <v>109</v>
       </c>
@@ -4675,7 +4683,7 @@
       <c r="AD74" s="11"/>
       <c r="AE74" s="11"/>
     </row>
-    <row r="75" ht="29.25" customHeight="1">
+    <row r="75" ht="29.25" hidden="1" customHeight="1">
       <c r="A75" s="5" t="s">
         <v>109</v>
       </c>
@@ -4688,7 +4696,7 @@
       <c r="D75" s="8"/>
       <c r="E75" s="8"/>
       <c r="F75" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G75" s="9">
         <v>46286.0</v>
@@ -4720,7 +4728,7 @@
       <c r="AD75" s="11"/>
       <c r="AE75" s="11"/>
     </row>
-    <row r="76" ht="29.25" customHeight="1">
+    <row r="76" ht="29.25" hidden="1" customHeight="1">
       <c r="A76" s="5" t="s">
         <v>109</v>
       </c>
@@ -4733,7 +4741,7 @@
       <c r="D76" s="8"/>
       <c r="E76" s="8"/>
       <c r="F76" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G76" s="9">
         <v>46287.0</v>
@@ -4765,7 +4773,7 @@
       <c r="AD76" s="11"/>
       <c r="AE76" s="11"/>
     </row>
-    <row r="77" ht="29.25" customHeight="1">
+    <row r="77" ht="29.25" hidden="1" customHeight="1">
       <c r="A77" s="5" t="s">
         <v>109</v>
       </c>
@@ -4778,7 +4786,7 @@
       <c r="D77" s="8"/>
       <c r="E77" s="8"/>
       <c r="F77" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G77" s="9">
         <v>46287.0</v>
@@ -4810,7 +4818,7 @@
       <c r="AD77" s="11"/>
       <c r="AE77" s="11"/>
     </row>
-    <row r="78" ht="29.25" customHeight="1">
+    <row r="78" ht="29.25" hidden="1" customHeight="1">
       <c r="A78" s="5" t="s">
         <v>109</v>
       </c>
@@ -4823,7 +4831,7 @@
       <c r="D78" s="8"/>
       <c r="E78" s="8"/>
       <c r="F78" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G78" s="9">
         <v>46296.0</v>
@@ -4855,7 +4863,7 @@
       <c r="AD78" s="11"/>
       <c r="AE78" s="11"/>
     </row>
-    <row r="79" ht="29.25" customHeight="1">
+    <row r="79" ht="29.25" hidden="1" customHeight="1">
       <c r="A79" s="5" t="s">
         <v>109</v>
       </c>
@@ -4868,7 +4876,7 @@
       <c r="D79" s="8"/>
       <c r="E79" s="8"/>
       <c r="F79" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G79" s="9">
         <v>46303.0</v>
@@ -4900,7 +4908,7 @@
       <c r="AD79" s="11"/>
       <c r="AE79" s="11"/>
     </row>
-    <row r="80" ht="29.25" customHeight="1">
+    <row r="80" ht="29.25" hidden="1" customHeight="1">
       <c r="A80" s="5" t="s">
         <v>12</v>
       </c>
@@ -4911,13 +4919,13 @@
         <v>123</v>
       </c>
       <c r="D80" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F80" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>80</v>
       </c>
       <c r="G80" s="9">
         <v>46305.0</v>
@@ -5016,6 +5024,13 @@
       <c r="AE82" s="11"/>
     </row>
   </sheetData>
+  <autoFilter ref="$A$1:$AE$80">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="Lucia"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="D2:D82">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Finalizada">
       <formula>NOT(ISERROR(SEARCH(("Finalizada"),(D2))))</formula>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-09-26 00:00</v>
+        <v>Plan de Proyecto: 2026-09-27 00:06</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-09-27 00:06</v>
+        <v>Plan de Proyecto: 2026-09-28 00:03</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-09-28 00:03</v>
+        <v>Plan de Proyecto: 2026-09-29 00:42</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-09-29 00:42</v>
+        <v>Plan de Proyecto: 2026-09-30 00:30</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-09-30 00:30</v>
+        <v>Plan de Proyecto: 2026-10-01 00:35</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-01 00:35</v>
+        <v>Plan de Proyecto: 2026-10-02 00:35</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-02 00:35</v>
+        <v>Plan de Proyecto: 2026-10-03 00:19</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-03 00:19</v>
+        <v>Plan de Proyecto: 2026-10-04 00:47</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-04 00:47</v>
+        <v>Plan de Proyecto: 2026-10-05 00:32</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-05 00:32</v>
+        <v>Plan de Proyecto: 2026-10-06 01:20</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-06 01:20</v>
+        <v>Plan de Proyecto: 2026-10-07 00:46</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-07 00:46</v>
+        <v>Plan de Proyecto: 2026-10-08 00:59</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-08 00:59</v>
+        <v>Plan de Proyecto: 2026-10-09 01:05</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-09 01:05</v>
+        <v>Plan de Proyecto: 2026-10-10 00:50</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-10 00:50</v>
+        <v>Plan de Proyecto: 2026-10-11 00:24</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-11 00:24</v>
+        <v>Plan de Proyecto: 2026-10-12 00:47</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-12 00:47</v>
+        <v>Plan de Proyecto: 2026-10-13 01:58</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-13 01:58</v>
+        <v>Plan de Proyecto: 2026-10-14 00:06</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-14 00:06</v>
+        <v>Plan de Proyecto: 2026-10-14 23:45</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-15 23:42</v>
+        <v>Plan de Proyecto: 2026-10-16 23:33</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-16 23:33</v>
+        <v>Plan de Proyecto: 2026-10-17 23:34</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-17 23:34</v>
+        <v>Plan de Proyecto: 2026-10-18 23:48</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-18 23:48</v>
+        <v>Plan de Proyecto: 2026-10-19 23:59</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-19 23:59</v>
+        <v>Plan de Proyecto: 2026-10-20 23:53</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-20 23:53</v>
+        <v>Plan de Proyecto: 2026-10-21 23:52</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-21 23:52</v>
+        <v>Plan de Proyecto: 2026-10-22 23:56</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-22 23:56</v>
+        <v>Plan de Proyecto: 2026-10-23 23:52</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-23 23:52</v>
+        <v>Plan de Proyecto: 2026-10-24 23:45</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-24 23:45</v>
+        <v>Plan de Proyecto: 2026-10-25 23:42</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-25 23:42</v>
+        <v>Plan de Proyecto: 2026-10-27 00:17</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-27 00:17</v>
+        <v>Plan de Proyecto: 2026-10-28 00:33</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-28 00:33</v>
+        <v>Plan de Proyecto: 2026-10-29 00:54</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-29 00:54</v>
+        <v>Plan de Proyecto: 2026-10-30 00:56</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>

--- a/tareas.xlsx
+++ b/tareas.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C2" s="7" t="str">
         <f>"Plan de Proyecto: " &amp; TEXT(NOW(), "yyyy-mm-dd hh:mm")</f>
-        <v>Plan de Proyecto: 2026-10-30 00:56</v>
+        <v>Plan de Proyecto: 2026-10-31 00:40</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>
